--- a/tables/Flexible CUE/Local_perf_matrix_protection_True_vo_True_CUE_True.xlsx
+++ b/tables/Flexible CUE/Local_perf_matrix_protection_True_vo_True_CUE_True.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -668,10 +668,10 @@
         <v>0.01736455621136393</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2301524983055982</v>
+        <v>0.001838908966245269</v>
       </c>
       <c r="L2" t="n">
-        <v>0.210230593928087</v>
+        <v>0.004818660655609108</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -680,16 +680,16 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>4.403789484409526</v>
+        <v>4.428549100137173</v>
       </c>
       <c r="P2" t="n">
-        <v>4.387950035876709</v>
+        <v>4.430351249159571</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9926328846449632</v>
+        <v>0.9913349116578273</v>
       </c>
       <c r="R2" t="n">
-        <v>0.005276090209800091</v>
+        <v>0.005722027948967221</v>
       </c>
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
@@ -699,38 +699,38 @@
       <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="n">
-        <v>0.9910495601199663</v>
+        <v>0.9999643989903475</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.006860790978622006</v>
+        <v>0.000432696274363199</v>
       </c>
       <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="n">
-        <v>0.9997239182999238</v>
+        <v>-1.02118814113178</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.000109328956670275</v>
+        <v>0.009354482439412466</v>
       </c>
       <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="n">
-        <v>0.9988929994060082</v>
+        <v>0.9994331133948459</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.001403842226832588</v>
+        <v>0.001004598377240635</v>
       </c>
       <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="n">
-        <v>0.9567662255957561</v>
+        <v>0.950674505839303</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.008847703463219728</v>
+        <v>0.009450498226264864</v>
       </c>
       <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="n">
-        <v>0.7155856821540079</v>
+        <v>0.5640019509773253</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.00160485074238434</v>
+        <v>0.001987015215006586</v>
       </c>
       <c r="AN2" t="inlineStr"/>
     </row>
@@ -772,10 +772,10 @@
         <v>0.02342462405894816</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001488718167071711</v>
+        <v>0.001488722301635292</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003536348979745706</v>
+        <v>0.003536350849402868</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -784,16 +784,16 @@
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>4.313657841931784</v>
+        <v>4.34036319288207</v>
       </c>
       <c r="P3" t="n">
-        <v>4.313366390510082</v>
+        <v>4.312953043785511</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.9918348185766739</v>
+        <v>0.9918348188986992</v>
       </c>
       <c r="R3" t="n">
-        <v>0.005494810110364544</v>
+        <v>0.005494810002010068</v>
       </c>
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
@@ -803,38 +803,38 @@
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="n">
-        <v>0.9990946627182734</v>
+        <v>0.9990946365685138</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.001933449104536642</v>
+        <v>0.001933477027204255</v>
       </c>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="n">
-        <v>-1.057186228100421</v>
+        <v>-1.057186228100312</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.003512210996364632</v>
+        <v>0.003512210996364539</v>
       </c>
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="n">
-        <v>0.9858892681721764</v>
+        <v>0.9858893082518353</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.005761316482658299</v>
+        <v>0.005761308300525506</v>
       </c>
       <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="n">
-        <v>0.8570086255907016</v>
+        <v>0.8570086349889083</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.009170751610220192</v>
+        <v>0.009170751308843197</v>
       </c>
       <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="n">
-        <v>0.3006278074245267</v>
+        <v>0.3006286318311833</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.003412176601081902</v>
+        <v>0.003412174589976826</v>
       </c>
       <c r="AN3" t="inlineStr"/>
     </row>
@@ -876,10 +876,10 @@
         <v>0.001786449637055907</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4340590818808676</v>
+        <v>0.4182132258886959</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2125870861129704</v>
+        <v>0.2208574833875513</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -888,16 +888,16 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>4.446044591924739</v>
+        <v>4.293493812215727</v>
       </c>
       <c r="P4" t="n">
-        <v>4.430890583381683</v>
+        <v>4.556604365269963</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.957985846005631</v>
+        <v>0.9607960700256233</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0134085520067957</v>
+        <v>0.01295235895535342</v>
       </c>
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
@@ -907,38 +907,38 @@
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="n">
-        <v>0.9753605798219629</v>
+        <v>0.9851931087589035</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.01382142566215505</v>
+        <v>0.01071444163995483</v>
       </c>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="n">
-        <v>0.9976117487608389</v>
+        <v>0.9985441501502312</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.0006082022414228988</v>
+        <v>0.0004748607820771584</v>
       </c>
       <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="n">
-        <v>0.4437369772226426</v>
+        <v>0.4346053706977421</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.02427434351553097</v>
+        <v>0.02447277611701979</v>
       </c>
       <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="n">
-        <v>0.9753242604985136</v>
+        <v>0.9695991175866484</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.006515802828328278</v>
+        <v>0.007232291800302154</v>
       </c>
       <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="n">
-        <v>0.375442869607936</v>
+        <v>0.348741996813437</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.004004837745606359</v>
+        <v>0.004089548628245454</v>
       </c>
       <c r="AN4" t="inlineStr"/>
     </row>
@@ -980,10 +980,10 @@
         <v>0.03029424940398749</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1851828485504524</v>
+        <v>0.1838378561531941</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2268830131406592</v>
+        <v>0.2238263003664408</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -992,16 +992,16 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>4.338269228295625</v>
+        <v>4.308694607789535</v>
       </c>
       <c r="P5" t="n">
-        <v>4.40569001102233</v>
+        <v>4.348799653163455</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9975464377295669</v>
+        <v>0.9975645952804997</v>
       </c>
       <c r="R5" t="n">
-        <v>0.002931813107893378</v>
+        <v>0.002920944542833359</v>
       </c>
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
@@ -1011,38 +1011,38 @@
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="n">
-        <v>0.9986145843648928</v>
+        <v>0.9986341249047619</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.002665984834499558</v>
+        <v>0.002647116929158683</v>
       </c>
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="n">
-        <v>0.9999962605695504</v>
+        <v>0.9999958712067397</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.191675051635293e-05</v>
+        <v>1.252179777625198e-05</v>
       </c>
       <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="n">
-        <v>0.9983663498798617</v>
+        <v>0.9983410348102747</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.001878857332519718</v>
+        <v>0.001893358772173806</v>
       </c>
       <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="n">
-        <v>0.9739700518598817</v>
+        <v>0.9742049301009937</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.005364263374970613</v>
+        <v>0.005340006624892956</v>
       </c>
       <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="n">
-        <v>0.9678247661577721</v>
+        <v>0.9674414155669334</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.0008363421682825474</v>
+        <v>0.0008413096990907708</v>
       </c>
       <c r="AN5" t="inlineStr"/>
     </row>
@@ -1084,10 +1084,10 @@
         <v>0.01850467691463906</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1709875190959763</v>
+        <v>0.1683825408883232</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2156216327059743</v>
+        <v>0.2127574220704695</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -1096,16 +1096,16 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>4.423356086505447</v>
+        <v>4.376451817448588</v>
       </c>
       <c r="P6" t="n">
-        <v>4.470794301600197</v>
+        <v>4.383120503648406</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.9773797178141664</v>
+        <v>0.9776389469217642</v>
       </c>
       <c r="R6" t="n">
-        <v>0.009091999157623631</v>
+        <v>0.009039751746489418</v>
       </c>
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
@@ -1115,38 +1115,38 @@
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="n">
-        <v>0.9911045447678213</v>
+        <v>0.9919311455338834</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.005440356035725465</v>
+        <v>0.00518142450076494</v>
       </c>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="n">
-        <v>0.9994815226589192</v>
+        <v>0.999485684576646</v>
       </c>
       <c r="AD6" t="n">
-        <v>6.081583287332377e-05</v>
+        <v>6.057125084102614e-05</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="n">
-        <v>0.995216213420449</v>
+        <v>0.9957776804957648</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.002836804379165872</v>
+        <v>0.002665133923721853</v>
       </c>
       <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="n">
-        <v>0.6732718828155784</v>
+        <v>0.6739619512424374</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.01856984152390023</v>
+        <v>0.01855022087598805</v>
       </c>
       <c r="AK6" t="inlineStr"/>
       <c r="AL6" t="n">
-        <v>0.4091125001335595</v>
+        <v>0.4087041476018173</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.001811357051909985</v>
+        <v>0.00181198284318882</v>
       </c>
       <c r="AN6" t="inlineStr"/>
     </row>
@@ -1188,10 +1188,10 @@
         <v>0.01739226579276497</v>
       </c>
       <c r="K7" t="n">
-        <v>0.001787394683151308</v>
+        <v>0.00178739823396281</v>
       </c>
       <c r="L7" t="n">
-        <v>0.004074574773310821</v>
+        <v>0.004074576617584719</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -1200,16 +1200,16 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>4.322490428799298</v>
+        <v>4.252970041033242</v>
       </c>
       <c r="P7" t="n">
-        <v>4.318419338489357</v>
+        <v>4.357590724711937</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.9887164268610639</v>
+        <v>0.9887164440336703</v>
       </c>
       <c r="R7" t="n">
-        <v>0.006454077855023241</v>
+        <v>0.006454072943751788</v>
       </c>
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
@@ -1219,38 +1219,38 @@
       <c r="X7" t="inlineStr"/>
       <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="n">
-        <v>0.9950534339568895</v>
+        <v>0.9950535028125729</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.00533621527260264</v>
+        <v>0.00533617813269342</v>
       </c>
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="n">
-        <v>-1.032359569609421</v>
+        <v>-1.032359569609433</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.006150454745414001</v>
+        <v>0.006150454745414018</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="n">
-        <v>0.9263790154616445</v>
+        <v>0.9263789633677032</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.01081673388319941</v>
+        <v>0.01081673771013954</v>
       </c>
       <c r="AH7" t="inlineStr"/>
       <c r="AI7" t="n">
-        <v>0.9997670238706274</v>
+        <v>0.99976701493855</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.0004019381576702073</v>
+        <v>0.0004019458625547618</v>
       </c>
       <c r="AK7" t="inlineStr"/>
       <c r="AL7" t="n">
-        <v>0.1556298186578343</v>
+        <v>0.1556294045148865</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.004851119026119603</v>
+        <v>0.004851120215797147</v>
       </c>
       <c r="AN7" t="inlineStr"/>
     </row>
@@ -1292,10 +1292,10 @@
         <v>0.02806021357785015</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1585030469725749</v>
+        <v>0.1601303832383536</v>
       </c>
       <c r="L8" t="n">
-        <v>0.14745024904207</v>
+        <v>0.152332376680562</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -1304,16 +1304,16 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>4.395443563473687</v>
+        <v>4.44514495646937</v>
       </c>
       <c r="P8" t="n">
-        <v>4.28134097431976</v>
+        <v>4.408363693557797</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.9923563248456057</v>
+        <v>0.9924118052272565</v>
       </c>
       <c r="R8" t="n">
-        <v>0.004709979157983257</v>
+        <v>0.004692854716115689</v>
       </c>
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
@@ -1323,38 +1323,38 @@
       <c r="X8" t="inlineStr"/>
       <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="n">
-        <v>0.9915946023800738</v>
+        <v>0.9916197156149756</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.006117651944607139</v>
+        <v>0.006108506097849402</v>
       </c>
       <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="n">
-        <v>0.9999760219162487</v>
+        <v>0.9999794606976998</v>
       </c>
       <c r="AD8" t="n">
-        <v>3.214136624574025e-05</v>
+        <v>2.974746352165192e-05</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="n">
-        <v>0.9857185383165551</v>
+        <v>0.9857993239608582</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.00591758982640117</v>
+        <v>0.005900829137295257</v>
       </c>
       <c r="AH8" t="inlineStr"/>
       <c r="AI8" t="n">
-        <v>0.9826667976051858</v>
+        <v>0.9829131051818217</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.005574698426295122</v>
+        <v>0.005534948028290435</v>
       </c>
       <c r="AK8" t="inlineStr"/>
       <c r="AL8" t="n">
-        <v>0.9997453595977451</v>
+        <v>0.9997306408882451</v>
       </c>
       <c r="AM8" t="n">
-        <v>5.829118574527763e-05</v>
+        <v>5.99521924014409e-05</v>
       </c>
       <c r="AN8" t="inlineStr"/>
     </row>
@@ -1396,10 +1396,10 @@
         <v>0.03857825619785213</v>
       </c>
       <c r="K9" t="n">
-        <v>0.001327231503641381</v>
+        <v>0.00132724233869487</v>
       </c>
       <c r="L9" t="n">
-        <v>0.004171892113710696</v>
+        <v>0.004171897903985853</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -1408,16 +1408,16 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>4.324191261447337</v>
+        <v>4.224225056384286</v>
       </c>
       <c r="P9" t="n">
-        <v>4.364487761227737</v>
+        <v>4.343860240323774</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.9891935711347982</v>
+        <v>0.9891935760862314</v>
       </c>
       <c r="R9" t="n">
-        <v>0.005622154369786554</v>
+        <v>0.005622153081769714</v>
       </c>
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
@@ -1427,38 +1427,38 @@
       <c r="X9" t="inlineStr"/>
       <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="n">
-        <v>0.9925333588543106</v>
+        <v>0.9925333805918996</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.006237018900922971</v>
+        <v>0.00623700982201794</v>
       </c>
       <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="n">
-        <v>-1.024352963218119</v>
+        <v>-1.024352963218107</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.008148373191661106</v>
+        <v>0.008148373191661083</v>
       </c>
       <c r="AE9" t="inlineStr"/>
       <c r="AF9" t="n">
-        <v>0.9995485032917689</v>
+        <v>0.9995484720134938</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.0008597957961964291</v>
+        <v>0.0008598255776580291</v>
       </c>
       <c r="AH9" t="inlineStr"/>
       <c r="AI9" t="n">
-        <v>0.9559999506676758</v>
+        <v>0.9559999545988799</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.007914587546962611</v>
+        <v>0.007914587193396426</v>
       </c>
       <c r="AK9" t="inlineStr"/>
       <c r="AL9" t="n">
-        <v>0.9733729215709866</v>
+        <v>0.9733729202520788</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.0009810974138328569</v>
+        <v>0.0009810974381310002</v>
       </c>
       <c r="AN9" t="inlineStr"/>
     </row>
@@ -1500,10 +1500,10 @@
         <v>0.033842442806071</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2213013737149055</v>
+        <v>0.2184121480973804</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1163451222266308</v>
+        <v>0.1178701599852213</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1512,16 +1512,16 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>4.165105484036478</v>
+        <v>4.114152557453664</v>
       </c>
       <c r="P10" t="n">
-        <v>4.177594006857848</v>
+        <v>4.235284883760527</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.9928759473303675</v>
+        <v>0.9928800860151742</v>
       </c>
       <c r="R10" t="n">
-        <v>0.005361593312149433</v>
+        <v>0.005360035689716553</v>
       </c>
       <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr"/>
@@ -1531,38 +1531,38 @@
       <c r="X10" t="inlineStr"/>
       <c r="Y10" t="inlineStr"/>
       <c r="Z10" t="n">
-        <v>0.999654215777697</v>
+        <v>0.9996888368913763</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.001644802180754617</v>
+        <v>0.001560289325626953</v>
       </c>
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="n">
-        <v>0.9999682083417054</v>
+        <v>0.9999699868124187</v>
       </c>
       <c r="AD10" t="n">
-        <v>4.712816945034608e-05</v>
+        <v>4.579099089893043e-05</v>
       </c>
       <c r="AE10" t="inlineStr"/>
       <c r="AF10" t="n">
-        <v>0.9300721341758624</v>
+        <v>0.9298621128959641</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.01081269665604974</v>
+        <v>0.01082892190343788</v>
       </c>
       <c r="AH10" t="inlineStr"/>
       <c r="AI10" t="n">
-        <v>0.9741442984174985</v>
+        <v>0.9749016422537981</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.002544060876079579</v>
+        <v>0.002506524699547092</v>
       </c>
       <c r="AK10" t="inlineStr"/>
       <c r="AL10" t="n">
-        <v>0.7854142741535119</v>
+        <v>0.7845764874392911</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.00283860475747014</v>
+        <v>0.002844140607237534</v>
       </c>
       <c r="AN10" t="inlineStr"/>
     </row>
@@ -1604,10 +1604,10 @@
         <v>0.02959337905881725</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1753512382165855</v>
+        <v>0.1757473902023626</v>
       </c>
       <c r="L11" t="n">
-        <v>0.3438559476343704</v>
+        <v>0.3457220789286981</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -1616,16 +1616,16 @@
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>4.094730808965064</v>
+        <v>4.070128680268422</v>
       </c>
       <c r="P11" t="n">
-        <v>4.244143343105087</v>
+        <v>4.260085923989431</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.9928330731359708</v>
+        <v>0.992885767090499</v>
       </c>
       <c r="R11" t="n">
-        <v>0.006298078052414509</v>
+        <v>0.006274882413107013</v>
       </c>
       <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr"/>
@@ -1635,38 +1635,38 @@
       <c r="X11" t="inlineStr"/>
       <c r="Y11" t="inlineStr"/>
       <c r="Z11" t="n">
-        <v>0.9898453284604752</v>
+        <v>0.9899235032775338</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.01259921479237116</v>
+        <v>0.012550624138312</v>
       </c>
       <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="n">
-        <v>0.9803375963511929</v>
+        <v>0.980246816791308</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.0009876771455266525</v>
+        <v>0.0009899545284780364</v>
       </c>
       <c r="AE11" t="inlineStr"/>
       <c r="AF11" t="n">
-        <v>0.937986984548524</v>
+        <v>0.9380888726315225</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.004414284147205099</v>
+        <v>0.004410656297151249</v>
       </c>
       <c r="AH11" t="inlineStr"/>
       <c r="AI11" t="n">
-        <v>0.9546117872337997</v>
+        <v>0.9554487016716159</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.002394002570921112</v>
+        <v>0.002371828339628546</v>
       </c>
       <c r="AK11" t="inlineStr"/>
       <c r="AL11" t="n">
-        <v>0.9721787245193744</v>
+        <v>0.9724148606916169</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.0007066138016958442</v>
+        <v>0.0007036086798859991</v>
       </c>
       <c r="AN11" t="inlineStr"/>
     </row>
@@ -1708,10 +1708,10 @@
         <v>0.0207241649964606</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1045250285804663</v>
+        <v>0.1058258334398891</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1653472002733141</v>
+        <v>0.1647301261806731</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1720,16 +1720,16 @@
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>4.059116436759205</v>
+        <v>4.069166306475234</v>
       </c>
       <c r="P12" t="n">
-        <v>4.069925363525642</v>
+        <v>4.116611958223732</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.9520617757348265</v>
+        <v>0.952020361439344</v>
       </c>
       <c r="R12" t="n">
-        <v>0.02382886077452389</v>
+        <v>0.02383915154404832</v>
       </c>
       <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr"/>
@@ -1739,38 +1739,38 @@
       <c r="X12" t="inlineStr"/>
       <c r="Y12" t="inlineStr"/>
       <c r="Z12" t="n">
-        <v>0.7306043312764661</v>
+        <v>0.7302072874414616</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.05130624219622137</v>
+        <v>0.05134403665481801</v>
       </c>
       <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="n">
-        <v>0.9790340115603234</v>
+        <v>0.9826113508413626</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.0003400390130029472</v>
+        <v>0.0003096734684946327</v>
       </c>
       <c r="AE12" t="inlineStr"/>
       <c r="AF12" t="n">
-        <v>0.9977729137283424</v>
+        <v>0.9989137189713839</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.001784481570185382</v>
+        <v>0.001246277183105788</v>
       </c>
       <c r="AH12" t="inlineStr"/>
       <c r="AI12" t="n">
-        <v>0.2494338834650059</v>
+        <v>0.246673468218876</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.003763997838697688</v>
+        <v>0.003770913059828923</v>
       </c>
       <c r="AK12" t="inlineStr"/>
       <c r="AL12" t="n">
-        <v>0.9897689675753327</v>
+        <v>0.9893310357842738</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.0002046141068295575</v>
+        <v>0.0002089473997565754</v>
       </c>
       <c r="AN12" t="inlineStr"/>
     </row>
@@ -1812,10 +1812,10 @@
         <v>0.05578662037324268</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1372751297687382</v>
+        <v>0.1485150072055759</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2036678629169416</v>
+        <v>0.22018022197519</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1824,16 +1824,16 @@
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>4.316000860305166</v>
+        <v>4.284045086843435</v>
       </c>
       <c r="P13" t="n">
-        <v>4.288695562750191</v>
+        <v>4.512729081527848</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.9978942748803202</v>
+        <v>0.9979048782818226</v>
       </c>
       <c r="R13" t="n">
-        <v>0.002625993005177493</v>
+        <v>0.002619373052930165</v>
       </c>
       <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr"/>
@@ -1843,38 +1843,38 @@
       <c r="X13" t="inlineStr"/>
       <c r="Y13" t="inlineStr"/>
       <c r="Z13" t="n">
-        <v>0.8322230137492239</v>
+        <v>0.8327039979257171</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.003229438034663111</v>
+        <v>0.003224805625040577</v>
       </c>
       <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="n">
-        <v>0.9986835145382262</v>
+        <v>0.9990436130842091</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.778683437293694e-05</v>
+        <v>2.368360731429251e-05</v>
       </c>
       <c r="AE13" t="inlineStr"/>
       <c r="AF13" t="n">
-        <v>0.6287210082119398</v>
+        <v>0.6303851705000185</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.004357245603232229</v>
+        <v>0.004347469521630255</v>
       </c>
       <c r="AH13" t="inlineStr"/>
       <c r="AI13" t="n">
-        <v>0.9999969534309426</v>
+        <v>0.999999259408615</v>
       </c>
       <c r="AJ13" t="n">
-        <v>7.051627943568286e-05</v>
+        <v>3.476747928290516e-05</v>
       </c>
       <c r="AK13" t="inlineStr"/>
       <c r="AL13" t="n">
-        <v>0.9508980055092403</v>
+        <v>0.9514284613609557</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.002249131475872487</v>
+        <v>0.002236949641904129</v>
       </c>
       <c r="AN13" t="inlineStr"/>
     </row>
@@ -1916,10 +1916,10 @@
         <v>0.008819171744597891</v>
       </c>
       <c r="K14" t="n">
-        <v>0.171587651340829</v>
+        <v>0.1727584722120463</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2977921534592498</v>
+        <v>0.2985452117301948</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1928,16 +1928,16 @@
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>4.329492817556477</v>
+        <v>4.415219190537966</v>
       </c>
       <c r="P14" t="n">
-        <v>4.32458388709269</v>
+        <v>4.362693183010549</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.9740814806644505</v>
+        <v>0.9739606621191087</v>
       </c>
       <c r="R14" t="n">
-        <v>0.00958738714563875</v>
+        <v>0.009609706850789872</v>
       </c>
       <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr"/>
@@ -1947,38 +1947,38 @@
       <c r="X14" t="inlineStr"/>
       <c r="Y14" t="inlineStr"/>
       <c r="Z14" t="n">
-        <v>0.9183467307433688</v>
+        <v>0.9178337375192679</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.01420758332867798</v>
+        <v>0.01425214359175016</v>
       </c>
       <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="n">
-        <v>0.6483121267827727</v>
+        <v>0.6483440915531236</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.00290834071561102</v>
+        <v>0.002908208543644586</v>
       </c>
       <c r="AE14" t="inlineStr"/>
       <c r="AF14" t="n">
-        <v>0.9833224576747561</v>
+        <v>0.9826286764636797</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.005581294361995839</v>
+        <v>0.005696201671489181</v>
       </c>
       <c r="AH14" t="inlineStr"/>
       <c r="AI14" t="n">
-        <v>0.5788981791289824</v>
+        <v>0.579718313893418</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.01466384296973629</v>
+        <v>0.01464955641466951</v>
       </c>
       <c r="AK14" t="inlineStr"/>
       <c r="AL14" t="n">
-        <v>0.2054541077854563</v>
+        <v>0.2059969770410767</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.001759816537612766</v>
+        <v>0.001759215242241763</v>
       </c>
       <c r="AN14" t="inlineStr"/>
     </row>
@@ -2020,10 +2020,10 @@
         <v>0.02024626170970604</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1960420645582539</v>
+        <v>0.1895470751595914</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2987234638753284</v>
+        <v>0.2933197078177879</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -2032,16 +2032,16 @@
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>4.259694900513283</v>
+        <v>4.12729937470144</v>
       </c>
       <c r="P15" t="n">
-        <v>4.326171788068061</v>
+        <v>4.250834185958639</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.9758299264655514</v>
+        <v>0.975807779438401</v>
       </c>
       <c r="R15" t="n">
-        <v>0.008216041372647021</v>
+        <v>0.008219804688209677</v>
       </c>
       <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr"/>
@@ -2051,38 +2051,38 @@
       <c r="X15" t="inlineStr"/>
       <c r="Y15" t="inlineStr"/>
       <c r="Z15" t="n">
-        <v>0.9198479839425594</v>
+        <v>0.9197776878023943</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.01394063060324258</v>
+        <v>0.01394674247539276</v>
       </c>
       <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="n">
-        <v>-0.5674697625966263</v>
+        <v>-0.5405604309778897</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.003276117533306433</v>
+        <v>0.003247874635409145</v>
       </c>
       <c r="AE15" t="inlineStr"/>
       <c r="AF15" t="n">
-        <v>0.9499523415761748</v>
+        <v>0.9498627388268558</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.008191726342240619</v>
+        <v>0.008199056085422594</v>
       </c>
       <c r="AH15" t="inlineStr"/>
       <c r="AI15" t="n">
-        <v>0.6580036165260398</v>
+        <v>0.656548015171428</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.006545002167554207</v>
+        <v>0.006558915762710387</v>
       </c>
       <c r="AK15" t="inlineStr"/>
       <c r="AL15" t="n">
-        <v>0.9999993764978298</v>
+        <v>0.9999995770694698</v>
       </c>
       <c r="AM15" t="n">
-        <v>2.92198706450867e-06</v>
+        <v>2.406544089539302e-06</v>
       </c>
       <c r="AN15" t="inlineStr"/>
     </row>
@@ -2124,10 +2124,10 @@
         <v>0.01569855494294647</v>
       </c>
       <c r="K16" t="n">
-        <v>0.5421174973423735</v>
+        <v>0.5109637156163565</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5411382860905174</v>
+        <v>0.524826409861138</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2136,16 +2136,16 @@
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>4.551455588325581</v>
+        <v>4.305324632016705</v>
       </c>
       <c r="P16" t="n">
-        <v>4.711496521050512</v>
+        <v>4.498954160381471</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.9745773048798684</v>
+        <v>0.9758602116143378</v>
       </c>
       <c r="R16" t="n">
-        <v>0.009697799156589715</v>
+        <v>0.00944994150527813</v>
       </c>
       <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr"/>
@@ -2155,31 +2155,31 @@
       <c r="X16" t="inlineStr"/>
       <c r="Y16" t="inlineStr"/>
       <c r="Z16" t="n">
-        <v>0.9936622043350898</v>
+        <v>0.9937953635733858</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.005868584924805389</v>
+        <v>0.005806607172569121</v>
       </c>
       <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="n">
-        <v>0.9551799432489315</v>
+        <v>0.9584743548070799</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.004363444170341738</v>
+        <v>0.00420002056613056</v>
       </c>
       <c r="AE16" t="inlineStr"/>
       <c r="AF16" t="n">
-        <v>0.9117894692335414</v>
+        <v>0.9091355120823432</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.003566147932465987</v>
+        <v>0.003619397056548504</v>
       </c>
       <c r="AH16" t="inlineStr"/>
       <c r="AI16" t="n">
-        <v>0.8337531422819788</v>
+        <v>0.8429217642719108</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.01847541587163382</v>
+        <v>0.01795872530642704</v>
       </c>
       <c r="AK16" t="inlineStr"/>
       <c r="AL16" t="inlineStr"/>
@@ -2226,10 +2226,10 @@
         <v>0.07189096045701066</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1403488321675085</v>
+        <v>0.1374919669067439</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2394775697462902</v>
+        <v>0.2307472800767105</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -2238,16 +2238,16 @@
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>4.075120312358837</v>
+        <v>3.873370159099385</v>
       </c>
       <c r="P17" t="n">
-        <v>4.197652259739989</v>
+        <v>4.005826835085653</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.9906035193295684</v>
+        <v>0.990508263237892</v>
       </c>
       <c r="R17" t="n">
-        <v>0.004499659549949551</v>
+        <v>0.004522409513129559</v>
       </c>
       <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr"/>
@@ -2257,38 +2257,38 @@
       <c r="X17" t="inlineStr"/>
       <c r="Y17" t="inlineStr"/>
       <c r="Z17" t="n">
-        <v>0.9705588137717303</v>
+        <v>0.9703343570829618</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.008631970950423921</v>
+        <v>0.008664813118846234</v>
       </c>
       <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="n">
-        <v>0.5685011185333939</v>
+        <v>0.5722843899820016</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.00203159150689671</v>
+        <v>0.002022665662481978</v>
       </c>
       <c r="AE17" t="inlineStr"/>
       <c r="AF17" t="n">
-        <v>0.9981135873422623</v>
+        <v>0.9983033150964806</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.001174611025484689</v>
+        <v>0.001113977245660156</v>
       </c>
       <c r="AH17" t="inlineStr"/>
       <c r="AI17" t="n">
-        <v>0.2163948688429833</v>
+        <v>0.193293955721858</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.004555462568102012</v>
+        <v>0.004622123041898624</v>
       </c>
       <c r="AK17" t="inlineStr"/>
       <c r="AL17" t="n">
-        <v>0.9950359014782972</v>
+        <v>0.9948075356462398</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.0006815009294453636</v>
+        <v>0.0006970003853739215</v>
       </c>
       <c r="AN17" t="inlineStr"/>
     </row>
@@ -2330,10 +2330,10 @@
         <v>0.03009288922194302</v>
       </c>
       <c r="K18" t="n">
-        <v>0.2393672981629223</v>
+        <v>0.24258952682581</v>
       </c>
       <c r="L18" t="n">
-        <v>0.262747064399152</v>
+        <v>0.2659670730655396</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2342,16 +2342,16 @@
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>4.246963527162229</v>
+        <v>4.300562681691318</v>
       </c>
       <c r="P18" t="n">
-        <v>4.250892789540532</v>
+        <v>4.300546436141598</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.9827202968096395</v>
+        <v>0.9827320056158617</v>
       </c>
       <c r="R18" t="n">
-        <v>0.006798400132103566</v>
+        <v>0.006796096428215015</v>
       </c>
       <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr"/>
@@ -2361,38 +2361,38 @@
       <c r="X18" t="inlineStr"/>
       <c r="Y18" t="inlineStr"/>
       <c r="Z18" t="n">
-        <v>0.9166055080799669</v>
+        <v>0.9166678208924395</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.01483000205489053</v>
+        <v>0.0148244604909142</v>
       </c>
       <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="n">
-        <v>0.9877503481609227</v>
+        <v>0.9869877379734456</v>
       </c>
       <c r="AD18" t="n">
-        <v>0.0003048386530148204</v>
+        <v>0.0003141843593608251</v>
       </c>
       <c r="AE18" t="inlineStr"/>
       <c r="AF18" t="n">
-        <v>0.9954446570369417</v>
+        <v>0.9954260882605082</v>
       </c>
       <c r="AG18" t="n">
-        <v>0.002025778400708347</v>
+        <v>0.002029903004613332</v>
       </c>
       <c r="AH18" t="inlineStr"/>
       <c r="AI18" t="n">
-        <v>0.9756112373990631</v>
+        <v>0.9756653168228163</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.002627270099104056</v>
+        <v>0.002624355639990265</v>
       </c>
       <c r="AK18" t="inlineStr"/>
       <c r="AL18" t="n">
-        <v>0.9955658579341767</v>
+        <v>0.9955281379648904</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.0002510137965868611</v>
+        <v>0.0002520791866744827</v>
       </c>
       <c r="AN18" t="inlineStr"/>
     </row>
@@ -2434,10 +2434,10 @@
         <v>0.01254934055241822</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1872651872905624</v>
+        <v>0.1618647634163979</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2401256141083021</v>
+        <v>0.2266520304402777</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -2446,16 +2446,16 @@
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>4.597747250805167</v>
+        <v>4.01013022703957</v>
       </c>
       <c r="P19" t="n">
-        <v>4.655386642815689</v>
+        <v>4.378894525126992</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.9879336459867739</v>
+        <v>0.9880043984450059</v>
       </c>
       <c r="R19" t="n">
-        <v>0.007739487098694492</v>
+        <v>0.007716763050895845</v>
       </c>
       <c r="S19" t="inlineStr"/>
       <c r="T19" t="inlineStr"/>
@@ -2465,38 +2465,38 @@
       <c r="X19" t="inlineStr"/>
       <c r="Y19" t="inlineStr"/>
       <c r="Z19" t="n">
-        <v>0.622721673326854</v>
+        <v>0.6261862384808998</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.009145703645993698</v>
+        <v>0.009103614075635955</v>
       </c>
       <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="n">
-        <v>-0.04774448265522935</v>
+        <v>-0.02407581613210419</v>
       </c>
       <c r="AD19" t="n">
-        <v>0.003049542932421957</v>
+        <v>0.003014901415834792</v>
       </c>
       <c r="AE19" t="inlineStr"/>
       <c r="AF19" t="n">
-        <v>0.7662419785943408</v>
+        <v>0.7666055143525095</v>
       </c>
       <c r="AG19" t="n">
-        <v>0.01364623034304395</v>
+        <v>0.01363561504322373</v>
       </c>
       <c r="AH19" t="inlineStr"/>
       <c r="AI19" t="n">
-        <v>0.8474625418062679</v>
+        <v>0.8511452672964697</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0.004505893059207675</v>
+        <v>0.004451167641450874</v>
       </c>
       <c r="AK19" t="inlineStr"/>
       <c r="AL19" t="n">
-        <v>0.9962539860275457</v>
+        <v>0.9960400729158702</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.0001789431217902211</v>
+        <v>0.0001839813951152159</v>
       </c>
       <c r="AN19" t="inlineStr"/>
     </row>
@@ -2538,10 +2538,10 @@
         <v>0.005481236733903614</v>
       </c>
       <c r="K20" t="n">
-        <v>0.2655681489740055</v>
+        <v>0.270337140109575</v>
       </c>
       <c r="L20" t="n">
-        <v>0.3008207078222745</v>
+        <v>0.306474044431695</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -2550,16 +2550,16 @@
         <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>4.545581196261954</v>
+        <v>4.622332151259288</v>
       </c>
       <c r="P20" t="n">
-        <v>4.510600408283932</v>
+        <v>4.589270355176144</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.9762103648614167</v>
+        <v>0.9761708549923681</v>
       </c>
       <c r="R20" t="n">
-        <v>0.00905531570841459</v>
+        <v>0.009062832131237158</v>
       </c>
       <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr"/>
@@ -2569,38 +2569,38 @@
       <c r="X20" t="inlineStr"/>
       <c r="Y20" t="inlineStr"/>
       <c r="Z20" t="n">
-        <v>0.8803079551071945</v>
+        <v>0.8787468901710448</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.01007862075707494</v>
+        <v>0.01014413226734182</v>
       </c>
       <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="n">
-        <v>0.8280280070612986</v>
+        <v>0.8252929229952188</v>
       </c>
       <c r="AD20" t="n">
-        <v>0.00282968168037066</v>
+        <v>0.002852094885726183</v>
       </c>
       <c r="AE20" t="inlineStr"/>
       <c r="AF20" t="n">
-        <v>0.9728822971329379</v>
+        <v>0.9733227802322076</v>
       </c>
       <c r="AG20" t="n">
-        <v>0.00439421516037828</v>
+        <v>0.004358380596989807</v>
       </c>
       <c r="AH20" t="inlineStr"/>
       <c r="AI20" t="n">
-        <v>0.7919072746511157</v>
+        <v>0.7922480009568221</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0.01675178518364538</v>
+        <v>0.01673806506865897</v>
       </c>
       <c r="AK20" t="inlineStr"/>
       <c r="AL20" t="n">
-        <v>0.4672811318595945</v>
+        <v>0.4651814554570201</v>
       </c>
       <c r="AM20" t="n">
-        <v>0.0006903509277416156</v>
+        <v>0.0006917100762121532</v>
       </c>
       <c r="AN20" t="inlineStr"/>
     </row>
@@ -2642,10 +2642,10 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0.1248690725745343</v>
+        <v>0.1205682193591666</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1431679535447021</v>
+        <v>0.1424141123167814</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -2654,16 +2654,16 @@
         <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>4.25389152450637</v>
+        <v>4.116445283604787</v>
       </c>
       <c r="P21" t="n">
-        <v>4.339785910113336</v>
+        <v>4.120922169320235</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.874488071611137</v>
+        <v>0.8640998623691123</v>
       </c>
       <c r="R21" t="n">
-        <v>0.02305595960368221</v>
+        <v>0.02399112699908035</v>
       </c>
       <c r="S21" t="inlineStr"/>
       <c r="T21" t="inlineStr"/>
@@ -2673,38 +2673,38 @@
       <c r="X21" t="inlineStr"/>
       <c r="Y21" t="inlineStr"/>
       <c r="Z21" t="n">
-        <v>0.9517999569680639</v>
+        <v>0.9562227590827219</v>
       </c>
       <c r="AA21" t="n">
-        <v>0.008624054597936286</v>
+        <v>0.008218867471995793</v>
       </c>
       <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="n">
-        <v>0.9953852012563222</v>
+        <v>0.9945489868070292</v>
       </c>
       <c r="AD21" t="n">
-        <v>0.002242398755649204</v>
+        <v>0.002437109695667851</v>
       </c>
       <c r="AE21" t="inlineStr"/>
       <c r="AF21" t="n">
-        <v>-3.602913264123998</v>
+        <v>-4.073243951911832</v>
       </c>
       <c r="AG21" t="n">
-        <v>0.04699213855396434</v>
+        <v>0.04933460861720036</v>
       </c>
       <c r="AH21" t="inlineStr"/>
       <c r="AI21" t="n">
-        <v>-0.273237339816524</v>
+        <v>-0.2741046317810907</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0.01922881058578043</v>
+        <v>0.01923535852204688</v>
       </c>
       <c r="AK21" t="inlineStr"/>
       <c r="AL21" t="n">
-        <v>0.555802247166186</v>
+        <v>0.552524461766148</v>
       </c>
       <c r="AM21" t="n">
-        <v>0.0006895316720808289</v>
+        <v>0.0006920710621326452</v>
       </c>
       <c r="AN21" t="inlineStr"/>
     </row>
@@ -2746,10 +2746,10 @@
         <v>0.02704531936448205</v>
       </c>
       <c r="K22" t="n">
-        <v>0.2789552405431617</v>
+        <v>0.2807614585076638</v>
       </c>
       <c r="L22" t="n">
-        <v>0.3265579435046984</v>
+        <v>0.323837837232865</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -2758,16 +2758,16 @@
         <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>4.357078932018656</v>
+        <v>4.13956210274015</v>
       </c>
       <c r="P22" t="n">
-        <v>4.394578277016188</v>
+        <v>4.30991763458454</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.9818931511310137</v>
+        <v>0.9819135739756599</v>
       </c>
       <c r="R22" t="n">
-        <v>0.006802168285059978</v>
+        <v>0.006798331095569802</v>
       </c>
       <c r="S22" t="inlineStr"/>
       <c r="T22" t="inlineStr"/>
@@ -2777,38 +2777,38 @@
       <c r="X22" t="inlineStr"/>
       <c r="Y22" t="inlineStr"/>
       <c r="Z22" t="n">
-        <v>0.8927811093612328</v>
+        <v>0.8928868837904936</v>
       </c>
       <c r="AA22" t="n">
-        <v>0.00965349932473691</v>
+        <v>0.009648736426454994</v>
       </c>
       <c r="AB22" t="inlineStr"/>
       <c r="AC22" t="n">
-        <v>0.9279544556607755</v>
+        <v>0.9302917151956532</v>
       </c>
       <c r="AD22" t="n">
-        <v>0.001487727362818336</v>
+        <v>0.001463396411492845</v>
       </c>
       <c r="AE22" t="inlineStr"/>
       <c r="AF22" t="n">
-        <v>0.3542982370187796</v>
+        <v>0.3550701173187961</v>
       </c>
       <c r="AG22" t="n">
-        <v>0.01109103993163452</v>
+        <v>0.01108440876247827</v>
       </c>
       <c r="AH22" t="inlineStr"/>
       <c r="AI22" t="n">
-        <v>0.9559861188920858</v>
+        <v>0.9557508786510324</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0.003004010047817902</v>
+        <v>0.003012027090635714</v>
       </c>
       <c r="AK22" t="inlineStr"/>
       <c r="AL22" t="n">
-        <v>0.7813196876358052</v>
+        <v>0.7812291634112993</v>
       </c>
       <c r="AM22" t="n">
-        <v>0.001977079118321328</v>
+        <v>0.001977488288753809</v>
       </c>
       <c r="AN22" t="inlineStr"/>
     </row>
@@ -2850,10 +2850,10 @@
         <v>0.0237900385797033</v>
       </c>
       <c r="K23" t="n">
-        <v>0.2148383705391921</v>
+        <v>0.2125758680225997</v>
       </c>
       <c r="L23" t="n">
-        <v>0.2761028473288084</v>
+        <v>0.2727119712918846</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -2862,16 +2862,16 @@
         <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>4.105159995358824</v>
+        <v>3.85839694517567</v>
       </c>
       <c r="P23" t="n">
-        <v>4.197681197311245</v>
+        <v>4.108349748657133</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.9820119454328401</v>
+        <v>0.9820276968781485</v>
       </c>
       <c r="R23" t="n">
-        <v>0.01004108520187838</v>
+        <v>0.01003668794360416</v>
       </c>
       <c r="S23" t="inlineStr"/>
       <c r="T23" t="inlineStr"/>
@@ -2881,38 +2881,38 @@
       <c r="X23" t="inlineStr"/>
       <c r="Y23" t="inlineStr"/>
       <c r="Z23" t="n">
-        <v>0.8989229421368836</v>
+        <v>0.8990071347727139</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.0222884312281346</v>
+        <v>0.02227914666474973</v>
       </c>
       <c r="AB23" t="inlineStr"/>
       <c r="AC23" t="n">
-        <v>-0.6276673375087622</v>
+        <v>-0.5755794039221183</v>
       </c>
       <c r="AD23" t="n">
-        <v>0.001218337930146313</v>
+        <v>0.001198685048847327</v>
       </c>
       <c r="AE23" t="inlineStr"/>
       <c r="AF23" t="n">
-        <v>0.9801140946593275</v>
+        <v>0.9801654878486934</v>
       </c>
       <c r="AG23" t="n">
-        <v>0.002375162603308308</v>
+        <v>0.002372091429300307</v>
       </c>
       <c r="AH23" t="inlineStr"/>
       <c r="AI23" t="n">
-        <v>0.9228259903258954</v>
+        <v>0.9096826062505989</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0.0004510278847813413</v>
+        <v>0.0004879255482581236</v>
       </c>
       <c r="AK23" t="inlineStr"/>
       <c r="AL23" t="n">
-        <v>0.9993723665521634</v>
+        <v>0.999382011747501</v>
       </c>
       <c r="AM23" t="n">
-        <v>0.0001167162738504424</v>
+        <v>0.0001158159793934014</v>
       </c>
       <c r="AN23" t="inlineStr"/>
     </row>
@@ -2954,10 +2954,10 @@
         <v>0.01655830938827357</v>
       </c>
       <c r="K24" t="n">
-        <v>0.3751494643248936</v>
+        <v>0.3899491530645845</v>
       </c>
       <c r="L24" t="n">
-        <v>0.4425806758753214</v>
+        <v>0.4733730306956111</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -2966,16 +2966,16 @@
         <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>4.176595398310353</v>
+        <v>4.330915049849626</v>
       </c>
       <c r="P24" t="n">
-        <v>4.128186592578381</v>
+        <v>4.386274849460652</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.9945537678825086</v>
+        <v>0.9946398898416594</v>
       </c>
       <c r="R24" t="n">
-        <v>0.004382629081729144</v>
+        <v>0.004347839465796365</v>
       </c>
       <c r="S24" t="inlineStr"/>
       <c r="T24" t="inlineStr"/>
@@ -2985,31 +2985,31 @@
       <c r="X24" t="inlineStr"/>
       <c r="Y24" t="inlineStr"/>
       <c r="Z24" t="n">
-        <v>0.999566133501516</v>
+        <v>0.9995320269809053</v>
       </c>
       <c r="AA24" t="n">
-        <v>0.001671477852291758</v>
+        <v>0.001735933064475865</v>
       </c>
       <c r="AB24" t="inlineStr"/>
       <c r="AC24" t="n">
-        <v>0.9599406914513025</v>
+        <v>0.9572293091745959</v>
       </c>
       <c r="AD24" t="n">
-        <v>0.003160098487630775</v>
+        <v>0.003265292013805306</v>
       </c>
       <c r="AE24" t="inlineStr"/>
       <c r="AF24" t="n">
-        <v>0.8840507310778634</v>
+        <v>0.8876443399180077</v>
       </c>
       <c r="AG24" t="n">
-        <v>0.008391554935814817</v>
+        <v>0.008260491953133008</v>
       </c>
       <c r="AH24" t="inlineStr"/>
       <c r="AI24" t="n">
-        <v>0.9992557077524161</v>
+        <v>0.9998960457205744</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0.0001843230634473673</v>
+        <v>6.888570670350077e-05</v>
       </c>
       <c r="AK24" t="inlineStr"/>
       <c r="AL24" t="inlineStr"/>
@@ -3056,10 +3056,10 @@
         <v>0.05553965571423582</v>
       </c>
       <c r="K25" t="n">
-        <v>0.2172140991091026</v>
+        <v>0.2158934749426978</v>
       </c>
       <c r="L25" t="n">
-        <v>0.2292204832758638</v>
+        <v>0.2288284659952428</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
@@ -3068,65 +3068,65 @@
         <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>4.335750152080124</v>
+        <v>4.311008836928643</v>
       </c>
       <c r="P25" t="n">
-        <v>4.343850982506539</v>
+        <v>4.340714662475478</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.9845613365229</v>
+        <v>0.9846063623632936</v>
       </c>
       <c r="R25" t="n">
-        <v>0.02060671386574989</v>
+        <v>0.02057664286603977</v>
       </c>
       <c r="S25" t="inlineStr"/>
       <c r="T25" t="n">
-        <v>-0.1707408655114686</v>
+        <v>-0.1671293684514767</v>
       </c>
       <c r="U25" t="n">
-        <v>0.03983670982053102</v>
+        <v>0.03977521829467955</v>
       </c>
       <c r="V25" t="inlineStr"/>
       <c r="W25" t="n">
-        <v>0.5378816542604836</v>
+        <v>0.5396289014954936</v>
       </c>
       <c r="X25" t="n">
-        <v>0.0008625667927485663</v>
+        <v>0.0008609345866895428</v>
       </c>
       <c r="Y25" t="inlineStr"/>
       <c r="Z25" t="n">
-        <v>0.8919468721132126</v>
+        <v>0.891680711966246</v>
       </c>
       <c r="AA25" t="n">
-        <v>0.01133202658393375</v>
+        <v>0.0113459747168711</v>
       </c>
       <c r="AB25" t="inlineStr"/>
       <c r="AC25" t="n">
-        <v>0.6600602660440471</v>
+        <v>0.6599589366982943</v>
       </c>
       <c r="AD25" t="n">
-        <v>0.002857253765045187</v>
+        <v>0.002857679578878689</v>
       </c>
       <c r="AE25" t="inlineStr"/>
       <c r="AF25" t="n">
-        <v>0.9805947811455071</v>
+        <v>0.9812367192575829</v>
       </c>
       <c r="AG25" t="n">
-        <v>0.002281907238891866</v>
+        <v>0.002243846283148287</v>
       </c>
       <c r="AH25" t="inlineStr"/>
       <c r="AI25" t="n">
-        <v>0.9738345626271234</v>
+        <v>0.9706334713670406</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0.001010321433814268</v>
+        <v>0.001070340289688523</v>
       </c>
       <c r="AK25" t="inlineStr"/>
       <c r="AL25" t="n">
-        <v>-0.02312743380997206</v>
+        <v>-0.02254649128062214</v>
       </c>
       <c r="AM25" t="n">
-        <v>0.003349470278728779</v>
+        <v>0.003348519211457814</v>
       </c>
       <c r="AN25" t="inlineStr"/>
     </row>
@@ -3168,10 +3168,10 @@
         <v>0.05246774739927379</v>
       </c>
       <c r="K26" t="n">
-        <v>0.3294247814180385</v>
+        <v>0.319605401855295</v>
       </c>
       <c r="L26" t="n">
-        <v>0.3144083729271104</v>
+        <v>0.3068276294006985</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -3180,65 +3180,65 @@
         <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>4.343361074649197</v>
+        <v>4.221808346553291</v>
       </c>
       <c r="P26" t="n">
-        <v>4.388941288746611</v>
+        <v>4.299156165421864</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.9809766417136976</v>
+        <v>0.9811515580484123</v>
       </c>
       <c r="R26" t="n">
-        <v>0.02119975890442162</v>
+        <v>0.0211020698554135</v>
       </c>
       <c r="S26" t="inlineStr"/>
       <c r="T26" t="n">
-        <v>0.3069129235847603</v>
+        <v>0.3137369123292557</v>
       </c>
       <c r="U26" t="n">
-        <v>0.04088343214703179</v>
+        <v>0.04068166947802393</v>
       </c>
       <c r="V26" t="inlineStr"/>
       <c r="W26" t="n">
-        <v>-0.3233253272397167</v>
+        <v>-0.3054739183158917</v>
       </c>
       <c r="X26" t="n">
-        <v>0.0008064236697790454</v>
+        <v>0.000800965949823007</v>
       </c>
       <c r="Y26" t="inlineStr"/>
       <c r="Z26" t="n">
-        <v>0.9476874383665761</v>
+        <v>0.9472173182030595</v>
       </c>
       <c r="AA26" t="n">
-        <v>0.01234825436216102</v>
+        <v>0.01240361562780566</v>
       </c>
       <c r="AB26" t="inlineStr"/>
       <c r="AC26" t="n">
-        <v>-0.2493011061677128</v>
+        <v>-0.238405234485211</v>
       </c>
       <c r="AD26" t="n">
-        <v>0.003832457425096157</v>
+        <v>0.003815708295467274</v>
       </c>
       <c r="AE26" t="inlineStr"/>
       <c r="AF26" t="n">
-        <v>0.9123927413903575</v>
+        <v>0.9126467246914984</v>
       </c>
       <c r="AG26" t="n">
-        <v>0.003961899192943252</v>
+        <v>0.00395615202870477</v>
       </c>
       <c r="AH26" t="inlineStr"/>
       <c r="AI26" t="n">
-        <v>0.9824082716162537</v>
+        <v>0.9823701306252515</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0.001128272964912834</v>
+        <v>0.001129495418667469</v>
       </c>
       <c r="AK26" t="inlineStr"/>
       <c r="AL26" t="n">
-        <v>0.467047362484114</v>
+        <v>0.4634037693418636</v>
       </c>
       <c r="AM26" t="n">
-        <v>0.001011612130225969</v>
+        <v>0.001015064242503256</v>
       </c>
       <c r="AN26" t="inlineStr"/>
     </row>
@@ -3280,10 +3280,10 @@
         <v>0.07321928484019485</v>
       </c>
       <c r="K27" t="n">
-        <v>0.2426473726089903</v>
+        <v>0.2452896402637705</v>
       </c>
       <c r="L27" t="n">
-        <v>0.3113334292707128</v>
+        <v>0.3101309629421319</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
@@ -3292,65 +3292,65 @@
         <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>4.128901529664978</v>
+        <v>4.171003209011483</v>
       </c>
       <c r="P27" t="n">
-        <v>4.155660784901317</v>
+        <v>4.149301127182595</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.9963887362304005</v>
+        <v>0.9964015897120301</v>
       </c>
       <c r="R27" t="n">
-        <v>0.009753438309825248</v>
+        <v>0.00973606525155314</v>
       </c>
       <c r="S27" t="inlineStr"/>
       <c r="T27" t="n">
-        <v>0.900394769765877</v>
+        <v>0.9008776392057188</v>
       </c>
       <c r="U27" t="n">
-        <v>0.01656770704296327</v>
+        <v>0.01652749952230578</v>
       </c>
       <c r="V27" t="inlineStr"/>
       <c r="W27" t="n">
-        <v>0.6636502133531045</v>
+        <v>0.6590828011894931</v>
       </c>
       <c r="X27" t="n">
-        <v>0.0006499314706697847</v>
+        <v>0.0006543294148296382</v>
       </c>
       <c r="Y27" t="inlineStr"/>
       <c r="Z27" t="n">
-        <v>0.9233151698620651</v>
+        <v>0.9235728252701322</v>
       </c>
       <c r="AA27" t="n">
-        <v>0.01174259819647834</v>
+        <v>0.0117228544635618</v>
       </c>
       <c r="AB27" t="inlineStr"/>
       <c r="AC27" t="n">
-        <v>0.9310416949635936</v>
+        <v>0.9298164463228387</v>
       </c>
       <c r="AD27" t="n">
-        <v>0.0009602667592423297</v>
+        <v>0.0009687601899360537</v>
       </c>
       <c r="AE27" t="inlineStr"/>
       <c r="AF27" t="n">
-        <v>0.9021873947343422</v>
+        <v>0.9014770953294831</v>
       </c>
       <c r="AG27" t="n">
-        <v>0.008736723922287188</v>
+        <v>0.008768388881661288</v>
       </c>
       <c r="AH27" t="inlineStr"/>
       <c r="AI27" t="n">
-        <v>0.6228850456888233</v>
+        <v>0.625950300483904</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0.003308433505979403</v>
+        <v>0.003294960315557175</v>
       </c>
       <c r="AK27" t="inlineStr"/>
       <c r="AL27" t="n">
-        <v>0.4381201234247535</v>
+        <v>0.4377434781411439</v>
       </c>
       <c r="AM27" t="n">
-        <v>0.004880754679166372</v>
+        <v>0.004882390264761079</v>
       </c>
       <c r="AN27" t="inlineStr"/>
     </row>
@@ -3392,10 +3392,10 @@
         <v>0.02087465183044777</v>
       </c>
       <c r="K28" t="n">
-        <v>0.4028027310904022</v>
+        <v>0.3983434145777525</v>
       </c>
       <c r="L28" t="n">
-        <v>0.3915066830577246</v>
+        <v>0.405290769298884</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
@@ -3404,16 +3404,16 @@
         <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>4.152089315711887</v>
+        <v>4.109024811393252</v>
       </c>
       <c r="P28" t="n">
-        <v>4.17001940002624</v>
+        <v>4.290280290141594</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.9411493485178295</v>
+        <v>0.9429312534649824</v>
       </c>
       <c r="R28" t="n">
-        <v>0.02526267253496361</v>
+        <v>0.02487727586192935</v>
       </c>
       <c r="S28" t="inlineStr"/>
       <c r="T28" t="inlineStr"/>
@@ -3425,38 +3425,38 @@
       </c>
       <c r="Y28" t="inlineStr"/>
       <c r="Z28" t="n">
-        <v>0.5891214422499327</v>
+        <v>0.6035707661033261</v>
       </c>
       <c r="AA28" t="n">
-        <v>0.05252391622264473</v>
+        <v>0.05159209905216341</v>
       </c>
       <c r="AB28" t="inlineStr"/>
       <c r="AC28" t="n">
-        <v>0.8219395114126131</v>
+        <v>0.8422659327249387</v>
       </c>
       <c r="AD28" t="n">
-        <v>0.005046854955511628</v>
+        <v>0.004750067642096628</v>
       </c>
       <c r="AE28" t="inlineStr"/>
       <c r="AF28" t="n">
-        <v>0.5279641332489722</v>
+        <v>0.5220856700598027</v>
       </c>
       <c r="AG28" t="n">
-        <v>0.01148505175260088</v>
+        <v>0.01155634459376397</v>
       </c>
       <c r="AH28" t="inlineStr"/>
       <c r="AI28" t="n">
-        <v>0.4046802938876518</v>
+        <v>0.4026817643609261</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0.01676625728247006</v>
+        <v>0.01679437644679514</v>
       </c>
       <c r="AK28" t="inlineStr"/>
       <c r="AL28" t="n">
-        <v>0.9887789673220276</v>
+        <v>0.9893995270751944</v>
       </c>
       <c r="AM28" t="n">
-        <v>0.0003667246272611076</v>
+        <v>0.0003564398751098696</v>
       </c>
       <c r="AN28" t="inlineStr"/>
     </row>
@@ -3498,10 +3498,10 @@
         <v>0.03864752444133265</v>
       </c>
       <c r="K29" t="n">
-        <v>0.512131704883432</v>
+        <v>0.5340055862294603</v>
       </c>
       <c r="L29" t="n">
-        <v>0.3414401435392915</v>
+        <v>0.3537813427846556</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
@@ -3510,16 +3510,16 @@
         <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>4.093722495858296</v>
+        <v>4.257333241600258</v>
       </c>
       <c r="P29" t="n">
-        <v>4.104754557777886</v>
+        <v>4.212624139423042</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.9471058787975153</v>
+        <v>0.9513053116423515</v>
       </c>
       <c r="R29" t="n">
-        <v>0.01484129408719915</v>
+        <v>0.01423996307855831</v>
       </c>
       <c r="S29" t="inlineStr"/>
       <c r="T29" t="inlineStr"/>
@@ -3531,38 +3531,38 @@
       </c>
       <c r="Y29" t="inlineStr"/>
       <c r="Z29" t="n">
-        <v>0.7678186752560218</v>
+        <v>0.7860660146354843</v>
       </c>
       <c r="AA29" t="n">
-        <v>0.03139968479525145</v>
+        <v>0.03014057525530507</v>
       </c>
       <c r="AB29" t="inlineStr"/>
       <c r="AC29" t="n">
-        <v>0.9275470979874074</v>
+        <v>0.9301519174395692</v>
       </c>
       <c r="AD29" t="n">
-        <v>0.009323243727810465</v>
+        <v>0.009154115532989501</v>
       </c>
       <c r="AE29" t="inlineStr"/>
       <c r="AF29" t="n">
-        <v>0.6243769738548826</v>
+        <v>0.6855713830580368</v>
       </c>
       <c r="AG29" t="n">
-        <v>0.008662529083873403</v>
+        <v>0.00792555410044218</v>
       </c>
       <c r="AH29" t="inlineStr"/>
       <c r="AI29" t="n">
-        <v>0.9923307451840083</v>
+        <v>0.9907652346544472</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0.002275430111427265</v>
+        <v>0.00249689252581046</v>
       </c>
       <c r="AK29" t="inlineStr"/>
       <c r="AL29" t="n">
-        <v>0.9071803652831271</v>
+        <v>0.9080252017825244</v>
       </c>
       <c r="AM29" t="n">
-        <v>0.001818236037785225</v>
+        <v>0.001809942407007152</v>
       </c>
       <c r="AN29" t="inlineStr"/>
     </row>
@@ -3604,10 +3604,10 @@
         <v>0.0191674492264043</v>
       </c>
       <c r="K30" t="n">
-        <v>0.4711354159409921</v>
+        <v>0.4943630247919258</v>
       </c>
       <c r="L30" t="n">
-        <v>0.3864618719412409</v>
+        <v>0.406758172022455</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -3616,16 +3616,16 @@
         <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>4.182807504896132</v>
+        <v>4.508966688135797</v>
       </c>
       <c r="P30" t="n">
-        <v>4.107967551112456</v>
+        <v>4.315806399300889</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.9723086941163093</v>
+        <v>0.9732717760724511</v>
       </c>
       <c r="R30" t="n">
-        <v>0.01371631995735505</v>
+        <v>0.01347568775327946</v>
       </c>
       <c r="S30" t="inlineStr"/>
       <c r="T30" t="inlineStr"/>
@@ -3637,38 +3637,38 @@
       </c>
       <c r="Y30" t="inlineStr"/>
       <c r="Z30" t="n">
-        <v>0.8616918689671982</v>
+        <v>0.8658231877362211</v>
       </c>
       <c r="AA30" t="n">
-        <v>0.02533190242065968</v>
+        <v>0.02495069716126713</v>
       </c>
       <c r="AB30" t="inlineStr"/>
       <c r="AC30" t="n">
-        <v>0.9893326192242875</v>
+        <v>0.9766646459310458</v>
       </c>
       <c r="AD30" t="n">
-        <v>0.0004654374146164617</v>
+        <v>0.0006883979844861363</v>
       </c>
       <c r="AE30" t="inlineStr"/>
       <c r="AF30" t="n">
-        <v>0.01803450541822449</v>
+        <v>0.08517065322587503</v>
       </c>
       <c r="AG30" t="n">
-        <v>0.01340110449741163</v>
+        <v>0.01293488357252917</v>
       </c>
       <c r="AH30" t="inlineStr"/>
       <c r="AI30" t="n">
-        <v>0.8435932984337757</v>
+        <v>0.8430311994530371</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0.008277551427421691</v>
+        <v>0.00829241214094489</v>
       </c>
       <c r="AK30" t="inlineStr"/>
       <c r="AL30" t="n">
-        <v>0.4840708709931306</v>
+        <v>0.485320244156739</v>
       </c>
       <c r="AM30" t="n">
-        <v>0.001931774298955258</v>
+        <v>0.001929433890419011</v>
       </c>
       <c r="AN30" t="inlineStr"/>
     </row>
@@ -3710,10 +3710,10 @@
         <v>0.02030227596285282</v>
       </c>
       <c r="K31" t="n">
-        <v>0.5036033975236921</v>
+        <v>0.4901448304506785</v>
       </c>
       <c r="L31" t="n">
-        <v>0.4306286015147403</v>
+        <v>0.4307390966259112</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -3722,16 +3722,16 @@
         <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>4.35839592105136</v>
+        <v>4.249026147841872</v>
       </c>
       <c r="P31" t="n">
-        <v>4.404571549628286</v>
+        <v>4.408534161760072</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.985805980365061</v>
+        <v>0.9859673610844005</v>
       </c>
       <c r="R31" t="n">
-        <v>0.007780532430995916</v>
+        <v>0.007736175110345476</v>
       </c>
       <c r="S31" t="inlineStr"/>
       <c r="T31" t="inlineStr"/>
@@ -3743,38 +3743,38 @@
       </c>
       <c r="Y31" t="inlineStr"/>
       <c r="Z31" t="n">
-        <v>0.9432709376871298</v>
+        <v>0.9455034404592624</v>
       </c>
       <c r="AA31" t="n">
-        <v>0.01272154897674931</v>
+        <v>0.01246871603733657</v>
       </c>
       <c r="AB31" t="inlineStr"/>
       <c r="AC31" t="n">
-        <v>0.8995517533593955</v>
+        <v>0.8982920028100511</v>
       </c>
       <c r="AD31" t="n">
-        <v>0.007716004897599537</v>
+        <v>0.007764238466934059</v>
       </c>
       <c r="AE31" t="inlineStr"/>
       <c r="AF31" t="n">
-        <v>0.1285860101680375</v>
+        <v>0.1038843795345048</v>
       </c>
       <c r="AG31" t="n">
-        <v>0.008488034635804543</v>
+        <v>0.008607497454891309</v>
       </c>
       <c r="AH31" t="inlineStr"/>
       <c r="AI31" t="n">
-        <v>0.9694162314579174</v>
+        <v>0.968753259220473</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0.002744196984223618</v>
+        <v>0.002773780852337383</v>
       </c>
       <c r="AK31" t="inlineStr"/>
       <c r="AL31" t="n">
-        <v>0.05945394724080455</v>
+        <v>0.05028342485048809</v>
       </c>
       <c r="AM31" t="n">
-        <v>0.004076238269457521</v>
+        <v>0.004096062156338966</v>
       </c>
       <c r="AN31" t="inlineStr"/>
     </row>
@@ -3816,10 +3816,10 @@
         <v>0.02773752553385222</v>
       </c>
       <c r="K32" t="n">
-        <v>0.4586807473470598</v>
+        <v>0.5003028185540506</v>
       </c>
       <c r="L32" t="n">
-        <v>0.3967883814998332</v>
+        <v>0.4274308509856222</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -3828,16 +3828,16 @@
         <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>4.175457408489923</v>
+        <v>4.530139452862152</v>
       </c>
       <c r="P32" t="n">
-        <v>4.108510545515194</v>
+        <v>4.426225949150417</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.9792549254251126</v>
+        <v>0.9797467054705858</v>
       </c>
       <c r="R32" t="n">
-        <v>0.01386920112993602</v>
+        <v>0.01370382441077479</v>
       </c>
       <c r="S32" t="inlineStr"/>
       <c r="T32" t="inlineStr"/>
@@ -3849,38 +3849,38 @@
       </c>
       <c r="Y32" t="inlineStr"/>
       <c r="Z32" t="n">
-        <v>0.891185877823179</v>
+        <v>0.9022466566662836</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.009408018494476865</v>
+        <v>0.008917052857534644</v>
       </c>
       <c r="AB32" t="inlineStr"/>
       <c r="AC32" t="n">
-        <v>0.226406781486729</v>
+        <v>0.2271863060437095</v>
       </c>
       <c r="AD32" t="n">
-        <v>0.01745877835284029</v>
+        <v>0.01744997981613056</v>
       </c>
       <c r="AE32" t="inlineStr"/>
       <c r="AF32" t="n">
-        <v>-0.6402773739714953</v>
+        <v>-0.5308905534094654</v>
       </c>
       <c r="AG32" t="n">
-        <v>0.01628735773514245</v>
+        <v>0.01573490262979552</v>
       </c>
       <c r="AH32" t="inlineStr"/>
       <c r="AI32" t="n">
-        <v>0.2372324392141342</v>
+        <v>0.2304359754871046</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0.01809619145659767</v>
+        <v>0.01817663362550467</v>
       </c>
       <c r="AK32" t="inlineStr"/>
       <c r="AL32" t="n">
-        <v>0.07910699016666978</v>
+        <v>0.0737867155481069</v>
       </c>
       <c r="AM32" t="n">
-        <v>0.004877751953142133</v>
+        <v>0.004891821777688604</v>
       </c>
       <c r="AN32" t="inlineStr"/>
     </row>
@@ -3920,10 +3920,10 @@
         <v>0.02495281852103528</v>
       </c>
       <c r="K33" t="n">
-        <v>0.2751054178962024</v>
+        <v>0.2845720576653915</v>
       </c>
       <c r="L33" t="n">
-        <v>0.2953103347016996</v>
+        <v>0.309385953827798</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
@@ -3932,16 +3932,16 @@
         <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>4.166252496298712</v>
+        <v>4.300519149462805</v>
       </c>
       <c r="P33" t="n">
-        <v>4.148037589858846</v>
+        <v>4.268926255577062</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.9654287632841264</v>
+        <v>0.9652966305421057</v>
       </c>
       <c r="R33" t="n">
-        <v>0.005898727853838917</v>
+        <v>0.005909989698078893</v>
       </c>
       <c r="S33" t="inlineStr"/>
       <c r="T33" t="inlineStr"/>
@@ -3951,38 +3951,38 @@
       <c r="X33" t="inlineStr"/>
       <c r="Y33" t="inlineStr"/>
       <c r="Z33" t="n">
-        <v>0.9309403751890426</v>
+        <v>0.930858457618045</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.01061915981576181</v>
+        <v>0.0106254560993633</v>
       </c>
       <c r="AB33" t="inlineStr"/>
       <c r="AC33" t="n">
-        <v>0.09764992118680038</v>
+        <v>0.1217477747227871</v>
       </c>
       <c r="AD33" t="n">
-        <v>0.006096050935522517</v>
+        <v>0.006014100569510049</v>
       </c>
       <c r="AE33" t="inlineStr"/>
       <c r="AF33" t="n">
-        <v>0.8713131497358847</v>
+        <v>0.8596925635331981</v>
       </c>
       <c r="AG33" t="n">
-        <v>0.004278925237478026</v>
+        <v>0.004467946433780625</v>
       </c>
       <c r="AH33" t="inlineStr"/>
       <c r="AI33" t="n">
-        <v>0.7720987787496164</v>
+        <v>0.7777413070225867</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0.002265194757533726</v>
+        <v>0.002236977416460872</v>
       </c>
       <c r="AK33" t="inlineStr"/>
       <c r="AL33" t="n">
-        <v>0.3798157655786184</v>
+        <v>0.3825736347723331</v>
       </c>
       <c r="AM33" t="n">
-        <v>0.0007786210821800718</v>
+        <v>0.0007768879458624871</v>
       </c>
       <c r="AN33" t="inlineStr"/>
     </row>
@@ -4024,10 +4024,10 @@
         <v>0.008784365836720525</v>
       </c>
       <c r="K34" t="n">
-        <v>0.5165578838213738</v>
+        <v>0.5337173211659239</v>
       </c>
       <c r="L34" t="n">
-        <v>0.4381577432281694</v>
+        <v>0.4597037194164731</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
@@ -4036,16 +4036,16 @@
         <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>4.125711815458049</v>
+        <v>4.254011730907492</v>
       </c>
       <c r="P34" t="n">
-        <v>4.126564361733847</v>
+        <v>4.289569332936278</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.8919539226295353</v>
+        <v>0.884790543811793</v>
       </c>
       <c r="R34" t="n">
-        <v>0.02292221682132348</v>
+        <v>0.02366988660435418</v>
       </c>
       <c r="S34" t="inlineStr"/>
       <c r="T34" t="inlineStr"/>
@@ -4057,38 +4057,38 @@
       </c>
       <c r="Y34" t="inlineStr"/>
       <c r="Z34" t="n">
-        <v>0.8230729551224383</v>
+        <v>0.8106991218732373</v>
       </c>
       <c r="AA34" t="n">
-        <v>0.05035338778649552</v>
+        <v>0.0520844278401577</v>
       </c>
       <c r="AB34" t="inlineStr"/>
       <c r="AC34" t="n">
-        <v>0.9911263759144169</v>
+        <v>0.9906423490482188</v>
       </c>
       <c r="AD34" t="n">
-        <v>0.002228307286102835</v>
+        <v>0.00228827379840637</v>
       </c>
       <c r="AE34" t="inlineStr"/>
       <c r="AF34" t="n">
-        <v>0.6922909200676028</v>
+        <v>0.7096376348842103</v>
       </c>
       <c r="AG34" t="n">
-        <v>0.004270445178423217</v>
+        <v>0.004148328667916342</v>
       </c>
       <c r="AH34" t="inlineStr"/>
       <c r="AI34" t="n">
-        <v>0.4393357697059542</v>
+        <v>0.4581789492888363</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0.008311718532057401</v>
+        <v>0.008170851925575123</v>
       </c>
       <c r="AK34" t="inlineStr"/>
       <c r="AL34" t="n">
-        <v>0.3322155998597326</v>
+        <v>0.3318348959972142</v>
       </c>
       <c r="AM34" t="n">
-        <v>0.0007944031990052936</v>
+        <v>0.0007946296113580733</v>
       </c>
       <c r="AN34" t="inlineStr"/>
     </row>
@@ -4130,10 +4130,10 @@
         <v>0.033117285160876</v>
       </c>
       <c r="K35" t="n">
-        <v>0.3001566209783726</v>
+        <v>0.3017567405934108</v>
       </c>
       <c r="L35" t="n">
-        <v>0.2368757434316089</v>
+        <v>0.2447387101592386</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
@@ -4142,16 +4142,16 @@
         <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>4.027064102812506</v>
+        <v>4.047146068348874</v>
       </c>
       <c r="P35" t="n">
-        <v>4.02862923397255</v>
+        <v>4.155126683074013</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.9967818950319526</v>
+        <v>0.9967899421229967</v>
       </c>
       <c r="R35" t="n">
-        <v>0.005651374466866431</v>
+        <v>0.005644304220467496</v>
       </c>
       <c r="S35" t="inlineStr"/>
       <c r="T35" t="inlineStr"/>
@@ -4161,10 +4161,10 @@
       <c r="X35" t="inlineStr"/>
       <c r="Y35" t="inlineStr"/>
       <c r="Z35" t="n">
-        <v>0.9820723637840054</v>
+        <v>0.9820833025179087</v>
       </c>
       <c r="AA35" t="n">
-        <v>0.007306442291860728</v>
+        <v>0.007304212900817048</v>
       </c>
       <c r="AB35" t="inlineStr"/>
       <c r="AC35" t="inlineStr"/>
@@ -4173,24 +4173,24 @@
       </c>
       <c r="AE35" t="inlineStr"/>
       <c r="AF35" t="n">
-        <v>0.6750227718300755</v>
+        <v>0.6763340926124476</v>
       </c>
       <c r="AG35" t="n">
-        <v>0.008513541623755295</v>
+        <v>0.00849634769774184</v>
       </c>
       <c r="AH35" t="inlineStr"/>
       <c r="AI35" t="n">
-        <v>0.7321567243824347</v>
+        <v>0.7315717490061899</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0.002091424273089776</v>
+        <v>0.002093706884864355</v>
       </c>
       <c r="AK35" t="inlineStr"/>
       <c r="AL35" t="n">
-        <v>0.5230971440667919</v>
+        <v>0.5251730074787959</v>
       </c>
       <c r="AM35" t="n">
-        <v>0.002344801988742898</v>
+        <v>0.002339693194615889</v>
       </c>
       <c r="AN35" t="inlineStr"/>
     </row>
@@ -4232,10 +4232,10 @@
         <v>0.02290841461070009</v>
       </c>
       <c r="K36" t="n">
-        <v>0.4200622561347667</v>
+        <v>0.4303510992459229</v>
       </c>
       <c r="L36" t="n">
-        <v>0.3831600102508279</v>
+        <v>0.3940041415817687</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
@@ -4244,16 +4244,16 @@
         <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>4.208803672383319</v>
+        <v>4.305403694774172</v>
       </c>
       <c r="P36" t="n">
-        <v>4.208581070838521</v>
+        <v>4.320738530966725</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.9835769469014141</v>
+        <v>0.9836102967342929</v>
       </c>
       <c r="R36" t="n">
-        <v>0.01161252434776945</v>
+        <v>0.01160072774237137</v>
       </c>
       <c r="S36" t="inlineStr"/>
       <c r="T36" t="inlineStr"/>
@@ -4265,38 +4265,38 @@
       </c>
       <c r="Y36" t="inlineStr"/>
       <c r="Z36" t="n">
-        <v>0.8060266221175501</v>
+        <v>0.8065746744763604</v>
       </c>
       <c r="AA36" t="n">
-        <v>0.01914531271103744</v>
+        <v>0.01911824699751956</v>
       </c>
       <c r="AB36" t="inlineStr"/>
       <c r="AC36" t="n">
-        <v>0.3677947154154995</v>
+        <v>0.367525906756115</v>
       </c>
       <c r="AD36" t="n">
-        <v>0.00815645596527957</v>
+        <v>0.008158189811100849</v>
       </c>
       <c r="AE36" t="inlineStr"/>
       <c r="AF36" t="n">
-        <v>0.1010078332160818</v>
+        <v>0.1028198803448294</v>
       </c>
       <c r="AG36" t="n">
-        <v>0.01322854592546969</v>
+        <v>0.01321520718857418</v>
       </c>
       <c r="AH36" t="inlineStr"/>
       <c r="AI36" t="n">
-        <v>0.7318201298142536</v>
+        <v>0.7311364352005947</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0.006066798590073802</v>
+        <v>0.006074526980104867</v>
       </c>
       <c r="AK36" t="inlineStr"/>
       <c r="AL36" t="n">
-        <v>0.1612504013843504</v>
+        <v>0.1631199438672212</v>
       </c>
       <c r="AM36" t="n">
-        <v>0.004049959099786035</v>
+        <v>0.004045442975723871</v>
       </c>
       <c r="AN36" t="inlineStr"/>
     </row>
@@ -4338,10 +4338,10 @@
         <v>0.007462828179086988</v>
       </c>
       <c r="K37" t="n">
-        <v>0.1057540787127461</v>
+        <v>0.1033156315000568</v>
       </c>
       <c r="L37" t="n">
-        <v>0.1089937639589356</v>
+        <v>0.105989240617094</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
@@ -4350,61 +4350,61 @@
         <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>4.325915956550759</v>
+        <v>4.2322895226395</v>
       </c>
       <c r="P37" t="n">
-        <v>4.362928199445947</v>
+        <v>4.263467469259709</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.9932588349070247</v>
+        <v>0.9932355178273524</v>
       </c>
       <c r="R37" t="n">
-        <v>0.005470868182428546</v>
+        <v>0.005480321633666626</v>
       </c>
       <c r="S37" t="inlineStr"/>
       <c r="T37" t="inlineStr"/>
       <c r="U37" t="inlineStr"/>
       <c r="V37" t="inlineStr"/>
       <c r="W37" t="n">
-        <v>0.0299938843851475</v>
+        <v>0.03028582223180765</v>
       </c>
       <c r="X37" t="n">
-        <v>0.0004213428384632135</v>
+        <v>0.0004212794289776973</v>
       </c>
       <c r="Y37" t="inlineStr"/>
       <c r="Z37" t="n">
-        <v>0.9983167693716564</v>
+        <v>0.9983483979738434</v>
       </c>
       <c r="AA37" t="n">
-        <v>0.001947876784427047</v>
+        <v>0.001929489290990243</v>
       </c>
       <c r="AB37" t="inlineStr"/>
       <c r="AC37" t="n">
-        <v>-0.5040702741241765</v>
+        <v>-0.5024649171995881</v>
       </c>
       <c r="AD37" t="n">
-        <v>0.007765111171380051</v>
+        <v>0.007760966051537448</v>
       </c>
       <c r="AE37" t="inlineStr"/>
       <c r="AF37" t="n">
-        <v>0.9144432373190192</v>
+        <v>0.9137853380899765</v>
       </c>
       <c r="AG37" t="n">
-        <v>0.009518724186465195</v>
+        <v>0.009555251799096498</v>
       </c>
       <c r="AH37" t="inlineStr"/>
       <c r="AI37" t="n">
-        <v>0.940203643404257</v>
+        <v>0.9403141793133138</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0.002193890175299171</v>
+        <v>0.002191861491347629</v>
       </c>
       <c r="AK37" t="inlineStr"/>
       <c r="AL37" t="n">
-        <v>0.9999999970704111</v>
+        <v>0.9999997601921665</v>
       </c>
       <c r="AM37" t="n">
-        <v>5.327937038481826e-08</v>
+        <v>4.82044827755296e-07</v>
       </c>
       <c r="AN37" t="inlineStr"/>
     </row>
@@ -4446,10 +4446,10 @@
         <v>0.003185097564105027</v>
       </c>
       <c r="K38" t="n">
-        <v>0.1483762115382365</v>
+        <v>0.1414949912042679</v>
       </c>
       <c r="L38" t="n">
-        <v>0.1138584835256079</v>
+        <v>0.1088639589686587</v>
       </c>
       <c r="M38" t="n">
         <v>0</v>
@@ -4458,61 +4458,61 @@
         <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>4.296526671931293</v>
+        <v>4.109497407226164</v>
       </c>
       <c r="P38" t="n">
-        <v>4.354336837449976</v>
+        <v>4.195433165024799</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.9538121928541338</v>
+        <v>0.9539271641807503</v>
       </c>
       <c r="R38" t="n">
-        <v>0.01205907118288497</v>
+        <v>0.01204405302805255</v>
       </c>
       <c r="S38" t="inlineStr"/>
       <c r="T38" t="inlineStr"/>
       <c r="U38" t="inlineStr"/>
       <c r="V38" t="inlineStr"/>
       <c r="W38" t="n">
-        <v>0.1887539275713247</v>
+        <v>0.1847479057418968</v>
       </c>
       <c r="X38" t="n">
-        <v>0.00118057454774713</v>
+        <v>0.001183485861193669</v>
       </c>
       <c r="Y38" t="inlineStr"/>
       <c r="Z38" t="n">
-        <v>0.8109250065975481</v>
+        <v>0.8115797081627778</v>
       </c>
       <c r="AA38" t="n">
-        <v>0.02097239677063583</v>
+        <v>0.02093605519128235</v>
       </c>
       <c r="AB38" t="inlineStr"/>
       <c r="AC38" t="n">
-        <v>-0.3913229412018957</v>
+        <v>-0.3873194027207028</v>
       </c>
       <c r="AD38" t="n">
-        <v>0.01712024780170345</v>
+        <v>0.01709559825877765</v>
       </c>
       <c r="AE38" t="inlineStr"/>
       <c r="AF38" t="n">
-        <v>0.966710356823042</v>
+        <v>0.9651012801458784</v>
       </c>
       <c r="AG38" t="n">
-        <v>0.004235246858030138</v>
+        <v>0.004336395720794464</v>
       </c>
       <c r="AH38" t="inlineStr"/>
       <c r="AI38" t="n">
-        <v>-1.178208910301884</v>
+        <v>-1.138275440562116</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0.00487533828142523</v>
+        <v>0.004830441356116479</v>
       </c>
       <c r="AK38" t="inlineStr"/>
       <c r="AL38" t="n">
-        <v>0.9999969927291992</v>
+        <v>0.999997220570763</v>
       </c>
       <c r="AM38" t="n">
-        <v>6.950305838317476e-07</v>
+        <v>6.681830546054594e-07</v>
       </c>
       <c r="AN38" t="inlineStr"/>
     </row>
@@ -4554,10 +4554,10 @@
         <v>0.03277409385829239</v>
       </c>
       <c r="K39" t="n">
-        <v>0.1491847814540822</v>
+        <v>0.1514588065490762</v>
       </c>
       <c r="L39" t="n">
-        <v>0.1317020544517115</v>
+        <v>0.1342714605126339</v>
       </c>
       <c r="M39" t="n">
         <v>0</v>
@@ -4566,16 +4566,16 @@
         <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>4.198070974628081</v>
+        <v>4.258033543989585</v>
       </c>
       <c r="P39" t="n">
-        <v>4.188954527563515</v>
+        <v>4.266349377449965</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.9827741907063748</v>
+        <v>0.9827773649056697</v>
       </c>
       <c r="R39" t="n">
-        <v>0.00878505941568368</v>
+        <v>0.008784249967092275</v>
       </c>
       <c r="S39" t="inlineStr"/>
       <c r="T39" t="inlineStr"/>
@@ -4585,38 +4585,38 @@
       <c r="X39" t="inlineStr"/>
       <c r="Y39" t="inlineStr"/>
       <c r="Z39" t="n">
-        <v>0.882220896621827</v>
+        <v>0.8822854639021227</v>
       </c>
       <c r="AA39" t="n">
-        <v>0.01148643567358987</v>
+        <v>0.01148328677211925</v>
       </c>
       <c r="AB39" t="inlineStr"/>
       <c r="AC39" t="n">
-        <v>0.1214846240723172</v>
+        <v>0.1222420223291134</v>
       </c>
       <c r="AD39" t="n">
-        <v>0.001394463945615677</v>
+        <v>0.001393862708387718</v>
       </c>
       <c r="AE39" t="inlineStr"/>
       <c r="AF39" t="n">
-        <v>-0.06326684280318329</v>
+        <v>-0.06332093944888362</v>
       </c>
       <c r="AG39" t="n">
-        <v>0.01476954400789191</v>
+        <v>0.01476991972384337</v>
       </c>
       <c r="AH39" t="inlineStr"/>
       <c r="AI39" t="n">
-        <v>0.7528771644452634</v>
+        <v>0.7529487446492968</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0.005394450712619433</v>
+        <v>0.005393669392982733</v>
       </c>
       <c r="AK39" t="inlineStr"/>
       <c r="AL39" t="n">
-        <v>-0.1190359810737407</v>
+        <v>-0.1190897937720492</v>
       </c>
       <c r="AM39" t="n">
-        <v>0.002182677670748964</v>
+        <v>0.002182730150903738</v>
       </c>
       <c r="AN39" t="inlineStr"/>
     </row>
@@ -4658,10 +4658,10 @@
         <v>0.003165060709665684</v>
       </c>
       <c r="K40" t="n">
-        <v>0.2411411590284251</v>
+        <v>0.2387698264019981</v>
       </c>
       <c r="L40" t="n">
-        <v>0.4026585712997566</v>
+        <v>0.3947185557296076</v>
       </c>
       <c r="M40" t="n">
         <v>0</v>
@@ -4670,16 +4670,16 @@
         <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>4.568405641987668</v>
+        <v>4.328495843657492</v>
       </c>
       <c r="P40" t="n">
-        <v>4.621037843935212</v>
+        <v>4.520219966400318</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.9927456753972665</v>
+        <v>0.9926881436121278</v>
       </c>
       <c r="R40" t="n">
-        <v>0.005116094488792457</v>
+        <v>0.005136341499494995</v>
       </c>
       <c r="S40" t="inlineStr"/>
       <c r="T40" t="inlineStr"/>
@@ -4689,38 +4689,38 @@
       <c r="X40" t="inlineStr"/>
       <c r="Y40" t="inlineStr"/>
       <c r="Z40" t="n">
-        <v>0.9760550928217256</v>
+        <v>0.9754593074877741</v>
       </c>
       <c r="AA40" t="n">
-        <v>0.009338309879830319</v>
+        <v>0.00945377168003148</v>
       </c>
       <c r="AB40" t="inlineStr"/>
       <c r="AC40" t="n">
-        <v>0.9466845081574171</v>
+        <v>0.9514586295839517</v>
       </c>
       <c r="AD40" t="n">
-        <v>0.0005253021090475295</v>
+        <v>0.0005012316091013193</v>
       </c>
       <c r="AE40" t="inlineStr"/>
       <c r="AF40" t="n">
-        <v>0.9780816957243846</v>
+        <v>0.9783357616732288</v>
       </c>
       <c r="AG40" t="n">
-        <v>0.003718662614183426</v>
+        <v>0.003697047360852378</v>
       </c>
       <c r="AH40" t="inlineStr"/>
       <c r="AI40" t="n">
-        <v>0.9918302083611374</v>
+        <v>0.9923511690346821</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0.004059122721349545</v>
+        <v>0.003927572614426075</v>
       </c>
       <c r="AK40" t="inlineStr"/>
       <c r="AL40" t="n">
-        <v>0.9999996779589894</v>
+        <v>0.9999996572715453</v>
       </c>
       <c r="AM40" t="n">
-        <v>3.450462551157391e-07</v>
+        <v>3.559564027537347e-07</v>
       </c>
       <c r="AN40" t="inlineStr"/>
     </row>
@@ -4762,10 +4762,10 @@
         <v>0.01422966781757511</v>
       </c>
       <c r="K41" t="n">
-        <v>0.2672649319402196</v>
+        <v>0.2578829215911677</v>
       </c>
       <c r="L41" t="n">
-        <v>0.2936142998702156</v>
+        <v>0.2872185104656401</v>
       </c>
       <c r="M41" t="n">
         <v>0</v>
@@ -4774,16 +4774,16 @@
         <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>4.586833780976132</v>
+        <v>4.435301806859223</v>
       </c>
       <c r="P41" t="n">
-        <v>4.61396694708275</v>
+        <v>4.505579336452995</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.99382172830668</v>
+        <v>0.9938802461812383</v>
       </c>
       <c r="R41" t="n">
-        <v>0.006091840271195767</v>
+        <v>0.006062922015975779</v>
       </c>
       <c r="S41" t="inlineStr"/>
       <c r="T41" t="inlineStr"/>
@@ -4793,38 +4793,38 @@
       <c r="X41" t="inlineStr"/>
       <c r="Y41" t="inlineStr"/>
       <c r="Z41" t="n">
-        <v>0.8654569427586279</v>
+        <v>0.8651955792843189</v>
       </c>
       <c r="AA41" t="n">
-        <v>0.0106816383037887</v>
+        <v>0.01069200835051347</v>
       </c>
       <c r="AB41" t="inlineStr"/>
       <c r="AC41" t="n">
-        <v>0.6582137419953473</v>
+        <v>0.6519294386498865</v>
       </c>
       <c r="AD41" t="n">
-        <v>0.001457973620451466</v>
+        <v>0.001471316191816905</v>
       </c>
       <c r="AE41" t="inlineStr"/>
       <c r="AF41" t="n">
-        <v>0.9799420538027465</v>
+        <v>0.981326448799946</v>
       </c>
       <c r="AG41" t="n">
-        <v>0.003797380291212975</v>
+        <v>0.00366399033495248</v>
       </c>
       <c r="AH41" t="inlineStr"/>
       <c r="AI41" t="n">
-        <v>0.9482023514175898</v>
+        <v>0.9491777690507551</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0.007337458937043548</v>
+        <v>0.007268043602594663</v>
       </c>
       <c r="AK41" t="inlineStr"/>
       <c r="AL41" t="n">
-        <v>0.8993246161722759</v>
+        <v>0.9001785172172251</v>
       </c>
       <c r="AM41" t="n">
-        <v>0.001034941925434154</v>
+        <v>0.001030543532037453</v>
       </c>
       <c r="AN41" t="inlineStr"/>
     </row>
@@ -4866,10 +4866,10 @@
         <v>0.01067227249555984</v>
       </c>
       <c r="K42" t="n">
-        <v>0.1903469762152839</v>
+        <v>0.277385678721059</v>
       </c>
       <c r="L42" t="n">
-        <v>0.4334743739516553</v>
+        <v>0.4374622634848779</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
@@ -4878,16 +4878,16 @@
         <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>4.524889107463629</v>
+        <v>4.541320208590085</v>
       </c>
       <c r="P42" t="n">
-        <v>4.609529862136304</v>
+        <v>4.559328256640657</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.9645048130014372</v>
+        <v>0.96449826283581</v>
       </c>
       <c r="R42" t="n">
-        <v>0.01247625025115848</v>
+        <v>0.01247740136124769</v>
       </c>
       <c r="S42" t="inlineStr"/>
       <c r="T42" t="inlineStr"/>
@@ -4897,31 +4897,31 @@
       <c r="X42" t="inlineStr"/>
       <c r="Y42" t="inlineStr"/>
       <c r="Z42" t="n">
-        <v>0.8248711825786337</v>
+        <v>0.82226935784296</v>
       </c>
       <c r="AA42" t="n">
-        <v>0.02296524178864405</v>
+        <v>0.02313520593773982</v>
       </c>
       <c r="AB42" t="inlineStr"/>
       <c r="AC42" t="n">
-        <v>0.9965388723330731</v>
+        <v>0.996102554969613</v>
       </c>
       <c r="AD42" t="n">
-        <v>0.0003144410286352279</v>
+        <v>0.0003336724868591206</v>
       </c>
       <c r="AE42" t="inlineStr"/>
       <c r="AF42" t="n">
-        <v>0.8427446900378334</v>
+        <v>0.8521008393374599</v>
       </c>
       <c r="AG42" t="n">
-        <v>0.01157363380579257</v>
+        <v>0.01122405877434713</v>
       </c>
       <c r="AH42" t="inlineStr"/>
       <c r="AI42" t="n">
-        <v>0.9863409822781105</v>
+        <v>0.9860836589571182</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0.00361423367433291</v>
+        <v>0.003648119243541842</v>
       </c>
       <c r="AK42" t="inlineStr"/>
       <c r="AL42" t="inlineStr"/>
@@ -4968,10 +4968,10 @@
         <v>0.0240059836138475</v>
       </c>
       <c r="K43" t="n">
-        <v>0.1504728716669206</v>
+        <v>0.1503222139950793</v>
       </c>
       <c r="L43" t="n">
-        <v>0.3646519039503563</v>
+        <v>0.3672857730929937</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
@@ -4980,16 +4980,16 @@
         <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>4.103051778684014</v>
+        <v>4.014610252289849</v>
       </c>
       <c r="P43" t="n">
-        <v>4.242700949384169</v>
+        <v>4.250246286412207</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.9514077351703787</v>
+        <v>0.9515311207326109</v>
       </c>
       <c r="R43" t="n">
-        <v>0.01346897996329369</v>
+        <v>0.01345186886574083</v>
       </c>
       <c r="S43" t="inlineStr"/>
       <c r="T43" t="inlineStr"/>
@@ -4999,38 +4999,38 @@
       <c r="X43" t="inlineStr"/>
       <c r="Y43" t="inlineStr"/>
       <c r="Z43" t="n">
-        <v>0.898216138595175</v>
+        <v>0.8984392778677907</v>
       </c>
       <c r="AA43" t="n">
-        <v>0.02743743969422875</v>
+        <v>0.02740734784356515</v>
       </c>
       <c r="AB43" t="inlineStr"/>
       <c r="AC43" t="n">
-        <v>0.726126807795418</v>
+        <v>0.7284211376014068</v>
       </c>
       <c r="AD43" t="n">
-        <v>0.002471485696687043</v>
+        <v>0.002461111682005627</v>
       </c>
       <c r="AE43" t="inlineStr"/>
       <c r="AF43" t="n">
-        <v>0.8582360372794891</v>
+        <v>0.8587680447637261</v>
       </c>
       <c r="AG43" t="n">
-        <v>0.01193198287880125</v>
+        <v>0.01190957284303482</v>
       </c>
       <c r="AH43" t="inlineStr"/>
       <c r="AI43" t="n">
-        <v>0.8242245959853057</v>
+        <v>0.826255233323128</v>
       </c>
       <c r="AJ43" t="n">
-        <v>0.002350245356979565</v>
+        <v>0.002336630369978089</v>
       </c>
       <c r="AK43" t="inlineStr"/>
       <c r="AL43" t="n">
-        <v>0.9841765887850686</v>
+        <v>0.9844027960266217</v>
       </c>
       <c r="AM43" t="n">
-        <v>0.0004998990664688415</v>
+        <v>0.0004963129924761006</v>
       </c>
       <c r="AN43" t="inlineStr"/>
     </row>
@@ -5072,10 +5072,10 @@
         <v>0.02192364384915694</v>
       </c>
       <c r="K44" t="n">
-        <v>0.1778728783246155</v>
+        <v>0.1750004298657557</v>
       </c>
       <c r="L44" t="n">
-        <v>0.3409782340247858</v>
+        <v>0.3271453757894115</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
@@ -5084,16 +5084,16 @@
         <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>4.33244628845221</v>
+        <v>4.26677501303533</v>
       </c>
       <c r="P44" t="n">
-        <v>4.578197656346277</v>
+        <v>4.389336156098157</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.9434428387582025</v>
+        <v>0.9436990976759149</v>
       </c>
       <c r="R44" t="n">
-        <v>0.008100194223064095</v>
+        <v>0.008081822512133931</v>
       </c>
       <c r="S44" t="inlineStr"/>
       <c r="T44" t="inlineStr"/>
@@ -5103,38 +5103,38 @@
       <c r="X44" t="inlineStr"/>
       <c r="Y44" t="inlineStr"/>
       <c r="Z44" t="n">
-        <v>0.9155363542052839</v>
+        <v>0.9160532059420502</v>
       </c>
       <c r="AA44" t="n">
-        <v>0.01303260108462765</v>
+        <v>0.01299266521197464</v>
       </c>
       <c r="AB44" t="inlineStr"/>
       <c r="AC44" t="n">
-        <v>0.8049811145483285</v>
+        <v>0.8046322025389985</v>
       </c>
       <c r="AD44" t="n">
-        <v>0.004897673762934648</v>
+        <v>0.004902053065829957</v>
       </c>
       <c r="AE44" t="inlineStr"/>
       <c r="AF44" t="n">
-        <v>0.9432158617603925</v>
+        <v>0.9424598499734625</v>
       </c>
       <c r="AG44" t="n">
-        <v>0.008334447346035377</v>
+        <v>0.008389745416451655</v>
       </c>
       <c r="AH44" t="inlineStr"/>
       <c r="AI44" t="n">
-        <v>0.8662003735362926</v>
+        <v>0.8693015582673569</v>
       </c>
       <c r="AJ44" t="n">
-        <v>0.007946437495022083</v>
+        <v>0.007853807024223858</v>
       </c>
       <c r="AK44" t="inlineStr"/>
       <c r="AL44" t="n">
-        <v>0.6386839128105477</v>
+        <v>0.627820126103811</v>
       </c>
       <c r="AM44" t="n">
-        <v>0.001273165940284053</v>
+        <v>0.001292164498384604</v>
       </c>
       <c r="AN44" t="inlineStr"/>
     </row>
@@ -5176,10 +5176,10 @@
         <v>0.02487778863857871</v>
       </c>
       <c r="K45" t="n">
-        <v>0.399617491041528</v>
+        <v>0.3970700662958236</v>
       </c>
       <c r="L45" t="n">
-        <v>0.3251304839370023</v>
+        <v>0.3275258470037932</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
@@ -5188,16 +5188,16 @@
         <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>4.249422615389083</v>
+        <v>4.224020019874794</v>
       </c>
       <c r="P45" t="n">
-        <v>4.339318974042655</v>
+        <v>4.375440194607536</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.9687516229047559</v>
+        <v>0.9687751708200327</v>
       </c>
       <c r="R45" t="n">
-        <v>0.008633240286353296</v>
+        <v>0.008629986787395804</v>
       </c>
       <c r="S45" t="inlineStr"/>
       <c r="T45" t="inlineStr"/>
@@ -5207,38 +5207,38 @@
       <c r="X45" t="inlineStr"/>
       <c r="Y45" t="inlineStr"/>
       <c r="Z45" t="n">
-        <v>0.9762309536946555</v>
+        <v>0.9762472131166755</v>
       </c>
       <c r="AA45" t="n">
-        <v>0.01318664428628866</v>
+        <v>0.01318213329558572</v>
       </c>
       <c r="AB45" t="inlineStr"/>
       <c r="AC45" t="n">
-        <v>0.9228672729477129</v>
+        <v>0.9229489468869232</v>
       </c>
       <c r="AD45" t="n">
-        <v>0.007283831622443354</v>
+        <v>0.007279974266374508</v>
       </c>
       <c r="AE45" t="inlineStr"/>
       <c r="AF45" t="n">
-        <v>0.8709201383226352</v>
+        <v>0.8710034196413887</v>
       </c>
       <c r="AG45" t="n">
-        <v>0.008537812805711842</v>
+        <v>0.008535058096236186</v>
       </c>
       <c r="AH45" t="inlineStr"/>
       <c r="AI45" t="n">
-        <v>0.9217780070382735</v>
+        <v>0.9218406137914298</v>
       </c>
       <c r="AJ45" t="n">
-        <v>0.008511309199529865</v>
+        <v>0.008507902407658757</v>
       </c>
       <c r="AK45" t="inlineStr"/>
       <c r="AL45" t="n">
-        <v>0.9799918004085818</v>
+        <v>0.9800276216909577</v>
       </c>
       <c r="AM45" t="n">
-        <v>0.0006211012614491868</v>
+        <v>0.000620545024227616</v>
       </c>
       <c r="AN45" t="inlineStr"/>
     </row>
@@ -5280,10 +5280,10 @@
         <v>0.04354702384994095</v>
       </c>
       <c r="K46" t="n">
-        <v>0.4729359869420497</v>
+        <v>0.4191548341898909</v>
       </c>
       <c r="L46" t="n">
-        <v>0.4308421582610232</v>
+        <v>0.4168763599596889</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
@@ -5292,16 +5292,16 @@
         <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>4.220017038479095</v>
+        <v>3.769550246054656</v>
       </c>
       <c r="P46" t="n">
-        <v>4.573524191133153</v>
+        <v>4.474246364770191</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.9665016990216085</v>
+        <v>0.9687411047786199</v>
       </c>
       <c r="R46" t="n">
-        <v>0.008726449747929462</v>
+        <v>0.008429717377463572</v>
       </c>
       <c r="S46" t="inlineStr"/>
       <c r="T46" t="inlineStr"/>
@@ -5311,38 +5311,38 @@
       <c r="X46" t="inlineStr"/>
       <c r="Y46" t="inlineStr"/>
       <c r="Z46" t="n">
-        <v>0.9805865427667279</v>
+        <v>0.9825621906838121</v>
       </c>
       <c r="AA46" t="n">
-        <v>0.01074397269041094</v>
+        <v>0.01018261717193388</v>
       </c>
       <c r="AB46" t="inlineStr"/>
       <c r="AC46" t="n">
-        <v>0.9215003125481068</v>
+        <v>0.9244883895932834</v>
       </c>
       <c r="AD46" t="n">
-        <v>0.01039959817555755</v>
+        <v>0.01019974845920663</v>
       </c>
       <c r="AE46" t="inlineStr"/>
       <c r="AF46" t="n">
-        <v>0.9736598631809625</v>
+        <v>0.9761741219411049</v>
       </c>
       <c r="AG46" t="n">
-        <v>0.002656669684523781</v>
+        <v>0.002526696065791834</v>
       </c>
       <c r="AH46" t="inlineStr"/>
       <c r="AI46" t="n">
-        <v>0.8639800730225278</v>
+        <v>0.8721008938082562</v>
       </c>
       <c r="AJ46" t="n">
-        <v>0.01221315986281886</v>
+        <v>0.0118429672374478</v>
       </c>
       <c r="AK46" t="inlineStr"/>
       <c r="AL46" t="n">
-        <v>0.9872533160827263</v>
+        <v>0.9873983451204669</v>
       </c>
       <c r="AM46" t="n">
-        <v>0.0009751240858975513</v>
+        <v>0.0009695608398424529</v>
       </c>
       <c r="AN46" t="inlineStr"/>
     </row>
@@ -5384,10 +5384,10 @@
         <v>0.01548193654302897</v>
       </c>
       <c r="K47" t="n">
-        <v>0.251984504906933</v>
+        <v>0.2534470292225203</v>
       </c>
       <c r="L47" t="n">
-        <v>0.384807069729783</v>
+        <v>0.3804221654864902</v>
       </c>
       <c r="M47" t="n">
         <v>0</v>
@@ -5396,16 +5396,16 @@
         <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>4.262041686410713</v>
+        <v>4.285238971656212</v>
       </c>
       <c r="P47" t="n">
-        <v>4.397325222758508</v>
+        <v>4.355338806089541</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.9501585453197885</v>
+        <v>0.9499675728583342</v>
       </c>
       <c r="R47" t="n">
-        <v>0.008389873890057674</v>
+        <v>0.008405931838519721</v>
       </c>
       <c r="S47" t="inlineStr"/>
       <c r="T47" t="inlineStr"/>
@@ -5415,38 +5415,38 @@
       <c r="X47" t="inlineStr"/>
       <c r="Y47" t="inlineStr"/>
       <c r="Z47" t="n">
-        <v>0.9281394194981591</v>
+        <v>0.9280134275048924</v>
       </c>
       <c r="AA47" t="n">
-        <v>0.0147702245474781</v>
+        <v>0.01478316707485817</v>
       </c>
       <c r="AB47" t="inlineStr"/>
       <c r="AC47" t="n">
-        <v>0.8111492368536617</v>
+        <v>0.8095213335784225</v>
       </c>
       <c r="AD47" t="n">
-        <v>0.006790072266121376</v>
+        <v>0.00681927485499712</v>
       </c>
       <c r="AE47" t="inlineStr"/>
       <c r="AF47" t="n">
-        <v>0.9153074343984091</v>
+        <v>0.9145169469472024</v>
       </c>
       <c r="AG47" t="n">
-        <v>0.008677169484748552</v>
+        <v>0.008717570094534379</v>
       </c>
       <c r="AH47" t="inlineStr"/>
       <c r="AI47" t="n">
-        <v>0.9499897256642864</v>
+        <v>0.9505309367183397</v>
       </c>
       <c r="AJ47" t="n">
-        <v>0.003468098191338427</v>
+        <v>0.003449281269043725</v>
       </c>
       <c r="AK47" t="inlineStr"/>
       <c r="AL47" t="n">
-        <v>0.9001869576478293</v>
+        <v>0.9012792860527055</v>
       </c>
       <c r="AM47" t="n">
-        <v>0.0006035971847728758</v>
+        <v>0.000600285292119425</v>
       </c>
       <c r="AN47" t="inlineStr"/>
     </row>
@@ -5488,10 +5488,10 @@
         <v>0.04054047652094685</v>
       </c>
       <c r="K48" t="n">
-        <v>0.1259930651411941</v>
+        <v>0.1132798991704734</v>
       </c>
       <c r="L48" t="n">
-        <v>0.3915823744017324</v>
+        <v>0.3941761000608428</v>
       </c>
       <c r="M48" t="n">
         <v>0</v>
@@ -5500,16 +5500,16 @@
         <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>4.090716553477905</v>
+        <v>3.703826593445649</v>
       </c>
       <c r="P48" t="n">
-        <v>4.345145418865432</v>
+        <v>4.323796651864424</v>
       </c>
       <c r="Q48" t="n">
-        <v>0.9824236689627371</v>
+        <v>0.9822785264617602</v>
       </c>
       <c r="R48" t="n">
-        <v>0.006835846719772154</v>
+        <v>0.006864013349149739</v>
       </c>
       <c r="S48" t="inlineStr"/>
       <c r="T48" t="inlineStr"/>
@@ -5519,38 +5519,38 @@
       <c r="X48" t="inlineStr"/>
       <c r="Y48" t="inlineStr"/>
       <c r="Z48" t="n">
-        <v>0.969358872862212</v>
+        <v>0.9685191461319849</v>
       </c>
       <c r="AA48" t="n">
-        <v>0.01279963530284998</v>
+        <v>0.01297383824231126</v>
       </c>
       <c r="AB48" t="inlineStr"/>
       <c r="AC48" t="n">
-        <v>0.8624571562506164</v>
+        <v>0.8641702082448598</v>
       </c>
       <c r="AD48" t="n">
-        <v>0.006264845236928058</v>
+        <v>0.006225709681120688</v>
       </c>
       <c r="AE48" t="inlineStr"/>
       <c r="AF48" t="n">
-        <v>0.9927038433513082</v>
+        <v>0.993280752478491</v>
       </c>
       <c r="AG48" t="n">
-        <v>0.004953444009906843</v>
+        <v>0.004753576674794105</v>
       </c>
       <c r="AH48" t="inlineStr"/>
       <c r="AI48" t="n">
-        <v>0.9124507303954397</v>
+        <v>0.913903805183183</v>
       </c>
       <c r="AJ48" t="n">
-        <v>0.002445137659202598</v>
+        <v>0.002424761510567896</v>
       </c>
       <c r="AK48" t="inlineStr"/>
       <c r="AL48" t="n">
-        <v>0.9991702163929184</v>
+        <v>0.9997081465432875</v>
       </c>
       <c r="AM48" t="n">
-        <v>0.0002230390565399479</v>
+        <v>0.0001322759577286648</v>
       </c>
       <c r="AN48" t="inlineStr"/>
     </row>
@@ -5592,10 +5592,10 @@
         <v>0.02297528417150188</v>
       </c>
       <c r="K49" t="n">
-        <v>0.3103231553047239</v>
+        <v>0.3104389713261222</v>
       </c>
       <c r="L49" t="n">
-        <v>0.4662250805240874</v>
+        <v>0.4651109104583399</v>
       </c>
       <c r="M49" t="n">
         <v>0</v>
@@ -5604,16 +5604,16 @@
         <v>0</v>
       </c>
       <c r="O49" t="n">
-        <v>4.312452942874997</v>
+        <v>4.067105644874856</v>
       </c>
       <c r="P49" t="n">
-        <v>4.417565021541686</v>
+        <v>4.395360617121717</v>
       </c>
       <c r="Q49" t="n">
-        <v>0.9296833761316583</v>
+        <v>0.9298662569964591</v>
       </c>
       <c r="R49" t="n">
-        <v>0.01256910294346034</v>
+        <v>0.01255274731637791</v>
       </c>
       <c r="S49" t="inlineStr"/>
       <c r="T49" t="inlineStr"/>
@@ -5623,38 +5623,38 @@
       <c r="X49" t="inlineStr"/>
       <c r="Y49" t="inlineStr"/>
       <c r="Z49" t="n">
-        <v>0.9286620394666337</v>
+        <v>0.9278683796381362</v>
       </c>
       <c r="AA49" t="n">
-        <v>0.01801619864871107</v>
+        <v>0.01811613971176503</v>
       </c>
       <c r="AB49" t="inlineStr"/>
       <c r="AC49" t="n">
-        <v>0.9262180754690128</v>
+        <v>0.9281822247005073</v>
       </c>
       <c r="AD49" t="n">
-        <v>0.002604862855876278</v>
+        <v>0.002569956943272327</v>
       </c>
       <c r="AE49" t="inlineStr"/>
       <c r="AF49" t="n">
-        <v>0.601710170256188</v>
+        <v>0.602764940493939</v>
       </c>
       <c r="AG49" t="n">
-        <v>0.01165130847932927</v>
+        <v>0.01163587047455489</v>
       </c>
       <c r="AH49" t="inlineStr"/>
       <c r="AI49" t="n">
-        <v>0.3350046591828763</v>
+        <v>0.3456108948472003</v>
       </c>
       <c r="AJ49" t="n">
-        <v>0.01791717032906908</v>
+        <v>0.01777371251000678</v>
       </c>
       <c r="AK49" t="inlineStr"/>
       <c r="AL49" t="n">
-        <v>0.8677381216521314</v>
+        <v>0.8681312853406065</v>
       </c>
       <c r="AM49" t="n">
-        <v>0.001328547284597241</v>
+        <v>0.001326571184939162</v>
       </c>
       <c r="AN49" t="inlineStr"/>
     </row>
@@ -5696,10 +5696,10 @@
         <v>0.02365077480082941</v>
       </c>
       <c r="K50" t="n">
-        <v>0.5222632463286973</v>
+        <v>0.5041804397675377</v>
       </c>
       <c r="L50" t="n">
-        <v>0.5295673622804894</v>
+        <v>0.527911915006419</v>
       </c>
       <c r="M50" t="n">
         <v>0</v>
@@ -5708,16 +5708,16 @@
         <v>0</v>
       </c>
       <c r="O50" t="n">
-        <v>4.388186391172322</v>
+        <v>4.245466267633814</v>
       </c>
       <c r="P50" t="n">
-        <v>4.631358351710457</v>
+        <v>4.52016536989635</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.966087730383056</v>
+        <v>0.9679338158247377</v>
       </c>
       <c r="R50" t="n">
-        <v>0.009842603193941698</v>
+        <v>0.009570953140782093</v>
       </c>
       <c r="S50" t="inlineStr"/>
       <c r="T50" t="inlineStr"/>
@@ -5727,31 +5727,31 @@
       <c r="X50" t="inlineStr"/>
       <c r="Y50" t="inlineStr"/>
       <c r="Z50" t="n">
-        <v>0.9943927576866218</v>
+        <v>0.9948739840009695</v>
       </c>
       <c r="AA50" t="n">
-        <v>0.006299672858289515</v>
+        <v>0.006023283624087662</v>
       </c>
       <c r="AB50" t="inlineStr"/>
       <c r="AC50" t="n">
-        <v>0.9284897254683484</v>
+        <v>0.9298759515224362</v>
       </c>
       <c r="AD50" t="n">
-        <v>0.005698026620616831</v>
+        <v>0.005642528247103462</v>
       </c>
       <c r="AE50" t="inlineStr"/>
       <c r="AF50" t="n">
-        <v>0.883312307286294</v>
+        <v>0.903708506244548</v>
       </c>
       <c r="AG50" t="n">
-        <v>0.003489996060662606</v>
+        <v>0.003170343885247073</v>
       </c>
       <c r="AH50" t="inlineStr"/>
       <c r="AI50" t="n">
-        <v>0.7967289153044008</v>
+        <v>0.8068174896992218</v>
       </c>
       <c r="AJ50" t="n">
-        <v>0.01809400734905745</v>
+        <v>0.0176392803456281</v>
       </c>
       <c r="AK50" t="inlineStr"/>
       <c r="AL50" t="inlineStr"/>
@@ -5798,10 +5798,10 @@
         <v>0.05173441476315732</v>
       </c>
       <c r="K51" t="n">
-        <v>0.3792927310630154</v>
+        <v>0.4031377924515371</v>
       </c>
       <c r="L51" t="n">
-        <v>0.4502013701030159</v>
+        <v>0.4642404432382035</v>
       </c>
       <c r="M51" t="n">
         <v>0</v>
@@ -5810,16 +5810,16 @@
         <v>0</v>
       </c>
       <c r="O51" t="n">
-        <v>4.210145903626906</v>
+        <v>3.865900326542421</v>
       </c>
       <c r="P51" t="n">
-        <v>4.330058983175388</v>
+        <v>4.478713032460986</v>
       </c>
       <c r="Q51" t="n">
-        <v>0.8629711391478186</v>
+        <v>0.8675421474075706</v>
       </c>
       <c r="R51" t="n">
-        <v>0.01486687613844281</v>
+        <v>0.01461680841000908</v>
       </c>
       <c r="S51" t="inlineStr"/>
       <c r="T51" t="inlineStr"/>
@@ -5829,38 +5829,38 @@
       <c r="X51" t="inlineStr"/>
       <c r="Y51" t="inlineStr"/>
       <c r="Z51" t="n">
-        <v>0.8592505752251678</v>
+        <v>0.8598963308920591</v>
       </c>
       <c r="AA51" t="n">
-        <v>0.02218001179706477</v>
+        <v>0.02212907256804585</v>
       </c>
       <c r="AB51" t="inlineStr"/>
       <c r="AC51" t="n">
-        <v>0.7168830118183066</v>
+        <v>0.688740154067252</v>
       </c>
       <c r="AD51" t="n">
-        <v>0.01698966323463816</v>
+        <v>0.0178140782121412</v>
       </c>
       <c r="AE51" t="inlineStr"/>
       <c r="AF51" t="n">
-        <v>-1.43249290409664</v>
+        <v>-1.472993427367163</v>
       </c>
       <c r="AG51" t="n">
-        <v>0.003912568730944688</v>
+        <v>0.003945006015510731</v>
       </c>
       <c r="AH51" t="inlineStr"/>
       <c r="AI51" t="n">
-        <v>0.7005187827154715</v>
+        <v>0.7623492897775955</v>
       </c>
       <c r="AJ51" t="n">
-        <v>0.01757028263362038</v>
+        <v>0.01565177193091006</v>
       </c>
       <c r="AK51" t="inlineStr"/>
       <c r="AL51" t="n">
-        <v>0.9927743530523816</v>
+        <v>0.9901236661944122</v>
       </c>
       <c r="AM51" t="n">
-        <v>0.000703864003189331</v>
+        <v>0.0008229022814392934</v>
       </c>
       <c r="AN51" t="inlineStr"/>
     </row>
@@ -5902,10 +5902,10 @@
         <v>0.004631983561397277</v>
       </c>
       <c r="K52" t="n">
-        <v>0.1593376026831239</v>
+        <v>0.1606943136811414</v>
       </c>
       <c r="L52" t="n">
-        <v>0.3352966651949248</v>
+        <v>0.3250751776916631</v>
       </c>
       <c r="M52" t="n">
         <v>0</v>
@@ -5914,16 +5914,16 @@
         <v>0</v>
       </c>
       <c r="O52" t="n">
-        <v>4.33297137534801</v>
+        <v>4.367592709598685</v>
       </c>
       <c r="P52" t="n">
-        <v>4.405472265423097</v>
+        <v>4.305155024986907</v>
       </c>
       <c r="Q52" t="n">
-        <v>0.9529886884557746</v>
+        <v>0.9535533906622496</v>
       </c>
       <c r="R52" t="n">
-        <v>0.01047018725675023</v>
+        <v>0.01040711306755313</v>
       </c>
       <c r="S52" t="inlineStr"/>
       <c r="T52" t="inlineStr"/>
@@ -5933,38 +5933,38 @@
       <c r="X52" t="inlineStr"/>
       <c r="Y52" t="inlineStr"/>
       <c r="Z52" t="n">
-        <v>0.9384275285691199</v>
+        <v>0.9383978124110627</v>
       </c>
       <c r="AA52" t="n">
-        <v>0.01136289117894953</v>
+        <v>0.01136563283225358</v>
       </c>
       <c r="AB52" t="inlineStr"/>
       <c r="AC52" t="n">
-        <v>0.8991173154021487</v>
+        <v>0.9006945621791339</v>
       </c>
       <c r="AD52" t="n">
-        <v>0.002246888035822697</v>
+        <v>0.002229254395263897</v>
       </c>
       <c r="AE52" t="inlineStr"/>
       <c r="AF52" t="n">
-        <v>0.8108916809264303</v>
+        <v>0.8134869125326483</v>
       </c>
       <c r="AG52" t="n">
-        <v>0.01561549512231153</v>
+        <v>0.01550797518812517</v>
       </c>
       <c r="AH52" t="inlineStr"/>
       <c r="AI52" t="n">
-        <v>0.3769421942942636</v>
+        <v>0.3887951259275094</v>
       </c>
       <c r="AJ52" t="n">
-        <v>0.01301338099207208</v>
+        <v>0.01288900459740433</v>
       </c>
       <c r="AK52" t="inlineStr"/>
       <c r="AL52" t="n">
-        <v>0.1731797818790902</v>
+        <v>0.1725753582760886</v>
       </c>
       <c r="AM52" t="n">
-        <v>0.0008766592309125617</v>
+        <v>0.0008769796008777883</v>
       </c>
       <c r="AN52" t="inlineStr"/>
     </row>
@@ -6006,10 +6006,10 @@
         <v>0.00319007047444387</v>
       </c>
       <c r="K53" t="n">
-        <v>0.331297244801841</v>
+        <v>0.3301843999480366</v>
       </c>
       <c r="L53" t="n">
-        <v>0.221178422090789</v>
+        <v>0.2246818306660378</v>
       </c>
       <c r="M53" t="n">
         <v>0</v>
@@ -6018,16 +6018,16 @@
         <v>0</v>
       </c>
       <c r="O53" t="n">
-        <v>4.395968424017083</v>
+        <v>4.382101377750191</v>
       </c>
       <c r="P53" t="n">
-        <v>4.342414579871032</v>
+        <v>4.425804736657819</v>
       </c>
       <c r="Q53" t="n">
-        <v>0.9866735358359816</v>
+        <v>0.9866128000843535</v>
       </c>
       <c r="R53" t="n">
-        <v>0.004963299225061927</v>
+        <v>0.004974596558670659</v>
       </c>
       <c r="S53" t="inlineStr"/>
       <c r="T53" t="inlineStr"/>
@@ -6037,38 +6037,38 @@
       <c r="X53" t="inlineStr"/>
       <c r="Y53" t="inlineStr"/>
       <c r="Z53" t="n">
-        <v>0.9820908643186255</v>
+        <v>0.9818876075911982</v>
       </c>
       <c r="AA53" t="n">
-        <v>0.007755890272792965</v>
+        <v>0.007799778186486004</v>
       </c>
       <c r="AB53" t="inlineStr"/>
       <c r="AC53" t="n">
-        <v>0.9131749387710607</v>
+        <v>0.9134016594240653</v>
       </c>
       <c r="AD53" t="n">
-        <v>0.003024838863117415</v>
+        <v>0.003020886998816808</v>
       </c>
       <c r="AE53" t="inlineStr"/>
       <c r="AF53" t="n">
-        <v>0.9710361836304994</v>
+        <v>0.9708082074032175</v>
       </c>
       <c r="AG53" t="n">
-        <v>0.004201707360180242</v>
+        <v>0.004218210915134934</v>
       </c>
       <c r="AH53" t="inlineStr"/>
       <c r="AI53" t="n">
-        <v>0.9645630027173671</v>
+        <v>0.964875161225224</v>
       </c>
       <c r="AJ53" t="n">
-        <v>0.005482031735142666</v>
+        <v>0.00545783318243831</v>
       </c>
       <c r="AK53" t="inlineStr"/>
       <c r="AL53" t="n">
-        <v>0.9822540329560205</v>
+        <v>0.9805745190653832</v>
       </c>
       <c r="AM53" t="n">
-        <v>5.899639528412201e-05</v>
+        <v>6.172506150984947e-05</v>
       </c>
       <c r="AN53" t="inlineStr"/>
     </row>
@@ -6110,10 +6110,10 @@
         <v>0.02695043454293275</v>
       </c>
       <c r="K54" t="n">
-        <v>0.1412187048639822</v>
+        <v>0.1364187938617844</v>
       </c>
       <c r="L54" t="n">
-        <v>0.4272318621484766</v>
+        <v>0.4098822051400439</v>
       </c>
       <c r="M54" t="n">
         <v>0</v>
@@ -6122,16 +6122,16 @@
         <v>0</v>
       </c>
       <c r="O54" t="n">
-        <v>4.248018727268365</v>
+        <v>4.231856710657762</v>
       </c>
       <c r="P54" t="n">
-        <v>4.472852888947165</v>
+        <v>4.305667743057564</v>
       </c>
       <c r="Q54" t="n">
-        <v>0.9303382828499467</v>
+        <v>0.9288941463766474</v>
       </c>
       <c r="R54" t="n">
-        <v>0.009584035235121514</v>
+        <v>0.009682867547932756</v>
       </c>
       <c r="S54" t="inlineStr"/>
       <c r="T54" t="inlineStr"/>
@@ -6141,38 +6141,38 @@
       <c r="X54" t="inlineStr"/>
       <c r="Y54" t="inlineStr"/>
       <c r="Z54" t="n">
-        <v>0.8752197401530292</v>
+        <v>0.8720243980738971</v>
       </c>
       <c r="AA54" t="n">
-        <v>0.018199682525724</v>
+        <v>0.01843123599311068</v>
       </c>
       <c r="AB54" t="inlineStr"/>
       <c r="AC54" t="n">
-        <v>0.4878415145651753</v>
+        <v>0.5001013526306184</v>
       </c>
       <c r="AD54" t="n">
-        <v>0.004127091431939513</v>
+        <v>0.00407739592881935</v>
       </c>
       <c r="AE54" t="inlineStr"/>
       <c r="AF54" t="n">
-        <v>0.9227544997538448</v>
+        <v>0.9208704566414408</v>
       </c>
       <c r="AG54" t="n">
-        <v>0.008242390824146512</v>
+        <v>0.008342302583320553</v>
       </c>
       <c r="AH54" t="inlineStr"/>
       <c r="AI54" t="n">
-        <v>0.7446819130870801</v>
+        <v>0.7463344680877373</v>
       </c>
       <c r="AJ54" t="n">
-        <v>0.006474677348604465</v>
+        <v>0.006453689547740568</v>
       </c>
       <c r="AK54" t="inlineStr"/>
       <c r="AL54" t="n">
-        <v>0.8676414954653991</v>
+        <v>0.8606133132805542</v>
       </c>
       <c r="AM54" t="n">
-        <v>0.001071856309873214</v>
+        <v>0.001099945812148236</v>
       </c>
       <c r="AN54" t="inlineStr"/>
     </row>
@@ -6214,10 +6214,10 @@
         <v>0.00266683139341308</v>
       </c>
       <c r="K55" t="n">
-        <v>0.09429883103599272</v>
+        <v>0.0949000769531866</v>
       </c>
       <c r="L55" t="n">
-        <v>0.4204823574704124</v>
+        <v>0.4209794484220377</v>
       </c>
       <c r="M55" t="n">
         <v>0</v>
@@ -6226,16 +6226,16 @@
         <v>0</v>
       </c>
       <c r="O55" t="n">
-        <v>4.345610810250299</v>
+        <v>4.425812673917372</v>
       </c>
       <c r="P55" t="n">
-        <v>4.37979976504603</v>
+        <v>4.388610012795088</v>
       </c>
       <c r="Q55" t="n">
-        <v>0.8821435248691771</v>
+        <v>0.8823237774824414</v>
       </c>
       <c r="R55" t="n">
-        <v>0.01384375707841557</v>
+        <v>0.01383316653496088</v>
       </c>
       <c r="S55" t="inlineStr"/>
       <c r="T55" t="inlineStr"/>
@@ -6245,38 +6245,38 @@
       <c r="X55" t="inlineStr"/>
       <c r="Y55" t="inlineStr"/>
       <c r="Z55" t="n">
-        <v>0.7269267094700684</v>
+        <v>0.7267103659389877</v>
       </c>
       <c r="AA55" t="n">
-        <v>0.02522465340649349</v>
+        <v>0.02523464360021534</v>
       </c>
       <c r="AB55" t="inlineStr"/>
       <c r="AC55" t="n">
-        <v>0.1895367595339116</v>
+        <v>0.1931560021694547</v>
       </c>
       <c r="AD55" t="n">
-        <v>0.003941744643355696</v>
+        <v>0.003932933575749521</v>
       </c>
       <c r="AE55" t="inlineStr"/>
       <c r="AF55" t="n">
-        <v>0.7348762540520608</v>
+        <v>0.7371667565614637</v>
       </c>
       <c r="AG55" t="n">
-        <v>0.01649344962050243</v>
+        <v>0.01642204855238225</v>
       </c>
       <c r="AH55" t="inlineStr"/>
       <c r="AI55" t="n">
-        <v>0.8331113484435948</v>
+        <v>0.8309366826475424</v>
       </c>
       <c r="AJ55" t="n">
-        <v>0.00583482787425344</v>
+        <v>0.005872720600430305</v>
       </c>
       <c r="AK55" t="inlineStr"/>
       <c r="AL55" t="n">
-        <v>0.8184625125196858</v>
+        <v>0.8151863357068518</v>
       </c>
       <c r="AM55" t="n">
-        <v>0.0005903077278353498</v>
+        <v>0.0005956105028809999</v>
       </c>
       <c r="AN55" t="inlineStr"/>
     </row>
@@ -6318,10 +6318,10 @@
         <v>0.03893815066809572</v>
       </c>
       <c r="K56" t="n">
-        <v>0.2182594007781727</v>
+        <v>0.2084054602031741</v>
       </c>
       <c r="L56" t="n">
-        <v>0.3624150887034048</v>
+        <v>0.3592757186724401</v>
       </c>
       <c r="M56" t="n">
         <v>0</v>
@@ -6330,16 +6330,16 @@
         <v>0</v>
       </c>
       <c r="O56" t="n">
-        <v>4.242619804626787</v>
+        <v>4.062930613106723</v>
       </c>
       <c r="P56" t="n">
-        <v>4.366012378101686</v>
+        <v>4.324180579402618</v>
       </c>
       <c r="Q56" t="n">
-        <v>0.8297178493993111</v>
+        <v>0.8306672697954849</v>
       </c>
       <c r="R56" t="n">
-        <v>0.01210762902556781</v>
+        <v>0.01207382836633396</v>
       </c>
       <c r="S56" t="inlineStr"/>
       <c r="T56" t="inlineStr"/>
@@ -6349,38 +6349,38 @@
       <c r="X56" t="inlineStr"/>
       <c r="Y56" t="inlineStr"/>
       <c r="Z56" t="n">
-        <v>0.6183503655090751</v>
+        <v>0.6192582351611474</v>
       </c>
       <c r="AA56" t="n">
-        <v>0.0215690001757411</v>
+        <v>0.02154333068974413</v>
       </c>
       <c r="AB56" t="inlineStr"/>
       <c r="AC56" t="n">
-        <v>-0.0866659922730646</v>
+        <v>-0.06835646104013682</v>
       </c>
       <c r="AD56" t="n">
-        <v>0.009136396749726355</v>
+        <v>0.009059098945100728</v>
       </c>
       <c r="AE56" t="inlineStr"/>
       <c r="AF56" t="n">
-        <v>0.7914091926860604</v>
+        <v>0.7918803514418224</v>
       </c>
       <c r="AG56" t="n">
-        <v>0.01207500041483076</v>
+        <v>0.01206135537804532</v>
       </c>
       <c r="AH56" t="inlineStr"/>
       <c r="AI56" t="n">
-        <v>0.8309088808158525</v>
+        <v>0.8368266521975809</v>
       </c>
       <c r="AJ56" t="n">
-        <v>0.005978503520327504</v>
+        <v>0.005872955389156894</v>
       </c>
       <c r="AK56" t="inlineStr"/>
       <c r="AL56" t="n">
-        <v>0.8785233296265451</v>
+        <v>0.8782279299369821</v>
       </c>
       <c r="AM56" t="n">
-        <v>0.001652195386024017</v>
+        <v>0.001654203021133236</v>
       </c>
       <c r="AN56" t="inlineStr"/>
     </row>
@@ -6422,10 +6422,10 @@
         <v>0.02444228773888892</v>
       </c>
       <c r="K57" t="n">
-        <v>0.3849234920957109</v>
+        <v>0.3825163888057561</v>
       </c>
       <c r="L57" t="n">
-        <v>0.4585099466523619</v>
+        <v>0.4554652399335732</v>
       </c>
       <c r="M57" t="n">
         <v>0</v>
@@ -6434,16 +6434,16 @@
         <v>0</v>
       </c>
       <c r="O57" t="n">
-        <v>4.301673038976071</v>
+        <v>4.276433697976676</v>
       </c>
       <c r="P57" t="n">
-        <v>4.399252767768986</v>
+        <v>4.373218250681789</v>
       </c>
       <c r="Q57" t="n">
-        <v>0.9023673164401923</v>
+        <v>0.9029720440596852</v>
       </c>
       <c r="R57" t="n">
-        <v>0.009501489570257088</v>
+        <v>0.00947201819921026</v>
       </c>
       <c r="S57" t="inlineStr"/>
       <c r="T57" t="inlineStr"/>
@@ -6453,38 +6453,38 @@
       <c r="X57" t="inlineStr"/>
       <c r="Y57" t="inlineStr"/>
       <c r="Z57" t="n">
-        <v>0.7773992660316782</v>
+        <v>0.7789594421356788</v>
       </c>
       <c r="AA57" t="n">
-        <v>0.01785777869724912</v>
+        <v>0.01779508737129534</v>
       </c>
       <c r="AB57" t="inlineStr"/>
       <c r="AC57" t="n">
-        <v>0.6320095499653745</v>
+        <v>0.6319165373354663</v>
       </c>
       <c r="AD57" t="n">
-        <v>0.008745371238518809</v>
+        <v>0.008746476401145379</v>
       </c>
       <c r="AE57" t="inlineStr"/>
       <c r="AF57" t="n">
-        <v>0.8626202526623995</v>
+        <v>0.861946511184812</v>
       </c>
       <c r="AG57" t="n">
-        <v>0.005690096577915133</v>
+        <v>0.005704032275727567</v>
       </c>
       <c r="AH57" t="inlineStr"/>
       <c r="AI57" t="n">
-        <v>0.9351658871807498</v>
+        <v>0.9373334118817404</v>
       </c>
       <c r="AJ57" t="n">
-        <v>0.004685760564021472</v>
+        <v>0.004606767898489069</v>
       </c>
       <c r="AK57" t="inlineStr"/>
       <c r="AL57" t="n">
-        <v>0.6645044771451201</v>
+        <v>0.6654703919347933</v>
       </c>
       <c r="AM57" t="n">
-        <v>0.001294677967582768</v>
+        <v>0.001292812890534761</v>
       </c>
       <c r="AN57" t="inlineStr"/>
     </row>
@@ -6526,10 +6526,10 @@
         <v>0.02625641629885448</v>
       </c>
       <c r="K58" t="n">
-        <v>0.08261752618468853</v>
+        <v>0.07740090498216673</v>
       </c>
       <c r="L58" t="n">
-        <v>0.4847708613814271</v>
+        <v>0.4661498136188804</v>
       </c>
       <c r="M58" t="n">
         <v>0</v>
@@ -6538,16 +6538,16 @@
         <v>0</v>
       </c>
       <c r="O58" t="n">
-        <v>4.317748846014766</v>
+        <v>4.225917546295505</v>
       </c>
       <c r="P58" t="n">
-        <v>4.73325163991603</v>
+        <v>4.40034843597916</v>
       </c>
       <c r="Q58" t="n">
-        <v>0.9630907793131949</v>
+        <v>0.961413423693779</v>
       </c>
       <c r="R58" t="n">
-        <v>0.008078629507088148</v>
+        <v>0.008260158425287616</v>
       </c>
       <c r="S58" t="inlineStr"/>
       <c r="T58" t="inlineStr"/>
@@ -6557,38 +6557,38 @@
       <c r="X58" t="inlineStr"/>
       <c r="Y58" t="inlineStr"/>
       <c r="Z58" t="n">
-        <v>0.9818042713805479</v>
+        <v>0.9806674950888711</v>
       </c>
       <c r="AA58" t="n">
-        <v>0.007826775670118576</v>
+        <v>0.008067560398018214</v>
       </c>
       <c r="AB58" t="inlineStr"/>
       <c r="AC58" t="n">
-        <v>0.9616214599184627</v>
+        <v>0.972581920210899</v>
       </c>
       <c r="AD58" t="n">
-        <v>0.001803018798433733</v>
+        <v>0.001523963437372552</v>
       </c>
       <c r="AE58" t="inlineStr"/>
       <c r="AF58" t="n">
-        <v>0.9809807930390162</v>
+        <v>0.9813207375705789</v>
       </c>
       <c r="AG58" t="n">
-        <v>0.005298954870613185</v>
+        <v>0.005251385255687553</v>
       </c>
       <c r="AH58" t="inlineStr"/>
       <c r="AI58" t="n">
-        <v>0.6458246325667558</v>
+        <v>0.6269871399538081</v>
       </c>
       <c r="AJ58" t="n">
-        <v>0.01526783317084317</v>
+        <v>0.01566859776351134</v>
       </c>
       <c r="AK58" t="inlineStr"/>
       <c r="AL58" t="n">
-        <v>0.9500669503604255</v>
+        <v>0.9472956928616748</v>
       </c>
       <c r="AM58" t="n">
-        <v>0.0007914081959499675</v>
+        <v>0.0008130730236359352</v>
       </c>
       <c r="AN58" t="inlineStr"/>
     </row>
@@ -6630,10 +6630,10 @@
         <v>0.02080322163891103</v>
       </c>
       <c r="K59" t="n">
-        <v>0.4698313368793378</v>
+        <v>0.4677808511850242</v>
       </c>
       <c r="L59" t="n">
-        <v>0.5164512686575472</v>
+        <v>0.5153612643385489</v>
       </c>
       <c r="M59" t="n">
         <v>0</v>
@@ -6642,16 +6642,16 @@
         <v>0</v>
       </c>
       <c r="O59" t="n">
-        <v>4.228884151391346</v>
+        <v>4.211580767596805</v>
       </c>
       <c r="P59" t="n">
-        <v>4.389073785606209</v>
+        <v>4.384899764120235</v>
       </c>
       <c r="Q59" t="n">
-        <v>0.7893275088673677</v>
+        <v>0.7968183518500273</v>
       </c>
       <c r="R59" t="n">
-        <v>0.01964630215318416</v>
+        <v>0.01929386090102111</v>
       </c>
       <c r="S59" t="inlineStr"/>
       <c r="T59" t="inlineStr"/>
@@ -6661,38 +6661,38 @@
       <c r="X59" t="inlineStr"/>
       <c r="Y59" t="inlineStr"/>
       <c r="Z59" t="n">
-        <v>0.7439640592654314</v>
+        <v>0.7650175493332589</v>
       </c>
       <c r="AA59" t="n">
-        <v>0.0317206638500916</v>
+        <v>0.03038851763229069</v>
       </c>
       <c r="AB59" t="inlineStr"/>
       <c r="AC59" t="n">
-        <v>0.4332103449310272</v>
+        <v>0.4193090726360488</v>
       </c>
       <c r="AD59" t="n">
-        <v>0.02326591410949451</v>
+        <v>0.02354949960259279</v>
       </c>
       <c r="AE59" t="inlineStr"/>
       <c r="AF59" t="n">
-        <v>0.3614317879357739</v>
+        <v>0.3572233705470572</v>
       </c>
       <c r="AG59" t="n">
-        <v>0.009270587210481438</v>
+        <v>0.009301085464528673</v>
       </c>
       <c r="AH59" t="inlineStr"/>
       <c r="AI59" t="n">
-        <v>-0.8845838158295363</v>
+        <v>-0.886482971900695</v>
       </c>
       <c r="AJ59" t="n">
-        <v>0.0170284648443267</v>
+        <v>0.0170370427512309</v>
       </c>
       <c r="AK59" t="inlineStr"/>
       <c r="AL59" t="n">
-        <v>-0.5967847477171018</v>
+        <v>-0.5926203320188457</v>
       </c>
       <c r="AM59" t="n">
-        <v>0.00254367152921646</v>
+        <v>0.002540352415209459</v>
       </c>
       <c r="AN59" t="inlineStr"/>
     </row>
@@ -6734,10 +6734,10 @@
         <v>0.0151609171982884</v>
       </c>
       <c r="K60" t="n">
-        <v>0.3312705578089989</v>
+        <v>0.3189569329734549</v>
       </c>
       <c r="L60" t="n">
-        <v>0.2477782911221035</v>
+        <v>0.2355319585675123</v>
       </c>
       <c r="M60" t="n">
         <v>0</v>
@@ -6746,16 +6746,16 @@
         <v>0</v>
       </c>
       <c r="O60" t="n">
-        <v>4.180622353107697</v>
+        <v>4.034948938354199</v>
       </c>
       <c r="P60" t="n">
-        <v>4.306032872794803</v>
+        <v>4.206395293982933</v>
       </c>
       <c r="Q60" t="n">
-        <v>0.882843797393462</v>
+        <v>0.8912738908521161</v>
       </c>
       <c r="R60" t="n">
-        <v>0.02128899630805915</v>
+        <v>0.02050876301984904</v>
       </c>
       <c r="S60" t="inlineStr"/>
       <c r="T60" t="inlineStr"/>
@@ -6765,38 +6765,38 @@
       <c r="X60" t="inlineStr"/>
       <c r="Y60" t="inlineStr"/>
       <c r="Z60" t="n">
-        <v>0.5746788543561976</v>
+        <v>0.6077686094538537</v>
       </c>
       <c r="AA60" t="n">
-        <v>0.04569034176020055</v>
+        <v>0.04387701686477997</v>
       </c>
       <c r="AB60" t="inlineStr"/>
       <c r="AC60" t="n">
-        <v>-1.407826216436158</v>
+        <v>-1.373376878000312</v>
       </c>
       <c r="AD60" t="n">
-        <v>0.008224056142357836</v>
+        <v>0.00816501243654</v>
       </c>
       <c r="AE60" t="inlineStr"/>
       <c r="AF60" t="n">
-        <v>0.4657752672030933</v>
+        <v>0.4574885809817287</v>
       </c>
       <c r="AG60" t="n">
-        <v>0.008060732921886828</v>
+        <v>0.008123009824027607</v>
       </c>
       <c r="AH60" t="inlineStr"/>
       <c r="AI60" t="n">
-        <v>-8.221829363850999</v>
+        <v>-8.08209179734647</v>
       </c>
       <c r="AJ60" t="n">
-        <v>0.006756847869363325</v>
+        <v>0.006705459495662812</v>
       </c>
       <c r="AK60" t="inlineStr"/>
       <c r="AL60" t="n">
-        <v>0.9379664608663421</v>
+        <v>0.9362937334714371</v>
       </c>
       <c r="AM60" t="n">
-        <v>0.0004837158861258842</v>
+        <v>0.0004901941772152147</v>
       </c>
       <c r="AN60" t="inlineStr"/>
     </row>
@@ -6838,10 +6838,10 @@
         <v>0.01715393264003622</v>
       </c>
       <c r="K61" t="n">
-        <v>0.3143533444338791</v>
+        <v>0.3156444100186744</v>
       </c>
       <c r="L61" t="n">
-        <v>0.2957279498593128</v>
+        <v>0.2995950838791099</v>
       </c>
       <c r="M61" t="n">
         <v>0</v>
@@ -6850,16 +6850,16 @@
         <v>0</v>
       </c>
       <c r="O61" t="n">
-        <v>4.076109010387499</v>
+        <v>3.852023036776635</v>
       </c>
       <c r="P61" t="n">
-        <v>4.184982611422497</v>
+        <v>4.243896250713388</v>
       </c>
       <c r="Q61" t="n">
-        <v>0.9799078089181468</v>
+        <v>0.9803046701940011</v>
       </c>
       <c r="R61" t="n">
-        <v>0.0101059838425086</v>
+        <v>0.01000567929166509</v>
       </c>
       <c r="S61" t="inlineStr"/>
       <c r="T61" t="inlineStr"/>
@@ -6871,38 +6871,38 @@
       </c>
       <c r="Y61" t="inlineStr"/>
       <c r="Z61" t="n">
-        <v>0.9659891888841704</v>
+        <v>0.9667840269562797</v>
       </c>
       <c r="AA61" t="n">
-        <v>0.02055345755046252</v>
+        <v>0.02031186892674284</v>
       </c>
       <c r="AB61" t="inlineStr"/>
       <c r="AC61" t="n">
-        <v>0.3651010463877723</v>
+        <v>0.3685145298057112</v>
       </c>
       <c r="AD61" t="n">
-        <v>0.004319329533203534</v>
+        <v>0.004307702619552763</v>
       </c>
       <c r="AE61" t="inlineStr"/>
       <c r="AF61" t="n">
-        <v>0.418597683297887</v>
+        <v>0.4196691407026517</v>
       </c>
       <c r="AG61" t="n">
-        <v>0.007725637091125832</v>
+        <v>0.007718515079348856</v>
       </c>
       <c r="AH61" t="inlineStr"/>
       <c r="AI61" t="n">
-        <v>0.916375984652875</v>
+        <v>0.9162565081189863</v>
       </c>
       <c r="AJ61" t="n">
-        <v>0.002311540645115674</v>
+        <v>0.002313191344907636</v>
       </c>
       <c r="AK61" t="inlineStr"/>
       <c r="AL61" t="n">
-        <v>0.2378611947177574</v>
+        <v>0.239746661186565</v>
       </c>
       <c r="AM61" t="n">
-        <v>0.002378190912320444</v>
+        <v>0.002375247369829084</v>
       </c>
       <c r="AN61" t="inlineStr"/>
     </row>
@@ -6944,10 +6944,10 @@
         <v>0.03097209188130944</v>
       </c>
       <c r="K62" t="n">
-        <v>0.1480862046118177</v>
+        <v>0.1479508876328734</v>
       </c>
       <c r="L62" t="n">
-        <v>0.2281044200802397</v>
+        <v>0.2328832249083791</v>
       </c>
       <c r="M62" t="n">
         <v>0</v>
@@ -6956,16 +6956,16 @@
         <v>0</v>
       </c>
       <c r="O62" t="n">
-        <v>4.099154174190237</v>
+        <v>4.143875794202612</v>
       </c>
       <c r="P62" t="n">
-        <v>4.116368179306527</v>
+        <v>4.19573426251733</v>
       </c>
       <c r="Q62" t="n">
-        <v>0.9873501215393495</v>
+        <v>0.9873690699491043</v>
       </c>
       <c r="R62" t="n">
-        <v>0.007417557868759035</v>
+        <v>0.007412000360874087</v>
       </c>
       <c r="S62" t="inlineStr"/>
       <c r="T62" t="inlineStr"/>
@@ -6977,38 +6977,38 @@
       </c>
       <c r="Y62" t="inlineStr"/>
       <c r="Z62" t="n">
-        <v>0.982992441247502</v>
+        <v>0.9830170096801526</v>
       </c>
       <c r="AA62" t="n">
-        <v>0.01360261229450176</v>
+        <v>0.01359278385153566</v>
       </c>
       <c r="AB62" t="inlineStr"/>
       <c r="AC62" t="n">
-        <v>0.1065576893286236</v>
+        <v>0.09231787743316255</v>
       </c>
       <c r="AD62" t="n">
-        <v>0.003146668495697096</v>
+        <v>0.00317164539502261</v>
       </c>
       <c r="AE62" t="inlineStr"/>
       <c r="AF62" t="n">
-        <v>0.5931608372716837</v>
+        <v>0.5948824546300484</v>
       </c>
       <c r="AG62" t="n">
-        <v>0.008539932645062111</v>
+        <v>0.008521844313444058</v>
       </c>
       <c r="AH62" t="inlineStr"/>
       <c r="AI62" t="n">
-        <v>0.9803898451527896</v>
+        <v>0.980323486664271</v>
       </c>
       <c r="AJ62" t="n">
-        <v>0.002078960506718985</v>
+        <v>0.002082475016616744</v>
       </c>
       <c r="AK62" t="inlineStr"/>
       <c r="AL62" t="n">
-        <v>0.854781326323284</v>
+        <v>0.8552099901601118</v>
       </c>
       <c r="AM62" t="n">
-        <v>0.001909094502279654</v>
+        <v>0.0019062747389344</v>
       </c>
       <c r="AN62" t="inlineStr"/>
     </row>
@@ -7050,10 +7050,10 @@
         <v>0.01715393264003622</v>
       </c>
       <c r="K63" t="n">
-        <v>0.2731492526497677</v>
+        <v>0.2740450099273068</v>
       </c>
       <c r="L63" t="n">
-        <v>0.2922058471495714</v>
+        <v>0.2958174673379184</v>
       </c>
       <c r="M63" t="n">
         <v>0</v>
@@ -7062,16 +7062,16 @@
         <v>0</v>
       </c>
       <c r="O63" t="n">
-        <v>4.076109010387499</v>
+        <v>3.971058122228126</v>
       </c>
       <c r="P63" t="n">
-        <v>4.19540980039159</v>
+        <v>4.236321138663175</v>
       </c>
       <c r="Q63" t="n">
-        <v>0.9877277253298972</v>
+        <v>0.9877619744920115</v>
       </c>
       <c r="R63" t="n">
-        <v>0.008102458480440392</v>
+        <v>0.008091144510379884</v>
       </c>
       <c r="S63" t="inlineStr"/>
       <c r="T63" t="inlineStr"/>
@@ -7083,38 +7083,38 @@
       </c>
       <c r="Y63" t="inlineStr"/>
       <c r="Z63" t="n">
-        <v>0.9748760719872706</v>
+        <v>0.974934956304608</v>
       </c>
       <c r="AA63" t="n">
-        <v>0.01745353972353435</v>
+        <v>0.01743307431959035</v>
       </c>
       <c r="AB63" t="inlineStr"/>
       <c r="AC63" t="n">
-        <v>0.9291412852821563</v>
+        <v>0.9328572023707579</v>
       </c>
       <c r="AD63" t="n">
-        <v>0.001162361412902265</v>
+        <v>0.001131473183474153</v>
       </c>
       <c r="AE63" t="inlineStr"/>
       <c r="AF63" t="n">
-        <v>0.949565910292785</v>
+        <v>0.9503402901017391</v>
       </c>
       <c r="AG63" t="n">
-        <v>0.002497621019280759</v>
+        <v>0.002478372242695531</v>
       </c>
       <c r="AH63" t="inlineStr"/>
       <c r="AI63" t="n">
-        <v>0.8391780026112378</v>
+        <v>0.8394671921765104</v>
       </c>
       <c r="AJ63" t="n">
-        <v>0.003576467983375299</v>
+        <v>0.003573250940262173</v>
       </c>
       <c r="AK63" t="inlineStr"/>
       <c r="AL63" t="n">
-        <v>0.2399428723707139</v>
+        <v>0.2428646488135878</v>
       </c>
       <c r="AM63" t="n">
-        <v>0.00201333063884353</v>
+        <v>0.002009457136430979</v>
       </c>
       <c r="AN63" t="inlineStr"/>
     </row>
@@ -7156,10 +7156,10 @@
         <v>0.03097209188130944</v>
       </c>
       <c r="K64" t="n">
-        <v>0.2197861281348692</v>
+        <v>0.2247029268396697</v>
       </c>
       <c r="L64" t="n">
-        <v>0.3150085961224029</v>
+        <v>0.3230744834918965</v>
       </c>
       <c r="M64" t="n">
         <v>0</v>
@@ -7168,16 +7168,16 @@
         <v>0</v>
       </c>
       <c r="O64" t="n">
-        <v>4.099154174190237</v>
+        <v>3.76527181006721</v>
       </c>
       <c r="P64" t="n">
-        <v>4.14589653938679</v>
+        <v>4.241789201588115</v>
       </c>
       <c r="Q64" t="n">
-        <v>0.9781706725822814</v>
+        <v>0.9784062232155598</v>
       </c>
       <c r="R64" t="n">
-        <v>0.009899216160722781</v>
+        <v>0.009845662264506016</v>
       </c>
       <c r="S64" t="inlineStr"/>
       <c r="T64" t="inlineStr"/>
@@ -7189,38 +7189,38 @@
       </c>
       <c r="Y64" t="inlineStr"/>
       <c r="Z64" t="n">
-        <v>0.9680380080335846</v>
+        <v>0.9685969619262981</v>
       </c>
       <c r="AA64" t="n">
-        <v>0.01888101078611631</v>
+        <v>0.01871518628081749</v>
       </c>
       <c r="AB64" t="inlineStr"/>
       <c r="AC64" t="n">
-        <v>0.5391101263831377</v>
+        <v>0.5249125827766687</v>
       </c>
       <c r="AD64" t="n">
-        <v>0.003666316057469826</v>
+        <v>0.003722357507941682</v>
       </c>
       <c r="AE64" t="inlineStr"/>
       <c r="AF64" t="n">
-        <v>0.2520487572353819</v>
+        <v>0.2482326743570318</v>
       </c>
       <c r="AG64" t="n">
-        <v>0.01052384259356401</v>
+        <v>0.01055065501068947</v>
       </c>
       <c r="AH64" t="inlineStr"/>
       <c r="AI64" t="n">
-        <v>0.9757422810648863</v>
+        <v>0.9758539827510931</v>
       </c>
       <c r="AJ64" t="n">
-        <v>0.002247802042679744</v>
+        <v>0.002242620743627632</v>
       </c>
       <c r="AK64" t="inlineStr"/>
       <c r="AL64" t="n">
-        <v>0.8343538019631812</v>
+        <v>0.8346890410923264</v>
       </c>
       <c r="AM64" t="n">
-        <v>0.002300566312803932</v>
+        <v>0.002298237160473179</v>
       </c>
       <c r="AN64" t="inlineStr"/>
     </row>
@@ -7262,10 +7262,10 @@
         <v>0.01715393264003622</v>
       </c>
       <c r="K65" t="n">
-        <v>0.2967152163516893</v>
+        <v>0.2977175138061146</v>
       </c>
       <c r="L65" t="n">
-        <v>0.366703943480061</v>
+        <v>0.3712407380229583</v>
       </c>
       <c r="M65" t="n">
         <v>0</v>
@@ -7274,16 +7274,16 @@
         <v>0</v>
       </c>
       <c r="O65" t="n">
-        <v>4.076109010387499</v>
+        <v>3.910917589484847</v>
       </c>
       <c r="P65" t="n">
-        <v>4.220253223373659</v>
+        <v>4.266056814900674</v>
       </c>
       <c r="Q65" t="n">
-        <v>0.978544892371388</v>
+        <v>0.9785935748815605</v>
       </c>
       <c r="R65" t="n">
-        <v>0.01055062373583287</v>
+        <v>0.01053864704129518</v>
       </c>
       <c r="S65" t="inlineStr"/>
       <c r="T65" t="inlineStr"/>
@@ -7295,38 +7295,38 @@
       </c>
       <c r="Y65" t="inlineStr"/>
       <c r="Z65" t="n">
-        <v>0.9646170266168463</v>
+        <v>0.9647044738332224</v>
       </c>
       <c r="AA65" t="n">
-        <v>0.02150465928034056</v>
+        <v>0.02147806900604718</v>
       </c>
       <c r="AB65" t="inlineStr"/>
       <c r="AC65" t="n">
-        <v>0.6959502366176264</v>
+        <v>0.6959254041051117</v>
       </c>
       <c r="AD65" t="n">
-        <v>0.00373383856647492</v>
+        <v>0.003733991039377373</v>
       </c>
       <c r="AE65" t="inlineStr"/>
       <c r="AF65" t="n">
-        <v>0.6397126517866802</v>
+        <v>0.6405554098540989</v>
       </c>
       <c r="AG65" t="n">
-        <v>0.008448500532850784</v>
+        <v>0.008438613687579354</v>
       </c>
       <c r="AH65" t="inlineStr"/>
       <c r="AI65" t="n">
-        <v>0.9198507708484952</v>
+        <v>0.9191517047424349</v>
       </c>
       <c r="AJ65" t="n">
-        <v>0.002442599830193543</v>
+        <v>0.00245322895044282</v>
       </c>
       <c r="AK65" t="inlineStr"/>
       <c r="AL65" t="n">
-        <v>0.5648116362928199</v>
+        <v>0.5657596363365138</v>
       </c>
       <c r="AM65" t="n">
-        <v>0.001885115940574173</v>
+        <v>0.001883061583841355</v>
       </c>
       <c r="AN65" t="inlineStr"/>
     </row>
@@ -7368,10 +7368,10 @@
         <v>0.03097209188130944</v>
       </c>
       <c r="K66" t="n">
-        <v>0.2596205515275795</v>
+        <v>0.2630911090154405</v>
       </c>
       <c r="L66" t="n">
-        <v>0.3096046631801753</v>
+        <v>0.3175574634796361</v>
       </c>
       <c r="M66" t="n">
         <v>0</v>
@@ -7380,16 +7380,16 @@
         <v>0</v>
       </c>
       <c r="O66" t="n">
-        <v>4.099154174190237</v>
+        <v>3.953139984689836</v>
       </c>
       <c r="P66" t="n">
-        <v>4.153542825944226</v>
+        <v>4.243873028532862</v>
       </c>
       <c r="Q66" t="n">
-        <v>0.9799057183318679</v>
+        <v>0.9798538807134622</v>
       </c>
       <c r="R66" t="n">
-        <v>0.009588038879692598</v>
+        <v>0.009600398141344545</v>
       </c>
       <c r="S66" t="inlineStr"/>
       <c r="T66" t="inlineStr"/>
@@ -7401,38 +7401,38 @@
       </c>
       <c r="Y66" t="inlineStr"/>
       <c r="Z66" t="n">
-        <v>0.9684741024643819</v>
+        <v>0.9683869499465346</v>
       </c>
       <c r="AA66" t="n">
-        <v>0.0186902261131512</v>
+        <v>0.01871604260344171</v>
       </c>
       <c r="AB66" t="inlineStr"/>
       <c r="AC66" t="n">
-        <v>0.6694438924889539</v>
+        <v>0.6635046232592573</v>
       </c>
       <c r="AD66" t="n">
-        <v>0.003544191987319166</v>
+        <v>0.003575890383385436</v>
       </c>
       <c r="AE66" t="inlineStr"/>
       <c r="AF66" t="n">
-        <v>0.6367010850099064</v>
+        <v>0.6363384882473182</v>
       </c>
       <c r="AG66" t="n">
-        <v>0.009208921242278753</v>
+        <v>0.009213515657702653</v>
       </c>
       <c r="AH66" t="inlineStr"/>
       <c r="AI66" t="n">
-        <v>0.952293922086019</v>
+        <v>0.9527060266693409</v>
       </c>
       <c r="AJ66" t="n">
-        <v>0.003037738635224071</v>
+        <v>0.003024589563424694</v>
       </c>
       <c r="AK66" t="inlineStr"/>
       <c r="AL66" t="n">
-        <v>0.8476563215974391</v>
+        <v>0.8480865104327875</v>
       </c>
       <c r="AM66" t="n">
-        <v>0.002160587977369305</v>
+        <v>0.002157535281263066</v>
       </c>
       <c r="AN66" t="inlineStr"/>
     </row>
@@ -7474,10 +7474,10 @@
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>0.4063693156807596</v>
+        <v>0.418401611669922</v>
       </c>
       <c r="L67" t="n">
-        <v>0.3754883524270142</v>
+        <v>0.3821256938063454</v>
       </c>
       <c r="M67" t="n">
         <v>0</v>
@@ -7486,61 +7486,61 @@
         <v>0</v>
       </c>
       <c r="O67" t="n">
-        <v>4.262792264471607</v>
+        <v>4.381125636492835</v>
       </c>
       <c r="P67" t="n">
-        <v>4.258573603837936</v>
+        <v>4.34406181085281</v>
       </c>
       <c r="Q67" t="n">
-        <v>0.8612831125799764</v>
+        <v>0.8652052824349274</v>
       </c>
       <c r="R67" t="n">
-        <v>0.02693869404416841</v>
+        <v>0.02655512234624559</v>
       </c>
       <c r="S67" t="inlineStr"/>
       <c r="T67" t="inlineStr"/>
       <c r="U67" t="inlineStr"/>
       <c r="V67" t="inlineStr"/>
       <c r="W67" t="n">
-        <v>0.8063172820364969</v>
+        <v>0.8071641175971108</v>
       </c>
       <c r="X67" t="n">
-        <v>0.0007649927651199615</v>
+        <v>0.0007633185508364196</v>
       </c>
       <c r="Y67" t="inlineStr"/>
       <c r="Z67" t="n">
-        <v>0.6130647098925764</v>
+        <v>0.6252317559356262</v>
       </c>
       <c r="AA67" t="n">
-        <v>0.06409562413825676</v>
+        <v>0.06307984279609716</v>
       </c>
       <c r="AB67" t="inlineStr"/>
       <c r="AC67" t="n">
-        <v>0.7684042961412765</v>
+        <v>0.7694401471717121</v>
       </c>
       <c r="AD67" t="n">
-        <v>0.002636494705905672</v>
+        <v>0.00263059201364216</v>
       </c>
       <c r="AE67" t="inlineStr"/>
       <c r="AF67" t="n">
-        <v>0.6599487847196395</v>
+        <v>0.6608983700798354</v>
       </c>
       <c r="AG67" t="n">
-        <v>0.01279054950719947</v>
+        <v>0.01277267836156645</v>
       </c>
       <c r="AH67" t="inlineStr"/>
       <c r="AI67" t="n">
-        <v>0.8259491540030421</v>
+        <v>0.8106537736777357</v>
       </c>
       <c r="AJ67" t="n">
-        <v>0.008639964098441621</v>
+        <v>0.009011606001879655</v>
       </c>
       <c r="AK67" t="inlineStr"/>
       <c r="AL67" t="n">
-        <v>0.8264333115138845</v>
+        <v>0.8067049225180842</v>
       </c>
       <c r="AM67" t="n">
-        <v>0.0001111855972821239</v>
+        <v>0.0001173345039910578</v>
       </c>
       <c r="AN67" t="inlineStr"/>
     </row>
@@ -7582,10 +7582,10 @@
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>0.4063693156807596</v>
+        <v>0.4256809874704212</v>
       </c>
       <c r="L68" t="n">
-        <v>0.3565393702912077</v>
+        <v>0.3705203685982623</v>
       </c>
       <c r="M68" t="n">
         <v>0</v>
@@ -7594,61 +7594,61 @@
         <v>0</v>
       </c>
       <c r="O68" t="n">
-        <v>4.262792264471607</v>
+        <v>4.452681279498788</v>
       </c>
       <c r="P68" t="n">
-        <v>4.191510109558156</v>
+        <v>4.341592065566686</v>
       </c>
       <c r="Q68" t="n">
-        <v>0.7995574008999248</v>
+        <v>0.8049131111357513</v>
       </c>
       <c r="R68" t="n">
-        <v>0.02986599630530236</v>
+        <v>0.02946429375497725</v>
       </c>
       <c r="S68" t="inlineStr"/>
       <c r="T68" t="inlineStr"/>
       <c r="U68" t="inlineStr"/>
       <c r="V68" t="inlineStr"/>
       <c r="W68" t="n">
-        <v>0.491349880273228</v>
+        <v>0.4850167914312021</v>
       </c>
       <c r="X68" t="n">
-        <v>0.001166338273658208</v>
+        <v>0.00117357672073808</v>
       </c>
       <c r="Y68" t="inlineStr"/>
       <c r="Z68" t="n">
-        <v>0.4584299511950864</v>
+        <v>0.4747389252301797</v>
       </c>
       <c r="AA68" t="n">
-        <v>0.07158574819068865</v>
+        <v>0.07049963336404443</v>
       </c>
       <c r="AB68" t="inlineStr"/>
       <c r="AC68" t="n">
-        <v>0.4745931554010342</v>
+        <v>0.4663226440179072</v>
       </c>
       <c r="AD68" t="n">
-        <v>0.003868414006119549</v>
+        <v>0.003898741778773778</v>
       </c>
       <c r="AE68" t="inlineStr"/>
       <c r="AF68" t="n">
-        <v>0.6954191670648295</v>
+        <v>0.6887807616993085</v>
       </c>
       <c r="AG68" t="n">
-        <v>0.008115642144618556</v>
+        <v>0.008203606518553111</v>
       </c>
       <c r="AH68" t="inlineStr"/>
       <c r="AI68" t="n">
-        <v>0.7159478551499857</v>
+        <v>0.6970705455301829</v>
       </c>
       <c r="AJ68" t="n">
-        <v>0.01201846978036402</v>
+        <v>0.01241140337891528</v>
       </c>
       <c r="AK68" t="inlineStr"/>
       <c r="AL68" t="n">
-        <v>0.2993138242386173</v>
+        <v>0.249383837800332</v>
       </c>
       <c r="AM68" t="n">
-        <v>0.000743945279597945</v>
+        <v>0.0007699954760900591</v>
       </c>
       <c r="AN68" t="inlineStr"/>
     </row>
@@ -7690,10 +7690,10 @@
         <v>0.04611530568392795</v>
       </c>
       <c r="K69" t="n">
-        <v>0.1547738540766385</v>
+        <v>0.1578375667668122</v>
       </c>
       <c r="L69" t="n">
-        <v>0.2113040000718849</v>
+        <v>0.2142730074772703</v>
       </c>
       <c r="M69" t="n">
         <v>0</v>
@@ -7702,16 +7702,16 @@
         <v>0</v>
       </c>
       <c r="O69" t="n">
-        <v>4.262919614482086</v>
+        <v>4.342039872316217</v>
       </c>
       <c r="P69" t="n">
-        <v>4.256185192496</v>
+        <v>4.303413304182833</v>
       </c>
       <c r="Q69" t="n">
-        <v>0.9734656079337696</v>
+        <v>0.973466531904749</v>
       </c>
       <c r="R69" t="n">
-        <v>0.00954709243755102</v>
+        <v>0.009546926213408365</v>
       </c>
       <c r="S69" t="inlineStr"/>
       <c r="T69" t="inlineStr"/>
@@ -7721,38 +7721,38 @@
       <c r="X69" t="inlineStr"/>
       <c r="Y69" t="inlineStr"/>
       <c r="Z69" t="n">
-        <v>0.9648035545181619</v>
+        <v>0.9649308018052815</v>
       </c>
       <c r="AA69" t="n">
-        <v>0.01039350733473922</v>
+        <v>0.01037470226615612</v>
       </c>
       <c r="AB69" t="inlineStr"/>
       <c r="AC69" t="n">
-        <v>0.4534318991265486</v>
+        <v>0.458396391489205</v>
       </c>
       <c r="AD69" t="n">
-        <v>0.004694912786907527</v>
+        <v>0.004673542140826365</v>
       </c>
       <c r="AE69" t="inlineStr"/>
       <c r="AF69" t="n">
-        <v>0.8644266184939671</v>
+        <v>0.8640858595624259</v>
       </c>
       <c r="AG69" t="n">
-        <v>0.01491012855586839</v>
+        <v>0.01492885483844594</v>
       </c>
       <c r="AH69" t="inlineStr"/>
       <c r="AI69" t="n">
-        <v>0.9076541033518778</v>
+        <v>0.9076361642234667</v>
       </c>
       <c r="AJ69" t="n">
-        <v>0.009220341024997931</v>
+        <v>0.009221236553957691</v>
       </c>
       <c r="AK69" t="inlineStr"/>
       <c r="AL69" t="n">
-        <v>0.5180018623746242</v>
+        <v>0.5180123767864011</v>
       </c>
       <c r="AM69" t="n">
-        <v>0.004282644871103801</v>
+        <v>0.004282598159577627</v>
       </c>
       <c r="AN69" t="inlineStr"/>
     </row>
@@ -7794,10 +7794,10 @@
         <v>0.03389921553245138</v>
       </c>
       <c r="K70" t="n">
-        <v>0.153202753067615</v>
+        <v>0.1548404427189273</v>
       </c>
       <c r="L70" t="n">
-        <v>0.2806403425895768</v>
+        <v>0.2798005208792019</v>
       </c>
       <c r="M70" t="n">
         <v>0</v>
@@ -7806,16 +7806,16 @@
         <v>0</v>
       </c>
       <c r="O70" t="n">
-        <v>4.3508196972905</v>
+        <v>4.394470536415335</v>
       </c>
       <c r="P70" t="n">
-        <v>4.369359318589514</v>
+        <v>4.362379885776532</v>
       </c>
       <c r="Q70" t="n">
-        <v>0.9659445971481412</v>
+        <v>0.965987268471406</v>
       </c>
       <c r="R70" t="n">
-        <v>0.009056194328969694</v>
+        <v>0.009050518857660008</v>
       </c>
       <c r="S70" t="inlineStr"/>
       <c r="T70" t="inlineStr"/>
@@ -7825,38 +7825,38 @@
       <c r="X70" t="inlineStr"/>
       <c r="Y70" t="inlineStr"/>
       <c r="Z70" t="n">
-        <v>0.9103630653369571</v>
+        <v>0.9105946226162333</v>
       </c>
       <c r="AA70" t="n">
-        <v>0.01336850055648339</v>
+        <v>0.01335122210202667</v>
       </c>
       <c r="AB70" t="inlineStr"/>
       <c r="AC70" t="n">
-        <v>0.9219866558655925</v>
+        <v>0.9219389840196544</v>
       </c>
       <c r="AD70" t="n">
-        <v>0.00323992427581504</v>
+        <v>0.003240914039709335</v>
       </c>
       <c r="AE70" t="inlineStr"/>
       <c r="AF70" t="n">
-        <v>0.9626947848226376</v>
+        <v>0.9627215048588192</v>
       </c>
       <c r="AG70" t="n">
-        <v>0.008770335173139167</v>
+        <v>0.008767193713566931</v>
       </c>
       <c r="AH70" t="inlineStr"/>
       <c r="AI70" t="n">
-        <v>0.8229049525683023</v>
+        <v>0.8229355510279825</v>
       </c>
       <c r="AJ70" t="n">
-        <v>0.01178667983435102</v>
+        <v>0.01178566153984561</v>
       </c>
       <c r="AK70" t="inlineStr"/>
       <c r="AL70" t="n">
-        <v>0.7539241257198928</v>
+        <v>0.7529163503012019</v>
       </c>
       <c r="AM70" t="n">
-        <v>0.00223936634160263</v>
+        <v>0.002243947189856084</v>
       </c>
       <c r="AN70" t="inlineStr"/>
     </row>
@@ -7898,10 +7898,10 @@
         <v>0.02861063360823382</v>
       </c>
       <c r="K71" t="n">
-        <v>0.3261006684563419</v>
+        <v>0.3259506110927289</v>
       </c>
       <c r="L71" t="n">
-        <v>0.3495488083686846</v>
+        <v>0.3486347098873965</v>
       </c>
       <c r="M71" t="n">
         <v>0</v>
@@ -7910,16 +7910,16 @@
         <v>0</v>
       </c>
       <c r="O71" t="n">
-        <v>4.438072623193317</v>
+        <v>4.436154054572222</v>
       </c>
       <c r="P71" t="n">
-        <v>4.457003126826023</v>
+        <v>4.440396206872959</v>
       </c>
       <c r="Q71" t="n">
-        <v>0.9607422787290285</v>
+        <v>0.9607948920053613</v>
       </c>
       <c r="R71" t="n">
-        <v>0.01081851722040209</v>
+        <v>0.01081126529064855</v>
       </c>
       <c r="S71" t="inlineStr"/>
       <c r="T71" t="inlineStr"/>
@@ -7929,38 +7929,38 @@
       <c r="X71" t="inlineStr"/>
       <c r="Y71" t="inlineStr"/>
       <c r="Z71" t="n">
-        <v>0.9430222570030538</v>
+        <v>0.9432467069920062</v>
       </c>
       <c r="AA71" t="n">
-        <v>0.01420634270854847</v>
+        <v>0.01417833387835802</v>
       </c>
       <c r="AB71" t="inlineStr"/>
       <c r="AC71" t="n">
-        <v>0.7405474700312662</v>
+        <v>0.7407857206215123</v>
       </c>
       <c r="AD71" t="n">
-        <v>0.004512007366406257</v>
+        <v>0.004509935243005926</v>
       </c>
       <c r="AE71" t="inlineStr"/>
       <c r="AF71" t="n">
-        <v>0.9024779376253617</v>
+        <v>0.9024282342438994</v>
       </c>
       <c r="AG71" t="n">
-        <v>0.009959921946509499</v>
+        <v>0.009962459724770861</v>
       </c>
       <c r="AH71" t="inlineStr"/>
       <c r="AI71" t="n">
-        <v>0.8435373599385118</v>
+        <v>0.8435488309205408</v>
       </c>
       <c r="AJ71" t="n">
-        <v>0.01621223827861748</v>
+        <v>0.01621164397155933</v>
       </c>
       <c r="AK71" t="inlineStr"/>
       <c r="AL71" t="n">
-        <v>0.9353651492544783</v>
+        <v>0.9354870836204331</v>
       </c>
       <c r="AM71" t="n">
-        <v>0.0009932146949270201</v>
+        <v>0.0009922773973696391</v>
       </c>
       <c r="AN71" t="inlineStr"/>
     </row>
@@ -8002,10 +8002,10 @@
         <v>0.03450948851818413</v>
       </c>
       <c r="K72" t="n">
-        <v>0.3263018165925168</v>
+        <v>0.3237573962818418</v>
       </c>
       <c r="L72" t="n">
-        <v>0.4214831291060785</v>
+        <v>0.4159121970215693</v>
       </c>
       <c r="M72" t="n">
         <v>0</v>
@@ -8014,16 +8014,16 @@
         <v>0</v>
       </c>
       <c r="O72" t="n">
-        <v>4.547889869855799</v>
+        <v>4.514536388254673</v>
       </c>
       <c r="P72" t="n">
-        <v>4.561848912256965</v>
+        <v>4.505731237331502</v>
       </c>
       <c r="Q72" t="n">
-        <v>0.9583660087194081</v>
+        <v>0.9584956209223118</v>
       </c>
       <c r="R72" t="n">
-        <v>0.01165209045993593</v>
+        <v>0.01163393906122562</v>
       </c>
       <c r="S72" t="inlineStr"/>
       <c r="T72" t="inlineStr"/>
@@ -8033,38 +8033,38 @@
       <c r="X72" t="inlineStr"/>
       <c r="Y72" t="inlineStr"/>
       <c r="Z72" t="n">
-        <v>0.870177595442528</v>
+        <v>0.8706524050963869</v>
       </c>
       <c r="AA72" t="n">
-        <v>0.01504844604738395</v>
+        <v>0.01502090190897186</v>
       </c>
       <c r="AB72" t="inlineStr"/>
       <c r="AC72" t="n">
-        <v>0.8080623011334103</v>
+        <v>0.8083387442247059</v>
       </c>
       <c r="AD72" t="n">
-        <v>0.004825728943423075</v>
+        <v>0.004822252502559896</v>
       </c>
       <c r="AE72" t="inlineStr"/>
       <c r="AF72" t="n">
-        <v>0.9534331659834825</v>
+        <v>0.9535455239329719</v>
       </c>
       <c r="AG72" t="n">
-        <v>0.006762516676927697</v>
+        <v>0.006754353341282688</v>
       </c>
       <c r="AH72" t="inlineStr"/>
       <c r="AI72" t="n">
-        <v>0.8562765374041598</v>
+        <v>0.8567071382991861</v>
       </c>
       <c r="AJ72" t="n">
-        <v>0.01952851540042021</v>
+        <v>0.01949923937294363</v>
       </c>
       <c r="AK72" t="inlineStr"/>
       <c r="AL72" t="n">
-        <v>0.9029273479746046</v>
+        <v>0.9028636026677657</v>
       </c>
       <c r="AM72" t="n">
-        <v>0.001420607829788853</v>
+        <v>0.001421074192962858</v>
       </c>
       <c r="AN72" t="inlineStr"/>
     </row>
@@ -8106,10 +8106,10 @@
         <v>0.01985208116188355</v>
       </c>
       <c r="K73" t="n">
-        <v>0.07823057899988078</v>
+        <v>0.08006297265283152</v>
       </c>
       <c r="L73" t="n">
-        <v>0.07924232650042848</v>
+        <v>0.08137571817139509</v>
       </c>
       <c r="M73" t="n">
         <v>0</v>
@@ -8118,16 +8118,16 @@
         <v>0</v>
       </c>
       <c r="O73" t="n">
-        <v>4.248593316158351</v>
+        <v>4.341883758983041</v>
       </c>
       <c r="P73" t="n">
-        <v>4.219362957573282</v>
+        <v>4.328693886773427</v>
       </c>
       <c r="Q73" t="n">
-        <v>0.9940101586958018</v>
+        <v>0.9939987049766698</v>
       </c>
       <c r="R73" t="n">
-        <v>0.005147066669713649</v>
+        <v>0.005151985406082198</v>
       </c>
       <c r="S73" t="inlineStr"/>
       <c r="T73" t="inlineStr"/>
@@ -8137,38 +8137,38 @@
       <c r="X73" t="inlineStr"/>
       <c r="Y73" t="inlineStr"/>
       <c r="Z73" t="n">
-        <v>0.9491220529728542</v>
+        <v>0.9490814218129882</v>
       </c>
       <c r="AA73" t="n">
-        <v>0.007744567208881133</v>
+        <v>0.007747658999801856</v>
       </c>
       <c r="AB73" t="inlineStr"/>
       <c r="AC73" t="n">
-        <v>0.6112191276303769</v>
+        <v>0.6117652657776269</v>
       </c>
       <c r="AD73" t="n">
-        <v>0.001246431655692332</v>
+        <v>0.001245555888451064</v>
       </c>
       <c r="AE73" t="inlineStr"/>
       <c r="AF73" t="n">
-        <v>0.9650589371089653</v>
+        <v>0.9649111723746878</v>
       </c>
       <c r="AG73" t="n">
-        <v>0.006271650348714358</v>
+        <v>0.006284897670915332</v>
       </c>
       <c r="AH73" t="inlineStr"/>
       <c r="AI73" t="n">
-        <v>0.8259568047831244</v>
+        <v>0.8256670362030982</v>
       </c>
       <c r="AJ73" t="n">
-        <v>0.005100856807103439</v>
+        <v>0.005105101308953068</v>
       </c>
       <c r="AK73" t="inlineStr"/>
       <c r="AL73" t="n">
-        <v>-0.07146806416313956</v>
+        <v>-0.07106758937209445</v>
       </c>
       <c r="AM73" t="n">
-        <v>0.002361614939844022</v>
+        <v>0.002361173556815051</v>
       </c>
       <c r="AN73" t="inlineStr"/>
     </row>
@@ -8210,10 +8210,10 @@
         <v>0.03595872786204279</v>
       </c>
       <c r="K74" t="n">
-        <v>0.08513405677699858</v>
+        <v>0.0844764733101903</v>
       </c>
       <c r="L74" t="n">
-        <v>0.1689500129333371</v>
+        <v>0.1658803230615703</v>
       </c>
       <c r="M74" t="n">
         <v>0</v>
@@ -8222,16 +8222,16 @@
         <v>0</v>
       </c>
       <c r="O74" t="n">
-        <v>4.431244325415121</v>
+        <v>4.399088907307153</v>
       </c>
       <c r="P74" t="n">
-        <v>4.457653587998073</v>
+        <v>4.387802559529828</v>
       </c>
       <c r="Q74" t="n">
-        <v>0.9726805955089844</v>
+        <v>0.97270653762638</v>
       </c>
       <c r="R74" t="n">
-        <v>0.007829805823413787</v>
+        <v>0.007826087404419544</v>
       </c>
       <c r="S74" t="inlineStr"/>
       <c r="T74" t="inlineStr"/>
@@ -8241,38 +8241,38 @@
       <c r="X74" t="inlineStr"/>
       <c r="Y74" t="inlineStr"/>
       <c r="Z74" t="n">
-        <v>0.8502939827020297</v>
+        <v>0.8506089235589397</v>
       </c>
       <c r="AA74" t="n">
-        <v>0.009244055636727555</v>
+        <v>0.009234327024506673</v>
       </c>
       <c r="AB74" t="inlineStr"/>
       <c r="AC74" t="n">
-        <v>0.8618552185413597</v>
+        <v>0.8619262195327839</v>
       </c>
       <c r="AD74" t="n">
-        <v>0.001235135725355559</v>
+        <v>0.001234818278937854</v>
       </c>
       <c r="AE74" t="inlineStr"/>
       <c r="AF74" t="n">
-        <v>0.898044546682023</v>
+        <v>0.8979989257542516</v>
       </c>
       <c r="AG74" t="n">
-        <v>0.01257305682687513</v>
+        <v>0.01257586947861658</v>
       </c>
       <c r="AH74" t="inlineStr"/>
       <c r="AI74" t="n">
-        <v>0.8597230345514771</v>
+        <v>0.8601893779407035</v>
       </c>
       <c r="AJ74" t="n">
-        <v>0.007572832894782517</v>
+        <v>0.007560234673324557</v>
       </c>
       <c r="AK74" t="inlineStr"/>
       <c r="AL74" t="n">
-        <v>0.7041811757220419</v>
+        <v>0.7035071016803413</v>
       </c>
       <c r="AM74" t="n">
-        <v>0.002030176165441486</v>
+        <v>0.002032487901956395</v>
       </c>
       <c r="AN74" t="inlineStr"/>
     </row>
@@ -8314,10 +8314,10 @@
         <v>0.05396179716059933</v>
       </c>
       <c r="K75" t="n">
-        <v>0.210319821056764</v>
+        <v>0.207879713293752</v>
       </c>
       <c r="L75" t="n">
-        <v>0.2645787813378834</v>
+        <v>0.2635591019267816</v>
       </c>
       <c r="M75" t="n">
         <v>0</v>
@@ -8326,16 +8326,16 @@
         <v>0</v>
       </c>
       <c r="O75" t="n">
-        <v>4.252039103170227</v>
+        <v>4.205773976883957</v>
       </c>
       <c r="P75" t="n">
-        <v>4.299243597059222</v>
+        <v>4.285134295724109</v>
       </c>
       <c r="Q75" t="n">
-        <v>0.9700469662964879</v>
+        <v>0.9700352220929257</v>
       </c>
       <c r="R75" t="n">
-        <v>0.006834941210109994</v>
+        <v>0.006836281025551389</v>
       </c>
       <c r="S75" t="inlineStr"/>
       <c r="T75" t="inlineStr"/>
@@ -8345,38 +8345,38 @@
       <c r="X75" t="inlineStr"/>
       <c r="Y75" t="inlineStr"/>
       <c r="Z75" t="n">
-        <v>0.8953969963061648</v>
+        <v>0.8952312768612467</v>
       </c>
       <c r="AA75" t="n">
-        <v>0.01155696709680736</v>
+        <v>0.01156611815438031</v>
       </c>
       <c r="AB75" t="inlineStr"/>
       <c r="AC75" t="n">
-        <v>0.8422532245447558</v>
+        <v>0.8435216367826263</v>
       </c>
       <c r="AD75" t="n">
-        <v>0.002396519932061428</v>
+        <v>0.002386865501858177</v>
       </c>
       <c r="AE75" t="inlineStr"/>
       <c r="AF75" t="n">
-        <v>0.9316235622403947</v>
+        <v>0.9316537784967639</v>
       </c>
       <c r="AG75" t="n">
-        <v>0.006862866271430834</v>
+        <v>0.006861349718007638</v>
       </c>
       <c r="AH75" t="inlineStr"/>
       <c r="AI75" t="n">
-        <v>0.8717042078087577</v>
+        <v>0.8718459282597438</v>
       </c>
       <c r="AJ75" t="n">
-        <v>0.006794252979355332</v>
+        <v>0.006790499346298951</v>
       </c>
       <c r="AK75" t="inlineStr"/>
       <c r="AL75" t="n">
-        <v>0.9731654708789172</v>
+        <v>0.9732191547832254</v>
       </c>
       <c r="AM75" t="n">
-        <v>0.00100722562508203</v>
+        <v>0.001006217616439601</v>
       </c>
       <c r="AN75" t="inlineStr"/>
     </row>
@@ -8418,10 +8418,10 @@
         <v>0.03136066852465918</v>
       </c>
       <c r="K76" t="n">
-        <v>0.01998426772365844</v>
+        <v>0.02053128897390902</v>
       </c>
       <c r="L76" t="n">
-        <v>0.02444715614173216</v>
+        <v>0.02507560144266702</v>
       </c>
       <c r="M76" t="n">
         <v>0</v>
@@ -8430,16 +8430,16 @@
         <v>0</v>
       </c>
       <c r="O76" t="n">
-        <v>4.249893838573551</v>
+        <v>4.358945383991737</v>
       </c>
       <c r="P76" t="n">
-        <v>4.216706930714855</v>
+        <v>4.318133968926499</v>
       </c>
       <c r="Q76" t="n">
-        <v>0.9931298524025587</v>
+        <v>0.9931292055639458</v>
       </c>
       <c r="R76" t="n">
-        <v>0.005201076932600544</v>
+        <v>0.005201321772915624</v>
       </c>
       <c r="S76" t="inlineStr"/>
       <c r="T76" t="inlineStr"/>
@@ -8449,38 +8449,38 @@
       <c r="X76" t="inlineStr"/>
       <c r="Y76" t="inlineStr"/>
       <c r="Z76" t="n">
-        <v>0.9362493856191604</v>
+        <v>0.9362500298616629</v>
       </c>
       <c r="AA76" t="n">
-        <v>0.007183613885165825</v>
+        <v>0.007183577587467957</v>
       </c>
       <c r="AB76" t="inlineStr"/>
       <c r="AC76" t="n">
-        <v>0.8851311195791087</v>
+        <v>0.8852010840946726</v>
       </c>
       <c r="AD76" t="n">
-        <v>0.0009344300523530738</v>
+        <v>0.0009341454369563394</v>
       </c>
       <c r="AE76" t="inlineStr"/>
       <c r="AF76" t="n">
-        <v>0.9547803517442455</v>
+        <v>0.9547729414807739</v>
       </c>
       <c r="AG76" t="n">
-        <v>0.008976853443979608</v>
+        <v>0.008977588944218092</v>
       </c>
       <c r="AH76" t="inlineStr"/>
       <c r="AI76" t="n">
-        <v>0.9887632241038931</v>
+        <v>0.9887546086081793</v>
       </c>
       <c r="AJ76" t="n">
-        <v>0.0008909203247997033</v>
+        <v>0.0008912618039564599</v>
       </c>
       <c r="AK76" t="inlineStr"/>
       <c r="AL76" t="n">
-        <v>0.5685367285366301</v>
+        <v>0.5685447733808981</v>
       </c>
       <c r="AM76" t="n">
-        <v>0.001183596865672547</v>
+        <v>0.001183585831249137</v>
       </c>
       <c r="AN76" t="inlineStr"/>
     </row>
@@ -8522,10 +8522,10 @@
         <v>0.02805201336700053</v>
       </c>
       <c r="K77" t="n">
-        <v>0.03972700182767472</v>
+        <v>0.03789390692492493</v>
       </c>
       <c r="L77" t="n">
-        <v>0.09014497000828862</v>
+        <v>0.08293632886498861</v>
       </c>
       <c r="M77" t="n">
         <v>0</v>
@@ -8534,16 +8534,16 @@
         <v>0</v>
       </c>
       <c r="O77" t="n">
-        <v>4.469822402045478</v>
+        <v>4.275909837651753</v>
       </c>
       <c r="P77" t="n">
-        <v>4.553917325990885</v>
+        <v>4.243293106379868</v>
       </c>
       <c r="Q77" t="n">
-        <v>0.9729265937794692</v>
+        <v>0.9728371946158348</v>
       </c>
       <c r="R77" t="n">
-        <v>0.009866872038998255</v>
+        <v>0.009883149324401437</v>
       </c>
       <c r="S77" t="inlineStr"/>
       <c r="T77" t="inlineStr"/>
@@ -8553,38 +8553,38 @@
       <c r="X77" t="inlineStr"/>
       <c r="Y77" t="inlineStr"/>
       <c r="Z77" t="n">
-        <v>0.541006760314628</v>
+        <v>0.5403022448950849</v>
       </c>
       <c r="AA77" t="n">
-        <v>0.01234336128498687</v>
+        <v>0.01235283065536421</v>
       </c>
       <c r="AB77" t="inlineStr"/>
       <c r="AC77" t="n">
-        <v>-0.6213109965600363</v>
+        <v>-0.6297403391754275</v>
       </c>
       <c r="AD77" t="n">
-        <v>0.001245197882691078</v>
+        <v>0.00124843063454326</v>
       </c>
       <c r="AE77" t="inlineStr"/>
       <c r="AF77" t="n">
-        <v>0.9218685259864257</v>
+        <v>0.9210674752498865</v>
       </c>
       <c r="AG77" t="n">
-        <v>0.01211719118503445</v>
+        <v>0.01217914913857419</v>
       </c>
       <c r="AH77" t="inlineStr"/>
       <c r="AI77" t="n">
-        <v>0.1686206329248439</v>
+        <v>0.1692933316843996</v>
       </c>
       <c r="AJ77" t="n">
-        <v>0.01361647822552445</v>
+        <v>0.01361096832113987</v>
       </c>
       <c r="AK77" t="inlineStr"/>
       <c r="AL77" t="n">
-        <v>0.8769632662559022</v>
+        <v>0.8749901634310162</v>
       </c>
       <c r="AM77" t="n">
-        <v>0.0007949415765946151</v>
+        <v>0.0008012903431373562</v>
       </c>
       <c r="AN77" t="inlineStr"/>
     </row>
@@ -8626,10 +8626,10 @@
         <v>0.01052672116974796</v>
       </c>
       <c r="K78" t="n">
-        <v>0.02841134719532212</v>
+        <v>0.02722131315634268</v>
       </c>
       <c r="L78" t="n">
-        <v>0.0822024536638621</v>
+        <v>0.07764629252821463</v>
       </c>
       <c r="M78" t="n">
         <v>0</v>
@@ -8638,16 +8638,16 @@
         <v>0</v>
       </c>
       <c r="O78" t="n">
-        <v>4.592870244659815</v>
+        <v>4.411801604657093</v>
       </c>
       <c r="P78" t="n">
-        <v>4.642155854354315</v>
+        <v>4.3775281730888</v>
       </c>
       <c r="Q78" t="n">
-        <v>0.9796106245546224</v>
+        <v>0.9790410756732091</v>
       </c>
       <c r="R78" t="n">
-        <v>0.01036892834776415</v>
+        <v>0.01051275169436136</v>
       </c>
       <c r="S78" t="inlineStr"/>
       <c r="T78" t="inlineStr"/>
@@ -8657,38 +8657,38 @@
       <c r="X78" t="inlineStr"/>
       <c r="Y78" t="inlineStr"/>
       <c r="Z78" t="n">
-        <v>0.1234549371150698</v>
+        <v>0.1225301556099971</v>
       </c>
       <c r="AA78" t="n">
-        <v>0.01134972650874777</v>
+        <v>0.01135571208248658</v>
       </c>
       <c r="AB78" t="inlineStr"/>
       <c r="AC78" t="n">
-        <v>0.7411142668666199</v>
+        <v>0.7096709745839889</v>
       </c>
       <c r="AD78" t="n">
-        <v>0.0005951425047757586</v>
+        <v>0.0006302489600751789</v>
       </c>
       <c r="AE78" t="inlineStr"/>
       <c r="AF78" t="n">
-        <v>0.8426017678716911</v>
+        <v>0.8348689263672254</v>
       </c>
       <c r="AG78" t="n">
-        <v>0.01631530084187625</v>
+        <v>0.01671127413344865</v>
       </c>
       <c r="AH78" t="inlineStr"/>
       <c r="AI78" t="n">
-        <v>-0.2282322311572544</v>
+        <v>-0.2437225258503379</v>
       </c>
       <c r="AJ78" t="n">
-        <v>0.0116755727891755</v>
+        <v>0.01174896745641607</v>
       </c>
       <c r="AK78" t="inlineStr"/>
       <c r="AL78" t="n">
-        <v>-1.70414381024056</v>
+        <v>-1.722751445451205</v>
       </c>
       <c r="AM78" t="n">
-        <v>0.00242793069602666</v>
+        <v>0.002436269859700756</v>
       </c>
       <c r="AN78" t="inlineStr"/>
     </row>
@@ -8730,10 +8730,10 @@
         <v>3.234988232153624e-17</v>
       </c>
       <c r="K79" t="n">
-        <v>0.2899193890845111</v>
+        <v>0.291298707758667</v>
       </c>
       <c r="L79" t="n">
-        <v>0.3201897700289114</v>
+        <v>0.3304035059681816</v>
       </c>
       <c r="M79" t="n">
         <v>0</v>
@@ -8742,58 +8742,58 @@
         <v>0</v>
       </c>
       <c r="O79" t="n">
-        <v>4.375531902801428</v>
+        <v>4.395075630781815</v>
       </c>
       <c r="P79" t="n">
-        <v>4.431605501335618</v>
+        <v>4.439066110577246</v>
       </c>
       <c r="Q79" t="n">
-        <v>0.9808407750009602</v>
+        <v>0.9810896195208271</v>
       </c>
       <c r="R79" t="n">
-        <v>0.0203610209736673</v>
+        <v>0.02022836194988157</v>
       </c>
       <c r="S79" t="inlineStr"/>
       <c r="T79" t="n">
-        <v>0.9160159304869085</v>
+        <v>0.9173823247709172</v>
       </c>
       <c r="U79" t="n">
-        <v>0.04501303030117679</v>
+        <v>0.04464535478460659</v>
       </c>
       <c r="V79" t="inlineStr"/>
       <c r="W79" t="n">
-        <v>0.3632543748068622</v>
+        <v>0.3691180979314987</v>
       </c>
       <c r="X79" t="n">
-        <v>0.002245803912084987</v>
+        <v>0.00223543930990148</v>
       </c>
       <c r="Y79" t="inlineStr"/>
       <c r="Z79" t="n">
-        <v>0.9958872603664474</v>
+        <v>0.9955889158578903</v>
       </c>
       <c r="AA79" t="n">
-        <v>0.005011922950510258</v>
+        <v>0.005190526931061067</v>
       </c>
       <c r="AB79" t="inlineStr"/>
       <c r="AC79" t="n">
-        <v>0.5828360033729389</v>
+        <v>0.5906689916039923</v>
       </c>
       <c r="AD79" t="n">
-        <v>0.004881611045587533</v>
+        <v>0.0048355634456624</v>
       </c>
       <c r="AE79" t="inlineStr"/>
       <c r="AF79" t="n">
-        <v>0.9877891831635069</v>
+        <v>0.9850466385376752</v>
       </c>
       <c r="AG79" t="n">
-        <v>0.003545412870967139</v>
+        <v>0.00392341162287957</v>
       </c>
       <c r="AH79" t="inlineStr"/>
       <c r="AI79" t="n">
-        <v>0.8681224779967041</v>
+        <v>0.8652278378842142</v>
       </c>
       <c r="AJ79" t="n">
-        <v>0.009704252803032248</v>
+        <v>0.009810176261362718</v>
       </c>
       <c r="AK79" t="inlineStr"/>
       <c r="AL79" t="inlineStr"/>
@@ -8838,10 +8838,10 @@
         <v>7.592549229303372e-17</v>
       </c>
       <c r="K80" t="n">
-        <v>0.1594873656769697</v>
+        <v>0.1623021847871931</v>
       </c>
       <c r="L80" t="n">
-        <v>0.2380167376080126</v>
+        <v>0.2458325049296386</v>
       </c>
       <c r="M80" t="n">
         <v>0</v>
@@ -8850,58 +8850,58 @@
         <v>0</v>
       </c>
       <c r="O80" t="n">
-        <v>4.443827784785064</v>
+        <v>4.51750010072576</v>
       </c>
       <c r="P80" t="n">
-        <v>4.462538015820062</v>
+        <v>4.474103812650267</v>
       </c>
       <c r="Q80" t="n">
-        <v>0.9939163145647836</v>
+        <v>0.9937421742225868</v>
       </c>
       <c r="R80" t="n">
-        <v>0.01078061741123134</v>
+        <v>0.01093382183032316</v>
       </c>
       <c r="S80" t="inlineStr"/>
       <c r="T80" t="n">
-        <v>0.979650390290028</v>
+        <v>0.9791557110882316</v>
       </c>
       <c r="U80" t="n">
-        <v>0.02265282804904696</v>
+        <v>0.02292650890581743</v>
       </c>
       <c r="V80" t="inlineStr"/>
       <c r="W80" t="n">
-        <v>0.7877400810217022</v>
+        <v>0.7965904666481212</v>
       </c>
       <c r="X80" t="n">
-        <v>0.0012323865532568</v>
+        <v>0.001206420214992126</v>
       </c>
       <c r="Y80" t="inlineStr"/>
       <c r="Z80" t="n">
-        <v>0.9982504634269294</v>
+        <v>0.9983500140171362</v>
       </c>
       <c r="AA80" t="n">
-        <v>0.002685480051424597</v>
+        <v>0.002607957713187918</v>
       </c>
       <c r="AB80" t="inlineStr"/>
       <c r="AC80" t="n">
-        <v>0.8134058294090788</v>
+        <v>0.8223784533859008</v>
       </c>
       <c r="AD80" t="n">
-        <v>0.003594111847223956</v>
+        <v>0.003506633486720634</v>
       </c>
       <c r="AE80" t="inlineStr"/>
       <c r="AF80" t="n">
-        <v>0.9786946622250571</v>
+        <v>0.9764504627317075</v>
       </c>
       <c r="AG80" t="n">
-        <v>0.007742101094082864</v>
+        <v>0.008139651575354715</v>
       </c>
       <c r="AH80" t="inlineStr"/>
       <c r="AI80" t="n">
-        <v>0.970153656990044</v>
+        <v>0.969382218542139</v>
       </c>
       <c r="AJ80" t="n">
-        <v>0.005659930212852742</v>
+        <v>0.005732609682370402</v>
       </c>
       <c r="AK80" t="inlineStr"/>
       <c r="AL80" t="inlineStr"/>
@@ -8946,10 +8946,10 @@
         <v>9.901399624920571e-18</v>
       </c>
       <c r="K81" t="n">
-        <v>0.2816063271155299</v>
+        <v>0.2797133348512963</v>
       </c>
       <c r="L81" t="n">
-        <v>0.2526936766772701</v>
+        <v>0.2614622828200588</v>
       </c>
       <c r="M81" t="n">
         <v>0</v>
@@ -8958,54 +8958,54 @@
         <v>0</v>
       </c>
       <c r="O81" t="n">
-        <v>4.554087837697824</v>
+        <v>4.547852263736372</v>
       </c>
       <c r="P81" t="n">
-        <v>4.557057010218827</v>
+        <v>4.585225404430166</v>
       </c>
       <c r="Q81" t="n">
-        <v>0.9912746715118521</v>
+        <v>0.9915073862567239</v>
       </c>
       <c r="R81" t="n">
-        <v>0.01269425643865079</v>
+        <v>0.01252382701626911</v>
       </c>
       <c r="S81" t="inlineStr"/>
       <c r="T81" t="n">
-        <v>0.9745485768843614</v>
+        <v>0.975550738508459</v>
       </c>
       <c r="U81" t="n">
-        <v>0.02390801399611583</v>
+        <v>0.02343259242457807</v>
       </c>
       <c r="V81" t="inlineStr"/>
       <c r="W81" t="inlineStr"/>
       <c r="X81" t="inlineStr"/>
       <c r="Y81" t="inlineStr"/>
       <c r="Z81" t="n">
-        <v>0.9801044692272356</v>
+        <v>0.9789300681838278</v>
       </c>
       <c r="AA81" t="n">
-        <v>0.00929616530361569</v>
+        <v>0.009566600492796364</v>
       </c>
       <c r="AB81" t="inlineStr"/>
       <c r="AC81" t="n">
-        <v>0.7535015334677546</v>
+        <v>0.7594125558772289</v>
       </c>
       <c r="AD81" t="n">
-        <v>0.003014825282567023</v>
+        <v>0.002978458250689731</v>
       </c>
       <c r="AE81" t="inlineStr"/>
       <c r="AF81" t="n">
-        <v>0.9564012119651009</v>
+        <v>0.9579897427500782</v>
       </c>
       <c r="AG81" t="n">
-        <v>0.006698846825791279</v>
+        <v>0.006575677562460379</v>
       </c>
       <c r="AH81" t="inlineStr"/>
       <c r="AI81" t="n">
-        <v>0.9601607637007809</v>
+        <v>0.9611088611477856</v>
       </c>
       <c r="AJ81" t="n">
-        <v>0.009682209963675536</v>
+        <v>0.00956630722825942</v>
       </c>
       <c r="AK81" t="inlineStr"/>
       <c r="AL81" t="inlineStr"/>
@@ -9050,10 +9050,10 @@
         <v>1.336850539002381e-17</v>
       </c>
       <c r="K82" t="n">
-        <v>0.1904621880632897</v>
+        <v>0.191395009818949</v>
       </c>
       <c r="L82" t="n">
-        <v>0.1461944578592645</v>
+        <v>0.1473499283749068</v>
       </c>
       <c r="M82" t="n">
         <v>0</v>
@@ -9062,54 +9062,54 @@
         <v>0</v>
       </c>
       <c r="O82" t="n">
-        <v>4.554008665274212</v>
+        <v>4.463985251926877</v>
       </c>
       <c r="P82" t="n">
-        <v>4.54177455512752</v>
+        <v>4.58495417747088</v>
       </c>
       <c r="Q82" t="n">
-        <v>0.968533523451119</v>
+        <v>0.9687450526266348</v>
       </c>
       <c r="R82" t="n">
-        <v>0.02392925185573157</v>
+        <v>0.0238486856326593</v>
       </c>
       <c r="S82" t="inlineStr"/>
       <c r="T82" t="n">
-        <v>0.912964405232653</v>
+        <v>0.9136616596404042</v>
       </c>
       <c r="U82" t="n">
-        <v>0.04606004900081478</v>
+        <v>0.04587518123605714</v>
       </c>
       <c r="V82" t="inlineStr"/>
       <c r="W82" t="inlineStr"/>
       <c r="X82" t="inlineStr"/>
       <c r="Y82" t="inlineStr"/>
       <c r="Z82" t="n">
-        <v>0.9467550717210867</v>
+        <v>0.9469512795381505</v>
       </c>
       <c r="AA82" t="n">
-        <v>0.01545047277362961</v>
+        <v>0.01542197896616796</v>
       </c>
       <c r="AB82" t="inlineStr"/>
       <c r="AC82" t="n">
-        <v>0.3002195960618442</v>
+        <v>0.3206913083963491</v>
       </c>
       <c r="AD82" t="n">
-        <v>0.002455190257670964</v>
+        <v>0.002419011034520423</v>
       </c>
       <c r="AE82" t="inlineStr"/>
       <c r="AF82" t="n">
-        <v>0.6830164577988214</v>
+        <v>0.6828999517878078</v>
       </c>
       <c r="AG82" t="n">
-        <v>0.02025527453051698</v>
+        <v>0.02025899656040794</v>
       </c>
       <c r="AH82" t="inlineStr"/>
       <c r="AI82" t="n">
-        <v>0.9690181622323836</v>
+        <v>0.9695000519933915</v>
       </c>
       <c r="AJ82" t="n">
-        <v>0.009300330288815752</v>
+        <v>0.009227718425119141</v>
       </c>
       <c r="AK82" t="inlineStr"/>
       <c r="AL82" t="inlineStr"/>
@@ -9152,10 +9152,10 @@
         <v>0.002282733977536599</v>
       </c>
       <c r="K83" t="n">
-        <v>0.1872142165502269</v>
+        <v>0.189934792401037</v>
       </c>
       <c r="L83" t="n">
-        <v>0.1744343568656718</v>
+        <v>0.1826267284946377</v>
       </c>
       <c r="M83" t="n">
         <v>0</v>
@@ -9164,54 +9164,54 @@
         <v>0</v>
       </c>
       <c r="O83" t="n">
-        <v>4.516876761044007</v>
+        <v>4.578578953049799</v>
       </c>
       <c r="P83" t="n">
-        <v>4.496770193524266</v>
+        <v>4.571960649035538</v>
       </c>
       <c r="Q83" t="n">
-        <v>0.9757351283802572</v>
+        <v>0.975739278735116</v>
       </c>
       <c r="R83" t="n">
-        <v>0.01864969681783473</v>
+        <v>0.01864810179250103</v>
       </c>
       <c r="S83" t="inlineStr"/>
       <c r="T83" t="n">
-        <v>0.9247042042227489</v>
+        <v>0.9247478164506443</v>
       </c>
       <c r="U83" t="n">
-        <v>0.03556262014093663</v>
+        <v>0.03555231950112275</v>
       </c>
       <c r="V83" t="inlineStr"/>
       <c r="W83" t="inlineStr"/>
       <c r="X83" t="inlineStr"/>
       <c r="Y83" t="inlineStr"/>
       <c r="Z83" t="n">
-        <v>0.9589703294091785</v>
+        <v>0.9595067108214487</v>
       </c>
       <c r="AA83" t="n">
-        <v>0.009767537762755551</v>
+        <v>0.009703482150566864</v>
       </c>
       <c r="AB83" t="inlineStr"/>
       <c r="AC83" t="n">
-        <v>0.2678064322599043</v>
+        <v>0.2721584302524647</v>
       </c>
       <c r="AD83" t="n">
-        <v>0.009563662233708191</v>
+        <v>0.009535197718484453</v>
       </c>
       <c r="AE83" t="inlineStr"/>
       <c r="AF83" t="n">
-        <v>0.9226521792167981</v>
+        <v>0.92071581695676</v>
       </c>
       <c r="AG83" t="n">
-        <v>0.01067618138995927</v>
+        <v>0.01080899162941539</v>
       </c>
       <c r="AH83" t="inlineStr"/>
       <c r="AI83" t="n">
-        <v>0.8751591374784887</v>
+        <v>0.8756106397787032</v>
       </c>
       <c r="AJ83" t="n">
-        <v>0.01317219523688434</v>
+        <v>0.01314835423107227</v>
       </c>
       <c r="AK83" t="inlineStr"/>
       <c r="AL83" t="inlineStr"/>
@@ -9254,10 +9254,10 @@
         <v>0.001579598306755124</v>
       </c>
       <c r="K84" t="n">
-        <v>0.1659043674747134</v>
+        <v>0.171344845273151</v>
       </c>
       <c r="L84" t="n">
-        <v>0.2938338308490022</v>
+        <v>0.3144608188889046</v>
       </c>
       <c r="M84" t="n">
         <v>0</v>
@@ -9266,54 +9266,54 @@
         <v>0</v>
       </c>
       <c r="O84" t="n">
-        <v>4.44868884650036</v>
+        <v>4.585710978228106</v>
       </c>
       <c r="P84" t="n">
-        <v>4.341325581286786</v>
+        <v>4.51504935164796</v>
       </c>
       <c r="Q84" t="n">
-        <v>0.9907038002269452</v>
+        <v>0.9903344577308121</v>
       </c>
       <c r="R84" t="n">
-        <v>0.01132252969980373</v>
+        <v>0.01154526369606604</v>
       </c>
       <c r="S84" t="inlineStr"/>
       <c r="T84" t="n">
-        <v>0.987138796729058</v>
+        <v>0.9873913956404577</v>
       </c>
       <c r="U84" t="n">
-        <v>0.01516784808686528</v>
+        <v>0.01501815830575804</v>
       </c>
       <c r="V84" t="inlineStr"/>
       <c r="W84" t="inlineStr"/>
       <c r="X84" t="inlineStr"/>
       <c r="Y84" t="inlineStr"/>
       <c r="Z84" t="n">
-        <v>0.9944013672726111</v>
+        <v>0.9933130550836702</v>
       </c>
       <c r="AA84" t="n">
-        <v>0.00510472761096804</v>
+        <v>0.005578859917414843</v>
       </c>
       <c r="AB84" t="inlineStr"/>
       <c r="AC84" t="n">
-        <v>0.4879190518881908</v>
+        <v>0.5270393210160504</v>
       </c>
       <c r="AD84" t="n">
-        <v>0.006478758690384553</v>
+        <v>0.006226371265389735</v>
       </c>
       <c r="AE84" t="inlineStr"/>
       <c r="AF84" t="n">
-        <v>0.8005550704679345</v>
+        <v>0.7830435084276691</v>
       </c>
       <c r="AG84" t="n">
-        <v>0.01840575374196602</v>
+        <v>0.01919678194774724</v>
       </c>
       <c r="AH84" t="inlineStr"/>
       <c r="AI84" t="n">
-        <v>0.9960190108711754</v>
+        <v>0.9975782452931089</v>
       </c>
       <c r="AJ84" t="n">
-        <v>0.00203235072469209</v>
+        <v>0.0015851422332806</v>
       </c>
       <c r="AK84" t="inlineStr"/>
       <c r="AL84" t="inlineStr"/>
@@ -9356,10 +9356,10 @@
         <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>0.2307899480131057</v>
+        <v>0.2347111018878213</v>
       </c>
       <c r="L85" t="n">
-        <v>0.2857637698969581</v>
+        <v>0.2950582658013271</v>
       </c>
       <c r="M85" t="n">
         <v>0</v>
@@ -9368,54 +9368,54 @@
         <v>0</v>
       </c>
       <c r="O85" t="n">
-        <v>4.429178952661008</v>
+        <v>4.499856930037251</v>
       </c>
       <c r="P85" t="n">
-        <v>4.439386013214333</v>
+        <v>4.494335338061362</v>
       </c>
       <c r="Q85" t="n">
-        <v>0.9784447043439806</v>
+        <v>0.9804738895804873</v>
       </c>
       <c r="R85" t="n">
-        <v>0.0183486138085498</v>
+        <v>0.01746361459638317</v>
       </c>
       <c r="S85" t="inlineStr"/>
       <c r="T85" t="n">
-        <v>0.9437043886202918</v>
+        <v>0.9535757123586837</v>
       </c>
       <c r="U85" t="n">
-        <v>0.03046067680985256</v>
+        <v>0.02766144752124787</v>
       </c>
       <c r="V85" t="inlineStr"/>
       <c r="W85" t="inlineStr"/>
       <c r="X85" t="inlineStr"/>
       <c r="Y85" t="inlineStr"/>
       <c r="Z85" t="n">
-        <v>0.9942412419406904</v>
+        <v>0.9918666485371912</v>
       </c>
       <c r="AA85" t="n">
-        <v>0.005848009430268191</v>
+        <v>0.006949897789780429</v>
       </c>
       <c r="AB85" t="inlineStr"/>
       <c r="AC85" t="n">
-        <v>-0.101578750083466</v>
+        <v>-0.08764342376728562</v>
       </c>
       <c r="AD85" t="n">
-        <v>0.01640118423367383</v>
+        <v>0.01629711392139493</v>
       </c>
       <c r="AE85" t="inlineStr"/>
       <c r="AF85" t="n">
-        <v>0.5690478649430026</v>
+        <v>0.572784553447327</v>
       </c>
       <c r="AG85" t="n">
-        <v>0.02120279747901276</v>
+        <v>0.02111067502000964</v>
       </c>
       <c r="AH85" t="inlineStr"/>
       <c r="AI85" t="n">
-        <v>0.9966263493138098</v>
+        <v>0.9997841094756301</v>
       </c>
       <c r="AJ85" t="n">
-        <v>0.001657899955602232</v>
+        <v>0.0004193967435592211</v>
       </c>
       <c r="AK85" t="inlineStr"/>
       <c r="AL85" t="inlineStr"/>
@@ -9458,10 +9458,10 @@
         <v>0.001282293415705915</v>
       </c>
       <c r="K86" t="n">
-        <v>0.1218510305567165</v>
+        <v>0.1247724149338163</v>
       </c>
       <c r="L86" t="n">
-        <v>0.1551652986346165</v>
+        <v>0.1593436216466051</v>
       </c>
       <c r="M86" t="n">
         <v>0</v>
@@ -9470,54 +9470,54 @@
         <v>0</v>
       </c>
       <c r="O86" t="n">
-        <v>4.469780948890098</v>
+        <v>4.570462719990509</v>
       </c>
       <c r="P86" t="n">
-        <v>4.395433839038261</v>
+        <v>4.515742961794027</v>
       </c>
       <c r="Q86" t="n">
-        <v>0.990282802309974</v>
+        <v>0.9903940418722199</v>
       </c>
       <c r="R86" t="n">
-        <v>0.01175686320578157</v>
+        <v>0.01168937498319476</v>
       </c>
       <c r="S86" t="inlineStr"/>
       <c r="T86" t="n">
-        <v>0.984862085679888</v>
+        <v>0.9850744497473672</v>
       </c>
       <c r="U86" t="n">
-        <v>0.01710222292237146</v>
+        <v>0.01698183892126025</v>
       </c>
       <c r="V86" t="inlineStr"/>
       <c r="W86" t="inlineStr"/>
       <c r="X86" t="inlineStr"/>
       <c r="Y86" t="inlineStr"/>
       <c r="Z86" t="n">
-        <v>0.9965056007730628</v>
+        <v>0.9963065060987834</v>
       </c>
       <c r="AA86" t="n">
-        <v>0.00343853972956603</v>
+        <v>0.003535138875647679</v>
       </c>
       <c r="AB86" t="inlineStr"/>
       <c r="AC86" t="n">
-        <v>-0.3863211730011531</v>
+        <v>-0.3773211717237219</v>
       </c>
       <c r="AD86" t="n">
-        <v>0.01762419116738577</v>
+        <v>0.01756688986452823</v>
       </c>
       <c r="AE86" t="inlineStr"/>
       <c r="AF86" t="n">
-        <v>0.980574327110707</v>
+        <v>0.9812247563569276</v>
       </c>
       <c r="AG86" t="n">
-        <v>0.007125767026673223</v>
+        <v>0.007005455428793422</v>
       </c>
       <c r="AH86" t="inlineStr"/>
       <c r="AI86" t="n">
-        <v>0.9759319261294759</v>
+        <v>0.9766567408923517</v>
       </c>
       <c r="AJ86" t="n">
-        <v>0.005041915094091606</v>
+        <v>0.004965415611374016</v>
       </c>
       <c r="AK86" t="inlineStr"/>
       <c r="AL86" t="inlineStr"/>
@@ -9560,10 +9560,10 @@
         <v>1.327388309752159e-16</v>
       </c>
       <c r="K87" t="n">
-        <v>0.1823831187847791</v>
+        <v>0.1836932533354582</v>
       </c>
       <c r="L87" t="n">
-        <v>0.3078920552834177</v>
+        <v>0.3212047022172082</v>
       </c>
       <c r="M87" t="n">
         <v>0</v>
@@ -9572,54 +9572,54 @@
         <v>0</v>
       </c>
       <c r="O87" t="n">
-        <v>4.595558295125066</v>
+        <v>4.671002060938001</v>
       </c>
       <c r="P87" t="n">
-        <v>4.466750497606537</v>
+        <v>4.625013059199635</v>
       </c>
       <c r="Q87" t="n">
-        <v>0.9518654351901263</v>
+        <v>0.9528376089871131</v>
       </c>
       <c r="R87" t="n">
-        <v>0.02459557499832856</v>
+        <v>0.02434592963474631</v>
       </c>
       <c r="S87" t="inlineStr"/>
       <c r="T87" t="n">
-        <v>0.9070150333890723</v>
+        <v>0.9101214237899498</v>
       </c>
       <c r="U87" t="n">
-        <v>0.03953907951569291</v>
+        <v>0.0388730195583844</v>
       </c>
       <c r="V87" t="inlineStr"/>
       <c r="W87" t="inlineStr"/>
       <c r="X87" t="inlineStr"/>
       <c r="Y87" t="inlineStr"/>
       <c r="Z87" t="n">
-        <v>0.8423650919992394</v>
+        <v>0.8400135984614169</v>
       </c>
       <c r="AA87" t="n">
-        <v>0.022190439173867</v>
+        <v>0.02235533765295454</v>
       </c>
       <c r="AB87" t="inlineStr"/>
       <c r="AC87" t="n">
-        <v>0.7637185158465309</v>
+        <v>0.770358936234994</v>
       </c>
       <c r="AD87" t="n">
-        <v>0.005697727382109719</v>
+        <v>0.005617092758887966</v>
       </c>
       <c r="AE87" t="inlineStr"/>
       <c r="AF87" t="n">
-        <v>0.3011096884043076</v>
+        <v>0.3037102188035828</v>
       </c>
       <c r="AG87" t="n">
-        <v>0.0295374714609248</v>
+        <v>0.02948246663492235</v>
       </c>
       <c r="AH87" t="inlineStr"/>
       <c r="AI87" t="n">
-        <v>0.9747029287334525</v>
+        <v>0.9794634899388649</v>
       </c>
       <c r="AJ87" t="n">
-        <v>0.008001926654803695</v>
+        <v>0.007209792493178158</v>
       </c>
       <c r="AK87" t="inlineStr"/>
       <c r="AL87" t="inlineStr"/>
@@ -9662,10 +9662,10 @@
         <v>1.912261794240524e-16</v>
       </c>
       <c r="K88" t="n">
-        <v>0.2319557577696864</v>
+        <v>0.2269187226468679</v>
       </c>
       <c r="L88" t="n">
-        <v>0.1636337507829403</v>
+        <v>0.1610926939247017</v>
       </c>
       <c r="M88" t="n">
         <v>0</v>
@@ -9674,54 +9674,54 @@
         <v>0</v>
       </c>
       <c r="O88" t="n">
-        <v>4.602089508487431</v>
+        <v>4.508038364188548</v>
       </c>
       <c r="P88" t="n">
-        <v>4.563870401527963</v>
+        <v>4.616014940025162</v>
       </c>
       <c r="Q88" t="n">
-        <v>0.9905880690717644</v>
+        <v>0.9911677616073298</v>
       </c>
       <c r="R88" t="n">
-        <v>0.01137441398714301</v>
+        <v>0.01101856547280698</v>
       </c>
       <c r="S88" t="inlineStr"/>
       <c r="T88" t="n">
-        <v>0.9722703975549388</v>
+        <v>0.9747457378410946</v>
       </c>
       <c r="U88" t="n">
-        <v>0.0209878107729249</v>
+        <v>0.02002915652684809</v>
       </c>
       <c r="V88" t="inlineStr"/>
       <c r="W88" t="inlineStr"/>
       <c r="X88" t="inlineStr"/>
       <c r="Y88" t="inlineStr"/>
       <c r="Z88" t="n">
-        <v>0.9848128493985854</v>
+        <v>0.9859123894171555</v>
       </c>
       <c r="AA88" t="n">
-        <v>0.006972711588793625</v>
+        <v>0.006715559807302352</v>
       </c>
       <c r="AB88" t="inlineStr"/>
       <c r="AC88" t="n">
-        <v>0.56027349641667</v>
+        <v>0.5661360363941335</v>
       </c>
       <c r="AD88" t="n">
-        <v>0.004136423252432203</v>
+        <v>0.004108756832110564</v>
       </c>
       <c r="AE88" t="inlineStr"/>
       <c r="AF88" t="n">
-        <v>0.955422189885437</v>
+        <v>0.9549354921117436</v>
       </c>
       <c r="AG88" t="n">
-        <v>0.006293157293096362</v>
+        <v>0.006327418183435707</v>
       </c>
       <c r="AH88" t="inlineStr"/>
       <c r="AI88" t="n">
-        <v>0.9512849079905705</v>
+        <v>0.9499380485828203</v>
       </c>
       <c r="AJ88" t="n">
-        <v>0.01005314546672131</v>
+        <v>0.01019117103755729</v>
       </c>
       <c r="AK88" t="inlineStr"/>
       <c r="AL88" t="inlineStr"/>
@@ -9764,10 +9764,10 @@
         <v>0</v>
       </c>
       <c r="K89" t="n">
-        <v>0.3362423670805384</v>
+        <v>0.3352916146113781</v>
       </c>
       <c r="L89" t="n">
-        <v>0.3293759878015077</v>
+        <v>0.3410086197232753</v>
       </c>
       <c r="M89" t="n">
         <v>0</v>
@@ -9776,54 +9776,54 @@
         <v>0</v>
       </c>
       <c r="O89" t="n">
-        <v>4.568276553466714</v>
+        <v>4.501914574676857</v>
       </c>
       <c r="P89" t="n">
-        <v>4.620541846795493</v>
+        <v>4.601731646475884</v>
       </c>
       <c r="Q89" t="n">
-        <v>0.9949934426743177</v>
+        <v>0.9957838033026417</v>
       </c>
       <c r="R89" t="n">
-        <v>0.008373375376873519</v>
+        <v>0.007684071480909165</v>
       </c>
       <c r="S89" t="inlineStr"/>
       <c r="T89" t="n">
-        <v>0.9911053125101519</v>
+        <v>0.9946008588252906</v>
       </c>
       <c r="U89" t="n">
-        <v>0.01288866170317462</v>
+        <v>0.0100416439721599</v>
       </c>
       <c r="V89" t="inlineStr"/>
       <c r="W89" t="inlineStr"/>
       <c r="X89" t="inlineStr"/>
       <c r="Y89" t="inlineStr"/>
       <c r="Z89" t="n">
-        <v>0.996150933772381</v>
+        <v>0.9957107577597389</v>
       </c>
       <c r="AA89" t="n">
-        <v>0.004727986197884163</v>
+        <v>0.004991014083450027</v>
       </c>
       <c r="AB89" t="inlineStr"/>
       <c r="AC89" t="n">
-        <v>0.7698894344885724</v>
+        <v>0.7657550291055167</v>
       </c>
       <c r="AD89" t="n">
-        <v>0.004648826298529203</v>
+        <v>0.004690403196969636</v>
       </c>
       <c r="AE89" t="inlineStr"/>
       <c r="AF89" t="n">
-        <v>0.9618503245952756</v>
+        <v>0.9544023076400937</v>
       </c>
       <c r="AG89" t="n">
-        <v>0.00474544647200824</v>
+        <v>0.005188037271933559</v>
       </c>
       <c r="AH89" t="inlineStr"/>
       <c r="AI89" t="n">
-        <v>0.9430356427600418</v>
+        <v>0.9417803380929247</v>
       </c>
       <c r="AJ89" t="n">
-        <v>0.01086115895525442</v>
+        <v>0.01098017870932351</v>
       </c>
       <c r="AK89" t="inlineStr"/>
       <c r="AL89" t="inlineStr"/>
@@ -9866,10 +9866,10 @@
         <v>0.03004752976171331</v>
       </c>
       <c r="K90" t="n">
-        <v>0.2010801060973464</v>
+        <v>0.2309014164628462</v>
       </c>
       <c r="L90" t="n">
-        <v>0.3846719249923702</v>
+        <v>0.4817050030759927</v>
       </c>
       <c r="M90" t="n">
         <v>0</v>
@@ -9878,54 +9878,54 @@
         <v>0</v>
       </c>
       <c r="O90" t="n">
-        <v>4.174898420666395</v>
+        <v>4.475080783493183</v>
       </c>
       <c r="P90" t="n">
-        <v>3.537180547501817</v>
+        <v>4.2844261121447</v>
       </c>
       <c r="Q90" t="n">
-        <v>0.9843026439748226</v>
+        <v>0.985661543993274</v>
       </c>
       <c r="R90" t="n">
-        <v>0.0165673497959853</v>
+        <v>0.01583401243658747</v>
       </c>
       <c r="S90" t="inlineStr"/>
       <c r="T90" t="n">
-        <v>0.9666582751351767</v>
+        <v>0.9692310029207792</v>
       </c>
       <c r="U90" t="n">
-        <v>0.02957194696128879</v>
+        <v>0.02840812414501118</v>
       </c>
       <c r="V90" t="inlineStr"/>
       <c r="W90" t="inlineStr"/>
       <c r="X90" t="inlineStr"/>
       <c r="Y90" t="inlineStr"/>
       <c r="Z90" t="n">
-        <v>0.9904862846595652</v>
+        <v>0.9923017691763977</v>
       </c>
       <c r="AA90" t="n">
-        <v>0.01260027831493061</v>
+        <v>0.01133445195626342</v>
       </c>
       <c r="AB90" t="inlineStr"/>
       <c r="AC90" t="n">
-        <v>0.8189579178577706</v>
+        <v>0.7983048294673831</v>
       </c>
       <c r="AD90" t="n">
-        <v>0.004847709570488672</v>
+        <v>0.005116754437832481</v>
       </c>
       <c r="AE90" t="inlineStr"/>
       <c r="AF90" t="n">
-        <v>0.989374500649741</v>
+        <v>0.9910837831172993</v>
       </c>
       <c r="AG90" t="n">
-        <v>0.0007851358516853509</v>
+        <v>0.0007192178317817351</v>
       </c>
       <c r="AH90" t="inlineStr"/>
       <c r="AI90" t="n">
-        <v>0.9860477582585785</v>
+        <v>0.9876793180592091</v>
       </c>
       <c r="AJ90" t="n">
-        <v>0.003871708321000222</v>
+        <v>0.003638295831568752</v>
       </c>
       <c r="AK90" t="inlineStr"/>
       <c r="AL90" t="inlineStr"/>

--- a/tables/Flexible CUE/Local_perf_matrix_protection_True_vo_True_CUE_True.xlsx
+++ b/tables/Flexible CUE/Local_perf_matrix_protection_True_vo_True_CUE_True.xlsx
@@ -653,25 +653,25 @@
         <v>70.85714285714286</v>
       </c>
       <c r="F2" t="n">
-        <v>0.432164952517398</v>
+        <v>0.4321649524844555</v>
       </c>
       <c r="G2" t="n">
         <v>0.04480286738351254</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2627803891781534</v>
+        <v>0.2627803892434106</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2428872347095719</v>
+        <v>0.2428872346838566</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01736455621136393</v>
+        <v>0.01736455620476475</v>
       </c>
       <c r="K2" t="n">
-        <v>0.001838908966245269</v>
+        <v>0.1674339198426332</v>
       </c>
       <c r="L2" t="n">
-        <v>0.004818660655609108</v>
+        <v>0.2035355470970822</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -680,16 +680,16 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>4.428549100137173</v>
+        <v>4.387464748584332</v>
       </c>
       <c r="P2" t="n">
-        <v>4.430351249159571</v>
+        <v>4.428870999953801</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9913349116578273</v>
+        <v>0.990546407256806</v>
       </c>
       <c r="R2" t="n">
-        <v>0.005722027948967221</v>
+        <v>0.00597670639936411</v>
       </c>
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
@@ -699,38 +699,38 @@
       <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="n">
-        <v>0.9999643989903475</v>
+        <v>0.988841933056589</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.000432696274363199</v>
+        <v>0.00766031237254714</v>
       </c>
       <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="n">
-        <v>-1.02118814113178</v>
+        <v>0.9996788178935155</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.009354482439412466</v>
+        <v>0.0001179212473376173</v>
       </c>
       <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="n">
-        <v>0.9994331133948459</v>
+        <v>0.9968213626581066</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.001004598377240635</v>
+        <v>0.002378837989076235</v>
       </c>
       <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="n">
-        <v>0.950674505839303</v>
+        <v>0.9452748773707047</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.009450498226264864</v>
+        <v>0.009954337334746089</v>
       </c>
       <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="n">
-        <v>0.5640019509773253</v>
+        <v>0.6399213684587218</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.001987015215006586</v>
+        <v>0.001805749866960041</v>
       </c>
       <c r="AN2" t="inlineStr"/>
     </row>
@@ -757,25 +757,25 @@
         <v>82.71186440677965</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4230480283044928</v>
+        <v>0.4230480283479805</v>
       </c>
       <c r="G3" t="n">
         <v>0.03838147280770231</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3417824749441816</v>
+        <v>0.341782474747073</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1733633998846752</v>
+        <v>0.1733633999809309</v>
       </c>
       <c r="J3" t="n">
-        <v>0.02342462405894816</v>
+        <v>0.02342462411631339</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001488722301635292</v>
+        <v>0.001198806640067375</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003536350849402868</v>
+        <v>0.002708738418391225</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -784,16 +784,16 @@
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>4.34036319288207</v>
+        <v>4.350145945842956</v>
       </c>
       <c r="P3" t="n">
-        <v>4.312953043785511</v>
+        <v>4.310668099570932</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.9918348188986992</v>
+        <v>0.9911327316483882</v>
       </c>
       <c r="R3" t="n">
-        <v>0.005494810002010068</v>
+        <v>0.005726176035692439</v>
       </c>
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
@@ -803,38 +803,38 @@
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="n">
-        <v>0.9990946365685138</v>
+        <v>0.997596952493387</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.001933477027204255</v>
+        <v>0.003149986700969085</v>
       </c>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="n">
-        <v>-1.057186228100312</v>
+        <v>-1.057186228100436</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.003512210996364539</v>
+        <v>0.003512210996364644</v>
       </c>
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="n">
-        <v>0.9858893082518353</v>
+        <v>0.9833285207150055</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.005761308300525506</v>
+        <v>0.00626230234808433</v>
       </c>
       <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="n">
-        <v>0.8570086349889083</v>
+        <v>0.8571624899463808</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.009170751308843197</v>
+        <v>0.009165816243314405</v>
       </c>
       <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="n">
-        <v>0.3006286318311833</v>
+        <v>0.3007462389030976</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.003412174589976826</v>
+        <v>0.003411887686429871</v>
       </c>
       <c r="AN3" t="inlineStr"/>
     </row>
@@ -861,25 +861,25 @@
         <v>38.828125</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5026131523004256</v>
+        <v>0.5026131523545405</v>
       </c>
       <c r="G4" t="n">
         <v>0.08176040369199321</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1418117772088146</v>
+        <v>0.1418117771640022</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2720282171617107</v>
+        <v>0.2720282171735377</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001786449637055907</v>
+        <v>0.00178644961592619</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4182132258886959</v>
+        <v>0.3797397164270677</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2208574833875513</v>
+        <v>0.3057569270462218</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -888,16 +888,16 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>4.293493812215727</v>
+        <v>4.273400973870871</v>
       </c>
       <c r="P4" t="n">
-        <v>4.556604365269963</v>
+        <v>4.553693221152459</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9607960700256233</v>
+        <v>0.9569257063863488</v>
       </c>
       <c r="R4" t="n">
-        <v>0.01295235895535342</v>
+        <v>0.01357666654333213</v>
       </c>
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
@@ -907,38 +907,38 @@
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="n">
-        <v>0.9851931087589035</v>
+        <v>0.9814532934471362</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.01071444163995483</v>
+        <v>0.01199143066748889</v>
       </c>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="n">
-        <v>0.9985441501502312</v>
+        <v>0.9972244344163206</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.0004748607820771584</v>
+        <v>0.0006556676511681519</v>
       </c>
       <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="n">
-        <v>0.4346053706977421</v>
+        <v>0.3677652704425984</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.02447277611701979</v>
+        <v>0.02587894526308376</v>
       </c>
       <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="n">
-        <v>0.9695991175866484</v>
+        <v>0.9841891716060412</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.007232291800302154</v>
+        <v>0.005215670631291929</v>
       </c>
       <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="n">
-        <v>0.348741996813437</v>
+        <v>0.2529883608024063</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.004089548628245454</v>
+        <v>0.004379883153506209</v>
       </c>
       <c r="AN4" t="inlineStr"/>
     </row>
@@ -965,25 +965,25 @@
         <v>67.8082191780822</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4142260612899763</v>
+        <v>0.414226061397911</v>
       </c>
       <c r="G5" t="n">
         <v>0.04681738015071348</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2912830177383198</v>
+        <v>0.2912830175544637</v>
       </c>
       <c r="I5" t="n">
-        <v>0.217379291417003</v>
+        <v>0.2173792914645093</v>
       </c>
       <c r="J5" t="n">
-        <v>0.03029424940398749</v>
+        <v>0.03029424943240262</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1838378561531941</v>
+        <v>0.1248483760324708</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2238263003664408</v>
+        <v>0.2040923172953695</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -992,16 +992,16 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>4.308694607789535</v>
+        <v>4.305059003950912</v>
       </c>
       <c r="P5" t="n">
-        <v>4.348799653163455</v>
+        <v>4.341263328027895</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9975645952804997</v>
+        <v>0.9964023904369254</v>
       </c>
       <c r="R5" t="n">
-        <v>0.002920944542833359</v>
+        <v>0.003550134069788458</v>
       </c>
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
@@ -1011,38 +1011,38 @@
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="n">
-        <v>0.9986341249047619</v>
+        <v>0.9980863912251179</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.002647116929158683</v>
+        <v>0.003133243946873672</v>
       </c>
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="n">
-        <v>0.9999958712067397</v>
+        <v>0.9999984322754838</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.252179777625198e-05</v>
+        <v>7.715960437001907e-06</v>
       </c>
       <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="n">
-        <v>0.9983410348102747</v>
+        <v>0.9967159693618171</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.001893358772173806</v>
+        <v>0.002663899762859329</v>
       </c>
       <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="n">
-        <v>0.9742049301009937</v>
+        <v>0.9625919843806482</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.005340006624892956</v>
+        <v>0.006430663383390186</v>
       </c>
       <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="n">
-        <v>0.9674414155669334</v>
+        <v>0.9747435659161258</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.0008413096990907708</v>
+        <v>0.00074098455529435</v>
       </c>
       <c r="AN5" t="inlineStr"/>
     </row>
@@ -1069,25 +1069,25 @@
         <v>77.65625</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3890909284533883</v>
+        <v>0.3890909284112034</v>
       </c>
       <c r="G6" t="n">
         <v>0.0408802018459966</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3036991224550851</v>
+        <v>0.3036991225960292</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2478250703308909</v>
+        <v>0.2478250702399798</v>
       </c>
       <c r="J6" t="n">
-        <v>0.01850467691463906</v>
+        <v>0.01850467690679097</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1683825408883232</v>
+        <v>0.1063085574200649</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2127574220704695</v>
+        <v>0.1720367115470464</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -1096,16 +1096,16 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>4.376451817448588</v>
+        <v>4.37329678087751</v>
       </c>
       <c r="P6" t="n">
-        <v>4.383120503648406</v>
+        <v>4.375747937845746</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.9776389469217642</v>
+        <v>0.9760429495779932</v>
       </c>
       <c r="R6" t="n">
-        <v>0.009039751746489418</v>
+        <v>0.009356793632250249</v>
       </c>
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
@@ -1115,38 +1115,38 @@
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="n">
-        <v>0.9919311455338834</v>
+        <v>0.9924428044228318</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.00518142450076494</v>
+        <v>0.005014452986617499</v>
       </c>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="n">
-        <v>0.999485684576646</v>
+        <v>0.9994556427573127</v>
       </c>
       <c r="AD6" t="n">
-        <v>6.057125084102614e-05</v>
+        <v>6.231516810802367e-05</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="n">
-        <v>0.9957776804957648</v>
+        <v>0.9904193238913391</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.002665133923721853</v>
+        <v>0.00401459343621742</v>
       </c>
       <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="n">
-        <v>0.6739619512424374</v>
+        <v>0.655398577393228</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.01855022087598805</v>
+        <v>0.0190710003961295</v>
       </c>
       <c r="AK6" t="inlineStr"/>
       <c r="AL6" t="n">
-        <v>0.4087041476018173</v>
+        <v>0.3521344826892905</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.00181198284318882</v>
+        <v>0.001896680147349072</v>
       </c>
       <c r="AN6" t="inlineStr"/>
     </row>
@@ -1173,25 +1173,25 @@
         <v>66.19718309859155</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4886958146778536</v>
+        <v>0.4886958146760266</v>
       </c>
       <c r="G7" t="n">
         <v>0.04795677136102667</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2566075839924613</v>
+        <v>0.2566075840123206</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1893475641758934</v>
+        <v>0.1893475641544703</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01739226579276497</v>
+        <v>0.01739226579615577</v>
       </c>
       <c r="K7" t="n">
-        <v>0.00178739823396281</v>
+        <v>0.001768829377981086</v>
       </c>
       <c r="L7" t="n">
-        <v>0.004074576617584719</v>
+        <v>0.004060168179274309</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -1200,16 +1200,16 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>4.252970041033242</v>
+        <v>4.241814344093751</v>
       </c>
       <c r="P7" t="n">
-        <v>4.357590724711937</v>
+        <v>4.360634737204032</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.9887164440336703</v>
+        <v>0.9889510049527583</v>
       </c>
       <c r="R7" t="n">
-        <v>0.006454072943751788</v>
+        <v>0.006386637479162763</v>
       </c>
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
@@ -1219,38 +1219,38 @@
       <c r="X7" t="inlineStr"/>
       <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="n">
-        <v>0.9950535028125729</v>
+        <v>0.9966947516593463</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.00533617813269342</v>
+        <v>0.004361978127028886</v>
       </c>
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="n">
-        <v>-1.032359569609433</v>
+        <v>-1.032359569609426</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.006150454745414018</v>
+        <v>0.006150454745414008</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="n">
-        <v>0.9263789633677032</v>
+        <v>0.9229510343292776</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.01081673771013954</v>
+        <v>0.01106569616108615</v>
       </c>
       <c r="AH7" t="inlineStr"/>
       <c r="AI7" t="n">
-        <v>0.99976701493855</v>
+        <v>0.9998215404596115</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.0004019458625547618</v>
+        <v>0.0003517818347092632</v>
       </c>
       <c r="AK7" t="inlineStr"/>
       <c r="AL7" t="n">
-        <v>0.1556294045148865</v>
+        <v>0.1557377449244484</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.004851120215797147</v>
+        <v>0.004850808984232075</v>
       </c>
       <c r="AN7" t="inlineStr"/>
     </row>
@@ -1277,25 +1277,25 @@
         <v>66.66666666666667</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3735503885622976</v>
+        <v>0.3735503886646729</v>
       </c>
       <c r="G8" t="n">
         <v>0.04761904761904761</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3017797553926043</v>
+        <v>0.3017797550644881</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2489905948482005</v>
+        <v>0.2489905949934041</v>
       </c>
       <c r="J8" t="n">
-        <v>0.02806021357785015</v>
+        <v>0.02806021365838738</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1601303832383536</v>
+        <v>0.1151345305983847</v>
       </c>
       <c r="L8" t="n">
-        <v>0.152332376680562</v>
+        <v>0.1547135596892878</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -1304,16 +1304,16 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>4.44514495646937</v>
+        <v>4.414448855077785</v>
       </c>
       <c r="P8" t="n">
-        <v>4.408363693557797</v>
+        <v>4.412985976300996</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.9924118052272565</v>
+        <v>0.9941192807951555</v>
       </c>
       <c r="R8" t="n">
-        <v>0.004692854716115689</v>
+        <v>0.004131265401232397</v>
       </c>
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
@@ -1323,38 +1323,38 @@
       <c r="X8" t="inlineStr"/>
       <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="n">
-        <v>0.9916197156149756</v>
+        <v>0.9948172379148296</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.006108506097849402</v>
+        <v>0.004803814957510502</v>
       </c>
       <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="n">
-        <v>0.9999794606976998</v>
+        <v>0.9999987201146814</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.974746352165192e-05</v>
+        <v>7.425789359526633e-06</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="n">
-        <v>0.9857993239608582</v>
+        <v>0.9859589718340386</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.005900829137295257</v>
+        <v>0.005867566010831895</v>
       </c>
       <c r="AH8" t="inlineStr"/>
       <c r="AI8" t="n">
-        <v>0.9829131051818217</v>
+        <v>0.9876582791142953</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.005534948028290435</v>
+        <v>0.004704027314179833</v>
       </c>
       <c r="AK8" t="inlineStr"/>
       <c r="AL8" t="n">
-        <v>0.9997306408882451</v>
+        <v>0.998892938829397</v>
       </c>
       <c r="AM8" t="n">
-        <v>5.99521924014409e-05</v>
+        <v>0.000121541626777644</v>
       </c>
       <c r="AN8" t="inlineStr"/>
     </row>
@@ -1381,25 +1381,25 @@
         <v>69.85074626865672</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4184346509008527</v>
+        <v>0.4184346509642805</v>
       </c>
       <c r="G9" t="n">
         <v>0.0454483787817121</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2664295170187482</v>
+        <v>0.2664295168783421</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2311091971008347</v>
+        <v>0.2311091971723147</v>
       </c>
       <c r="J9" t="n">
-        <v>0.03857825619785213</v>
+        <v>0.03857825620335059</v>
       </c>
       <c r="K9" t="n">
-        <v>0.00132724233869487</v>
+        <v>0.001015091906080705</v>
       </c>
       <c r="L9" t="n">
-        <v>0.004171897903985853</v>
+        <v>0.003248189721842049</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -1408,16 +1408,16 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>4.224225056384286</v>
+        <v>4.215658680689763</v>
       </c>
       <c r="P9" t="n">
-        <v>4.343860240323774</v>
+        <v>4.344678470159911</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.9891935760862314</v>
+        <v>0.989499638139715</v>
       </c>
       <c r="R9" t="n">
-        <v>0.005622153081769714</v>
+        <v>0.005541965265217679</v>
       </c>
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
@@ -1427,38 +1427,38 @@
       <c r="X9" t="inlineStr"/>
       <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="n">
-        <v>0.9925333805918996</v>
+        <v>0.9933844729239701</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.00623700982201794</v>
+        <v>0.00587079135795671</v>
       </c>
       <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="n">
-        <v>-1.024352963218107</v>
+        <v>-1.024352963218117</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.008148373191661083</v>
+        <v>0.008148373191661102</v>
       </c>
       <c r="AE9" t="inlineStr"/>
       <c r="AF9" t="n">
-        <v>0.9995484720134938</v>
+        <v>0.9993355362958505</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.0008598255776580291</v>
+        <v>0.00104304646235335</v>
       </c>
       <c r="AH9" t="inlineStr"/>
       <c r="AI9" t="n">
-        <v>0.9559999545988799</v>
+        <v>0.9560634311165023</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.007914587193396426</v>
+        <v>0.007908876158796291</v>
       </c>
       <c r="AK9" t="inlineStr"/>
       <c r="AL9" t="n">
-        <v>0.9733729202520788</v>
+        <v>0.9734254747580841</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.0009810974381310002</v>
+        <v>0.0009801287520451334</v>
       </c>
       <c r="AN9" t="inlineStr"/>
     </row>
@@ -1485,25 +1485,25 @@
         <v>52.61363636363636</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5306916825504616</v>
+        <v>0.5306916826579526</v>
       </c>
       <c r="G10" t="n">
         <v>0.0603380301004491</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2597511503162143</v>
+        <v>0.2597511501438604</v>
       </c>
       <c r="I10" t="n">
-        <v>0.115376694226804</v>
+        <v>0.1153766942703101</v>
       </c>
       <c r="J10" t="n">
-        <v>0.033842442806071</v>
+        <v>0.03384244282742767</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2184121480973804</v>
+        <v>0.1598414344543621</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1178701599852213</v>
+        <v>0.1276622554906347</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1512,16 +1512,16 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>4.114152557453664</v>
+        <v>4.094150895426115</v>
       </c>
       <c r="P10" t="n">
-        <v>4.235284883760527</v>
+        <v>4.236448476296292</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.9928800860151742</v>
+        <v>0.9917514210563582</v>
       </c>
       <c r="R10" t="n">
-        <v>0.005360035689716553</v>
+        <v>0.005769256866009632</v>
       </c>
       <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr"/>
@@ -1531,38 +1531,38 @@
       <c r="X10" t="inlineStr"/>
       <c r="Y10" t="inlineStr"/>
       <c r="Z10" t="n">
-        <v>0.9996888368913763</v>
+        <v>0.9992487625664687</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.001560289325626953</v>
+        <v>0.002424374441342532</v>
       </c>
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="n">
-        <v>0.9999699868124187</v>
+        <v>0.999956463940635</v>
       </c>
       <c r="AD10" t="n">
-        <v>4.579099089893043e-05</v>
+        <v>5.515038373844868e-05</v>
       </c>
       <c r="AE10" t="inlineStr"/>
       <c r="AF10" t="n">
-        <v>0.9298621128959641</v>
+        <v>0.9174006767986006</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.01082892190343788</v>
+        <v>0.01175160340269951</v>
       </c>
       <c r="AH10" t="inlineStr"/>
       <c r="AI10" t="n">
-        <v>0.9749016422537981</v>
+        <v>0.9904057714056357</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.002506524699547092</v>
+        <v>0.001549724030216725</v>
       </c>
       <c r="AK10" t="inlineStr"/>
       <c r="AL10" t="n">
-        <v>0.7845764874392911</v>
+        <v>0.7617730584004592</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.002844140607237534</v>
+        <v>0.002990886616948382</v>
       </c>
       <c r="AN10" t="inlineStr"/>
     </row>
@@ -1589,25 +1589,25 @@
         <v>61.69014084507042</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6976459379986636</v>
+        <v>0.6976459379735106</v>
       </c>
       <c r="G11" t="n">
         <v>0.05146046241936653</v>
       </c>
       <c r="H11" t="n">
-        <v>0.128689928922737</v>
+        <v>0.1286899289623047</v>
       </c>
       <c r="I11" t="n">
-        <v>0.09261029160041566</v>
+        <v>0.09261029157801856</v>
       </c>
       <c r="J11" t="n">
-        <v>0.02959337905881725</v>
+        <v>0.02959337906679948</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1757473902023626</v>
+        <v>0.1415564032536594</v>
       </c>
       <c r="L11" t="n">
-        <v>0.3457220789286981</v>
+        <v>0.3404344694220039</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -1616,16 +1616,16 @@
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>4.070128680268422</v>
+        <v>4.047587447108629</v>
       </c>
       <c r="P11" t="n">
-        <v>4.260085923989431</v>
+        <v>4.255307224990352</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.992885767090499</v>
+        <v>0.9952476846809135</v>
       </c>
       <c r="R11" t="n">
-        <v>0.006274882413107013</v>
+        <v>0.005128545070690911</v>
       </c>
       <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr"/>
@@ -1635,38 +1635,38 @@
       <c r="X11" t="inlineStr"/>
       <c r="Y11" t="inlineStr"/>
       <c r="Z11" t="n">
-        <v>0.9899235032775338</v>
+        <v>0.9938998734382933</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.012550624138312</v>
+        <v>0.009765173467199576</v>
       </c>
       <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="n">
-        <v>0.980246816791308</v>
+        <v>0.9959743304728947</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.0009899545284780364</v>
+        <v>0.0004469055631128388</v>
       </c>
       <c r="AE11" t="inlineStr"/>
       <c r="AF11" t="n">
-        <v>0.9380888726315225</v>
+        <v>0.9216017204568262</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.004410656297151249</v>
+        <v>0.004963318289598623</v>
       </c>
       <c r="AH11" t="inlineStr"/>
       <c r="AI11" t="n">
-        <v>0.9554487016716159</v>
+        <v>0.9823109065054654</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.002371828339628546</v>
+        <v>0.001494534207214114</v>
       </c>
       <c r="AK11" t="inlineStr"/>
       <c r="AL11" t="n">
-        <v>0.9724148606916169</v>
+        <v>0.9786800875149558</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.0007036086798859991</v>
+        <v>0.0006185663721171376</v>
       </c>
       <c r="AN11" t="inlineStr"/>
     </row>
@@ -1693,25 +1693,25 @@
         <v>1182.5</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6580079528637066</v>
+        <v>0.658007952809377</v>
       </c>
       <c r="G12" t="n">
         <v>0.002684653847444545</v>
       </c>
       <c r="H12" t="n">
-        <v>0.3185832282923884</v>
+        <v>0.3185832283714021</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0207241649964606</v>
+        <v>0.02072416497177636</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1058258334398891</v>
+        <v>0.08868436874967696</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1647301261806731</v>
+        <v>0.170893547593671</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1720,16 +1720,16 @@
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>4.069166306475234</v>
+        <v>4.093013469766094</v>
       </c>
       <c r="P12" t="n">
-        <v>4.116611958223732</v>
+        <v>4.126601184488354</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.952020361439344</v>
+        <v>0.9527771488518032</v>
       </c>
       <c r="R12" t="n">
-        <v>0.02383915154404832</v>
+        <v>0.02365039566525368</v>
       </c>
       <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr"/>
@@ -1739,38 +1739,38 @@
       <c r="X12" t="inlineStr"/>
       <c r="Y12" t="inlineStr"/>
       <c r="Z12" t="n">
-        <v>0.7302072874414616</v>
+        <v>0.7394208759986733</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.05134403665481801</v>
+        <v>0.05045970560007496</v>
       </c>
       <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="n">
-        <v>0.9826113508413626</v>
+        <v>0.9985527788203644</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.0003096734684946327</v>
+        <v>8.933847416228581e-05</v>
       </c>
       <c r="AE12" t="inlineStr"/>
       <c r="AF12" t="n">
-        <v>0.9989137189713839</v>
+        <v>0.9666269882539512</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.001246277183105788</v>
+        <v>0.006907823735283787</v>
       </c>
       <c r="AH12" t="inlineStr"/>
       <c r="AI12" t="n">
-        <v>0.246673468218876</v>
+        <v>0.1345541708228669</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.003770913059828923</v>
+        <v>0.00404180013893422</v>
       </c>
       <c r="AK12" t="inlineStr"/>
       <c r="AL12" t="n">
-        <v>0.9893310357842738</v>
+        <v>0.9956950194184384</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.0002089473997565754</v>
+        <v>0.0001327276604496481</v>
       </c>
       <c r="AN12" t="inlineStr"/>
     </row>
@@ -1797,25 +1797,25 @@
         <v>37.30769230769231</v>
       </c>
       <c r="F13" t="n">
-        <v>0.3764292995365501</v>
+        <v>0.3764292995885038</v>
       </c>
       <c r="G13" t="n">
         <v>0.08509245622647683</v>
       </c>
       <c r="H13" t="n">
-        <v>0.20530781079537</v>
+        <v>0.2053078106416003</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2773838130683605</v>
+        <v>0.2773838131849478</v>
       </c>
       <c r="J13" t="n">
-        <v>0.05578662037324268</v>
+        <v>0.0557866203584713</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1485150072055759</v>
+        <v>0.1318957320315873</v>
       </c>
       <c r="L13" t="n">
-        <v>0.22018022197519</v>
+        <v>0.1981338621623199</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1824,16 +1824,16 @@
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>4.284045086843435</v>
+        <v>4.278667842899751</v>
       </c>
       <c r="P13" t="n">
-        <v>4.512729081527848</v>
+        <v>4.51567981292892</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.9979048782818226</v>
+        <v>0.9979548017383153</v>
       </c>
       <c r="R13" t="n">
-        <v>0.002619373052930165</v>
+        <v>0.002587977126947264</v>
       </c>
       <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr"/>
@@ -1843,38 +1843,38 @@
       <c r="X13" t="inlineStr"/>
       <c r="Y13" t="inlineStr"/>
       <c r="Z13" t="n">
-        <v>0.8327039979257171</v>
+        <v>0.848275509167002</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.003224805625040577</v>
+        <v>0.003071062135423367</v>
       </c>
       <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="n">
-        <v>0.9990436130842091</v>
+        <v>0.9950338238187981</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.368360731429251e-05</v>
+        <v>5.396871778259927e-05</v>
       </c>
       <c r="AE13" t="inlineStr"/>
       <c r="AF13" t="n">
-        <v>0.6303851705000185</v>
+        <v>0.628995171700221</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.004347469521630255</v>
+        <v>0.004355636531317803</v>
       </c>
       <c r="AH13" t="inlineStr"/>
       <c r="AI13" t="n">
-        <v>0.999999259408615</v>
+        <v>0.9999956538545575</v>
       </c>
       <c r="AJ13" t="n">
-        <v>3.476747928290516e-05</v>
+        <v>8.422402761676619e-05</v>
       </c>
       <c r="AK13" t="inlineStr"/>
       <c r="AL13" t="n">
-        <v>0.9514284613609557</v>
+        <v>0.9507374852856839</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.002236949641904129</v>
+        <v>0.002252804808700185</v>
       </c>
       <c r="AN13" t="inlineStr"/>
     </row>
@@ -1901,25 +1901,25 @@
         <v>44</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4685666630154797</v>
+        <v>0.4685666629631464</v>
       </c>
       <c r="G14" t="n">
         <v>0.07215007215007214</v>
       </c>
       <c r="H14" t="n">
-        <v>0.2791093997172449</v>
+        <v>0.2791093997308827</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1713546933726054</v>
+        <v>0.1713546934252931</v>
       </c>
       <c r="J14" t="n">
-        <v>0.008819171744597891</v>
+        <v>0.008819171730605837</v>
       </c>
       <c r="K14" t="n">
-        <v>0.1727584722120463</v>
+        <v>0.1444543606302343</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2985452117301948</v>
+        <v>0.2448899776909093</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1928,16 +1928,16 @@
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>4.415219190537966</v>
+        <v>4.410185119042559</v>
       </c>
       <c r="P14" t="n">
-        <v>4.362693183010549</v>
+        <v>4.354117562833399</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.9739606621191087</v>
+        <v>0.9714959764328339</v>
       </c>
       <c r="R14" t="n">
-        <v>0.009609706850789872</v>
+        <v>0.01005421701828002</v>
       </c>
       <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr"/>
@@ -1947,38 +1947,38 @@
       <c r="X14" t="inlineStr"/>
       <c r="Y14" t="inlineStr"/>
       <c r="Z14" t="n">
-        <v>0.9178337375192679</v>
+        <v>0.9046288324684035</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.01425214359175016</v>
+        <v>0.01535472251793486</v>
       </c>
       <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="n">
-        <v>0.6483440915531236</v>
+        <v>0.8589258248351418</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.002908208543644586</v>
+        <v>0.001842003056293363</v>
       </c>
       <c r="AE14" t="inlineStr"/>
       <c r="AF14" t="n">
-        <v>0.9826286764636797</v>
+        <v>0.978053732586909</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.005696201671489181</v>
+        <v>0.006402494817855852</v>
       </c>
       <c r="AH14" t="inlineStr"/>
       <c r="AI14" t="n">
-        <v>0.579718313893418</v>
+        <v>0.5651806127435923</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.01464955641466951</v>
+        <v>0.01490076936621891</v>
       </c>
       <c r="AK14" t="inlineStr"/>
       <c r="AL14" t="n">
-        <v>0.2059969770410767</v>
+        <v>0.1659190105414179</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.001759215242241763</v>
+        <v>0.001803067606405368</v>
       </c>
       <c r="AN14" t="inlineStr"/>
     </row>
@@ -2005,25 +2005,25 @@
         <v>37.66666666666666</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4676168791864762</v>
+        <v>0.467616879374457</v>
       </c>
       <c r="G15" t="n">
         <v>0.08428150021070376</v>
       </c>
       <c r="H15" t="n">
-        <v>0.2808036479653256</v>
+        <v>0.280803647842334</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1470517109277883</v>
+        <v>0.1470517108760386</v>
       </c>
       <c r="J15" t="n">
-        <v>0.02024626170970604</v>
+        <v>0.02024626169646662</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1895470751595914</v>
+        <v>0.1316028009711741</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2933197078177879</v>
+        <v>0.2398210285828282</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -2032,16 +2032,16 @@
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>4.12729937470144</v>
+        <v>4.10389600519784</v>
       </c>
       <c r="P15" t="n">
-        <v>4.250834185958639</v>
+        <v>4.229309989855801</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.975807779438401</v>
+        <v>0.9723719010837693</v>
       </c>
       <c r="R15" t="n">
-        <v>0.008219804688209677</v>
+        <v>0.008784137649752883</v>
       </c>
       <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr"/>
@@ -2051,38 +2051,38 @@
       <c r="X15" t="inlineStr"/>
       <c r="Y15" t="inlineStr"/>
       <c r="Z15" t="n">
-        <v>0.9197776878023943</v>
+        <v>0.9122309846182808</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.01394674247539276</v>
+        <v>0.01458800181605403</v>
       </c>
       <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="n">
-        <v>-0.5405604309778897</v>
+        <v>-0.2793519889950717</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.003247874635409145</v>
+        <v>0.00295974920418698</v>
       </c>
       <c r="AE15" t="inlineStr"/>
       <c r="AF15" t="n">
-        <v>0.9498627388268558</v>
+        <v>0.9341697294443785</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.008199056085422594</v>
+        <v>0.009394991091547898</v>
       </c>
       <c r="AH15" t="inlineStr"/>
       <c r="AI15" t="n">
-        <v>0.656548015171428</v>
+        <v>0.5988272842315192</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.006558915762710387</v>
+        <v>0.007088669615262781</v>
       </c>
       <c r="AK15" t="inlineStr"/>
       <c r="AL15" t="n">
-        <v>0.9999995770694698</v>
+        <v>0.999999309430799</v>
       </c>
       <c r="AM15" t="n">
-        <v>2.406544089539302e-06</v>
+        <v>3.075125948709012e-06</v>
       </c>
       <c r="AN15" t="inlineStr"/>
     </row>
@@ -2109,25 +2109,25 @@
         <v>21.39130434782609</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3751087963773801</v>
+        <v>0.3751087964018581</v>
       </c>
       <c r="G16" t="n">
         <v>0.1484062459672215</v>
       </c>
       <c r="H16" t="n">
-        <v>0.06809149804835848</v>
+        <v>0.06809149804106746</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3926949046640935</v>
+        <v>0.3926949046425352</v>
       </c>
       <c r="J16" t="n">
-        <v>0.01569855494294647</v>
+        <v>0.01569855494731771</v>
       </c>
       <c r="K16" t="n">
-        <v>0.5109637156163565</v>
+        <v>0.5058025943758175</v>
       </c>
       <c r="L16" t="n">
-        <v>0.524826409861138</v>
+        <v>0.5112679067249624</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2136,16 +2136,16 @@
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>4.305324632016705</v>
+        <v>4.349769392665977</v>
       </c>
       <c r="P16" t="n">
-        <v>4.498954160381471</v>
+        <v>4.494212568469672</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.9758602116143378</v>
+        <v>0.9780806864735132</v>
       </c>
       <c r="R16" t="n">
-        <v>0.00944994150527813</v>
+        <v>0.009004837194415022</v>
       </c>
       <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr"/>
@@ -2155,31 +2155,31 @@
       <c r="X16" t="inlineStr"/>
       <c r="Y16" t="inlineStr"/>
       <c r="Z16" t="n">
-        <v>0.9937953635733858</v>
+        <v>0.9931187910124818</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.005806607172569121</v>
+        <v>0.006115002670665429</v>
       </c>
       <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="n">
-        <v>0.9584743548070799</v>
+        <v>0.9606768476260641</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.00420002056613056</v>
+        <v>0.004087119968068924</v>
       </c>
       <c r="AE16" t="inlineStr"/>
       <c r="AF16" t="n">
-        <v>0.9091355120823432</v>
+        <v>0.9586049850166881</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.003619397056548504</v>
+        <v>0.002442942018882891</v>
       </c>
       <c r="AH16" t="inlineStr"/>
       <c r="AI16" t="n">
-        <v>0.8429217642719108</v>
+        <v>0.8581194634580227</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.01795872530642704</v>
+        <v>0.01706785368915487</v>
       </c>
       <c r="AK16" t="inlineStr"/>
       <c r="AL16" t="inlineStr"/>
@@ -2211,25 +2211,25 @@
         <v>51.25</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4780640258980272</v>
+        <v>0.478064025668827</v>
       </c>
       <c r="G17" t="n">
         <v>0.06194347657762291</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2550441184335309</v>
+        <v>0.2550441188812936</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1330574186338084</v>
+        <v>0.1330574185135598</v>
       </c>
       <c r="J17" t="n">
-        <v>0.07189096045701066</v>
+        <v>0.07189096035869673</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1374919669067439</v>
+        <v>0.1560962956401372</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2307472800767105</v>
+        <v>0.2175514994452316</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -2238,16 +2238,16 @@
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>3.873370159099385</v>
+        <v>3.850449758009987</v>
       </c>
       <c r="P17" t="n">
-        <v>4.005826835085653</v>
+        <v>4.003179503233808</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.990508263237892</v>
+        <v>0.989395773756511</v>
       </c>
       <c r="R17" t="n">
-        <v>0.004522409513129559</v>
+        <v>0.004780095086875108</v>
       </c>
       <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr"/>
@@ -2257,38 +2257,38 @@
       <c r="X17" t="inlineStr"/>
       <c r="Y17" t="inlineStr"/>
       <c r="Z17" t="n">
-        <v>0.9703343570829618</v>
+        <v>0.9671886010536744</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.008664813118846234</v>
+        <v>0.009112650025133584</v>
       </c>
       <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="n">
-        <v>0.5722843899820016</v>
+        <v>0.7637638902948169</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.002022665662481978</v>
+        <v>0.001503210125636759</v>
       </c>
       <c r="AE17" t="inlineStr"/>
       <c r="AF17" t="n">
-        <v>0.9983033150964806</v>
+        <v>0.9951995204429213</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.001113977245660156</v>
+        <v>0.001873777567383604</v>
       </c>
       <c r="AH17" t="inlineStr"/>
       <c r="AI17" t="n">
-        <v>0.193293955721858</v>
+        <v>0.06028482131748891</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.004622123041898624</v>
+        <v>0.004988637692951708</v>
       </c>
       <c r="AK17" t="inlineStr"/>
       <c r="AL17" t="n">
-        <v>0.9948075356462398</v>
+        <v>0.9941325061227066</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.0006970003853739215</v>
+        <v>0.0007409221496791715</v>
       </c>
       <c r="AN17" t="inlineStr"/>
     </row>
@@ -2315,25 +2315,25 @@
         <v>31.46666666666667</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4515185462382498</v>
+        <v>0.451518546451847</v>
       </c>
       <c r="G18" t="n">
         <v>0.1008878127522195</v>
       </c>
       <c r="H18" t="n">
-        <v>0.2508910324934933</v>
+        <v>0.2508910318037907</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1666097192940944</v>
+        <v>0.1666097196951048</v>
       </c>
       <c r="J18" t="n">
-        <v>0.03009288922194302</v>
+        <v>0.03009288929703804</v>
       </c>
       <c r="K18" t="n">
-        <v>0.24258952682581</v>
+        <v>0.181582972876025</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2659670730655396</v>
+        <v>0.2290876771575064</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2342,16 +2342,16 @@
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>4.300562681691318</v>
+        <v>4.287479093745305</v>
       </c>
       <c r="P18" t="n">
-        <v>4.300546436141598</v>
+        <v>4.290293133107553</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.9827320056158617</v>
+        <v>0.9834307340455976</v>
       </c>
       <c r="R18" t="n">
-        <v>0.006796096428215015</v>
+        <v>0.006657178736919413</v>
       </c>
       <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr"/>
@@ -2361,38 +2361,38 @@
       <c r="X18" t="inlineStr"/>
       <c r="Y18" t="inlineStr"/>
       <c r="Z18" t="n">
-        <v>0.9166678208924395</v>
+        <v>0.9188971460343478</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.0148244604909142</v>
+        <v>0.01462482226341714</v>
       </c>
       <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="n">
-        <v>0.9869877379734456</v>
+        <v>0.9950960822804436</v>
       </c>
       <c r="AD18" t="n">
-        <v>0.0003141843593608251</v>
+        <v>0.0001928766918933566</v>
       </c>
       <c r="AE18" t="inlineStr"/>
       <c r="AF18" t="n">
-        <v>0.9954260882605082</v>
+        <v>0.997063837665212</v>
       </c>
       <c r="AG18" t="n">
-        <v>0.002029903004613332</v>
+        <v>0.001626377754650541</v>
       </c>
       <c r="AH18" t="inlineStr"/>
       <c r="AI18" t="n">
-        <v>0.9756653168228163</v>
+        <v>0.9825587128979482</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.002624355639990265</v>
+        <v>0.002221770049806808</v>
       </c>
       <c r="AK18" t="inlineStr"/>
       <c r="AL18" t="n">
-        <v>0.9955281379648904</v>
+        <v>0.9939373011154781</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.0002520791866744827</v>
+        <v>0.0002935119530814854</v>
       </c>
       <c r="AN18" t="inlineStr"/>
     </row>
@@ -2419,25 +2419,25 @@
         <v>77.71428571428571</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2928786705374068</v>
+        <v>0.2928786705098768</v>
       </c>
       <c r="G19" t="n">
         <v>0.04084967320261438</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2980196009674419</v>
+        <v>0.2980196010147655</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3557027147401188</v>
+        <v>0.3557027147337084</v>
       </c>
       <c r="J19" t="n">
-        <v>0.01254934055241822</v>
+        <v>0.01254934053903507</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1618647634163979</v>
+        <v>0.1080512787950732</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2266520304402777</v>
+        <v>0.1790722548535144</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -2446,16 +2446,16 @@
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>4.01013022703957</v>
+        <v>4.009989320724906</v>
       </c>
       <c r="P19" t="n">
-        <v>4.378894525126992</v>
+        <v>4.367861340697792</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.9880043984450059</v>
+        <v>0.9874880419236483</v>
       </c>
       <c r="R19" t="n">
-        <v>0.007716763050895845</v>
+        <v>0.007881099117136484</v>
       </c>
       <c r="S19" t="inlineStr"/>
       <c r="T19" t="inlineStr"/>
@@ -2465,38 +2465,38 @@
       <c r="X19" t="inlineStr"/>
       <c r="Y19" t="inlineStr"/>
       <c r="Z19" t="n">
-        <v>0.6261862384808998</v>
+        <v>0.6061652585070408</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.009103614075635955</v>
+        <v>0.009344223277594219</v>
       </c>
       <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="n">
-        <v>-0.02407581613210419</v>
+        <v>-0.08336883317022514</v>
       </c>
       <c r="AD19" t="n">
-        <v>0.003014901415834792</v>
+        <v>0.003100953324724859</v>
       </c>
       <c r="AE19" t="inlineStr"/>
       <c r="AF19" t="n">
-        <v>0.7666055143525095</v>
+        <v>0.7548656808224014</v>
       </c>
       <c r="AG19" t="n">
-        <v>0.01363561504322373</v>
+        <v>0.01397434611544685</v>
       </c>
       <c r="AH19" t="inlineStr"/>
       <c r="AI19" t="n">
-        <v>0.8511452672964697</v>
+        <v>0.8624702772165457</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0.004451167641450874</v>
+        <v>0.00427849384267343</v>
       </c>
       <c r="AK19" t="inlineStr"/>
       <c r="AL19" t="n">
-        <v>0.9960400729158702</v>
+        <v>0.9952810327469641</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.0001839813951152159</v>
+        <v>0.0002008416562685653</v>
       </c>
       <c r="AN19" t="inlineStr"/>
     </row>
@@ -2523,25 +2523,25 @@
         <v>55.77777777777778</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3719943274037391</v>
+        <v>0.3719943273800574</v>
       </c>
       <c r="G20" t="n">
         <v>0.05691519635742743</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2459185029100323</v>
+        <v>0.2459185030013721</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3196907365948976</v>
+        <v>0.3196907365258876</v>
       </c>
       <c r="J20" t="n">
-        <v>0.005481236733903614</v>
+        <v>0.005481236735255395</v>
       </c>
       <c r="K20" t="n">
-        <v>0.270337140109575</v>
+        <v>0.2057008732256997</v>
       </c>
       <c r="L20" t="n">
-        <v>0.306474044431695</v>
+        <v>0.2526578928640004</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -2550,16 +2550,16 @@
         <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>4.622332151259288</v>
+        <v>4.630704694731168</v>
       </c>
       <c r="P20" t="n">
-        <v>4.589270355176144</v>
+        <v>4.594532944806889</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.9761708549923681</v>
+        <v>0.9754314623975737</v>
       </c>
       <c r="R20" t="n">
-        <v>0.009062832131237158</v>
+        <v>0.009202362966604805</v>
       </c>
       <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr"/>
@@ -2569,38 +2569,38 @@
       <c r="X20" t="inlineStr"/>
       <c r="Y20" t="inlineStr"/>
       <c r="Z20" t="n">
-        <v>0.8787468901710448</v>
+        <v>0.8760234864453152</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.01014413226734182</v>
+        <v>0.01025742073304349</v>
       </c>
       <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="n">
-        <v>0.8252929229952188</v>
+        <v>0.8598776904134131</v>
       </c>
       <c r="AD20" t="n">
-        <v>0.002852094885726183</v>
+        <v>0.002554243898056018</v>
       </c>
       <c r="AE20" t="inlineStr"/>
       <c r="AF20" t="n">
-        <v>0.9733227802322076</v>
+        <v>0.9633945976303636</v>
       </c>
       <c r="AG20" t="n">
-        <v>0.004358380596989807</v>
+        <v>0.00510537282433304</v>
       </c>
       <c r="AH20" t="inlineStr"/>
       <c r="AI20" t="n">
-        <v>0.7922480009568221</v>
+        <v>0.7885841436497428</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0.01673806506865897</v>
+        <v>0.01688501398373737</v>
       </c>
       <c r="AK20" t="inlineStr"/>
       <c r="AL20" t="n">
-        <v>0.4651814554570201</v>
+        <v>0.4298738448077102</v>
       </c>
       <c r="AM20" t="n">
-        <v>0.0006917100762121532</v>
+        <v>0.0007141778166719271</v>
       </c>
       <c r="AN20" t="inlineStr"/>
     </row>
@@ -2627,25 +2627,25 @@
         <v>17.60714285714286</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3926349948370401</v>
+        <v>0.3926349942752794</v>
       </c>
       <c r="G21" t="n">
         <v>0.1803020058598151</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3377870452012128</v>
+        <v>0.3377870456849771</v>
       </c>
       <c r="I21" t="n">
-        <v>0.08927595410193191</v>
+        <v>0.08927595417992841</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>5.04831636563563e-18</v>
       </c>
       <c r="K21" t="n">
-        <v>0.1205682193591666</v>
+        <v>0.07288078000139452</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1424141123167814</v>
+        <v>0.1367673415201617</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -2654,16 +2654,16 @@
         <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>4.116445283604787</v>
+        <v>4.177714502255803</v>
       </c>
       <c r="P21" t="n">
-        <v>4.120922169320235</v>
+        <v>4.130381200405711</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.8640998623691123</v>
+        <v>0.7989176483960193</v>
       </c>
       <c r="R21" t="n">
-        <v>0.02399112699908035</v>
+        <v>0.02918284840588656</v>
       </c>
       <c r="S21" t="inlineStr"/>
       <c r="T21" t="inlineStr"/>
@@ -2673,38 +2673,38 @@
       <c r="X21" t="inlineStr"/>
       <c r="Y21" t="inlineStr"/>
       <c r="Z21" t="n">
-        <v>0.9562227590827219</v>
+        <v>0.9722703901857831</v>
       </c>
       <c r="AA21" t="n">
-        <v>0.008218867471995793</v>
+        <v>0.006541233651922158</v>
       </c>
       <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="n">
-        <v>0.9945489868070292</v>
+        <v>0.9887950074904146</v>
       </c>
       <c r="AD21" t="n">
-        <v>0.002437109695667851</v>
+        <v>0.003494155642657436</v>
       </c>
       <c r="AE21" t="inlineStr"/>
       <c r="AF21" t="n">
-        <v>-4.073243951911832</v>
+        <v>-6.945409851308082</v>
       </c>
       <c r="AG21" t="n">
-        <v>0.04933460861720036</v>
+        <v>0.06174004864604357</v>
       </c>
       <c r="AH21" t="inlineStr"/>
       <c r="AI21" t="n">
-        <v>-0.2741046317810907</v>
+        <v>-0.3456658601142357</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0.01923535852204688</v>
+        <v>0.0197681648706782</v>
       </c>
       <c r="AK21" t="inlineStr"/>
       <c r="AL21" t="n">
-        <v>0.552524461766148</v>
+        <v>0.4558915442913252</v>
       </c>
       <c r="AM21" t="n">
-        <v>0.0006920710621326452</v>
+        <v>0.000763148013481959</v>
       </c>
       <c r="AN21" t="inlineStr"/>
     </row>
@@ -2731,25 +2731,25 @@
         <v>29.3125</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4135808655857899</v>
+        <v>0.4135808655594087</v>
       </c>
       <c r="G22" t="n">
         <v>0.1083020272785731</v>
       </c>
       <c r="H22" t="n">
-        <v>0.2033297621759581</v>
+        <v>0.203329762176548</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2477420255951969</v>
+        <v>0.247742025507402</v>
       </c>
       <c r="J22" t="n">
-        <v>0.02704531936448205</v>
+        <v>0.02704531947806826</v>
       </c>
       <c r="K22" t="n">
-        <v>0.2807614585076638</v>
+        <v>0.2533994605117408</v>
       </c>
       <c r="L22" t="n">
-        <v>0.323837837232865</v>
+        <v>0.27968496220302</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -2758,16 +2758,16 @@
         <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>4.13956210274015</v>
+        <v>4.12741070069084</v>
       </c>
       <c r="P22" t="n">
-        <v>4.30991763458454</v>
+        <v>4.297532263907768</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.9819135739756599</v>
+        <v>0.9813794767452618</v>
       </c>
       <c r="R22" t="n">
-        <v>0.006798331095569802</v>
+        <v>0.006897979101460696</v>
       </c>
       <c r="S22" t="inlineStr"/>
       <c r="T22" t="inlineStr"/>
@@ -2777,38 +2777,38 @@
       <c r="X22" t="inlineStr"/>
       <c r="Y22" t="inlineStr"/>
       <c r="Z22" t="n">
-        <v>0.8928868837904936</v>
+        <v>0.8948923903623964</v>
       </c>
       <c r="AA22" t="n">
-        <v>0.009648736426454994</v>
+        <v>0.009557981711974761</v>
       </c>
       <c r="AB22" t="inlineStr"/>
       <c r="AC22" t="n">
-        <v>0.9302917151956532</v>
+        <v>0.8824736985539618</v>
       </c>
       <c r="AD22" t="n">
-        <v>0.001463396411492845</v>
+        <v>0.001900147531612422</v>
       </c>
       <c r="AE22" t="inlineStr"/>
       <c r="AF22" t="n">
-        <v>0.3550701173187961</v>
+        <v>0.3206820783252198</v>
       </c>
       <c r="AG22" t="n">
-        <v>0.01108440876247827</v>
+        <v>0.01137608476929768</v>
       </c>
       <c r="AH22" t="inlineStr"/>
       <c r="AI22" t="n">
-        <v>0.9557508786510324</v>
+        <v>0.9534285454374214</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0.003012027090635714</v>
+        <v>0.003090056693940743</v>
       </c>
       <c r="AK22" t="inlineStr"/>
       <c r="AL22" t="n">
-        <v>0.7812291634112993</v>
+        <v>0.7772689070465226</v>
       </c>
       <c r="AM22" t="n">
-        <v>0.001977488288753809</v>
+        <v>0.001995306573584923</v>
       </c>
       <c r="AN22" t="inlineStr"/>
     </row>
@@ -2835,25 +2835,25 @@
         <v>39.58333333333334</v>
       </c>
       <c r="F23" t="n">
-        <v>0.6238519511711706</v>
+        <v>0.6238519513177977</v>
       </c>
       <c r="G23" t="n">
         <v>0.08020050125313281</v>
       </c>
       <c r="H23" t="n">
-        <v>0.2028318968739128</v>
+        <v>0.2028318965921395</v>
       </c>
       <c r="I23" t="n">
-        <v>0.06932561212208042</v>
+        <v>0.06932561224073039</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0237900385797033</v>
+        <v>0.02379003859619956</v>
       </c>
       <c r="K23" t="n">
-        <v>0.2125758680225997</v>
+        <v>0.1677259721457121</v>
       </c>
       <c r="L23" t="n">
-        <v>0.2727119712918846</v>
+        <v>0.2348553597711815</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -2862,16 +2862,16 @@
         <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>3.85839694517567</v>
+        <v>3.852888542897317</v>
       </c>
       <c r="P23" t="n">
-        <v>4.108349748657133</v>
+        <v>4.087704451166312</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.9820276968781485</v>
+        <v>0.9833760106464656</v>
       </c>
       <c r="R23" t="n">
-        <v>0.01003668794360416</v>
+        <v>0.009652863836895405</v>
       </c>
       <c r="S23" t="inlineStr"/>
       <c r="T23" t="inlineStr"/>
@@ -2881,38 +2881,38 @@
       <c r="X23" t="inlineStr"/>
       <c r="Y23" t="inlineStr"/>
       <c r="Z23" t="n">
-        <v>0.8990071347727139</v>
+        <v>0.9070889073756504</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.02227914666474973</v>
+        <v>0.02136913731416221</v>
       </c>
       <c r="AB23" t="inlineStr"/>
       <c r="AC23" t="n">
-        <v>-0.5755794039221183</v>
+        <v>-0.4684360991933718</v>
       </c>
       <c r="AD23" t="n">
-        <v>0.001198685048847327</v>
+        <v>0.001157210770510432</v>
       </c>
       <c r="AE23" t="inlineStr"/>
       <c r="AF23" t="n">
-        <v>0.9801654878486934</v>
+        <v>0.9744070398788179</v>
       </c>
       <c r="AG23" t="n">
-        <v>0.002372091429300307</v>
+        <v>0.002694516954856406</v>
       </c>
       <c r="AH23" t="inlineStr"/>
       <c r="AI23" t="n">
-        <v>0.9096826062505989</v>
+        <v>0.7569479403916649</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0.0004879255482581236</v>
+        <v>0.0008004192382418373</v>
       </c>
       <c r="AK23" t="inlineStr"/>
       <c r="AL23" t="n">
-        <v>0.999382011747501</v>
+        <v>0.9996018229526996</v>
       </c>
       <c r="AM23" t="n">
-        <v>0.0001158159793934014</v>
+        <v>9.296436066547548e-05</v>
       </c>
       <c r="AN23" t="inlineStr"/>
     </row>
@@ -2939,25 +2939,25 @@
         <v>18.8</v>
       </c>
       <c r="F24" t="n">
-        <v>0.5366376492551596</v>
+        <v>0.5366376495537714</v>
       </c>
       <c r="G24" t="n">
         <v>0.1688618709895305</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1622397270835717</v>
+        <v>0.1622397269217724</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1157024432834648</v>
+        <v>0.1157024431484001</v>
       </c>
       <c r="J24" t="n">
-        <v>0.01655830938827357</v>
+        <v>0.01655830938652574</v>
       </c>
       <c r="K24" t="n">
-        <v>0.3899491530645845</v>
+        <v>0.3438194492405634</v>
       </c>
       <c r="L24" t="n">
-        <v>0.4733730306956111</v>
+        <v>0.4370754758342919</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -2966,16 +2966,16 @@
         <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>4.330915049849626</v>
+        <v>4.306058852366302</v>
       </c>
       <c r="P24" t="n">
-        <v>4.386274849460652</v>
+        <v>4.362205987875905</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.9946398898416594</v>
+        <v>0.9924754700166334</v>
       </c>
       <c r="R24" t="n">
-        <v>0.004347839465796365</v>
+        <v>0.005151412552851958</v>
       </c>
       <c r="S24" t="inlineStr"/>
       <c r="T24" t="inlineStr"/>
@@ -2985,31 +2985,31 @@
       <c r="X24" t="inlineStr"/>
       <c r="Y24" t="inlineStr"/>
       <c r="Z24" t="n">
-        <v>0.9995320269809053</v>
+        <v>0.9998174282838287</v>
       </c>
       <c r="AA24" t="n">
-        <v>0.001735933064475865</v>
+        <v>0.001084274681937463</v>
       </c>
       <c r="AB24" t="inlineStr"/>
       <c r="AC24" t="n">
-        <v>0.9572293091745959</v>
+        <v>0.9533619187960144</v>
       </c>
       <c r="AD24" t="n">
-        <v>0.003265292013805306</v>
+        <v>0.003409724033920006</v>
       </c>
       <c r="AE24" t="inlineStr"/>
       <c r="AF24" t="n">
-        <v>0.8876443399180077</v>
+        <v>0.833920957804832</v>
       </c>
       <c r="AG24" t="n">
-        <v>0.008260491953133008</v>
+        <v>0.01004305527790222</v>
       </c>
       <c r="AH24" t="inlineStr"/>
       <c r="AI24" t="n">
-        <v>0.9998960457205744</v>
+        <v>0.9708841993311144</v>
       </c>
       <c r="AJ24" t="n">
-        <v>6.888570670350077e-05</v>
+        <v>0.001152848660305331</v>
       </c>
       <c r="AK24" t="inlineStr"/>
       <c r="AL24" t="inlineStr"/>
@@ -3041,25 +3041,25 @@
         <v>68</v>
       </c>
       <c r="F25" t="n">
-        <v>0.3559522748638808</v>
+        <v>0.3559522750970078</v>
       </c>
       <c r="G25" t="n">
         <v>0.04668534080298786</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2688668009066632</v>
+        <v>0.2688668010518658</v>
       </c>
       <c r="I25" t="n">
-        <v>0.2729559277122325</v>
+        <v>0.2729559273787527</v>
       </c>
       <c r="J25" t="n">
-        <v>0.05553965571423582</v>
+        <v>0.05553965566938588</v>
       </c>
       <c r="K25" t="n">
-        <v>0.2158934749426978</v>
+        <v>0.1556531723472595</v>
       </c>
       <c r="L25" t="n">
-        <v>0.2288284659952428</v>
+        <v>0.179981678237344</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
@@ -3068,65 +3068,65 @@
         <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>4.311008836928643</v>
+        <v>4.318162033299422</v>
       </c>
       <c r="P25" t="n">
-        <v>4.340714662475478</v>
+        <v>4.341427466773419</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.9846063623632936</v>
+        <v>0.9853071365363835</v>
       </c>
       <c r="R25" t="n">
-        <v>0.02057664286603977</v>
+        <v>0.02010282591377737</v>
       </c>
       <c r="S25" t="inlineStr"/>
       <c r="T25" t="n">
-        <v>-0.1671293684514767</v>
+        <v>-0.1010552173370118</v>
       </c>
       <c r="U25" t="n">
-        <v>0.03977521829467955</v>
+        <v>0.03863292782602717</v>
       </c>
       <c r="V25" t="inlineStr"/>
       <c r="W25" t="n">
-        <v>0.5396289014954936</v>
+        <v>0.5625258423556363</v>
       </c>
       <c r="X25" t="n">
-        <v>0.0008609345866895428</v>
+        <v>0.0008392518966037371</v>
       </c>
       <c r="Y25" t="inlineStr"/>
       <c r="Z25" t="n">
-        <v>0.891680711966246</v>
+        <v>0.8851903906322472</v>
       </c>
       <c r="AA25" t="n">
-        <v>0.0113459747168711</v>
+        <v>0.01168094643692828</v>
       </c>
       <c r="AB25" t="inlineStr"/>
       <c r="AC25" t="n">
-        <v>0.6599589366982943</v>
+        <v>0.5179388739532054</v>
       </c>
       <c r="AD25" t="n">
-        <v>0.002857679578878689</v>
+        <v>0.003402506033728945</v>
       </c>
       <c r="AE25" t="inlineStr"/>
       <c r="AF25" t="n">
-        <v>0.9812367192575829</v>
+        <v>0.8905160488125115</v>
       </c>
       <c r="AG25" t="n">
-        <v>0.002243846283148287</v>
+        <v>0.00542018298426477</v>
       </c>
       <c r="AH25" t="inlineStr"/>
       <c r="AI25" t="n">
-        <v>0.9706334713670406</v>
+        <v>0.858321224010683</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0.001070340289688523</v>
+        <v>0.002350974698048462</v>
       </c>
       <c r="AK25" t="inlineStr"/>
       <c r="AL25" t="n">
-        <v>-0.02254649128062214</v>
+        <v>-0.01505143120291974</v>
       </c>
       <c r="AM25" t="n">
-        <v>0.003348519211457814</v>
+        <v>0.003336224627519976</v>
       </c>
       <c r="AN25" t="inlineStr"/>
     </row>
@@ -3153,25 +3153,25 @@
         <v>55</v>
       </c>
       <c r="F26" t="n">
-        <v>0.4002539035826087</v>
+        <v>0.4002539033355717</v>
       </c>
       <c r="G26" t="n">
         <v>0.05772005772005771</v>
       </c>
       <c r="H26" t="n">
-        <v>0.1994618786146296</v>
+        <v>0.199461878586617</v>
       </c>
       <c r="I26" t="n">
-        <v>0.2900964126834302</v>
+        <v>0.2900964128573777</v>
       </c>
       <c r="J26" t="n">
-        <v>0.05246774739927379</v>
+        <v>0.0524677475003759</v>
       </c>
       <c r="K26" t="n">
-        <v>0.319605401855295</v>
+        <v>0.2654673820478013</v>
       </c>
       <c r="L26" t="n">
-        <v>0.3068276294006985</v>
+        <v>0.2648773224868717</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -3180,65 +3180,65 @@
         <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>4.221808346553291</v>
+        <v>4.203760876198466</v>
       </c>
       <c r="P26" t="n">
-        <v>4.299156165421864</v>
+        <v>4.287796380406703</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.9811515580484123</v>
+        <v>0.981881702079807</v>
       </c>
       <c r="R26" t="n">
-        <v>0.0211020698554135</v>
+        <v>0.02068931092760875</v>
       </c>
       <c r="S26" t="inlineStr"/>
       <c r="T26" t="n">
-        <v>0.3137369123292557</v>
+        <v>0.3413798759521499</v>
       </c>
       <c r="U26" t="n">
-        <v>0.04068166947802393</v>
+        <v>0.03985391087389716</v>
       </c>
       <c r="V26" t="inlineStr"/>
       <c r="W26" t="n">
-        <v>-0.3054739183158917</v>
+        <v>-0.3217583309895442</v>
       </c>
       <c r="X26" t="n">
-        <v>0.000800965949823007</v>
+        <v>0.0008059460709795743</v>
       </c>
       <c r="Y26" t="inlineStr"/>
       <c r="Z26" t="n">
-        <v>0.9472173182030595</v>
+        <v>0.9476588692718971</v>
       </c>
       <c r="AA26" t="n">
-        <v>0.01240361562780566</v>
+        <v>0.01235162572699503</v>
       </c>
       <c r="AB26" t="inlineStr"/>
       <c r="AC26" t="n">
-        <v>-0.238405234485211</v>
+        <v>-0.236966017219387</v>
       </c>
       <c r="AD26" t="n">
-        <v>0.003815708295467274</v>
+        <v>0.003813490431085914</v>
       </c>
       <c r="AE26" t="inlineStr"/>
       <c r="AF26" t="n">
-        <v>0.9126467246914984</v>
+        <v>0.9082374109049972</v>
       </c>
       <c r="AG26" t="n">
-        <v>0.00395615202870477</v>
+        <v>0.004054769803590008</v>
       </c>
       <c r="AH26" t="inlineStr"/>
       <c r="AI26" t="n">
-        <v>0.9823701306252515</v>
+        <v>0.9828872426332702</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0.001129495418667469</v>
+        <v>0.001112807196600675</v>
       </c>
       <c r="AK26" t="inlineStr"/>
       <c r="AL26" t="n">
-        <v>0.4634037693418636</v>
+        <v>0.4357263571757508</v>
       </c>
       <c r="AM26" t="n">
-        <v>0.001015064242503256</v>
+        <v>0.00104091340858113</v>
       </c>
       <c r="AN26" t="inlineStr"/>
     </row>
@@ -3265,25 +3265,25 @@
         <v>67</v>
       </c>
       <c r="F27" t="n">
-        <v>0.4605706049045288</v>
+        <v>0.4605706047574397</v>
       </c>
       <c r="G27" t="n">
         <v>0.04738213693437573</v>
       </c>
       <c r="H27" t="n">
-        <v>0.2439684145997375</v>
+        <v>0.2439684149537734</v>
       </c>
       <c r="I27" t="n">
-        <v>0.174859558721163</v>
+        <v>0.1748595584867289</v>
       </c>
       <c r="J27" t="n">
-        <v>0.07321928484019485</v>
+        <v>0.07321928486768225</v>
       </c>
       <c r="K27" t="n">
-        <v>0.2452896402637705</v>
+        <v>0.1860906494832026</v>
       </c>
       <c r="L27" t="n">
-        <v>0.3101309629421319</v>
+        <v>0.2607653987707845</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
@@ -3292,65 +3292,65 @@
         <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>4.171003209011483</v>
+        <v>4.150022463863345</v>
       </c>
       <c r="P27" t="n">
-        <v>4.149301127182595</v>
+        <v>4.128570591900765</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.9964015897120301</v>
+        <v>0.9964395706014962</v>
       </c>
       <c r="R27" t="n">
-        <v>0.00973606525155314</v>
+        <v>0.009684547312754982</v>
       </c>
       <c r="S27" t="inlineStr"/>
       <c r="T27" t="n">
-        <v>0.9008776392057188</v>
+        <v>0.9021838115673453</v>
       </c>
       <c r="U27" t="n">
-        <v>0.01652749952230578</v>
+        <v>0.01641824388675052</v>
       </c>
       <c r="V27" t="inlineStr"/>
       <c r="W27" t="n">
-        <v>0.6590828011894931</v>
+        <v>0.7273096774152902</v>
       </c>
       <c r="X27" t="n">
-        <v>0.0006543294148296382</v>
+        <v>0.0005852034142300281</v>
       </c>
       <c r="Y27" t="inlineStr"/>
       <c r="Z27" t="n">
-        <v>0.9235728252701322</v>
+        <v>0.9268511346765662</v>
       </c>
       <c r="AA27" t="n">
-        <v>0.0117228544635618</v>
+        <v>0.01146867556174578</v>
       </c>
       <c r="AB27" t="inlineStr"/>
       <c r="AC27" t="n">
-        <v>0.9298164463228387</v>
+        <v>0.954722055955601</v>
       </c>
       <c r="AD27" t="n">
-        <v>0.0009687601899360537</v>
+        <v>0.0007781117179898312</v>
       </c>
       <c r="AE27" t="inlineStr"/>
       <c r="AF27" t="n">
-        <v>0.9014770953294831</v>
+        <v>0.8954597434535414</v>
       </c>
       <c r="AG27" t="n">
-        <v>0.008768388881661288</v>
+        <v>0.009032188262673085</v>
       </c>
       <c r="AH27" t="inlineStr"/>
       <c r="AI27" t="n">
-        <v>0.625950300483904</v>
+        <v>0.5861519284753167</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0.003294960315557175</v>
+        <v>0.003465819961290841</v>
       </c>
       <c r="AK27" t="inlineStr"/>
       <c r="AL27" t="n">
-        <v>0.4377434781411439</v>
+        <v>0.4409162238694539</v>
       </c>
       <c r="AM27" t="n">
-        <v>0.004882390264761079</v>
+        <v>0.004868595415099214</v>
       </c>
       <c r="AN27" t="inlineStr"/>
     </row>
@@ -3377,25 +3377,25 @@
         <v>274.6</v>
       </c>
       <c r="F28" t="n">
-        <v>0.7158795401171276</v>
+        <v>0.7158795401305122</v>
       </c>
       <c r="G28" t="n">
         <v>0.01156082729280107</v>
       </c>
       <c r="H28" t="n">
-        <v>0.1423140067580003</v>
+        <v>0.1423140067686963</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1093709740016232</v>
+        <v>0.1093709739889803</v>
       </c>
       <c r="J28" t="n">
-        <v>0.02087465183044777</v>
+        <v>0.02087465181901007</v>
       </c>
       <c r="K28" t="n">
-        <v>0.3983434145777525</v>
+        <v>0.3628997599405132</v>
       </c>
       <c r="L28" t="n">
-        <v>0.405290769298884</v>
+        <v>0.3889457506766575</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
@@ -3404,16 +3404,16 @@
         <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>4.109024811393252</v>
+        <v>4.105048742406989</v>
       </c>
       <c r="P28" t="n">
-        <v>4.290280290141594</v>
+        <v>4.285679441466086</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.9429312534649824</v>
+        <v>0.9417275840405985</v>
       </c>
       <c r="R28" t="n">
-        <v>0.02487727586192935</v>
+        <v>0.02513825730940722</v>
       </c>
       <c r="S28" t="inlineStr"/>
       <c r="T28" t="inlineStr"/>
@@ -3425,38 +3425,38 @@
       </c>
       <c r="Y28" t="inlineStr"/>
       <c r="Z28" t="n">
-        <v>0.6035707661033261</v>
+        <v>0.5942104530148915</v>
       </c>
       <c r="AA28" t="n">
-        <v>0.05159209905216341</v>
+        <v>0.05219763052410342</v>
       </c>
       <c r="AB28" t="inlineStr"/>
       <c r="AC28" t="n">
-        <v>0.8422659327249387</v>
+        <v>0.7821617319660152</v>
       </c>
       <c r="AD28" t="n">
-        <v>0.004750067642096628</v>
+        <v>0.005582183805071616</v>
       </c>
       <c r="AE28" t="inlineStr"/>
       <c r="AF28" t="n">
-        <v>0.5220856700598027</v>
+        <v>0.5395062491534799</v>
       </c>
       <c r="AG28" t="n">
-        <v>0.01155634459376397</v>
+        <v>0.01134376776304701</v>
       </c>
       <c r="AH28" t="inlineStr"/>
       <c r="AI28" t="n">
-        <v>0.4026817643609261</v>
+        <v>0.4008925018139573</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0.01679437644679514</v>
+        <v>0.01681951134692959</v>
       </c>
       <c r="AK28" t="inlineStr"/>
       <c r="AL28" t="n">
-        <v>0.9893995270751944</v>
+        <v>0.9900161165015631</v>
       </c>
       <c r="AM28" t="n">
-        <v>0.0003564398751098696</v>
+        <v>0.0003459182018541039</v>
       </c>
       <c r="AN28" t="inlineStr"/>
     </row>
@@ -3483,25 +3483,25 @@
         <v>15.1</v>
       </c>
       <c r="F29" t="n">
-        <v>0.5922072970736373</v>
+        <v>0.5922072966992186</v>
       </c>
       <c r="G29" t="n">
         <v>0.2102386208346473</v>
       </c>
       <c r="H29" t="n">
-        <v>0.01553978349820245</v>
+        <v>0.01553978410683548</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1433667741521803</v>
+        <v>0.1433667739479109</v>
       </c>
       <c r="J29" t="n">
-        <v>0.03864752444133265</v>
+        <v>0.03864752441138786</v>
       </c>
       <c r="K29" t="n">
-        <v>0.5340055862294603</v>
+        <v>0.5406426407248554</v>
       </c>
       <c r="L29" t="n">
-        <v>0.3537813427846556</v>
+        <v>0.5159633858091727</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
@@ -3510,16 +3510,16 @@
         <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>4.257333241600258</v>
+        <v>4.311389929681745</v>
       </c>
       <c r="P29" t="n">
-        <v>4.212624139423042</v>
+        <v>4.268928312171505</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.9513053116423515</v>
+        <v>0.9367424776906661</v>
       </c>
       <c r="R29" t="n">
-        <v>0.01423996307855831</v>
+        <v>0.01623021064203043</v>
       </c>
       <c r="S29" t="inlineStr"/>
       <c r="T29" t="inlineStr"/>
@@ -3531,38 +3531,38 @@
       </c>
       <c r="Y29" t="inlineStr"/>
       <c r="Z29" t="n">
-        <v>0.7860660146354843</v>
+        <v>0.7166297277960055</v>
       </c>
       <c r="AA29" t="n">
-        <v>0.03014057525530507</v>
+        <v>0.03468876108814913</v>
       </c>
       <c r="AB29" t="inlineStr"/>
       <c r="AC29" t="n">
-        <v>0.9301519174395692</v>
+        <v>0.9296525780633477</v>
       </c>
       <c r="AD29" t="n">
-        <v>0.009154115532989501</v>
+        <v>0.009186778343636718</v>
       </c>
       <c r="AE29" t="inlineStr"/>
       <c r="AF29" t="n">
-        <v>0.6855713830580368</v>
+        <v>0.6586437614714842</v>
       </c>
       <c r="AG29" t="n">
-        <v>0.00792555410044218</v>
+        <v>0.008257955166226995</v>
       </c>
       <c r="AH29" t="inlineStr"/>
       <c r="AI29" t="n">
-        <v>0.9907652346544472</v>
+        <v>0.9635099446641047</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0.00249689252581046</v>
+        <v>0.004963341723281445</v>
       </c>
       <c r="AK29" t="inlineStr"/>
       <c r="AL29" t="n">
-        <v>0.9080252017825244</v>
+        <v>0.9321117304022962</v>
       </c>
       <c r="AM29" t="n">
-        <v>0.001809942407007152</v>
+        <v>0.001554990366296473</v>
       </c>
       <c r="AN29" t="inlineStr"/>
     </row>
@@ -3589,25 +3589,25 @@
         <v>45.4</v>
       </c>
       <c r="F30" t="n">
-        <v>0.6915723419858851</v>
+        <v>0.6915723419696138</v>
       </c>
       <c r="G30" t="n">
         <v>0.06992518005733864</v>
       </c>
       <c r="H30" t="n">
-        <v>0.07335276932576335</v>
+        <v>0.07335276911610503</v>
       </c>
       <c r="I30" t="n">
-        <v>0.1459822594046087</v>
+        <v>0.1459822596625786</v>
       </c>
       <c r="J30" t="n">
-        <v>0.0191674492264043</v>
+        <v>0.01916744919436398</v>
       </c>
       <c r="K30" t="n">
-        <v>0.4943630247919258</v>
+        <v>0.4607304856375612</v>
       </c>
       <c r="L30" t="n">
-        <v>0.406758172022455</v>
+        <v>0.4540678435450236</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -3616,16 +3616,16 @@
         <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>4.508966688135797</v>
+        <v>4.513720172905545</v>
       </c>
       <c r="P30" t="n">
-        <v>4.315806399300889</v>
+        <v>4.323825850891984</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.9732717760724511</v>
+        <v>0.9730393464168864</v>
       </c>
       <c r="R30" t="n">
-        <v>0.01347568775327946</v>
+        <v>0.01353415347073175</v>
       </c>
       <c r="S30" t="inlineStr"/>
       <c r="T30" t="inlineStr"/>
@@ -3637,38 +3637,38 @@
       </c>
       <c r="Y30" t="inlineStr"/>
       <c r="Z30" t="n">
-        <v>0.8658231877362211</v>
+        <v>0.864052115532465</v>
       </c>
       <c r="AA30" t="n">
-        <v>0.02495069716126713</v>
+        <v>0.02511482619231361</v>
       </c>
       <c r="AB30" t="inlineStr"/>
       <c r="AC30" t="n">
-        <v>0.9766646459310458</v>
+        <v>0.956051277835522</v>
       </c>
       <c r="AD30" t="n">
-        <v>0.0006883979844861363</v>
+        <v>0.0009447252626868647</v>
       </c>
       <c r="AE30" t="inlineStr"/>
       <c r="AF30" t="n">
-        <v>0.08517065322587503</v>
+        <v>0.04138713278085959</v>
       </c>
       <c r="AG30" t="n">
-        <v>0.01293488357252917</v>
+        <v>0.01324079644246542</v>
       </c>
       <c r="AH30" t="inlineStr"/>
       <c r="AI30" t="n">
-        <v>0.8430311994530371</v>
+        <v>0.8632191055819859</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0.00829241214094489</v>
+        <v>0.007740819294470558</v>
       </c>
       <c r="AK30" t="inlineStr"/>
       <c r="AL30" t="n">
-        <v>0.485320244156739</v>
+        <v>0.4976543072498499</v>
       </c>
       <c r="AM30" t="n">
-        <v>0.001929433890419011</v>
+        <v>0.001906174688405254</v>
       </c>
       <c r="AN30" t="inlineStr"/>
     </row>
@@ -3695,25 +3695,25 @@
         <v>26.3</v>
       </c>
       <c r="F31" t="n">
-        <v>0.5100618132893889</v>
+        <v>0.510061813306836</v>
       </c>
       <c r="G31" t="n">
         <v>0.1207073450419458</v>
       </c>
       <c r="H31" t="n">
-        <v>0.08244690044211486</v>
+        <v>0.08244690045861332</v>
       </c>
       <c r="I31" t="n">
-        <v>0.2664816652636977</v>
+        <v>0.2664816652601923</v>
       </c>
       <c r="J31" t="n">
-        <v>0.02030227596285282</v>
+        <v>0.02030227593241257</v>
       </c>
       <c r="K31" t="n">
-        <v>0.4901448304506785</v>
+        <v>0.4758642080817636</v>
       </c>
       <c r="L31" t="n">
-        <v>0.4307390966259112</v>
+        <v>0.440730465403657</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -3722,16 +3722,16 @@
         <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>4.249026147841872</v>
+        <v>4.25445111063005</v>
       </c>
       <c r="P31" t="n">
-        <v>4.408534161760072</v>
+        <v>4.406586360079447</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.9859673610844005</v>
+        <v>0.9863371577821206</v>
       </c>
       <c r="R31" t="n">
-        <v>0.007736175110345476</v>
+        <v>0.007633560343934555</v>
       </c>
       <c r="S31" t="inlineStr"/>
       <c r="T31" t="inlineStr"/>
@@ -3743,38 +3743,38 @@
       </c>
       <c r="Y31" t="inlineStr"/>
       <c r="Z31" t="n">
-        <v>0.9455034404592624</v>
+        <v>0.9478575063333322</v>
       </c>
       <c r="AA31" t="n">
-        <v>0.01246871603733657</v>
+        <v>0.01219644018026552</v>
       </c>
       <c r="AB31" t="inlineStr"/>
       <c r="AC31" t="n">
-        <v>0.8982920028100511</v>
+        <v>0.9078559546203802</v>
       </c>
       <c r="AD31" t="n">
-        <v>0.007764238466934059</v>
+        <v>0.007390178906657691</v>
       </c>
       <c r="AE31" t="inlineStr"/>
       <c r="AF31" t="n">
-        <v>0.1038843795345048</v>
+        <v>0.06387997556877245</v>
       </c>
       <c r="AG31" t="n">
-        <v>0.008607497454891309</v>
+        <v>0.008797527826739641</v>
       </c>
       <c r="AH31" t="inlineStr"/>
       <c r="AI31" t="n">
-        <v>0.968753259220473</v>
+        <v>0.9706691252251705</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0.002773780852337383</v>
+        <v>0.002687399858427753</v>
       </c>
       <c r="AK31" t="inlineStr"/>
       <c r="AL31" t="n">
-        <v>0.05028342485048809</v>
+        <v>0.03637723251015268</v>
       </c>
       <c r="AM31" t="n">
-        <v>0.004096062156338966</v>
+        <v>0.004125941406032561</v>
       </c>
       <c r="AN31" t="inlineStr"/>
     </row>
@@ -3801,25 +3801,25 @@
         <v>32.6</v>
       </c>
       <c r="F32" t="n">
-        <v>0.6207177798737793</v>
+        <v>0.6207177798836309</v>
       </c>
       <c r="G32" t="n">
         <v>0.09738046547862497</v>
       </c>
       <c r="H32" t="n">
-        <v>0.1026556514757471</v>
+        <v>0.102655651448909</v>
       </c>
       <c r="I32" t="n">
-        <v>0.1515085776379964</v>
+        <v>0.1515085776593587</v>
       </c>
       <c r="J32" t="n">
-        <v>0.02773752553385222</v>
+        <v>0.0277375255294765</v>
       </c>
       <c r="K32" t="n">
-        <v>0.5003028185540506</v>
+        <v>0.4784031200138491</v>
       </c>
       <c r="L32" t="n">
-        <v>0.4274308509856222</v>
+        <v>0.439342754298783</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -3828,16 +3828,16 @@
         <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>4.530139452862152</v>
+        <v>4.543747350314697</v>
       </c>
       <c r="P32" t="n">
-        <v>4.426225949150417</v>
+        <v>4.42327411692884</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.9797467054705858</v>
+        <v>0.9797145492792403</v>
       </c>
       <c r="R32" t="n">
-        <v>0.01370382441077479</v>
+        <v>0.01371469888950881</v>
       </c>
       <c r="S32" t="inlineStr"/>
       <c r="T32" t="inlineStr"/>
@@ -3849,38 +3849,38 @@
       </c>
       <c r="Y32" t="inlineStr"/>
       <c r="Z32" t="n">
-        <v>0.9022466566662836</v>
+        <v>0.8829612493193515</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.008917052857534644</v>
+        <v>0.009757091318487524</v>
       </c>
       <c r="AB32" t="inlineStr"/>
       <c r="AC32" t="n">
-        <v>0.2271863060437095</v>
+        <v>0.2241076532917549</v>
       </c>
       <c r="AD32" t="n">
-        <v>0.01744997981613056</v>
+        <v>0.01748470300064492</v>
       </c>
       <c r="AE32" t="inlineStr"/>
       <c r="AF32" t="n">
-        <v>-0.5308905534094654</v>
+        <v>-0.5407369447280272</v>
       </c>
       <c r="AG32" t="n">
-        <v>0.01573490262979552</v>
+        <v>0.01578542348501133</v>
       </c>
       <c r="AH32" t="inlineStr"/>
       <c r="AI32" t="n">
-        <v>0.2304359754871046</v>
+        <v>0.2695019688636628</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0.01817663362550467</v>
+        <v>0.01770926756719963</v>
       </c>
       <c r="AK32" t="inlineStr"/>
       <c r="AL32" t="n">
-        <v>0.0737867155481069</v>
+        <v>0.07979660580422476</v>
       </c>
       <c r="AM32" t="n">
-        <v>0.004891821777688604</v>
+        <v>0.004875925263071819</v>
       </c>
       <c r="AN32" t="inlineStr"/>
     </row>
@@ -3905,25 +3905,25 @@
       </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="n">
-        <v>0.6421516036650835</v>
+        <v>0.642151603719554</v>
       </c>
       <c r="G33" t="n">
-        <v>0.002523163010079717</v>
+        <v>0.002523163255140709</v>
       </c>
       <c r="H33" t="n">
-        <v>0.2245698007084695</v>
+        <v>0.2245698005775707</v>
       </c>
       <c r="I33" t="n">
-        <v>0.1058026140953321</v>
+        <v>0.1058026139657058</v>
       </c>
       <c r="J33" t="n">
-        <v>0.02495281852103528</v>
+        <v>0.0249528184820288</v>
       </c>
       <c r="K33" t="n">
-        <v>0.2845720576653915</v>
+        <v>0.2253351707878397</v>
       </c>
       <c r="L33" t="n">
-        <v>0.309385953827798</v>
+        <v>0.2836881609170623</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
@@ -3932,16 +3932,16 @@
         <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>4.300519149462805</v>
+        <v>4.284692602034447</v>
       </c>
       <c r="P33" t="n">
-        <v>4.268926255577062</v>
+        <v>4.261159703030888</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.9652966305421057</v>
+        <v>0.9631504538818184</v>
       </c>
       <c r="R33" t="n">
-        <v>0.005909989698078893</v>
+        <v>0.006089995523445896</v>
       </c>
       <c r="S33" t="inlineStr"/>
       <c r="T33" t="inlineStr"/>
@@ -3951,38 +3951,38 @@
       <c r="X33" t="inlineStr"/>
       <c r="Y33" t="inlineStr"/>
       <c r="Z33" t="n">
-        <v>0.930858457618045</v>
+        <v>0.9266112143651719</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.0106254560993633</v>
+        <v>0.01094694410000108</v>
       </c>
       <c r="AB33" t="inlineStr"/>
       <c r="AC33" t="n">
-        <v>0.1217477747227871</v>
+        <v>-0.01301735255472813</v>
       </c>
       <c r="AD33" t="n">
-        <v>0.006014100569510049</v>
+        <v>0.006459062645712495</v>
       </c>
       <c r="AE33" t="inlineStr"/>
       <c r="AF33" t="n">
-        <v>0.8596925635331981</v>
+        <v>0.8628040376576007</v>
       </c>
       <c r="AG33" t="n">
-        <v>0.004467946433780625</v>
+        <v>0.004418127832775455</v>
       </c>
       <c r="AH33" t="inlineStr"/>
       <c r="AI33" t="n">
-        <v>0.7777413070225867</v>
+        <v>0.8298583952955196</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0.002236977416460872</v>
+        <v>0.001957210252354471</v>
       </c>
       <c r="AK33" t="inlineStr"/>
       <c r="AL33" t="n">
-        <v>0.3825736347723331</v>
+        <v>0.4530862169841673</v>
       </c>
       <c r="AM33" t="n">
-        <v>0.0007768879458624871</v>
+        <v>0.0007311815571399508</v>
       </c>
       <c r="AN33" t="inlineStr"/>
     </row>
@@ -4009,25 +4009,25 @@
         <v>26</v>
       </c>
       <c r="F34" t="n">
-        <v>0.7519633395058384</v>
+        <v>0.7519633396250179</v>
       </c>
       <c r="G34" t="n">
         <v>0.1221001221001221</v>
       </c>
       <c r="H34" t="n">
-        <v>0.01478397129559729</v>
+        <v>0.0147839710365304</v>
       </c>
       <c r="I34" t="n">
-        <v>0.1023682012617217</v>
+        <v>0.1023682013871307</v>
       </c>
       <c r="J34" t="n">
-        <v>0.008784365836720525</v>
+        <v>0.008784365851198749</v>
       </c>
       <c r="K34" t="n">
-        <v>0.5337173211659239</v>
+        <v>0.5349204065807047</v>
       </c>
       <c r="L34" t="n">
-        <v>0.4597037194164731</v>
+        <v>0.5196710249322933</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
@@ -4036,16 +4036,16 @@
         <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>4.254011730907492</v>
+        <v>4.266981556961285</v>
       </c>
       <c r="P34" t="n">
-        <v>4.289569332936278</v>
+        <v>4.30879922454559</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.884790543811793</v>
+        <v>0.9359184571647376</v>
       </c>
       <c r="R34" t="n">
-        <v>0.02366988660435418</v>
+        <v>0.01765300294935502</v>
       </c>
       <c r="S34" t="inlineStr"/>
       <c r="T34" t="inlineStr"/>
@@ -4057,38 +4057,38 @@
       </c>
       <c r="Y34" t="inlineStr"/>
       <c r="Z34" t="n">
-        <v>0.8106991218732373</v>
+        <v>0.8973782844154106</v>
       </c>
       <c r="AA34" t="n">
-        <v>0.0520844278401577</v>
+        <v>0.03834875056764673</v>
       </c>
       <c r="AB34" t="inlineStr"/>
       <c r="AC34" t="n">
-        <v>0.9906423490482188</v>
+        <v>0.9933416258310109</v>
       </c>
       <c r="AD34" t="n">
-        <v>0.00228827379840637</v>
+        <v>0.001930228243301977</v>
       </c>
       <c r="AE34" t="inlineStr"/>
       <c r="AF34" t="n">
-        <v>0.7096376348842103</v>
+        <v>0.7224700749082362</v>
       </c>
       <c r="AG34" t="n">
-        <v>0.004148328667916342</v>
+        <v>0.004055626075440664</v>
       </c>
       <c r="AH34" t="inlineStr"/>
       <c r="AI34" t="n">
-        <v>0.4581789492888363</v>
+        <v>0.4521431696809568</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0.008170851925575123</v>
+        <v>0.008216236725118377</v>
       </c>
       <c r="AK34" t="inlineStr"/>
       <c r="AL34" t="n">
-        <v>0.3318348959972142</v>
+        <v>0.1884799510435298</v>
       </c>
       <c r="AM34" t="n">
-        <v>0.0007946296113580733</v>
+        <v>0.000875734525807103</v>
       </c>
       <c r="AN34" t="inlineStr"/>
     </row>
@@ -4115,25 +4115,25 @@
         <v>74.09999999999999</v>
       </c>
       <c r="F35" t="n">
-        <v>0.687523750659823</v>
+        <v>0.6875237506860816</v>
       </c>
       <c r="G35" t="n">
         <v>0.042842148105306</v>
       </c>
       <c r="H35" t="n">
-        <v>0.2018749037744333</v>
+        <v>0.201874903841659</v>
       </c>
       <c r="I35" t="n">
-        <v>0.03464191229956181</v>
+        <v>0.03464191218332047</v>
       </c>
       <c r="J35" t="n">
-        <v>0.033117285160876</v>
+        <v>0.03311728518363292</v>
       </c>
       <c r="K35" t="n">
-        <v>0.3017567405934108</v>
+        <v>0.2503626538263644</v>
       </c>
       <c r="L35" t="n">
-        <v>0.2447387101592386</v>
+        <v>0.2453617369460943</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
@@ -4142,16 +4142,16 @@
         <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>4.047146068348874</v>
+        <v>4.042303821541178</v>
       </c>
       <c r="P35" t="n">
-        <v>4.155126683074013</v>
+        <v>4.150547923019706</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.9967899421229967</v>
+        <v>0.9960908700017697</v>
       </c>
       <c r="R35" t="n">
-        <v>0.005644304220467496</v>
+        <v>0.006228651593670391</v>
       </c>
       <c r="S35" t="inlineStr"/>
       <c r="T35" t="inlineStr"/>
@@ -4161,10 +4161,10 @@
       <c r="X35" t="inlineStr"/>
       <c r="Y35" t="inlineStr"/>
       <c r="Z35" t="n">
-        <v>0.9820833025179087</v>
+        <v>0.9736807264410772</v>
       </c>
       <c r="AA35" t="n">
-        <v>0.007304212900817048</v>
+        <v>0.008852815067839881</v>
       </c>
       <c r="AB35" t="inlineStr"/>
       <c r="AC35" t="inlineStr"/>
@@ -4173,24 +4173,24 @@
       </c>
       <c r="AE35" t="inlineStr"/>
       <c r="AF35" t="n">
-        <v>0.6763340926124476</v>
+        <v>0.658123933994359</v>
       </c>
       <c r="AG35" t="n">
-        <v>0.00849634769774184</v>
+        <v>0.008732088884506835</v>
       </c>
       <c r="AH35" t="inlineStr"/>
       <c r="AI35" t="n">
-        <v>0.7315717490061899</v>
+        <v>0.7252724679452519</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0.002093706884864355</v>
+        <v>0.002118131219592847</v>
       </c>
       <c r="AK35" t="inlineStr"/>
       <c r="AL35" t="n">
-        <v>0.5251730074787959</v>
+        <v>0.4990580597081085</v>
       </c>
       <c r="AM35" t="n">
-        <v>0.002339693194615889</v>
+        <v>0.002403172298119602</v>
       </c>
       <c r="AN35" t="inlineStr"/>
     </row>
@@ -4217,25 +4217,25 @@
         <v>46.2</v>
       </c>
       <c r="F36" t="n">
-        <v>0.6184344404805445</v>
+        <v>0.6184344404849657</v>
       </c>
       <c r="G36" t="n">
         <v>0.06871435442864013</v>
       </c>
       <c r="H36" t="n">
-        <v>0.1345326977341799</v>
+        <v>0.1345326978111002</v>
       </c>
       <c r="I36" t="n">
-        <v>0.1554100927459354</v>
+        <v>0.1554100926475006</v>
       </c>
       <c r="J36" t="n">
-        <v>0.02290841461070009</v>
+        <v>0.0229084146277933</v>
       </c>
       <c r="K36" t="n">
-        <v>0.4303510992459229</v>
+        <v>0.3952543891983995</v>
       </c>
       <c r="L36" t="n">
-        <v>0.3940041415817687</v>
+        <v>0.374846467773324</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
@@ -4244,16 +4244,16 @@
         <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>4.305403694774172</v>
+        <v>4.294431636644179</v>
       </c>
       <c r="P36" t="n">
-        <v>4.320738530966725</v>
+        <v>4.313974128141081</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.9836102967342929</v>
+        <v>0.9833676561162499</v>
       </c>
       <c r="R36" t="n">
-        <v>0.01160072774237137</v>
+        <v>0.01168628347461962</v>
       </c>
       <c r="S36" t="inlineStr"/>
       <c r="T36" t="inlineStr"/>
@@ -4265,38 +4265,38 @@
       </c>
       <c r="Y36" t="inlineStr"/>
       <c r="Z36" t="n">
-        <v>0.8065746744763604</v>
+        <v>0.7999614290772936</v>
       </c>
       <c r="AA36" t="n">
-        <v>0.01911824699751956</v>
+        <v>0.01944232826491277</v>
       </c>
       <c r="AB36" t="inlineStr"/>
       <c r="AC36" t="n">
-        <v>0.367525906756115</v>
+        <v>0.3887434750196476</v>
       </c>
       <c r="AD36" t="n">
-        <v>0.008158189811100849</v>
+        <v>0.008020181463785039</v>
       </c>
       <c r="AE36" t="inlineStr"/>
       <c r="AF36" t="n">
-        <v>0.1028198803448294</v>
+        <v>0.1072239133883213</v>
       </c>
       <c r="AG36" t="n">
-        <v>0.01321520718857418</v>
+        <v>0.01318273226316066</v>
       </c>
       <c r="AH36" t="inlineStr"/>
       <c r="AI36" t="n">
-        <v>0.7311364352005947</v>
+        <v>0.7363838781743055</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0.006074526980104867</v>
+        <v>0.006014956256179966</v>
       </c>
       <c r="AK36" t="inlineStr"/>
       <c r="AL36" t="n">
-        <v>0.1631199438672212</v>
+        <v>0.1481979617625339</v>
       </c>
       <c r="AM36" t="n">
-        <v>0.004045442975723871</v>
+        <v>0.004081349744541902</v>
       </c>
       <c r="AN36" t="inlineStr"/>
     </row>
@@ -4323,25 +4323,25 @@
         <v>55</v>
       </c>
       <c r="F37" t="n">
-        <v>0.4310490712245829</v>
+        <v>0.4310490710111513</v>
       </c>
       <c r="G37" t="n">
         <v>0.05772005772005771</v>
       </c>
       <c r="H37" t="n">
-        <v>0.3585099706610048</v>
+        <v>0.3585099709374001</v>
       </c>
       <c r="I37" t="n">
-        <v>0.1452580722152676</v>
+        <v>0.1452580721451264</v>
       </c>
       <c r="J37" t="n">
-        <v>0.007462828179086988</v>
+        <v>0.007462828186264588</v>
       </c>
       <c r="K37" t="n">
-        <v>0.1033156315000568</v>
+        <v>0.05739037544262496</v>
       </c>
       <c r="L37" t="n">
-        <v>0.105989240617094</v>
+        <v>0.07228330439348842</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
@@ -4350,61 +4350,61 @@
         <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>4.2322895226395</v>
+        <v>4.220030963149969</v>
       </c>
       <c r="P37" t="n">
-        <v>4.263467469259709</v>
+        <v>4.254859614301782</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.9932355178273524</v>
+        <v>0.9930230072873667</v>
       </c>
       <c r="R37" t="n">
-        <v>0.005480321633666626</v>
+        <v>0.005565739859991835</v>
       </c>
       <c r="S37" t="inlineStr"/>
       <c r="T37" t="inlineStr"/>
       <c r="U37" t="inlineStr"/>
       <c r="V37" t="inlineStr"/>
       <c r="W37" t="n">
-        <v>0.03028582223180765</v>
+        <v>0.1026155043353122</v>
       </c>
       <c r="X37" t="n">
-        <v>0.0004212794289776973</v>
+        <v>0.0004052636591472696</v>
       </c>
       <c r="Y37" t="inlineStr"/>
       <c r="Z37" t="n">
-        <v>0.9983483979738434</v>
+        <v>0.9987582652911129</v>
       </c>
       <c r="AA37" t="n">
-        <v>0.001929489290990243</v>
+        <v>0.001673031350135655</v>
       </c>
       <c r="AB37" t="inlineStr"/>
       <c r="AC37" t="n">
-        <v>-0.5024649171995881</v>
+        <v>-0.5171799534715542</v>
       </c>
       <c r="AD37" t="n">
-        <v>0.007760966051537448</v>
+        <v>0.007798878523200177</v>
       </c>
       <c r="AE37" t="inlineStr"/>
       <c r="AF37" t="n">
-        <v>0.9137853380899765</v>
+        <v>0.9094781454965661</v>
       </c>
       <c r="AG37" t="n">
-        <v>0.009555251799096498</v>
+        <v>0.009791028018575766</v>
       </c>
       <c r="AH37" t="inlineStr"/>
       <c r="AI37" t="n">
-        <v>0.9403141793133138</v>
+        <v>0.9302063765600646</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0.002191861491347629</v>
+        <v>0.002370202181982599</v>
       </c>
       <c r="AK37" t="inlineStr"/>
       <c r="AL37" t="n">
-        <v>0.9999997601921665</v>
+        <v>0.9999993435116497</v>
       </c>
       <c r="AM37" t="n">
-        <v>4.82044827755296e-07</v>
+        <v>7.975708171174633e-07</v>
       </c>
       <c r="AN37" t="inlineStr"/>
     </row>
@@ -4431,25 +4431,25 @@
         <v>23</v>
       </c>
       <c r="F38" t="n">
-        <v>0.4115513533477569</v>
+        <v>0.4115513534924096</v>
       </c>
       <c r="G38" t="n">
         <v>0.1380262249827467</v>
       </c>
       <c r="H38" t="n">
-        <v>0.3184506857669814</v>
+        <v>0.318450685478181</v>
       </c>
       <c r="I38" t="n">
-        <v>0.1287866383384099</v>
+        <v>0.1287866384976123</v>
       </c>
       <c r="J38" t="n">
-        <v>0.003185097564105027</v>
+        <v>0.003185097549050355</v>
       </c>
       <c r="K38" t="n">
-        <v>0.1414949912042679</v>
+        <v>0.08860067203198282</v>
       </c>
       <c r="L38" t="n">
-        <v>0.1088639589686587</v>
+        <v>0.07293721235908138</v>
       </c>
       <c r="M38" t="n">
         <v>0</v>
@@ -4458,61 +4458,61 @@
         <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>4.109497407226164</v>
+        <v>4.08380765192147</v>
       </c>
       <c r="P38" t="n">
-        <v>4.195433165024799</v>
+        <v>4.186533632916368</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.9539271641807503</v>
+        <v>0.9589362293045761</v>
       </c>
       <c r="R38" t="n">
-        <v>0.01204405302805255</v>
+        <v>0.01137050096935783</v>
       </c>
       <c r="S38" t="inlineStr"/>
       <c r="T38" t="inlineStr"/>
       <c r="U38" t="inlineStr"/>
       <c r="V38" t="inlineStr"/>
       <c r="W38" t="n">
-        <v>0.1847479057418968</v>
+        <v>0.02361633944584107</v>
       </c>
       <c r="X38" t="n">
-        <v>0.001183485861193669</v>
+        <v>0.001295171752197655</v>
       </c>
       <c r="Y38" t="inlineStr"/>
       <c r="Z38" t="n">
-        <v>0.8115797081627778</v>
+        <v>0.8474225581793295</v>
       </c>
       <c r="AA38" t="n">
-        <v>0.02093605519128235</v>
+        <v>0.01883979547072534</v>
       </c>
       <c r="AB38" t="inlineStr"/>
       <c r="AC38" t="n">
-        <v>-0.3873194027207028</v>
+        <v>-0.3385750184694458</v>
       </c>
       <c r="AD38" t="n">
-        <v>0.01709559825877765</v>
+        <v>0.01679257981986883</v>
       </c>
       <c r="AE38" t="inlineStr"/>
       <c r="AF38" t="n">
-        <v>0.9651012801458784</v>
+        <v>0.9432759963134295</v>
       </c>
       <c r="AG38" t="n">
-        <v>0.004336395720794464</v>
+        <v>0.005528503570625018</v>
       </c>
       <c r="AH38" t="inlineStr"/>
       <c r="AI38" t="n">
-        <v>-1.138275440562116</v>
+        <v>-0.917704313608851</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0.004830441356116479</v>
+        <v>0.004574523254234405</v>
       </c>
       <c r="AK38" t="inlineStr"/>
       <c r="AL38" t="n">
-        <v>0.999997220570763</v>
+        <v>0.9999949787051727</v>
       </c>
       <c r="AM38" t="n">
-        <v>6.681830546054594e-07</v>
+        <v>8.98101701931208e-07</v>
       </c>
       <c r="AN38" t="inlineStr"/>
     </row>
@@ -4539,25 +4539,25 @@
         <v>48</v>
       </c>
       <c r="F39" t="n">
-        <v>0.464866072408512</v>
+        <v>0.4648660724078407</v>
       </c>
       <c r="G39" t="n">
         <v>0.06613756613756613</v>
       </c>
       <c r="H39" t="n">
-        <v>0.3147165341115007</v>
+        <v>0.3147165341147267</v>
       </c>
       <c r="I39" t="n">
-        <v>0.1215057334841287</v>
+        <v>0.1215057334732506</v>
       </c>
       <c r="J39" t="n">
-        <v>0.03277409385829239</v>
+        <v>0.03277409386661587</v>
       </c>
       <c r="K39" t="n">
-        <v>0.1514588065490762</v>
+        <v>0.09603082938732513</v>
       </c>
       <c r="L39" t="n">
-        <v>0.1342714605126339</v>
+        <v>0.0975585124493681</v>
       </c>
       <c r="M39" t="n">
         <v>0</v>
@@ -4566,16 +4566,16 @@
         <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>4.258033543989585</v>
+        <v>4.238213191185915</v>
       </c>
       <c r="P39" t="n">
-        <v>4.266349377449965</v>
+        <v>4.257540678441487</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.9827773649056697</v>
+        <v>0.9836023776255305</v>
       </c>
       <c r="R39" t="n">
-        <v>0.008784249967092275</v>
+        <v>0.008571272963500078</v>
       </c>
       <c r="S39" t="inlineStr"/>
       <c r="T39" t="inlineStr"/>
@@ -4585,38 +4585,38 @@
       <c r="X39" t="inlineStr"/>
       <c r="Y39" t="inlineStr"/>
       <c r="Z39" t="n">
-        <v>0.8822854639021227</v>
+        <v>0.8975048503453751</v>
       </c>
       <c r="AA39" t="n">
-        <v>0.01148328677211925</v>
+        <v>0.01071526262419945</v>
       </c>
       <c r="AB39" t="inlineStr"/>
       <c r="AC39" t="n">
-        <v>0.1222420223291134</v>
+        <v>0.1061210277456606</v>
       </c>
       <c r="AD39" t="n">
-        <v>0.001393862708387718</v>
+        <v>0.001406604384784172</v>
       </c>
       <c r="AE39" t="inlineStr"/>
       <c r="AF39" t="n">
-        <v>-0.06332093944888362</v>
+        <v>-0.05969536745992166</v>
       </c>
       <c r="AG39" t="n">
-        <v>0.01476991972384337</v>
+        <v>0.01474471795802389</v>
       </c>
       <c r="AH39" t="inlineStr"/>
       <c r="AI39" t="n">
-        <v>0.7529487446492968</v>
+        <v>0.7587896540650656</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0.005393669392982733</v>
+        <v>0.005329528093693399</v>
       </c>
       <c r="AK39" t="inlineStr"/>
       <c r="AL39" t="n">
-        <v>-0.1190897937720492</v>
+        <v>-0.1104749122313691</v>
       </c>
       <c r="AM39" t="n">
-        <v>0.002182730150903738</v>
+        <v>0.002174312468376622</v>
       </c>
       <c r="AN39" t="inlineStr"/>
     </row>
@@ -4643,25 +4643,25 @@
         <v>70.70000000000002</v>
       </c>
       <c r="F40" t="n">
-        <v>0.4301189564620539</v>
+        <v>0.4301189564542686</v>
       </c>
       <c r="G40" t="n">
         <v>0.04490244942861631</v>
       </c>
       <c r="H40" t="n">
-        <v>0.1726240369116226</v>
+        <v>0.1726240368983525</v>
       </c>
       <c r="I40" t="n">
-        <v>0.3491894964880415</v>
+        <v>0.3491894964967999</v>
       </c>
       <c r="J40" t="n">
-        <v>0.003165060709665684</v>
+        <v>0.00316506072196271</v>
       </c>
       <c r="K40" t="n">
-        <v>0.2387698264019981</v>
+        <v>0.218083522895272</v>
       </c>
       <c r="L40" t="n">
-        <v>0.3947185557296076</v>
+        <v>0.3839114819405398</v>
       </c>
       <c r="M40" t="n">
         <v>0</v>
@@ -4670,16 +4670,16 @@
         <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>4.328495843657492</v>
+        <v>4.338385918030463</v>
       </c>
       <c r="P40" t="n">
-        <v>4.520219966400318</v>
+        <v>4.513532739244368</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.9926881436121278</v>
+        <v>0.99261655269342</v>
       </c>
       <c r="R40" t="n">
-        <v>0.005136341499494995</v>
+        <v>0.005161425396147539</v>
       </c>
       <c r="S40" t="inlineStr"/>
       <c r="T40" t="inlineStr"/>
@@ -4689,38 +4689,38 @@
       <c r="X40" t="inlineStr"/>
       <c r="Y40" t="inlineStr"/>
       <c r="Z40" t="n">
-        <v>0.9754593074877741</v>
+        <v>0.9759153087953359</v>
       </c>
       <c r="AA40" t="n">
-        <v>0.00945377168003148</v>
+        <v>0.009365527506874537</v>
       </c>
       <c r="AB40" t="inlineStr"/>
       <c r="AC40" t="n">
-        <v>0.9514586295839517</v>
+        <v>0.9662876340892759</v>
       </c>
       <c r="AD40" t="n">
-        <v>0.0005012316091013193</v>
+        <v>0.000417712094919103</v>
       </c>
       <c r="AE40" t="inlineStr"/>
       <c r="AF40" t="n">
-        <v>0.9783357616732288</v>
+        <v>0.9829489635023324</v>
       </c>
       <c r="AG40" t="n">
-        <v>0.003697047360852378</v>
+        <v>0.0032798855802066</v>
       </c>
       <c r="AH40" t="inlineStr"/>
       <c r="AI40" t="n">
-        <v>0.9923511690346821</v>
+        <v>0.9894701367647508</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0.003927572614426075</v>
+        <v>0.004608271487346084</v>
       </c>
       <c r="AK40" t="inlineStr"/>
       <c r="AL40" t="n">
-        <v>0.9999996572715453</v>
+        <v>0.9999992243000642</v>
       </c>
       <c r="AM40" t="n">
-        <v>3.559564027537347e-07</v>
+        <v>5.35511252289457e-07</v>
       </c>
       <c r="AN40" t="inlineStr"/>
     </row>
@@ -4747,25 +4747,25 @@
         <v>84.84</v>
       </c>
       <c r="F41" t="n">
-        <v>0.3369254806988865</v>
+        <v>0.3369254807409055</v>
       </c>
       <c r="G41" t="n">
         <v>0.03741870785718027</v>
       </c>
       <c r="H41" t="n">
-        <v>0.2464337952095151</v>
+        <v>0.2464337951089697</v>
       </c>
       <c r="I41" t="n">
-        <v>0.3649923484168429</v>
+        <v>0.3649923484758453</v>
       </c>
       <c r="J41" t="n">
-        <v>0.01422966781757511</v>
+        <v>0.0142296678170992</v>
       </c>
       <c r="K41" t="n">
-        <v>0.2578829215911677</v>
+        <v>0.195968443087551</v>
       </c>
       <c r="L41" t="n">
-        <v>0.2872185104656401</v>
+        <v>0.245853781485187</v>
       </c>
       <c r="M41" t="n">
         <v>0</v>
@@ -4774,16 +4774,16 @@
         <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>4.435301806859223</v>
+        <v>4.44269170170953</v>
       </c>
       <c r="P41" t="n">
-        <v>4.505579336452995</v>
+        <v>4.502759565677078</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.9938802461812383</v>
+        <v>0.9936493883636396</v>
       </c>
       <c r="R41" t="n">
-        <v>0.006062922015975779</v>
+        <v>0.006176220373786573</v>
       </c>
       <c r="S41" t="inlineStr"/>
       <c r="T41" t="inlineStr"/>
@@ -4793,38 +4793,38 @@
       <c r="X41" t="inlineStr"/>
       <c r="Y41" t="inlineStr"/>
       <c r="Z41" t="n">
-        <v>0.8651955792843189</v>
+        <v>0.866668683051001</v>
       </c>
       <c r="AA41" t="n">
-        <v>0.01069200835051347</v>
+        <v>0.01063342828432315</v>
       </c>
       <c r="AB41" t="inlineStr"/>
       <c r="AC41" t="n">
-        <v>0.6519294386498865</v>
+        <v>0.6752166607769611</v>
       </c>
       <c r="AD41" t="n">
-        <v>0.001471316191816905</v>
+        <v>0.001421245945982734</v>
       </c>
       <c r="AE41" t="inlineStr"/>
       <c r="AF41" t="n">
-        <v>0.981326448799946</v>
+        <v>0.9741347597593044</v>
       </c>
       <c r="AG41" t="n">
-        <v>0.00366399033495248</v>
+        <v>0.004312202225055366</v>
       </c>
       <c r="AH41" t="inlineStr"/>
       <c r="AI41" t="n">
-        <v>0.9491777690507551</v>
+        <v>0.9461313588175961</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0.007268043602594663</v>
+        <v>0.007482705826813548</v>
       </c>
       <c r="AK41" t="inlineStr"/>
       <c r="AL41" t="n">
-        <v>0.9001785172172251</v>
+        <v>0.9010471058021745</v>
       </c>
       <c r="AM41" t="n">
-        <v>0.001030543532037453</v>
+        <v>0.001026050140423945</v>
       </c>
       <c r="AN41" t="inlineStr"/>
     </row>
@@ -4851,25 +4851,25 @@
         <v>124.31</v>
       </c>
       <c r="F42" t="n">
-        <v>0.4255446328458828</v>
+        <v>0.4255446328415167</v>
       </c>
       <c r="G42" t="n">
         <v>0.02553779401981477</v>
       </c>
       <c r="H42" t="n">
-        <v>0.2146647956812922</v>
+        <v>0.214664795708344</v>
       </c>
       <c r="I42" t="n">
-        <v>0.3235805049574504</v>
+        <v>0.3235805049438804</v>
       </c>
       <c r="J42" t="n">
-        <v>0.01067227249555984</v>
+        <v>0.01067227248644411</v>
       </c>
       <c r="K42" t="n">
-        <v>0.277385678721059</v>
+        <v>0.1441683716926044</v>
       </c>
       <c r="L42" t="n">
-        <v>0.4374622634848779</v>
+        <v>0.3883846994920952</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
@@ -4878,16 +4878,16 @@
         <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>4.541320208590085</v>
+        <v>2.686505160363577</v>
       </c>
       <c r="P42" t="n">
-        <v>4.559328256640657</v>
+        <v>4.43739274358984</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.96449826283581</v>
+        <v>0.9567736905082446</v>
       </c>
       <c r="R42" t="n">
-        <v>0.01247740136124769</v>
+        <v>0.01376808131936453</v>
       </c>
       <c r="S42" t="inlineStr"/>
       <c r="T42" t="inlineStr"/>
@@ -4897,31 +4897,31 @@
       <c r="X42" t="inlineStr"/>
       <c r="Y42" t="inlineStr"/>
       <c r="Z42" t="n">
-        <v>0.82226935784296</v>
+        <v>0.8066681781172742</v>
       </c>
       <c r="AA42" t="n">
-        <v>0.02313520593773982</v>
+        <v>0.02412925351981513</v>
       </c>
       <c r="AB42" t="inlineStr"/>
       <c r="AC42" t="n">
-        <v>0.996102554969613</v>
+        <v>0.9541721668031266</v>
       </c>
       <c r="AD42" t="n">
-        <v>0.0003336724868591206</v>
+        <v>0.00114418186675509</v>
       </c>
       <c r="AE42" t="inlineStr"/>
       <c r="AF42" t="n">
-        <v>0.8521008393374599</v>
+        <v>0.7275200541578014</v>
       </c>
       <c r="AG42" t="n">
-        <v>0.01122405877434713</v>
+        <v>0.01523471555443897</v>
       </c>
       <c r="AH42" t="inlineStr"/>
       <c r="AI42" t="n">
-        <v>0.9860836589571182</v>
+        <v>0.9939348494105537</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0.003648119243541842</v>
+        <v>0.002408392620199177</v>
       </c>
       <c r="AK42" t="inlineStr"/>
       <c r="AL42" t="inlineStr"/>
@@ -4953,25 +4953,25 @@
         <v>40.1</v>
       </c>
       <c r="F43" t="n">
-        <v>0.5997176448026437</v>
+        <v>0.5997176446896944</v>
       </c>
       <c r="G43" t="n">
         <v>0.0791671614614258</v>
       </c>
       <c r="H43" t="n">
-        <v>0.2378772798847145</v>
+        <v>0.2378772801295146</v>
       </c>
       <c r="I43" t="n">
-        <v>0.05923193023736853</v>
+        <v>0.05923193014095748</v>
       </c>
       <c r="J43" t="n">
-        <v>0.0240059836138475</v>
+        <v>0.02400598357840774</v>
       </c>
       <c r="K43" t="n">
-        <v>0.1503222139950793</v>
+        <v>0.1272625710749766</v>
       </c>
       <c r="L43" t="n">
-        <v>0.3672857730929937</v>
+        <v>0.2924639470468462</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
@@ -4980,16 +4980,16 @@
         <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>4.014610252289849</v>
+        <v>3.9221433094044</v>
       </c>
       <c r="P43" t="n">
-        <v>4.250246286412207</v>
+        <v>4.223879978955339</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.9515311207326109</v>
+        <v>0.9546074402960421</v>
       </c>
       <c r="R43" t="n">
-        <v>0.01345186886574083</v>
+        <v>0.0130179761885285</v>
       </c>
       <c r="S43" t="inlineStr"/>
       <c r="T43" t="inlineStr"/>
@@ -4999,38 +4999,38 @@
       <c r="X43" t="inlineStr"/>
       <c r="Y43" t="inlineStr"/>
       <c r="Z43" t="n">
-        <v>0.8984392778677907</v>
+        <v>0.9236313390030888</v>
       </c>
       <c r="AA43" t="n">
-        <v>0.02740734784356515</v>
+        <v>0.02376630736544756</v>
       </c>
       <c r="AB43" t="inlineStr"/>
       <c r="AC43" t="n">
-        <v>0.7284211376014068</v>
+        <v>0.8021650271220314</v>
       </c>
       <c r="AD43" t="n">
-        <v>0.002461111682005627</v>
+        <v>0.002100558946532184</v>
       </c>
       <c r="AE43" t="inlineStr"/>
       <c r="AF43" t="n">
-        <v>0.8587680447637261</v>
+        <v>0.7264258538162475</v>
       </c>
       <c r="AG43" t="n">
-        <v>0.01190957284303482</v>
+        <v>0.01657552246093934</v>
       </c>
       <c r="AH43" t="inlineStr"/>
       <c r="AI43" t="n">
-        <v>0.826255233323128</v>
+        <v>0.9060851494752681</v>
       </c>
       <c r="AJ43" t="n">
-        <v>0.002336630369978089</v>
+        <v>0.001717913476270159</v>
       </c>
       <c r="AK43" t="inlineStr"/>
       <c r="AL43" t="n">
-        <v>0.9844027960266217</v>
+        <v>0.9753286219630812</v>
       </c>
       <c r="AM43" t="n">
-        <v>0.0004963129924761006</v>
+        <v>0.0006242074844447039</v>
       </c>
       <c r="AN43" t="inlineStr"/>
     </row>
@@ -5057,25 +5057,25 @@
         <v>25.2</v>
       </c>
       <c r="F44" t="n">
-        <v>0.3587984910438237</v>
+        <v>0.3587984911488203</v>
       </c>
       <c r="G44" t="n">
         <v>0.1259763164525069</v>
       </c>
       <c r="H44" t="n">
-        <v>0.2964643700107539</v>
+        <v>0.2964643700757857</v>
       </c>
       <c r="I44" t="n">
-        <v>0.1968371786437586</v>
+        <v>0.1968371786061268</v>
       </c>
       <c r="J44" t="n">
-        <v>0.02192364384915694</v>
+        <v>0.02192364371676016</v>
       </c>
       <c r="K44" t="n">
-        <v>0.1750004298657557</v>
+        <v>0.1168265495049782</v>
       </c>
       <c r="L44" t="n">
-        <v>0.3271453757894115</v>
+        <v>0.2994081960988988</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
@@ -5084,16 +5084,16 @@
         <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>4.26677501303533</v>
+        <v>4.250053691127665</v>
       </c>
       <c r="P44" t="n">
-        <v>4.389336156098157</v>
+        <v>4.370005680540043</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.9436990976759149</v>
+        <v>0.9347306317150316</v>
       </c>
       <c r="R44" t="n">
-        <v>0.008081822512133931</v>
+        <v>0.008701744665127126</v>
       </c>
       <c r="S44" t="inlineStr"/>
       <c r="T44" t="inlineStr"/>
@@ -5103,38 +5103,38 @@
       <c r="X44" t="inlineStr"/>
       <c r="Y44" t="inlineStr"/>
       <c r="Z44" t="n">
-        <v>0.9160532059420502</v>
+        <v>0.9123185714714283</v>
       </c>
       <c r="AA44" t="n">
-        <v>0.01299266521197464</v>
+        <v>0.01327852999748711</v>
       </c>
       <c r="AB44" t="inlineStr"/>
       <c r="AC44" t="n">
-        <v>0.8046322025389985</v>
+        <v>0.8018588932526468</v>
       </c>
       <c r="AD44" t="n">
-        <v>0.004902053065829957</v>
+        <v>0.004936723576667084</v>
       </c>
       <c r="AE44" t="inlineStr"/>
       <c r="AF44" t="n">
-        <v>0.9424598499734625</v>
+        <v>0.9160373553013601</v>
       </c>
       <c r="AG44" t="n">
-        <v>0.008389745416451655</v>
+        <v>0.01013459370535977</v>
       </c>
       <c r="AH44" t="inlineStr"/>
       <c r="AI44" t="n">
-        <v>0.8693015582673569</v>
+        <v>0.8437560386802269</v>
       </c>
       <c r="AJ44" t="n">
-        <v>0.007853807024223858</v>
+        <v>0.008587102389063305</v>
       </c>
       <c r="AK44" t="inlineStr"/>
       <c r="AL44" t="n">
-        <v>0.627820126103811</v>
+        <v>0.6739174048644032</v>
       </c>
       <c r="AM44" t="n">
-        <v>0.001292164498384604</v>
+        <v>0.001209498038767343</v>
       </c>
       <c r="AN44" t="inlineStr"/>
     </row>
@@ -5161,25 +5161,25 @@
         <v>20</v>
       </c>
       <c r="F45" t="n">
-        <v>0.4805050132618147</v>
+        <v>0.4805050130472089</v>
       </c>
       <c r="G45" t="n">
         <v>0.1587301587301587</v>
       </c>
       <c r="H45" t="n">
-        <v>0.1510431451475349</v>
+        <v>0.1510431452397918</v>
       </c>
       <c r="I45" t="n">
-        <v>0.1848438942219129</v>
+        <v>0.1848438943574318</v>
       </c>
       <c r="J45" t="n">
-        <v>0.02487778863857871</v>
+        <v>0.02487778862540869</v>
       </c>
       <c r="K45" t="n">
-        <v>0.3970700662958236</v>
+        <v>0.3530798955686953</v>
       </c>
       <c r="L45" t="n">
-        <v>0.3275258470037932</v>
+        <v>0.438882466947964</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
@@ -5188,16 +5188,16 @@
         <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>4.224020019874794</v>
+        <v>4.170472779500921</v>
       </c>
       <c r="P45" t="n">
-        <v>4.375440194607536</v>
+        <v>4.431580090448737</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.9687751708200327</v>
+        <v>0.9704543770865897</v>
       </c>
       <c r="R45" t="n">
-        <v>0.008629986787395804</v>
+        <v>0.008394728800950511</v>
       </c>
       <c r="S45" t="inlineStr"/>
       <c r="T45" t="inlineStr"/>
@@ -5207,38 +5207,38 @@
       <c r="X45" t="inlineStr"/>
       <c r="Y45" t="inlineStr"/>
       <c r="Z45" t="n">
-        <v>0.9762472131166755</v>
+        <v>0.977866647905786</v>
       </c>
       <c r="AA45" t="n">
-        <v>0.01318213329558572</v>
+        <v>0.01272483058369885</v>
       </c>
       <c r="AB45" t="inlineStr"/>
       <c r="AC45" t="n">
-        <v>0.9229489468869232</v>
+        <v>0.9258866503986516</v>
       </c>
       <c r="AD45" t="n">
-        <v>0.007279974266374508</v>
+        <v>0.007139844867595662</v>
       </c>
       <c r="AE45" t="inlineStr"/>
       <c r="AF45" t="n">
-        <v>0.8710034196413887</v>
+        <v>0.8713113067914287</v>
       </c>
       <c r="AG45" t="n">
-        <v>0.008535058096236186</v>
+        <v>0.008524866343177898</v>
       </c>
       <c r="AH45" t="inlineStr"/>
       <c r="AI45" t="n">
-        <v>0.9218406137914298</v>
+        <v>0.9282568240875458</v>
       </c>
       <c r="AJ45" t="n">
-        <v>0.008507902407658757</v>
+        <v>0.008151212755507172</v>
       </c>
       <c r="AK45" t="inlineStr"/>
       <c r="AL45" t="n">
-        <v>0.9800276216909577</v>
+        <v>0.9822076343583939</v>
       </c>
       <c r="AM45" t="n">
-        <v>0.000620545024227616</v>
+        <v>0.0005857000390816052</v>
       </c>
       <c r="AN45" t="inlineStr"/>
     </row>
@@ -5265,25 +5265,25 @@
         <v>13.8</v>
       </c>
       <c r="F46" t="n">
-        <v>0.4123104193140011</v>
+        <v>0.4123104194730447</v>
       </c>
       <c r="G46" t="n">
         <v>0.2300437083045778</v>
       </c>
       <c r="H46" t="n">
-        <v>0.09500900007204896</v>
+        <v>0.09500899989902098</v>
       </c>
       <c r="I46" t="n">
-        <v>0.2190898484594311</v>
+        <v>0.2190898485295714</v>
       </c>
       <c r="J46" t="n">
-        <v>0.04354702384994095</v>
+        <v>0.04354702379378513</v>
       </c>
       <c r="K46" t="n">
-        <v>0.4191548341898909</v>
+        <v>0.4067201208266214</v>
       </c>
       <c r="L46" t="n">
-        <v>0.4168763599596889</v>
+        <v>0.4651192217474678</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
@@ -5292,16 +5292,16 @@
         <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>3.769550246054656</v>
+        <v>3.808282305100428</v>
       </c>
       <c r="P46" t="n">
-        <v>4.474246364770191</v>
+        <v>4.464640131032324</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.9687411047786199</v>
+        <v>0.9755176126925588</v>
       </c>
       <c r="R46" t="n">
-        <v>0.008429717377463572</v>
+        <v>0.007460244894914106</v>
       </c>
       <c r="S46" t="inlineStr"/>
       <c r="T46" t="inlineStr"/>
@@ -5311,38 +5311,38 @@
       <c r="X46" t="inlineStr"/>
       <c r="Y46" t="inlineStr"/>
       <c r="Z46" t="n">
-        <v>0.9825621906838121</v>
+        <v>0.9876104445831971</v>
       </c>
       <c r="AA46" t="n">
-        <v>0.01018261717193388</v>
+        <v>0.008583043539077554</v>
       </c>
       <c r="AB46" t="inlineStr"/>
       <c r="AC46" t="n">
-        <v>0.9244883895932834</v>
+        <v>0.9394068385419058</v>
       </c>
       <c r="AD46" t="n">
-        <v>0.01019974845920663</v>
+        <v>0.009136805955219807</v>
       </c>
       <c r="AE46" t="inlineStr"/>
       <c r="AF46" t="n">
-        <v>0.9761741219411049</v>
+        <v>0.9666203419057247</v>
       </c>
       <c r="AG46" t="n">
-        <v>0.002526696065791834</v>
+        <v>0.002990676844390995</v>
       </c>
       <c r="AH46" t="inlineStr"/>
       <c r="AI46" t="n">
-        <v>0.8721008938082562</v>
+        <v>0.8984930464433223</v>
       </c>
       <c r="AJ46" t="n">
-        <v>0.0118429672374478</v>
+        <v>0.0105505395579633</v>
       </c>
       <c r="AK46" t="inlineStr"/>
       <c r="AL46" t="n">
-        <v>0.9873983451204669</v>
+        <v>0.9883591206559087</v>
       </c>
       <c r="AM46" t="n">
-        <v>0.0009695608398424529</v>
+        <v>0.000931867507585639</v>
       </c>
       <c r="AN46" t="inlineStr"/>
     </row>
@@ -5369,25 +5369,25 @@
         <v>19</v>
       </c>
       <c r="F47" t="n">
-        <v>0.4235443992070436</v>
+        <v>0.4235443991299785</v>
       </c>
       <c r="G47" t="n">
         <v>0.1670843776106934</v>
       </c>
       <c r="H47" t="n">
-        <v>0.2433419961172016</v>
+        <v>0.2433419961113411</v>
       </c>
       <c r="I47" t="n">
-        <v>0.1505472905220324</v>
+        <v>0.1505472906218897</v>
       </c>
       <c r="J47" t="n">
-        <v>0.01548193654302897</v>
+        <v>0.01548193652609739</v>
       </c>
       <c r="K47" t="n">
-        <v>0.2534470292225203</v>
+        <v>0.1898361565792907</v>
       </c>
       <c r="L47" t="n">
-        <v>0.3804221654864902</v>
+        <v>0.3169032945385671</v>
       </c>
       <c r="M47" t="n">
         <v>0</v>
@@ -5396,16 +5396,16 @@
         <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>4.285238971656212</v>
+        <v>4.207363086855939</v>
       </c>
       <c r="P47" t="n">
-        <v>4.355338806089541</v>
+        <v>4.332208809417659</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.9499675728583342</v>
+        <v>0.9422344135229537</v>
       </c>
       <c r="R47" t="n">
-        <v>0.008405931838519721</v>
+        <v>0.009032223420366551</v>
       </c>
       <c r="S47" t="inlineStr"/>
       <c r="T47" t="inlineStr"/>
@@ -5415,38 +5415,38 @@
       <c r="X47" t="inlineStr"/>
       <c r="Y47" t="inlineStr"/>
       <c r="Z47" t="n">
-        <v>0.9280134275048924</v>
+        <v>0.9340796280954476</v>
       </c>
       <c r="AA47" t="n">
-        <v>0.01478316707485817</v>
+        <v>0.01414658331459803</v>
       </c>
       <c r="AB47" t="inlineStr"/>
       <c r="AC47" t="n">
-        <v>0.8095213335784225</v>
+        <v>0.8430142070877258</v>
       </c>
       <c r="AD47" t="n">
-        <v>0.00681927485499712</v>
+        <v>0.006190777561609706</v>
       </c>
       <c r="AE47" t="inlineStr"/>
       <c r="AF47" t="n">
-        <v>0.9145169469472024</v>
+        <v>0.8168267329271227</v>
       </c>
       <c r="AG47" t="n">
-        <v>0.008717570094534379</v>
+        <v>0.01276105208855585</v>
       </c>
       <c r="AH47" t="inlineStr"/>
       <c r="AI47" t="n">
-        <v>0.9505309367183397</v>
+        <v>0.9738090136769656</v>
       </c>
       <c r="AJ47" t="n">
-        <v>0.003449281269043725</v>
+        <v>0.002509791788499669</v>
       </c>
       <c r="AK47" t="inlineStr"/>
       <c r="AL47" t="n">
-        <v>0.9012792860527055</v>
+        <v>0.915003322683424</v>
       </c>
       <c r="AM47" t="n">
-        <v>0.000600285292119425</v>
+        <v>0.0005569991512027919</v>
       </c>
       <c r="AN47" t="inlineStr"/>
     </row>
@@ -5473,25 +5473,25 @@
         <v>26.5</v>
       </c>
       <c r="F48" t="n">
-        <v>0.4466462867107708</v>
+        <v>0.4466462865765082</v>
       </c>
       <c r="G48" t="n">
         <v>0.1197963462114405</v>
       </c>
       <c r="H48" t="n">
-        <v>0.3318502634836513</v>
+        <v>0.3318502636697235</v>
       </c>
       <c r="I48" t="n">
-        <v>0.06116662707319055</v>
+        <v>0.06116662702741293</v>
       </c>
       <c r="J48" t="n">
-        <v>0.04054047652094685</v>
+        <v>0.04054047651491494</v>
       </c>
       <c r="K48" t="n">
-        <v>0.1132798991704734</v>
+        <v>0.07057579079882771</v>
       </c>
       <c r="L48" t="n">
-        <v>0.3941761000608428</v>
+        <v>0.4720007512014078</v>
       </c>
       <c r="M48" t="n">
         <v>0</v>
@@ -5500,16 +5500,16 @@
         <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>3.703826593445649</v>
+        <v>3.801459647451884</v>
       </c>
       <c r="P48" t="n">
-        <v>4.323796651864424</v>
+        <v>4.343627455556366</v>
       </c>
       <c r="Q48" t="n">
-        <v>0.9822785264617602</v>
+        <v>0.9814312171008718</v>
       </c>
       <c r="R48" t="n">
-        <v>0.006864013349149739</v>
+        <v>0.007026190546959434</v>
       </c>
       <c r="S48" t="inlineStr"/>
       <c r="T48" t="inlineStr"/>
@@ -5519,38 +5519,38 @@
       <c r="X48" t="inlineStr"/>
       <c r="Y48" t="inlineStr"/>
       <c r="Z48" t="n">
-        <v>0.9685191461319849</v>
+        <v>0.9695301940322909</v>
       </c>
       <c r="AA48" t="n">
-        <v>0.01297383824231126</v>
+        <v>0.0127638023770996</v>
       </c>
       <c r="AB48" t="inlineStr"/>
       <c r="AC48" t="n">
-        <v>0.8641702082448598</v>
+        <v>0.8525345616848152</v>
       </c>
       <c r="AD48" t="n">
-        <v>0.006225709681120688</v>
+        <v>0.006486889054935323</v>
       </c>
       <c r="AE48" t="inlineStr"/>
       <c r="AF48" t="n">
-        <v>0.993280752478491</v>
+        <v>0.9892177781084788</v>
       </c>
       <c r="AG48" t="n">
-        <v>0.004753576674794105</v>
+        <v>0.006021633461030734</v>
       </c>
       <c r="AH48" t="inlineStr"/>
       <c r="AI48" t="n">
-        <v>0.913903805183183</v>
+        <v>0.9184292895740682</v>
       </c>
       <c r="AJ48" t="n">
-        <v>0.002424761510567896</v>
+        <v>0.002360174822177773</v>
       </c>
       <c r="AK48" t="inlineStr"/>
       <c r="AL48" t="n">
-        <v>0.9997081465432875</v>
+        <v>0.9998016291181303</v>
       </c>
       <c r="AM48" t="n">
-        <v>0.0001322759577286648</v>
+        <v>0.0001090529594766197</v>
       </c>
       <c r="AN48" t="inlineStr"/>
     </row>
@@ -5577,25 +5577,25 @@
         <v>27.2</v>
       </c>
       <c r="F49" t="n">
-        <v>0.4784766675558373</v>
+        <v>0.4784766676196412</v>
       </c>
       <c r="G49" t="n">
         <v>0.1167133520074696</v>
       </c>
       <c r="H49" t="n">
-        <v>0.1617722833471003</v>
+        <v>0.1617722832354314</v>
       </c>
       <c r="I49" t="n">
-        <v>0.2200624129180908</v>
+        <v>0.2200624129775048</v>
       </c>
       <c r="J49" t="n">
-        <v>0.02297528417150188</v>
+        <v>0.0229752841599529</v>
       </c>
       <c r="K49" t="n">
-        <v>0.3104389713261222</v>
+        <v>0.3223441909441093</v>
       </c>
       <c r="L49" t="n">
-        <v>0.4651109104583399</v>
+        <v>0.4524705173230785</v>
       </c>
       <c r="M49" t="n">
         <v>0</v>
@@ -5604,16 +5604,16 @@
         <v>0</v>
       </c>
       <c r="O49" t="n">
-        <v>4.067105644874856</v>
+        <v>4.043607044971687</v>
       </c>
       <c r="P49" t="n">
-        <v>4.395360617121717</v>
+        <v>4.381750913413947</v>
       </c>
       <c r="Q49" t="n">
-        <v>0.9298662569964591</v>
+        <v>0.9259987085580834</v>
       </c>
       <c r="R49" t="n">
-        <v>0.01255274731637791</v>
+        <v>0.012894215590958</v>
       </c>
       <c r="S49" t="inlineStr"/>
       <c r="T49" t="inlineStr"/>
@@ -5623,38 +5623,38 @@
       <c r="X49" t="inlineStr"/>
       <c r="Y49" t="inlineStr"/>
       <c r="Z49" t="n">
-        <v>0.9278683796381362</v>
+        <v>0.9234620013922974</v>
       </c>
       <c r="AA49" t="n">
-        <v>0.01811613971176503</v>
+        <v>0.01866127736981387</v>
       </c>
       <c r="AB49" t="inlineStr"/>
       <c r="AC49" t="n">
-        <v>0.9281822247005073</v>
+        <v>0.9428261356784841</v>
       </c>
       <c r="AD49" t="n">
-        <v>0.002569956943272327</v>
+        <v>0.00229302424499428</v>
       </c>
       <c r="AE49" t="inlineStr"/>
       <c r="AF49" t="n">
-        <v>0.602764940493939</v>
+        <v>0.3775760053403944</v>
       </c>
       <c r="AG49" t="n">
-        <v>0.01163587047455489</v>
+        <v>0.01456526045341957</v>
       </c>
       <c r="AH49" t="inlineStr"/>
       <c r="AI49" t="n">
-        <v>0.3456108948472003</v>
+        <v>0.4531337396093245</v>
       </c>
       <c r="AJ49" t="n">
-        <v>0.01777371251000678</v>
+        <v>0.0162480290238472</v>
       </c>
       <c r="AK49" t="inlineStr"/>
       <c r="AL49" t="n">
-        <v>0.8681312853406065</v>
+        <v>0.8757974439744302</v>
       </c>
       <c r="AM49" t="n">
-        <v>0.001326571184939162</v>
+        <v>0.001287433894821116</v>
       </c>
       <c r="AN49" t="inlineStr"/>
     </row>
@@ -5681,25 +5681,25 @@
         <v>22.6</v>
       </c>
       <c r="F50" t="n">
-        <v>0.4707222729765161</v>
+        <v>0.4707222730832482</v>
       </c>
       <c r="G50" t="n">
         <v>0.1404691670178395</v>
       </c>
       <c r="H50" t="n">
-        <v>0.06718571998428063</v>
+        <v>0.06718571980350242</v>
       </c>
       <c r="I50" t="n">
-        <v>0.2979720652205344</v>
+        <v>0.2979720652617544</v>
       </c>
       <c r="J50" t="n">
-        <v>0.02365077480082941</v>
+        <v>0.02365077483365554</v>
       </c>
       <c r="K50" t="n">
-        <v>0.5041804397675377</v>
+        <v>0.4969413621409701</v>
       </c>
       <c r="L50" t="n">
-        <v>0.527911915006419</v>
+        <v>0.5553044354690182</v>
       </c>
       <c r="M50" t="n">
         <v>0</v>
@@ -5708,16 +5708,16 @@
         <v>0</v>
       </c>
       <c r="O50" t="n">
-        <v>4.245466267633814</v>
+        <v>4.269727495470134</v>
       </c>
       <c r="P50" t="n">
-        <v>4.52016536989635</v>
+        <v>4.548757021969247</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.9679338158247377</v>
+        <v>0.9678559888381575</v>
       </c>
       <c r="R50" t="n">
-        <v>0.009570953140782093</v>
+        <v>0.009582560807423363</v>
       </c>
       <c r="S50" t="inlineStr"/>
       <c r="T50" t="inlineStr"/>
@@ -5727,31 +5727,31 @@
       <c r="X50" t="inlineStr"/>
       <c r="Y50" t="inlineStr"/>
       <c r="Z50" t="n">
-        <v>0.9948739840009695</v>
+        <v>0.9891594584304694</v>
       </c>
       <c r="AA50" t="n">
-        <v>0.006023283624087662</v>
+        <v>0.008759288378582608</v>
       </c>
       <c r="AB50" t="inlineStr"/>
       <c r="AC50" t="n">
-        <v>0.9298759515224362</v>
+        <v>0.9333387564326594</v>
       </c>
       <c r="AD50" t="n">
-        <v>0.005642528247103462</v>
+        <v>0.005501447296656798</v>
       </c>
       <c r="AE50" t="inlineStr"/>
       <c r="AF50" t="n">
-        <v>0.903708506244548</v>
+        <v>0.9224738018722216</v>
       </c>
       <c r="AG50" t="n">
-        <v>0.003170343885247073</v>
+        <v>0.002844701176735095</v>
       </c>
       <c r="AH50" t="inlineStr"/>
       <c r="AI50" t="n">
-        <v>0.8068174896992218</v>
+        <v>0.8291500497736886</v>
       </c>
       <c r="AJ50" t="n">
-        <v>0.0176392803456281</v>
+        <v>0.0165883957746635</v>
       </c>
       <c r="AK50" t="inlineStr"/>
       <c r="AL50" t="inlineStr"/>
@@ -5783,25 +5783,25 @@
         <v>12.2</v>
       </c>
       <c r="F51" t="n">
-        <v>0.4132915616414226</v>
+        <v>0.4132915619983448</v>
       </c>
       <c r="G51" t="n">
         <v>0.2602133749674733</v>
       </c>
       <c r="H51" t="n">
-        <v>0.02750138666645612</v>
+        <v>0.02750138682641973</v>
       </c>
       <c r="I51" t="n">
-        <v>0.2472592619614906</v>
+        <v>0.247259261508163</v>
       </c>
       <c r="J51" t="n">
-        <v>0.05173441476315732</v>
+        <v>0.05173441469959904</v>
       </c>
       <c r="K51" t="n">
-        <v>0.4031377924515371</v>
+        <v>0.4799319100595422</v>
       </c>
       <c r="L51" t="n">
-        <v>0.4642404432382035</v>
+        <v>0.5530320514064616</v>
       </c>
       <c r="M51" t="n">
         <v>0</v>
@@ -5810,16 +5810,16 @@
         <v>0</v>
       </c>
       <c r="O51" t="n">
-        <v>3.865900326542421</v>
+        <v>3.888757795315895</v>
       </c>
       <c r="P51" t="n">
-        <v>4.478713032460986</v>
+        <v>4.438191855078272</v>
       </c>
       <c r="Q51" t="n">
-        <v>0.8675421474075706</v>
+        <v>0.9380349752801062</v>
       </c>
       <c r="R51" t="n">
-        <v>0.01461680841000908</v>
+        <v>0.009997398720551878</v>
       </c>
       <c r="S51" t="inlineStr"/>
       <c r="T51" t="inlineStr"/>
@@ -5829,38 +5829,38 @@
       <c r="X51" t="inlineStr"/>
       <c r="Y51" t="inlineStr"/>
       <c r="Z51" t="n">
-        <v>0.8598963308920591</v>
+        <v>0.9533882300368478</v>
       </c>
       <c r="AA51" t="n">
-        <v>0.02212907256804585</v>
+        <v>0.01276398414948861</v>
       </c>
       <c r="AB51" t="inlineStr"/>
       <c r="AC51" t="n">
-        <v>0.688740154067252</v>
+        <v>0.7884320000375069</v>
       </c>
       <c r="AD51" t="n">
-        <v>0.0178140782121412</v>
+        <v>0.01468678698328693</v>
       </c>
       <c r="AE51" t="inlineStr"/>
       <c r="AF51" t="n">
-        <v>-1.472993427367163</v>
+        <v>-1.162343268271194</v>
       </c>
       <c r="AG51" t="n">
-        <v>0.003945006015510731</v>
+        <v>0.003688913822760039</v>
       </c>
       <c r="AH51" t="inlineStr"/>
       <c r="AI51" t="n">
-        <v>0.7623492897775955</v>
+        <v>0.8960340585384622</v>
       </c>
       <c r="AJ51" t="n">
-        <v>0.01565177193091006</v>
+        <v>0.01035236312321744</v>
       </c>
       <c r="AK51" t="inlineStr"/>
       <c r="AL51" t="n">
-        <v>0.9901236661944122</v>
+        <v>0.9950500031188587</v>
       </c>
       <c r="AM51" t="n">
-        <v>0.0008229022814392934</v>
+        <v>0.0005825763477143982</v>
       </c>
       <c r="AN51" t="inlineStr"/>
     </row>
@@ -5887,25 +5887,25 @@
         <v>28.5</v>
       </c>
       <c r="F52" t="n">
-        <v>0.4153806106757402</v>
+        <v>0.4153806106021484</v>
       </c>
       <c r="G52" t="n">
         <v>0.1113895850737956</v>
       </c>
       <c r="H52" t="n">
-        <v>0.3106906626687218</v>
+        <v>0.3106906628036006</v>
       </c>
       <c r="I52" t="n">
-        <v>0.1579071580203451</v>
+        <v>0.1579071579734052</v>
       </c>
       <c r="J52" t="n">
-        <v>0.004631983561397277</v>
+        <v>0.004631983547050241</v>
       </c>
       <c r="K52" t="n">
-        <v>0.1606943136811414</v>
+        <v>0.1030582047638746</v>
       </c>
       <c r="L52" t="n">
-        <v>0.3250751776916631</v>
+        <v>0.2453096720579171</v>
       </c>
       <c r="M52" t="n">
         <v>0</v>
@@ -5914,16 +5914,16 @@
         <v>0</v>
       </c>
       <c r="O52" t="n">
-        <v>4.367592709598685</v>
+        <v>4.3471512475704</v>
       </c>
       <c r="P52" t="n">
-        <v>4.305155024986907</v>
+        <v>4.280027701675652</v>
       </c>
       <c r="Q52" t="n">
-        <v>0.9535533906622496</v>
+        <v>0.9476854399683274</v>
       </c>
       <c r="R52" t="n">
-        <v>0.01040711306755313</v>
+        <v>0.01104497033751219</v>
       </c>
       <c r="S52" t="inlineStr"/>
       <c r="T52" t="inlineStr"/>
@@ -5933,38 +5933,38 @@
       <c r="X52" t="inlineStr"/>
       <c r="Y52" t="inlineStr"/>
       <c r="Z52" t="n">
-        <v>0.9383978124110627</v>
+        <v>0.9203373852114963</v>
       </c>
       <c r="AA52" t="n">
-        <v>0.01136563283225358</v>
+        <v>0.01292477028628217</v>
       </c>
       <c r="AB52" t="inlineStr"/>
       <c r="AC52" t="n">
-        <v>0.9006945621791339</v>
+        <v>0.8765969541237223</v>
       </c>
       <c r="AD52" t="n">
-        <v>0.002229254395263897</v>
+        <v>0.002485055290944442</v>
       </c>
       <c r="AE52" t="inlineStr"/>
       <c r="AF52" t="n">
-        <v>0.8134869125326483</v>
+        <v>0.8138331205181377</v>
       </c>
       <c r="AG52" t="n">
-        <v>0.01550797518812517</v>
+        <v>0.01549357545635527</v>
       </c>
       <c r="AH52" t="inlineStr"/>
       <c r="AI52" t="n">
-        <v>0.3887951259275094</v>
+        <v>0.2796267424050218</v>
       </c>
       <c r="AJ52" t="n">
-        <v>0.01288900459740433</v>
+        <v>0.01399280449607417</v>
       </c>
       <c r="AK52" t="inlineStr"/>
       <c r="AL52" t="n">
-        <v>0.1725753582760886</v>
+        <v>0.0508858028980399</v>
       </c>
       <c r="AM52" t="n">
-        <v>0.0008769796008777883</v>
+        <v>0.0009392571230924022</v>
       </c>
       <c r="AN52" t="inlineStr"/>
     </row>
@@ -5991,25 +5991,25 @@
         <v>26.8</v>
       </c>
       <c r="F53" t="n">
-        <v>0.4510893860666219</v>
+        <v>0.4510893861537268</v>
       </c>
       <c r="G53" t="n">
         <v>0.1184553423359393</v>
       </c>
       <c r="H53" t="n">
-        <v>0.200863297038614</v>
+        <v>0.2008632968133135</v>
       </c>
       <c r="I53" t="n">
-        <v>0.2264019040843809</v>
+        <v>0.2264019042000988</v>
       </c>
       <c r="J53" t="n">
-        <v>0.00319007047444387</v>
+        <v>0.003190070496921492</v>
       </c>
       <c r="K53" t="n">
-        <v>0.3301843999480366</v>
+        <v>0.2718345787311342</v>
       </c>
       <c r="L53" t="n">
-        <v>0.2246818306660378</v>
+        <v>0.2634149802841641</v>
       </c>
       <c r="M53" t="n">
         <v>0</v>
@@ -6018,16 +6018,16 @@
         <v>0</v>
       </c>
       <c r="O53" t="n">
-        <v>4.382101377750191</v>
+        <v>4.337572452346413</v>
       </c>
       <c r="P53" t="n">
-        <v>4.425804736657819</v>
+        <v>4.430537292061633</v>
       </c>
       <c r="Q53" t="n">
-        <v>0.9866128000843535</v>
+        <v>0.9855847065833223</v>
       </c>
       <c r="R53" t="n">
-        <v>0.004974596558670659</v>
+        <v>0.00516208003826434</v>
       </c>
       <c r="S53" t="inlineStr"/>
       <c r="T53" t="inlineStr"/>
@@ -6037,38 +6037,38 @@
       <c r="X53" t="inlineStr"/>
       <c r="Y53" t="inlineStr"/>
       <c r="Z53" t="n">
-        <v>0.9818876075911982</v>
+        <v>0.9758571800734815</v>
       </c>
       <c r="AA53" t="n">
-        <v>0.007799778186486004</v>
+        <v>0.009005095866673571</v>
       </c>
       <c r="AB53" t="inlineStr"/>
       <c r="AC53" t="n">
-        <v>0.9134016594240653</v>
+        <v>0.9339715887437132</v>
       </c>
       <c r="AD53" t="n">
-        <v>0.003020886998816808</v>
+        <v>0.002637819769958912</v>
       </c>
       <c r="AE53" t="inlineStr"/>
       <c r="AF53" t="n">
-        <v>0.9708082074032175</v>
+        <v>0.9694189581196966</v>
       </c>
       <c r="AG53" t="n">
-        <v>0.004218210915134934</v>
+        <v>0.00431741749530783</v>
       </c>
       <c r="AH53" t="inlineStr"/>
       <c r="AI53" t="n">
-        <v>0.964875161225224</v>
+        <v>0.9765670210422174</v>
       </c>
       <c r="AJ53" t="n">
-        <v>0.00545783318243831</v>
+        <v>0.00445786424728602</v>
       </c>
       <c r="AK53" t="inlineStr"/>
       <c r="AL53" t="n">
-        <v>0.9805745190653832</v>
+        <v>0.9245965504993117</v>
       </c>
       <c r="AM53" t="n">
-        <v>6.172506150984947e-05</v>
+        <v>0.0001216105482566218</v>
       </c>
       <c r="AN53" t="inlineStr"/>
     </row>
@@ -6095,25 +6095,25 @@
         <v>25</v>
       </c>
       <c r="F54" t="n">
-        <v>0.4286683890706328</v>
+        <v>0.4286683889482371</v>
       </c>
       <c r="G54" t="n">
         <v>0.1269841269841269</v>
       </c>
       <c r="H54" t="n">
-        <v>0.2576179527120835</v>
+        <v>0.2576179529315623</v>
       </c>
       <c r="I54" t="n">
-        <v>0.1597790966902238</v>
+        <v>0.15977909662141</v>
       </c>
       <c r="J54" t="n">
-        <v>0.02695043454293275</v>
+        <v>0.02695043451466368</v>
       </c>
       <c r="K54" t="n">
-        <v>0.1364187938617844</v>
+        <v>0.1304722568169745</v>
       </c>
       <c r="L54" t="n">
-        <v>0.4098822051400439</v>
+        <v>0.3930748436041146</v>
       </c>
       <c r="M54" t="n">
         <v>0</v>
@@ -6122,16 +6122,16 @@
         <v>0</v>
       </c>
       <c r="O54" t="n">
-        <v>4.231856710657762</v>
+        <v>4.211287370114428</v>
       </c>
       <c r="P54" t="n">
-        <v>4.305667743057564</v>
+        <v>4.290894549984938</v>
       </c>
       <c r="Q54" t="n">
-        <v>0.9288941463766474</v>
+        <v>0.9080160558447211</v>
       </c>
       <c r="R54" t="n">
-        <v>0.009682867547932756</v>
+        <v>0.01101304281984711</v>
       </c>
       <c r="S54" t="inlineStr"/>
       <c r="T54" t="inlineStr"/>
@@ -6141,38 +6141,38 @@
       <c r="X54" t="inlineStr"/>
       <c r="Y54" t="inlineStr"/>
       <c r="Z54" t="n">
-        <v>0.8720243980738971</v>
+        <v>0.8472280242052882</v>
       </c>
       <c r="AA54" t="n">
-        <v>0.01843123599311068</v>
+        <v>0.02013783215476568</v>
       </c>
       <c r="AB54" t="inlineStr"/>
       <c r="AC54" t="n">
-        <v>0.5001013526306184</v>
+        <v>0.490768253633562</v>
       </c>
       <c r="AD54" t="n">
-        <v>0.00407739592881935</v>
+        <v>0.004115282367107684</v>
       </c>
       <c r="AE54" t="inlineStr"/>
       <c r="AF54" t="n">
-        <v>0.9208704566414408</v>
+        <v>0.8549311048339701</v>
       </c>
       <c r="AG54" t="n">
-        <v>0.008342302583320553</v>
+        <v>0.01129545580934411</v>
       </c>
       <c r="AH54" t="inlineStr"/>
       <c r="AI54" t="n">
-        <v>0.7463344680877373</v>
+        <v>0.6632987986491015</v>
       </c>
       <c r="AJ54" t="n">
-        <v>0.006453689547740568</v>
+        <v>0.007435320181383121</v>
       </c>
       <c r="AK54" t="inlineStr"/>
       <c r="AL54" t="n">
-        <v>0.8606133132805542</v>
+        <v>0.8736848126798372</v>
       </c>
       <c r="AM54" t="n">
-        <v>0.001099945812148236</v>
+        <v>0.001047100646480257</v>
       </c>
       <c r="AN54" t="inlineStr"/>
     </row>
@@ -6199,25 +6199,25 @@
         <v>29</v>
       </c>
       <c r="F55" t="n">
-        <v>0.4347068963260962</v>
+        <v>0.4347068963151978</v>
       </c>
       <c r="G55" t="n">
         <v>0.1094690749863163</v>
       </c>
       <c r="H55" t="n">
-        <v>0.2837256736143648</v>
+        <v>0.2837256736186445</v>
       </c>
       <c r="I55" t="n">
-        <v>0.1694315236798098</v>
+        <v>0.1694315237196296</v>
       </c>
       <c r="J55" t="n">
-        <v>0.00266683139341308</v>
+        <v>0.002666831360211718</v>
       </c>
       <c r="K55" t="n">
-        <v>0.0949000769531866</v>
+        <v>0.06740234337865918</v>
       </c>
       <c r="L55" t="n">
-        <v>0.4209794484220377</v>
+        <v>0.4409654279629999</v>
       </c>
       <c r="M55" t="n">
         <v>0</v>
@@ -6226,16 +6226,16 @@
         <v>0</v>
       </c>
       <c r="O55" t="n">
-        <v>4.425812673917372</v>
+        <v>4.447550900380855</v>
       </c>
       <c r="P55" t="n">
-        <v>4.388610012795088</v>
+        <v>4.385018365748226</v>
       </c>
       <c r="Q55" t="n">
-        <v>0.8823237774824414</v>
+        <v>0.8501643592291335</v>
       </c>
       <c r="R55" t="n">
-        <v>0.01383316653496088</v>
+        <v>0.01560934971445943</v>
       </c>
       <c r="S55" t="inlineStr"/>
       <c r="T55" t="inlineStr"/>
@@ -6245,38 +6245,38 @@
       <c r="X55" t="inlineStr"/>
       <c r="Y55" t="inlineStr"/>
       <c r="Z55" t="n">
-        <v>0.7267103659389877</v>
+        <v>0.6936983736544673</v>
       </c>
       <c r="AA55" t="n">
-        <v>0.02523464360021534</v>
+        <v>0.02671531178917272</v>
       </c>
       <c r="AB55" t="inlineStr"/>
       <c r="AC55" t="n">
-        <v>0.1931560021694547</v>
+        <v>0.1387024363444129</v>
       </c>
       <c r="AD55" t="n">
-        <v>0.003932933575749521</v>
+        <v>0.004063482882645296</v>
       </c>
       <c r="AE55" t="inlineStr"/>
       <c r="AF55" t="n">
-        <v>0.7371667565614637</v>
+        <v>0.5545422244078534</v>
       </c>
       <c r="AG55" t="n">
-        <v>0.01642204855238225</v>
+        <v>0.02137915110073455</v>
       </c>
       <c r="AH55" t="inlineStr"/>
       <c r="AI55" t="n">
-        <v>0.8309366826475424</v>
+        <v>0.8501006192640108</v>
       </c>
       <c r="AJ55" t="n">
-        <v>0.005872720600430305</v>
+        <v>0.005529865471460369</v>
       </c>
       <c r="AK55" t="inlineStr"/>
       <c r="AL55" t="n">
-        <v>0.8151863357068518</v>
+        <v>0.7959368399840463</v>
       </c>
       <c r="AM55" t="n">
-        <v>0.0005956105028809999</v>
+        <v>0.0006258606000718695</v>
       </c>
       <c r="AN55" t="inlineStr"/>
     </row>
@@ -6303,25 +6303,25 @@
         <v>19.9</v>
       </c>
       <c r="F56" t="n">
-        <v>0.3573142119608926</v>
+        <v>0.3573142119374196</v>
       </c>
       <c r="G56" t="n">
         <v>0.1595277977187525</v>
       </c>
       <c r="H56" t="n">
-        <v>0.2647607177751945</v>
+        <v>0.2647607177672366</v>
       </c>
       <c r="I56" t="n">
-        <v>0.1794591218770647</v>
+        <v>0.179459121882217</v>
       </c>
       <c r="J56" t="n">
-        <v>0.03893815066809572</v>
+        <v>0.03893815069437438</v>
       </c>
       <c r="K56" t="n">
-        <v>0.2084054602031741</v>
+        <v>0.1490350938530598</v>
       </c>
       <c r="L56" t="n">
-        <v>0.3592757186724401</v>
+        <v>0.3125216993416861</v>
       </c>
       <c r="M56" t="n">
         <v>0</v>
@@ -6330,16 +6330,16 @@
         <v>0</v>
       </c>
       <c r="O56" t="n">
-        <v>4.062930613106723</v>
+        <v>4.00125006971951</v>
       </c>
       <c r="P56" t="n">
-        <v>4.324180579402618</v>
+        <v>4.299404185760473</v>
       </c>
       <c r="Q56" t="n">
-        <v>0.8306672697954849</v>
+        <v>0.8174901852503408</v>
       </c>
       <c r="R56" t="n">
-        <v>0.01207382836633396</v>
+        <v>0.01253480709345885</v>
       </c>
       <c r="S56" t="inlineStr"/>
       <c r="T56" t="inlineStr"/>
@@ -6349,38 +6349,38 @@
       <c r="X56" t="inlineStr"/>
       <c r="Y56" t="inlineStr"/>
       <c r="Z56" t="n">
-        <v>0.6192582351611474</v>
+        <v>0.6142392245008291</v>
       </c>
       <c r="AA56" t="n">
-        <v>0.02154333068974413</v>
+        <v>0.02168485993586439</v>
       </c>
       <c r="AB56" t="inlineStr"/>
       <c r="AC56" t="n">
-        <v>-0.06835646104013682</v>
+        <v>-0.004804287138294061</v>
       </c>
       <c r="AD56" t="n">
-        <v>0.009059098945100728</v>
+        <v>0.008785523654689277</v>
       </c>
       <c r="AE56" t="inlineStr"/>
       <c r="AF56" t="n">
-        <v>0.7918803514418224</v>
+        <v>0.6954007335875005</v>
       </c>
       <c r="AG56" t="n">
-        <v>0.01206135537804532</v>
+        <v>0.01459163638707931</v>
       </c>
       <c r="AH56" t="inlineStr"/>
       <c r="AI56" t="n">
-        <v>0.8368266521975809</v>
+        <v>0.8940138697282077</v>
       </c>
       <c r="AJ56" t="n">
-        <v>0.005872955389156894</v>
+        <v>0.004733219094339752</v>
       </c>
       <c r="AK56" t="inlineStr"/>
       <c r="AL56" t="n">
-        <v>0.8782279299369821</v>
+        <v>0.8723197530774978</v>
       </c>
       <c r="AM56" t="n">
-        <v>0.001654203021133236</v>
+        <v>0.001693857307511539</v>
       </c>
       <c r="AN56" t="inlineStr"/>
     </row>
@@ -6407,25 +6407,25 @@
         <v>13.4</v>
       </c>
       <c r="F57" t="n">
-        <v>0.3569988198360919</v>
+        <v>0.3569988198034146</v>
       </c>
       <c r="G57" t="n">
         <v>0.2369106846718786</v>
       </c>
       <c r="H57" t="n">
-        <v>0.1636235303975117</v>
+        <v>0.1636235302919157</v>
       </c>
       <c r="I57" t="n">
-        <v>0.2180246773556286</v>
+        <v>0.2180246774233276</v>
       </c>
       <c r="J57" t="n">
-        <v>0.02444228773888892</v>
+        <v>0.02444228780946331</v>
       </c>
       <c r="K57" t="n">
-        <v>0.3825163888057561</v>
+        <v>0.3369187868683771</v>
       </c>
       <c r="L57" t="n">
-        <v>0.4554652399335732</v>
+        <v>0.4317429546646928</v>
       </c>
       <c r="M57" t="n">
         <v>0</v>
@@ -6434,16 +6434,16 @@
         <v>0</v>
       </c>
       <c r="O57" t="n">
-        <v>4.276433697976676</v>
+        <v>4.255979924055767</v>
       </c>
       <c r="P57" t="n">
-        <v>4.373218250681789</v>
+        <v>4.360199978275563</v>
       </c>
       <c r="Q57" t="n">
-        <v>0.9029720440596852</v>
+        <v>0.8968403047892316</v>
       </c>
       <c r="R57" t="n">
-        <v>0.00947201819921026</v>
+        <v>0.009766728332298099</v>
       </c>
       <c r="S57" t="inlineStr"/>
       <c r="T57" t="inlineStr"/>
@@ -6453,38 +6453,38 @@
       <c r="X57" t="inlineStr"/>
       <c r="Y57" t="inlineStr"/>
       <c r="Z57" t="n">
-        <v>0.7789594421356788</v>
+        <v>0.7764367289373596</v>
       </c>
       <c r="AA57" t="n">
-        <v>0.01779508737129534</v>
+        <v>0.01789634602317635</v>
       </c>
       <c r="AB57" t="inlineStr"/>
       <c r="AC57" t="n">
-        <v>0.6319165373354663</v>
+        <v>0.6613530782949664</v>
       </c>
       <c r="AD57" t="n">
-        <v>0.008746476401145379</v>
+        <v>0.008389451001929902</v>
       </c>
       <c r="AE57" t="inlineStr"/>
       <c r="AF57" t="n">
-        <v>0.861946511184812</v>
+        <v>0.7122760588478749</v>
       </c>
       <c r="AG57" t="n">
-        <v>0.005704032275727567</v>
+        <v>0.00823467153110621</v>
       </c>
       <c r="AH57" t="inlineStr"/>
       <c r="AI57" t="n">
-        <v>0.9373334118817404</v>
+        <v>0.949724634310491</v>
       </c>
       <c r="AJ57" t="n">
-        <v>0.004606767898489069</v>
+        <v>0.004126253699102189</v>
       </c>
       <c r="AK57" t="inlineStr"/>
       <c r="AL57" t="n">
-        <v>0.6654703919347933</v>
+        <v>0.7103703286468852</v>
       </c>
       <c r="AM57" t="n">
-        <v>0.001292812890534761</v>
+        <v>0.001202928790479239</v>
       </c>
       <c r="AN57" t="inlineStr"/>
     </row>
@@ -6511,25 +6511,25 @@
         <v>26</v>
       </c>
       <c r="F58" t="n">
-        <v>0.3897461385626112</v>
+        <v>0.3897461386008995</v>
       </c>
       <c r="G58" t="n">
         <v>0.1221001221001221</v>
       </c>
       <c r="H58" t="n">
-        <v>0.2557628102080468</v>
+        <v>0.2557628103268892</v>
       </c>
       <c r="I58" t="n">
-        <v>0.2061345128303654</v>
+        <v>0.2061345125957501</v>
       </c>
       <c r="J58" t="n">
-        <v>0.02625641629885448</v>
+        <v>0.02625641637633904</v>
       </c>
       <c r="K58" t="n">
-        <v>0.07740090498216673</v>
+        <v>0.07176931293700974</v>
       </c>
       <c r="L58" t="n">
-        <v>0.4661498136188804</v>
+        <v>0.4676731929667106</v>
       </c>
       <c r="M58" t="n">
         <v>0</v>
@@ -6538,16 +6538,16 @@
         <v>0</v>
       </c>
       <c r="O58" t="n">
-        <v>4.225917546295505</v>
+        <v>4.208071932580222</v>
       </c>
       <c r="P58" t="n">
-        <v>4.40034843597916</v>
+        <v>4.392334116006208</v>
       </c>
       <c r="Q58" t="n">
-        <v>0.961413423693779</v>
+        <v>0.9541968123769429</v>
       </c>
       <c r="R58" t="n">
-        <v>0.008260158425287616</v>
+        <v>0.008999494281674134</v>
       </c>
       <c r="S58" t="inlineStr"/>
       <c r="T58" t="inlineStr"/>
@@ -6557,38 +6557,38 @@
       <c r="X58" t="inlineStr"/>
       <c r="Y58" t="inlineStr"/>
       <c r="Z58" t="n">
-        <v>0.9806674950888711</v>
+        <v>0.9759519337441472</v>
       </c>
       <c r="AA58" t="n">
-        <v>0.008067560398018214</v>
+        <v>0.008997839474636057</v>
       </c>
       <c r="AB58" t="inlineStr"/>
       <c r="AC58" t="n">
-        <v>0.972581920210899</v>
+        <v>0.9712741698420423</v>
       </c>
       <c r="AD58" t="n">
-        <v>0.001523963437372552</v>
+        <v>0.001559884073202594</v>
       </c>
       <c r="AE58" t="inlineStr"/>
       <c r="AF58" t="n">
-        <v>0.9813207375705789</v>
+        <v>0.9771044172022045</v>
       </c>
       <c r="AG58" t="n">
-        <v>0.005251385255687553</v>
+        <v>0.005813930957142151</v>
       </c>
       <c r="AH58" t="inlineStr"/>
       <c r="AI58" t="n">
-        <v>0.6269871399538081</v>
+        <v>0.5637048652347503</v>
       </c>
       <c r="AJ58" t="n">
-        <v>0.01566859776351134</v>
+        <v>0.01694565709868596</v>
       </c>
       <c r="AK58" t="inlineStr"/>
       <c r="AL58" t="n">
-        <v>0.9472956928616748</v>
+        <v>0.9519230375548007</v>
       </c>
       <c r="AM58" t="n">
-        <v>0.0008130730236359352</v>
+        <v>0.0007765599884203435</v>
       </c>
       <c r="AN58" t="inlineStr"/>
     </row>
@@ -6615,25 +6615,25 @@
         <v>10.6506024096385</v>
       </c>
       <c r="F59" t="n">
-        <v>0.4031657915982697</v>
+        <v>0.4031657917179133</v>
       </c>
       <c r="G59" t="n">
         <v>0.2980679451267702</v>
       </c>
       <c r="H59" t="n">
-        <v>0.09858303468278869</v>
+        <v>0.098583034577217</v>
       </c>
       <c r="I59" t="n">
-        <v>0.1793800069532604</v>
+        <v>0.1793800069472718</v>
       </c>
       <c r="J59" t="n">
-        <v>0.02080322163891103</v>
+        <v>0.02080322163082778</v>
       </c>
       <c r="K59" t="n">
-        <v>0.4677808511850242</v>
+        <v>0.4429337950329169</v>
       </c>
       <c r="L59" t="n">
-        <v>0.5153612643385489</v>
+        <v>0.5114740174138053</v>
       </c>
       <c r="M59" t="n">
         <v>0</v>
@@ -6642,16 +6642,16 @@
         <v>0</v>
       </c>
       <c r="O59" t="n">
-        <v>4.211580767596805</v>
+        <v>4.170892786605078</v>
       </c>
       <c r="P59" t="n">
-        <v>4.384899764120235</v>
+        <v>4.381655194938801</v>
       </c>
       <c r="Q59" t="n">
-        <v>0.7968183518500273</v>
+        <v>0.8130744715364817</v>
       </c>
       <c r="R59" t="n">
-        <v>0.01929386090102111</v>
+        <v>0.01850594266619156</v>
       </c>
       <c r="S59" t="inlineStr"/>
       <c r="T59" t="inlineStr"/>
@@ -6661,38 +6661,38 @@
       <c r="X59" t="inlineStr"/>
       <c r="Y59" t="inlineStr"/>
       <c r="Z59" t="n">
-        <v>0.7650175493332589</v>
+        <v>0.8069397210222856</v>
       </c>
       <c r="AA59" t="n">
-        <v>0.03038851763229069</v>
+        <v>0.02754471390780444</v>
       </c>
       <c r="AB59" t="inlineStr"/>
       <c r="AC59" t="n">
-        <v>0.4193090726360488</v>
+        <v>0.4250805879115527</v>
       </c>
       <c r="AD59" t="n">
-        <v>0.02354949960259279</v>
+        <v>0.02343217754817799</v>
       </c>
       <c r="AE59" t="inlineStr"/>
       <c r="AF59" t="n">
-        <v>0.3572233705470572</v>
+        <v>-0.1037890286713492</v>
       </c>
       <c r="AG59" t="n">
-        <v>0.009301085464528673</v>
+        <v>0.01218839811416335</v>
       </c>
       <c r="AH59" t="inlineStr"/>
       <c r="AI59" t="n">
-        <v>-0.886482971900695</v>
+        <v>-0.6248736759685991</v>
       </c>
       <c r="AJ59" t="n">
-        <v>0.0170370427512309</v>
+        <v>0.01581166374199917</v>
       </c>
       <c r="AK59" t="inlineStr"/>
       <c r="AL59" t="n">
-        <v>-0.5926203320188457</v>
+        <v>-0.4821114616609457</v>
       </c>
       <c r="AM59" t="n">
-        <v>0.002540352415209459</v>
+        <v>0.002450632985643054</v>
       </c>
       <c r="AN59" t="inlineStr"/>
     </row>
@@ -6719,25 +6719,25 @@
         <v>45.2784503631961</v>
       </c>
       <c r="F60" t="n">
-        <v>0.6185024514073951</v>
+        <v>0.6185024514128479</v>
       </c>
       <c r="G60" t="n">
         <v>0.07011289364230544</v>
       </c>
       <c r="H60" t="n">
-        <v>0.1901432799511997</v>
+        <v>0.1901432797896153</v>
       </c>
       <c r="I60" t="n">
-        <v>0.1060804578008114</v>
+        <v>0.1060804579527164</v>
       </c>
       <c r="J60" t="n">
-        <v>0.0151609171982884</v>
+        <v>0.015160917202515</v>
       </c>
       <c r="K60" t="n">
-        <v>0.3189569329734549</v>
+        <v>0.2695921991018025</v>
       </c>
       <c r="L60" t="n">
-        <v>0.2355319585675123</v>
+        <v>0.2153563064280021</v>
       </c>
       <c r="M60" t="n">
         <v>0</v>
@@ -6746,16 +6746,16 @@
         <v>0</v>
       </c>
       <c r="O60" t="n">
-        <v>4.034948938354199</v>
+        <v>4.021231498279722</v>
       </c>
       <c r="P60" t="n">
-        <v>4.206395293982933</v>
+        <v>4.20531273593707</v>
       </c>
       <c r="Q60" t="n">
-        <v>0.8912738908521161</v>
+        <v>0.9363902886404148</v>
       </c>
       <c r="R60" t="n">
-        <v>0.02050876301984904</v>
+        <v>0.01568679625642222</v>
       </c>
       <c r="S60" t="inlineStr"/>
       <c r="T60" t="inlineStr"/>
@@ -6765,38 +6765,38 @@
       <c r="X60" t="inlineStr"/>
       <c r="Y60" t="inlineStr"/>
       <c r="Z60" t="n">
-        <v>0.6077686094538537</v>
+        <v>0.784835337458864</v>
       </c>
       <c r="AA60" t="n">
-        <v>0.04387701686477997</v>
+        <v>0.0324976077527894</v>
       </c>
       <c r="AB60" t="inlineStr"/>
       <c r="AC60" t="n">
-        <v>-1.373376878000312</v>
+        <v>-1.457786684198819</v>
       </c>
       <c r="AD60" t="n">
-        <v>0.00816501243654</v>
+        <v>0.008308939381095335</v>
       </c>
       <c r="AE60" t="inlineStr"/>
       <c r="AF60" t="n">
-        <v>0.4574885809817287</v>
+        <v>0.458911623941109</v>
       </c>
       <c r="AG60" t="n">
-        <v>0.008123009824027607</v>
+        <v>0.008112349221362352</v>
       </c>
       <c r="AH60" t="inlineStr"/>
       <c r="AI60" t="n">
-        <v>-8.08209179734647</v>
+        <v>-6.915135659825919</v>
       </c>
       <c r="AJ60" t="n">
-        <v>0.006705459495662812</v>
+        <v>0.006259862362424788</v>
       </c>
       <c r="AK60" t="inlineStr"/>
       <c r="AL60" t="n">
-        <v>0.9362937334714371</v>
+        <v>0.9340339281176424</v>
       </c>
       <c r="AM60" t="n">
-        <v>0.0004901941772152147</v>
+        <v>0.0004988125637908041</v>
       </c>
       <c r="AN60" t="inlineStr"/>
     </row>
@@ -6823,25 +6823,25 @@
         <v>53.51961950059453</v>
       </c>
       <c r="F61" t="n">
-        <v>0.7472990942554644</v>
+        <v>0.7472990942424869</v>
       </c>
       <c r="G61" t="n">
         <v>0.05931662452435613</v>
       </c>
       <c r="H61" t="n">
-        <v>0.1189424488256474</v>
+        <v>0.1189424488653025</v>
       </c>
       <c r="I61" t="n">
-        <v>0.05728789975449577</v>
+        <v>0.05728789972030301</v>
       </c>
       <c r="J61" t="n">
-        <v>0.01715393264003622</v>
+        <v>0.01715393264755156</v>
       </c>
       <c r="K61" t="n">
-        <v>0.3156444100186744</v>
+        <v>0.226423205536829</v>
       </c>
       <c r="L61" t="n">
-        <v>0.2995950838791099</v>
+        <v>0.3349454411207358</v>
       </c>
       <c r="M61" t="n">
         <v>0</v>
@@ -6850,16 +6850,16 @@
         <v>0</v>
       </c>
       <c r="O61" t="n">
-        <v>3.852023036776635</v>
+        <v>3.899472266641207</v>
       </c>
       <c r="P61" t="n">
-        <v>4.243896250713388</v>
+        <v>4.259241686204809</v>
       </c>
       <c r="Q61" t="n">
-        <v>0.9803046701940011</v>
+        <v>0.9810480533984541</v>
       </c>
       <c r="R61" t="n">
-        <v>0.01000567929166509</v>
+        <v>0.00981503520548891</v>
       </c>
       <c r="S61" t="inlineStr"/>
       <c r="T61" t="inlineStr"/>
@@ -6871,38 +6871,38 @@
       </c>
       <c r="Y61" t="inlineStr"/>
       <c r="Z61" t="n">
-        <v>0.9667840269562797</v>
+        <v>0.9669979613265901</v>
       </c>
       <c r="AA61" t="n">
-        <v>0.02031186892674284</v>
+        <v>0.02024635185779625</v>
       </c>
       <c r="AB61" t="inlineStr"/>
       <c r="AC61" t="n">
-        <v>0.3685145298057112</v>
+        <v>0.4089569686277317</v>
       </c>
       <c r="AD61" t="n">
-        <v>0.004307702619552763</v>
+        <v>0.004167480520567869</v>
       </c>
       <c r="AE61" t="inlineStr"/>
       <c r="AF61" t="n">
-        <v>0.4196691407026517</v>
+        <v>0.5553429594502142</v>
       </c>
       <c r="AG61" t="n">
-        <v>0.007718515079348856</v>
+        <v>0.006756293568419665</v>
       </c>
       <c r="AH61" t="inlineStr"/>
       <c r="AI61" t="n">
-        <v>0.9162565081189863</v>
+        <v>0.9317152734568087</v>
       </c>
       <c r="AJ61" t="n">
-        <v>0.002313191344907636</v>
+        <v>0.002088804593008311</v>
       </c>
       <c r="AK61" t="inlineStr"/>
       <c r="AL61" t="n">
-        <v>0.239746661186565</v>
+        <v>0.2620019751575027</v>
       </c>
       <c r="AM61" t="n">
-        <v>0.002375247369829084</v>
+        <v>0.002340223166572468</v>
       </c>
       <c r="AN61" t="inlineStr"/>
     </row>
@@ -6929,25 +6929,25 @@
         <v>54.48315911730546</v>
       </c>
       <c r="F62" t="n">
-        <v>0.6806747812354861</v>
+        <v>0.6806747812675474</v>
       </c>
       <c r="G62" t="n">
         <v>0.05826760463298514</v>
       </c>
       <c r="H62" t="n">
-        <v>0.1324809677416384</v>
+        <v>0.1324809676982178</v>
       </c>
       <c r="I62" t="n">
-        <v>0.09760455450858101</v>
+        <v>0.09760455450536588</v>
       </c>
       <c r="J62" t="n">
-        <v>0.03097209188130944</v>
+        <v>0.0309720918958838</v>
       </c>
       <c r="K62" t="n">
-        <v>0.1479508876328734</v>
+        <v>0.1165417096757402</v>
       </c>
       <c r="L62" t="n">
-        <v>0.2328832249083791</v>
+        <v>0.2703697576933006</v>
       </c>
       <c r="M62" t="n">
         <v>0</v>
@@ -6956,16 +6956,16 @@
         <v>0</v>
       </c>
       <c r="O62" t="n">
-        <v>4.143875794202612</v>
+        <v>4.119557613484383</v>
       </c>
       <c r="P62" t="n">
-        <v>4.19573426251733</v>
+        <v>4.207872592099356</v>
       </c>
       <c r="Q62" t="n">
-        <v>0.9873690699491043</v>
+        <v>0.9855160916843333</v>
       </c>
       <c r="R62" t="n">
-        <v>0.007412000360874087</v>
+        <v>0.007937078037095615</v>
       </c>
       <c r="S62" t="inlineStr"/>
       <c r="T62" t="inlineStr"/>
@@ -6977,38 +6977,38 @@
       </c>
       <c r="Y62" t="inlineStr"/>
       <c r="Z62" t="n">
-        <v>0.9830170096801526</v>
+        <v>0.9782806271083877</v>
       </c>
       <c r="AA62" t="n">
-        <v>0.01359278385153566</v>
+        <v>0.01537180868713839</v>
       </c>
       <c r="AB62" t="inlineStr"/>
       <c r="AC62" t="n">
-        <v>0.09231787743316255</v>
+        <v>0.1538750430889146</v>
       </c>
       <c r="AD62" t="n">
-        <v>0.00317164539502261</v>
+        <v>0.003062210110520209</v>
       </c>
       <c r="AE62" t="inlineStr"/>
       <c r="AF62" t="n">
-        <v>0.5948824546300484</v>
+        <v>0.6470013413912619</v>
       </c>
       <c r="AG62" t="n">
-        <v>0.008521844313444058</v>
+        <v>0.007954806077548596</v>
       </c>
       <c r="AH62" t="inlineStr"/>
       <c r="AI62" t="n">
-        <v>0.980323486664271</v>
+        <v>0.9848863985415596</v>
       </c>
       <c r="AJ62" t="n">
-        <v>0.002082475016616744</v>
+        <v>0.001825112798942598</v>
       </c>
       <c r="AK62" t="inlineStr"/>
       <c r="AL62" t="n">
-        <v>0.8552099901601118</v>
+        <v>0.8652048361974399</v>
       </c>
       <c r="AM62" t="n">
-        <v>0.0019062747389344</v>
+        <v>0.0018393032986379</v>
       </c>
       <c r="AN62" t="inlineStr"/>
     </row>
@@ -7035,25 +7035,25 @@
         <v>53.51961950059453</v>
       </c>
       <c r="F63" t="n">
-        <v>0.7472990942554644</v>
+        <v>0.7472990942424869</v>
       </c>
       <c r="G63" t="n">
         <v>0.05931662452435613</v>
       </c>
       <c r="H63" t="n">
-        <v>0.1189424488256474</v>
+        <v>0.1189424488653025</v>
       </c>
       <c r="I63" t="n">
-        <v>0.05728789975449577</v>
+        <v>0.05728789972030301</v>
       </c>
       <c r="J63" t="n">
-        <v>0.01715393264003622</v>
+        <v>0.01715393264755156</v>
       </c>
       <c r="K63" t="n">
-        <v>0.2740450099273068</v>
+        <v>0.2127859095014644</v>
       </c>
       <c r="L63" t="n">
-        <v>0.2958174673379184</v>
+        <v>0.3354515216960652</v>
       </c>
       <c r="M63" t="n">
         <v>0</v>
@@ -7062,16 +7062,16 @@
         <v>0</v>
       </c>
       <c r="O63" t="n">
-        <v>3.971058122228126</v>
+        <v>3.979056729897652</v>
       </c>
       <c r="P63" t="n">
-        <v>4.236321138663175</v>
+        <v>4.238326836441605</v>
       </c>
       <c r="Q63" t="n">
-        <v>0.9877619744920115</v>
+        <v>0.9850301550649025</v>
       </c>
       <c r="R63" t="n">
-        <v>0.008091144510379884</v>
+        <v>0.008948761462177511</v>
       </c>
       <c r="S63" t="inlineStr"/>
       <c r="T63" t="inlineStr"/>
@@ -7083,38 +7083,38 @@
       </c>
       <c r="Y63" t="inlineStr"/>
       <c r="Z63" t="n">
-        <v>0.974934956304608</v>
+        <v>0.9687629645692027</v>
       </c>
       <c r="AA63" t="n">
-        <v>0.01743307431959035</v>
+        <v>0.01946142575155501</v>
       </c>
       <c r="AB63" t="inlineStr"/>
       <c r="AC63" t="n">
-        <v>0.9328572023707579</v>
+        <v>0.9300691021909906</v>
       </c>
       <c r="AD63" t="n">
-        <v>0.001131473183474153</v>
+        <v>0.001154726409655635</v>
       </c>
       <c r="AE63" t="inlineStr"/>
       <c r="AF63" t="n">
-        <v>0.9503402901017391</v>
+        <v>0.9799513931236753</v>
       </c>
       <c r="AG63" t="n">
-        <v>0.002478372242695531</v>
+        <v>0.001574731619329955</v>
       </c>
       <c r="AH63" t="inlineStr"/>
       <c r="AI63" t="n">
-        <v>0.8394671921765104</v>
+        <v>0.8132309067386392</v>
       </c>
       <c r="AJ63" t="n">
-        <v>0.003573250940262173</v>
+        <v>0.003854198886245592</v>
       </c>
       <c r="AK63" t="inlineStr"/>
       <c r="AL63" t="n">
-        <v>0.2428646488135878</v>
+        <v>0.3000048543703934</v>
       </c>
       <c r="AM63" t="n">
-        <v>0.002009457136430979</v>
+        <v>0.001932144030173437</v>
       </c>
       <c r="AN63" t="inlineStr"/>
     </row>
@@ -7141,25 +7141,25 @@
         <v>54.48315911730546</v>
       </c>
       <c r="F64" t="n">
-        <v>0.6806747812354861</v>
+        <v>0.6806747812675474</v>
       </c>
       <c r="G64" t="n">
         <v>0.05826760463298514</v>
       </c>
       <c r="H64" t="n">
-        <v>0.1324809677416384</v>
+        <v>0.1324809676982178</v>
       </c>
       <c r="I64" t="n">
-        <v>0.09760455450858101</v>
+        <v>0.09760455450536588</v>
       </c>
       <c r="J64" t="n">
-        <v>0.03097209188130944</v>
+        <v>0.0309720918958838</v>
       </c>
       <c r="K64" t="n">
-        <v>0.2247029268396697</v>
+        <v>0.1803589411167572</v>
       </c>
       <c r="L64" t="n">
-        <v>0.3230744834918965</v>
+        <v>0.3437889311268936</v>
       </c>
       <c r="M64" t="n">
         <v>0</v>
@@ -7168,16 +7168,16 @@
         <v>0</v>
       </c>
       <c r="O64" t="n">
-        <v>3.76527181006721</v>
+        <v>3.834210013489763</v>
       </c>
       <c r="P64" t="n">
-        <v>4.241789201588115</v>
+        <v>4.254078208091204</v>
       </c>
       <c r="Q64" t="n">
-        <v>0.9784062232155598</v>
+        <v>0.9808961311444295</v>
       </c>
       <c r="R64" t="n">
-        <v>0.009845662264506016</v>
+        <v>0.009260646239782202</v>
       </c>
       <c r="S64" t="inlineStr"/>
       <c r="T64" t="inlineStr"/>
@@ -7189,38 +7189,38 @@
       </c>
       <c r="Y64" t="inlineStr"/>
       <c r="Z64" t="n">
-        <v>0.9685969619262981</v>
+        <v>0.9732348380197525</v>
       </c>
       <c r="AA64" t="n">
-        <v>0.01871518628081749</v>
+        <v>0.01727799163364637</v>
       </c>
       <c r="AB64" t="inlineStr"/>
       <c r="AC64" t="n">
-        <v>0.5249125827766687</v>
+        <v>0.5817821854141971</v>
       </c>
       <c r="AD64" t="n">
-        <v>0.003722357507941682</v>
+        <v>0.003492469194237072</v>
       </c>
       <c r="AE64" t="inlineStr"/>
       <c r="AF64" t="n">
-        <v>0.2482326743570318</v>
+        <v>0.25759509361272</v>
       </c>
       <c r="AG64" t="n">
-        <v>0.01055065501068947</v>
+        <v>0.01048475087993331</v>
       </c>
       <c r="AH64" t="inlineStr"/>
       <c r="AI64" t="n">
-        <v>0.9758539827510931</v>
+        <v>0.9808252421696382</v>
       </c>
       <c r="AJ64" t="n">
-        <v>0.002242620743627632</v>
+        <v>0.00199847180494095</v>
       </c>
       <c r="AK64" t="inlineStr"/>
       <c r="AL64" t="n">
-        <v>0.8346890410923264</v>
+        <v>0.8377365687872778</v>
       </c>
       <c r="AM64" t="n">
-        <v>0.002298237160473179</v>
+        <v>0.002276954478438781</v>
       </c>
       <c r="AN64" t="inlineStr"/>
     </row>
@@ -7247,25 +7247,25 @@
         <v>53.51961950059453</v>
       </c>
       <c r="F65" t="n">
-        <v>0.7472990942554644</v>
+        <v>0.7472990942424869</v>
       </c>
       <c r="G65" t="n">
         <v>0.05931662452435613</v>
       </c>
       <c r="H65" t="n">
-        <v>0.1189424488256474</v>
+        <v>0.1189424488653025</v>
       </c>
       <c r="I65" t="n">
-        <v>0.05728789975449577</v>
+        <v>0.05728789972030301</v>
       </c>
       <c r="J65" t="n">
-        <v>0.01715393264003622</v>
+        <v>0.01715393264755156</v>
       </c>
       <c r="K65" t="n">
-        <v>0.2977175138061146</v>
+        <v>0.2347993178879203</v>
       </c>
       <c r="L65" t="n">
-        <v>0.3712407380229583</v>
+        <v>0.3907202173945382</v>
       </c>
       <c r="M65" t="n">
         <v>0</v>
@@ -7274,16 +7274,16 @@
         <v>0</v>
       </c>
       <c r="O65" t="n">
-        <v>3.910917589484847</v>
+        <v>3.926683483740697</v>
       </c>
       <c r="P65" t="n">
-        <v>4.266056814900674</v>
+        <v>4.267838730983512</v>
       </c>
       <c r="Q65" t="n">
-        <v>0.9785935748815605</v>
+        <v>0.9762036281779813</v>
       </c>
       <c r="R65" t="n">
-        <v>0.01053864704129518</v>
+        <v>0.0111113840726227</v>
       </c>
       <c r="S65" t="inlineStr"/>
       <c r="T65" t="inlineStr"/>
@@ -7295,38 +7295,38 @@
       </c>
       <c r="Y65" t="inlineStr"/>
       <c r="Z65" t="n">
-        <v>0.9647044738332224</v>
+        <v>0.9600159759103836</v>
       </c>
       <c r="AA65" t="n">
-        <v>0.02147806900604718</v>
+        <v>0.02286012776494337</v>
       </c>
       <c r="AB65" t="inlineStr"/>
       <c r="AC65" t="n">
-        <v>0.6959254041051117</v>
+        <v>0.7115558295030111</v>
       </c>
       <c r="AD65" t="n">
-        <v>0.003733991039377373</v>
+        <v>0.003636755330506183</v>
       </c>
       <c r="AE65" t="inlineStr"/>
       <c r="AF65" t="n">
-        <v>0.6405554098540989</v>
+        <v>0.6392380198405319</v>
       </c>
       <c r="AG65" t="n">
-        <v>0.008438613687579354</v>
+        <v>0.008454063606069649</v>
       </c>
       <c r="AH65" t="inlineStr"/>
       <c r="AI65" t="n">
-        <v>0.9191517047424349</v>
+        <v>0.9017780200232551</v>
       </c>
       <c r="AJ65" t="n">
-        <v>0.00245322895044282</v>
+        <v>0.002704001888492949</v>
       </c>
       <c r="AK65" t="inlineStr"/>
       <c r="AL65" t="n">
-        <v>0.5657596363365138</v>
+        <v>0.583624557246556</v>
       </c>
       <c r="AM65" t="n">
-        <v>0.001883061583841355</v>
+        <v>0.001843919607359135</v>
       </c>
       <c r="AN65" t="inlineStr"/>
     </row>
@@ -7353,25 +7353,25 @@
         <v>54.48315911730546</v>
       </c>
       <c r="F66" t="n">
-        <v>0.6806747812354861</v>
+        <v>0.6806747812675474</v>
       </c>
       <c r="G66" t="n">
         <v>0.05826760463298514</v>
       </c>
       <c r="H66" t="n">
-        <v>0.1324809677416384</v>
+        <v>0.1324809676982178</v>
       </c>
       <c r="I66" t="n">
-        <v>0.09760455450858101</v>
+        <v>0.09760455450536588</v>
       </c>
       <c r="J66" t="n">
-        <v>0.03097209188130944</v>
+        <v>0.0309720918958838</v>
       </c>
       <c r="K66" t="n">
-        <v>0.2630911090154405</v>
+        <v>0.2134227876690054</v>
       </c>
       <c r="L66" t="n">
-        <v>0.3175574634796361</v>
+        <v>0.3563932692498737</v>
       </c>
       <c r="M66" t="n">
         <v>0</v>
@@ -7380,16 +7380,16 @@
         <v>0</v>
       </c>
       <c r="O66" t="n">
-        <v>3.953139984689836</v>
+        <v>3.96341282918015</v>
       </c>
       <c r="P66" t="n">
-        <v>4.243873028532862</v>
+        <v>4.257276765028695</v>
       </c>
       <c r="Q66" t="n">
-        <v>0.9798538807134622</v>
+        <v>0.9796161416027704</v>
       </c>
       <c r="R66" t="n">
-        <v>0.009600398141344545</v>
+        <v>0.009656877904525974</v>
       </c>
       <c r="S66" t="inlineStr"/>
       <c r="T66" t="inlineStr"/>
@@ -7401,38 +7401,38 @@
       </c>
       <c r="Y66" t="inlineStr"/>
       <c r="Z66" t="n">
-        <v>0.9683869499465346</v>
+        <v>0.9673442097053362</v>
       </c>
       <c r="AA66" t="n">
-        <v>0.01871604260344171</v>
+        <v>0.01902220794284974</v>
       </c>
       <c r="AB66" t="inlineStr"/>
       <c r="AC66" t="n">
-        <v>0.6635046232592573</v>
+        <v>0.6845168680316047</v>
       </c>
       <c r="AD66" t="n">
-        <v>0.003575890383385436</v>
+        <v>0.003462443688946829</v>
       </c>
       <c r="AE66" t="inlineStr"/>
       <c r="AF66" t="n">
-        <v>0.6363384882473182</v>
+        <v>0.6505845678149704</v>
       </c>
       <c r="AG66" t="n">
-        <v>0.009213515657702653</v>
+        <v>0.009031247603300306</v>
       </c>
       <c r="AH66" t="inlineStr"/>
       <c r="AI66" t="n">
-        <v>0.9527060266693409</v>
+        <v>0.9623085427415365</v>
       </c>
       <c r="AJ66" t="n">
-        <v>0.003024589563424694</v>
+        <v>0.002700132104153043</v>
       </c>
       <c r="AK66" t="inlineStr"/>
       <c r="AL66" t="n">
-        <v>0.8480865104327875</v>
+        <v>0.8535761049246614</v>
       </c>
       <c r="AM66" t="n">
-        <v>0.002157535281263066</v>
+        <v>0.002118193907103112</v>
       </c>
       <c r="AN66" t="inlineStr"/>
     </row>
@@ -7459,25 +7459,25 @@
         <v>54.52272727272727</v>
       </c>
       <c r="F67" t="n">
-        <v>0.6524665781462966</v>
+        <v>0.652466577913562</v>
       </c>
       <c r="G67" t="n">
         <v>0.0582253187505376</v>
       </c>
       <c r="H67" t="n">
-        <v>0.1475232058308549</v>
+        <v>0.147523206464546</v>
       </c>
       <c r="I67" t="n">
-        <v>0.1417848972723109</v>
+        <v>0.1417848968713543</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>0.418401611669922</v>
+        <v>0.378033758727203</v>
       </c>
       <c r="L67" t="n">
-        <v>0.3821256938063454</v>
+        <v>0.3948417330132951</v>
       </c>
       <c r="M67" t="n">
         <v>0</v>
@@ -7486,61 +7486,61 @@
         <v>0</v>
       </c>
       <c r="O67" t="n">
-        <v>4.381125636492835</v>
+        <v>4.371122571078349</v>
       </c>
       <c r="P67" t="n">
-        <v>4.34406181085281</v>
+        <v>4.339379530579538</v>
       </c>
       <c r="Q67" t="n">
-        <v>0.8652052824349274</v>
+        <v>0.8953818411368462</v>
       </c>
       <c r="R67" t="n">
-        <v>0.02655512234624559</v>
+        <v>0.02339458828307652</v>
       </c>
       <c r="S67" t="inlineStr"/>
       <c r="T67" t="inlineStr"/>
       <c r="U67" t="inlineStr"/>
       <c r="V67" t="inlineStr"/>
       <c r="W67" t="n">
-        <v>0.8071641175971108</v>
+        <v>0.7187069804915085</v>
       </c>
       <c r="X67" t="n">
-        <v>0.0007633185508364196</v>
+        <v>0.0009219160372857722</v>
       </c>
       <c r="Y67" t="inlineStr"/>
       <c r="Z67" t="n">
-        <v>0.6252317559356262</v>
+        <v>0.7141588546977088</v>
       </c>
       <c r="AA67" t="n">
-        <v>0.06307984279609716</v>
+        <v>0.05508984899955284</v>
       </c>
       <c r="AB67" t="inlineStr"/>
       <c r="AC67" t="n">
-        <v>0.7694401471717121</v>
+        <v>0.6668454057309083</v>
       </c>
       <c r="AD67" t="n">
-        <v>0.00263059201364216</v>
+        <v>0.003162165218828757</v>
       </c>
       <c r="AE67" t="inlineStr"/>
       <c r="AF67" t="n">
-        <v>0.6608983700798354</v>
+        <v>0.6538971006555838</v>
       </c>
       <c r="AG67" t="n">
-        <v>0.01277267836156645</v>
+        <v>0.01290386046948996</v>
       </c>
       <c r="AH67" t="inlineStr"/>
       <c r="AI67" t="n">
-        <v>0.8106537736777357</v>
+        <v>0.8334959102843912</v>
       </c>
       <c r="AJ67" t="n">
-        <v>0.009011606001879655</v>
+        <v>0.008450576145094158</v>
       </c>
       <c r="AK67" t="inlineStr"/>
       <c r="AL67" t="n">
-        <v>0.8067049225180842</v>
+        <v>0.8587792381770776</v>
       </c>
       <c r="AM67" t="n">
-        <v>0.0001173345039910578</v>
+        <v>0.0001002916210320744</v>
       </c>
       <c r="AN67" t="inlineStr"/>
     </row>
@@ -7567,25 +7567,25 @@
         <v>54.52272727272727</v>
       </c>
       <c r="F68" t="n">
-        <v>0.6524665781462966</v>
+        <v>0.652466577913562</v>
       </c>
       <c r="G68" t="n">
         <v>0.0582253187505376</v>
       </c>
       <c r="H68" t="n">
-        <v>0.1475232058308549</v>
+        <v>0.147523206464546</v>
       </c>
       <c r="I68" t="n">
-        <v>0.1417848972723109</v>
+        <v>0.1417848968713543</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>0.4256809874704212</v>
+        <v>0.3818260119870678</v>
       </c>
       <c r="L68" t="n">
-        <v>0.3705203685982623</v>
+        <v>0.3806272564507771</v>
       </c>
       <c r="M68" t="n">
         <v>0</v>
@@ -7594,61 +7594,61 @@
         <v>0</v>
       </c>
       <c r="O68" t="n">
-        <v>4.452681279498788</v>
+        <v>4.412285529802531</v>
       </c>
       <c r="P68" t="n">
-        <v>4.341592065566686</v>
+        <v>4.339675967763494</v>
       </c>
       <c r="Q68" t="n">
-        <v>0.8049131111357513</v>
+        <v>0.850144148681274</v>
       </c>
       <c r="R68" t="n">
-        <v>0.02946429375497725</v>
+        <v>0.02582372253932241</v>
       </c>
       <c r="S68" t="inlineStr"/>
       <c r="T68" t="inlineStr"/>
       <c r="U68" t="inlineStr"/>
       <c r="V68" t="inlineStr"/>
       <c r="W68" t="n">
-        <v>0.4850167914312021</v>
+        <v>0.3405068013847646</v>
       </c>
       <c r="X68" t="n">
-        <v>0.00117357672073808</v>
+        <v>0.00132806738801465</v>
       </c>
       <c r="Y68" t="inlineStr"/>
       <c r="Z68" t="n">
-        <v>0.4747389252301797</v>
+        <v>0.6038380891145212</v>
       </c>
       <c r="AA68" t="n">
-        <v>0.07049963336404443</v>
+        <v>0.06122596067672573</v>
       </c>
       <c r="AB68" t="inlineStr"/>
       <c r="AC68" t="n">
-        <v>0.4663226440179072</v>
+        <v>0.3237094162941404</v>
       </c>
       <c r="AD68" t="n">
-        <v>0.003898741778773778</v>
+        <v>0.004388860270192974</v>
       </c>
       <c r="AE68" t="inlineStr"/>
       <c r="AF68" t="n">
-        <v>0.6887807616993085</v>
+        <v>0.6480917258126857</v>
       </c>
       <c r="AG68" t="n">
-        <v>0.008203606518553111</v>
+        <v>0.008723411199317063</v>
       </c>
       <c r="AH68" t="inlineStr"/>
       <c r="AI68" t="n">
-        <v>0.6970705455301829</v>
+        <v>0.6957599236785921</v>
       </c>
       <c r="AJ68" t="n">
-        <v>0.01241140337891528</v>
+        <v>0.0124382232892692</v>
       </c>
       <c r="AK68" t="inlineStr"/>
       <c r="AL68" t="n">
-        <v>0.249383837800332</v>
+        <v>0.392780066212191</v>
       </c>
       <c r="AM68" t="n">
-        <v>0.0007699954760900591</v>
+        <v>0.000692551746791683</v>
       </c>
       <c r="AN68" t="inlineStr"/>
     </row>
@@ -7675,25 +7675,25 @@
         <v>51.72972972972973</v>
       </c>
       <c r="F69" t="n">
-        <v>0.387003570840844</v>
+        <v>0.3870035708733858</v>
       </c>
       <c r="G69" t="n">
         <v>0.06136902688626825</v>
       </c>
       <c r="H69" t="n">
-        <v>0.3121616657195941</v>
+        <v>0.3121616658061397</v>
       </c>
       <c r="I69" t="n">
-        <v>0.1933504308693656</v>
+        <v>0.1933504307114432</v>
       </c>
       <c r="J69" t="n">
-        <v>0.04611530568392795</v>
+        <v>0.04611530572276303</v>
       </c>
       <c r="K69" t="n">
-        <v>0.1578375667668122</v>
+        <v>0.1011765085600368</v>
       </c>
       <c r="L69" t="n">
-        <v>0.2142730074772703</v>
+        <v>0.1771833945991779</v>
       </c>
       <c r="M69" t="n">
         <v>0</v>
@@ -7702,16 +7702,16 @@
         <v>0</v>
       </c>
       <c r="O69" t="n">
-        <v>4.342039872316217</v>
+        <v>4.336669816495358</v>
       </c>
       <c r="P69" t="n">
-        <v>4.303413304182833</v>
+        <v>4.293816703300208</v>
       </c>
       <c r="Q69" t="n">
-        <v>0.973466531904749</v>
+        <v>0.9723700197053096</v>
       </c>
       <c r="R69" t="n">
-        <v>0.009546926213408365</v>
+        <v>0.00974219558485041</v>
       </c>
       <c r="S69" t="inlineStr"/>
       <c r="T69" t="inlineStr"/>
@@ -7721,38 +7721,38 @@
       <c r="X69" t="inlineStr"/>
       <c r="Y69" t="inlineStr"/>
       <c r="Z69" t="n">
-        <v>0.9649308018052815</v>
+        <v>0.9662528374517387</v>
       </c>
       <c r="AA69" t="n">
-        <v>0.01037470226615612</v>
+        <v>0.01017727139120128</v>
       </c>
       <c r="AB69" t="inlineStr"/>
       <c r="AC69" t="n">
-        <v>0.458396391489205</v>
+        <v>0.4256171120647994</v>
       </c>
       <c r="AD69" t="n">
-        <v>0.004673542140826365</v>
+        <v>0.004812892205250306</v>
       </c>
       <c r="AE69" t="inlineStr"/>
       <c r="AF69" t="n">
-        <v>0.8640858595624259</v>
+        <v>0.8563731327617941</v>
       </c>
       <c r="AG69" t="n">
-        <v>0.01492885483844594</v>
+        <v>0.01534659449124235</v>
       </c>
       <c r="AH69" t="inlineStr"/>
       <c r="AI69" t="n">
-        <v>0.9076361642234667</v>
+        <v>0.8977165977517902</v>
       </c>
       <c r="AJ69" t="n">
-        <v>0.009221236553957691</v>
+        <v>0.009703776059976778</v>
       </c>
       <c r="AK69" t="inlineStr"/>
       <c r="AL69" t="n">
-        <v>0.5180123767864011</v>
+        <v>0.5235518753573127</v>
       </c>
       <c r="AM69" t="n">
-        <v>0.004282598159577627</v>
+        <v>0.004257917027968281</v>
       </c>
       <c r="AN69" t="inlineStr"/>
     </row>
@@ -7779,25 +7779,25 @@
         <v>33.0828025477707</v>
       </c>
       <c r="F70" t="n">
-        <v>0.3260336956980185</v>
+        <v>0.3260336958414495</v>
       </c>
       <c r="G70" t="n">
         <v>0.09595931813875594</v>
       </c>
       <c r="H70" t="n">
-        <v>0.3161491466910983</v>
+        <v>0.31614914647049</v>
       </c>
       <c r="I70" t="n">
-        <v>0.2279586239396759</v>
+        <v>0.2279586239311767</v>
       </c>
       <c r="J70" t="n">
-        <v>0.03389921553245138</v>
+        <v>0.03389921561812766</v>
       </c>
       <c r="K70" t="n">
-        <v>0.1548404427189273</v>
+        <v>0.09853776886812335</v>
       </c>
       <c r="L70" t="n">
-        <v>0.2798005208792019</v>
+        <v>0.2509557916829193</v>
       </c>
       <c r="M70" t="n">
         <v>0</v>
@@ -7806,16 +7806,16 @@
         <v>0</v>
       </c>
       <c r="O70" t="n">
-        <v>4.394470536415335</v>
+        <v>4.406147207166384</v>
       </c>
       <c r="P70" t="n">
-        <v>4.362379885776532</v>
+        <v>4.351469129086955</v>
       </c>
       <c r="Q70" t="n">
-        <v>0.965987268471406</v>
+        <v>0.9657806898956811</v>
       </c>
       <c r="R70" t="n">
-        <v>0.009050518857660008</v>
+        <v>0.009077961714299646</v>
       </c>
       <c r="S70" t="inlineStr"/>
       <c r="T70" t="inlineStr"/>
@@ -7825,38 +7825,38 @@
       <c r="X70" t="inlineStr"/>
       <c r="Y70" t="inlineStr"/>
       <c r="Z70" t="n">
-        <v>0.9105946226162333</v>
+        <v>0.9199835835155253</v>
       </c>
       <c r="AA70" t="n">
-        <v>0.01335122210202667</v>
+        <v>0.01263073865750221</v>
       </c>
       <c r="AB70" t="inlineStr"/>
       <c r="AC70" t="n">
-        <v>0.9219389840196544</v>
+        <v>0.9217559607563544</v>
       </c>
       <c r="AD70" t="n">
-        <v>0.003240914039709335</v>
+        <v>0.003244711168008335</v>
       </c>
       <c r="AE70" t="inlineStr"/>
       <c r="AF70" t="n">
-        <v>0.9627215048588192</v>
+        <v>0.9541645992777731</v>
       </c>
       <c r="AG70" t="n">
-        <v>0.008767193713566931</v>
+        <v>0.009721469817497557</v>
       </c>
       <c r="AH70" t="inlineStr"/>
       <c r="AI70" t="n">
-        <v>0.8229355510279825</v>
+        <v>0.8181221774585553</v>
       </c>
       <c r="AJ70" t="n">
-        <v>0.01178566153984561</v>
+        <v>0.01194477991049761</v>
       </c>
       <c r="AK70" t="inlineStr"/>
       <c r="AL70" t="n">
-        <v>0.7529163503012019</v>
+        <v>0.764536528087583</v>
       </c>
       <c r="AM70" t="n">
-        <v>0.002243947189856084</v>
+        <v>0.00219054612158454</v>
       </c>
       <c r="AN70" t="inlineStr"/>
     </row>
@@ -7883,25 +7883,25 @@
         <v>47.07964601769911</v>
       </c>
       <c r="F71" t="n">
-        <v>0.3936990724378037</v>
+        <v>0.3936990724969831</v>
       </c>
       <c r="G71" t="n">
         <v>0.06743048096431555</v>
       </c>
       <c r="H71" t="n">
-        <v>0.2058669949880412</v>
+        <v>0.2058669949713333</v>
       </c>
       <c r="I71" t="n">
-        <v>0.3043928180016056</v>
+        <v>0.3043928180135104</v>
       </c>
       <c r="J71" t="n">
-        <v>0.02861063360823382</v>
+        <v>0.02861063355385755</v>
       </c>
       <c r="K71" t="n">
-        <v>0.3259506110927289</v>
+        <v>0.2686805224204179</v>
       </c>
       <c r="L71" t="n">
-        <v>0.3486347098873965</v>
+        <v>0.3297962845322103</v>
       </c>
       <c r="M71" t="n">
         <v>0</v>
@@ -7910,16 +7910,16 @@
         <v>0</v>
       </c>
       <c r="O71" t="n">
-        <v>4.436154054572222</v>
+        <v>4.434548768386005</v>
       </c>
       <c r="P71" t="n">
-        <v>4.440396206872959</v>
+        <v>4.434211644840024</v>
       </c>
       <c r="Q71" t="n">
-        <v>0.9607948920053613</v>
+        <v>0.9609546735475067</v>
       </c>
       <c r="R71" t="n">
-        <v>0.01081126529064855</v>
+        <v>0.01078921198759127</v>
       </c>
       <c r="S71" t="inlineStr"/>
       <c r="T71" t="inlineStr"/>
@@ -7929,38 +7929,38 @@
       <c r="X71" t="inlineStr"/>
       <c r="Y71" t="inlineStr"/>
       <c r="Z71" t="n">
-        <v>0.9432467069920062</v>
+        <v>0.9441063864742447</v>
       </c>
       <c r="AA71" t="n">
-        <v>0.01417833387835802</v>
+        <v>0.01407053984044895</v>
       </c>
       <c r="AB71" t="inlineStr"/>
       <c r="AC71" t="n">
-        <v>0.7407857206215123</v>
+        <v>0.7367902280790937</v>
       </c>
       <c r="AD71" t="n">
-        <v>0.004509935243005926</v>
+        <v>0.004544560082242368</v>
       </c>
       <c r="AE71" t="inlineStr"/>
       <c r="AF71" t="n">
-        <v>0.9024282342438994</v>
+        <v>0.9119903640483601</v>
       </c>
       <c r="AG71" t="n">
-        <v>0.009962459724770861</v>
+        <v>0.009461709465718737</v>
       </c>
       <c r="AH71" t="inlineStr"/>
       <c r="AI71" t="n">
-        <v>0.8435488309205408</v>
+        <v>0.8377375913220934</v>
       </c>
       <c r="AJ71" t="n">
-        <v>0.01621164397155933</v>
+        <v>0.01650998240497623</v>
       </c>
       <c r="AK71" t="inlineStr"/>
       <c r="AL71" t="n">
-        <v>0.9354870836204331</v>
+        <v>0.914895187568743</v>
       </c>
       <c r="AM71" t="n">
-        <v>0.0009922773973696391</v>
+        <v>0.001139690219685772</v>
       </c>
       <c r="AN71" t="inlineStr"/>
     </row>
@@ -7987,25 +7987,25 @@
         <v>37.36805555555556</v>
       </c>
       <c r="F72" t="n">
-        <v>0.2796444532400447</v>
+        <v>0.279644453194911</v>
       </c>
       <c r="G72" t="n">
         <v>0.08495500039822655</v>
       </c>
       <c r="H72" t="n">
-        <v>0.2106458171229023</v>
+        <v>0.2106458171994461</v>
       </c>
       <c r="I72" t="n">
-        <v>0.3902452407206423</v>
+        <v>0.3902452407095023</v>
       </c>
       <c r="J72" t="n">
-        <v>0.03450948851818413</v>
+        <v>0.03450948849791399</v>
       </c>
       <c r="K72" t="n">
-        <v>0.3237573962818418</v>
+        <v>0.2657819781201773</v>
       </c>
       <c r="L72" t="n">
-        <v>0.4159121970215693</v>
+        <v>0.3859035770342941</v>
       </c>
       <c r="M72" t="n">
         <v>0</v>
@@ -8014,16 +8014,16 @@
         <v>0</v>
       </c>
       <c r="O72" t="n">
-        <v>4.514536388254673</v>
+        <v>4.534002379268917</v>
       </c>
       <c r="P72" t="n">
-        <v>4.505731237331502</v>
+        <v>4.499376278439726</v>
       </c>
       <c r="Q72" t="n">
-        <v>0.9584956209223118</v>
+        <v>0.9568340883953047</v>
       </c>
       <c r="R72" t="n">
-        <v>0.01163393906122562</v>
+        <v>0.01186452300052458</v>
       </c>
       <c r="S72" t="inlineStr"/>
       <c r="T72" t="inlineStr"/>
@@ -8033,38 +8033,38 @@
       <c r="X72" t="inlineStr"/>
       <c r="Y72" t="inlineStr"/>
       <c r="Z72" t="n">
-        <v>0.8706524050963869</v>
+        <v>0.8758639166168503</v>
       </c>
       <c r="AA72" t="n">
-        <v>0.01502090190897186</v>
+        <v>0.01471518920374563</v>
       </c>
       <c r="AB72" t="inlineStr"/>
       <c r="AC72" t="n">
-        <v>0.8083387442247059</v>
+        <v>0.7990727877130628</v>
       </c>
       <c r="AD72" t="n">
-        <v>0.004822252502559896</v>
+        <v>0.004937443760387808</v>
       </c>
       <c r="AE72" t="inlineStr"/>
       <c r="AF72" t="n">
-        <v>0.9535455239329719</v>
+        <v>0.9546346828963432</v>
       </c>
       <c r="AG72" t="n">
-        <v>0.006754353341282688</v>
+        <v>0.006674703350368066</v>
       </c>
       <c r="AH72" t="inlineStr"/>
       <c r="AI72" t="n">
-        <v>0.8567071382991861</v>
+        <v>0.8431211361650002</v>
       </c>
       <c r="AJ72" t="n">
-        <v>0.01949923937294363</v>
+        <v>0.02040269843360602</v>
       </c>
       <c r="AK72" t="inlineStr"/>
       <c r="AL72" t="n">
-        <v>0.9028636026677657</v>
+        <v>0.8991037925144849</v>
       </c>
       <c r="AM72" t="n">
-        <v>0.001421074192962858</v>
+        <v>0.001448315494902864</v>
       </c>
       <c r="AN72" t="inlineStr"/>
     </row>
@@ -8091,25 +8091,25 @@
         <v>80.48333333333333</v>
       </c>
       <c r="F73" t="n">
-        <v>0.4426967929782777</v>
+        <v>0.4426967930157429</v>
       </c>
       <c r="G73" t="n">
         <v>0.03944423078819433</v>
       </c>
       <c r="H73" t="n">
-        <v>0.3881444762932012</v>
+        <v>0.388144476200794</v>
       </c>
       <c r="I73" t="n">
-        <v>0.1098624187784432</v>
+        <v>0.1098624188419678</v>
       </c>
       <c r="J73" t="n">
-        <v>0.01985208116188355</v>
+        <v>0.01985208115330091</v>
       </c>
       <c r="K73" t="n">
-        <v>0.08006297265283152</v>
+        <v>0.04025470310716591</v>
       </c>
       <c r="L73" t="n">
-        <v>0.08137571817139509</v>
+        <v>0.05542117802268435</v>
       </c>
       <c r="M73" t="n">
         <v>0</v>
@@ -8118,16 +8118,16 @@
         <v>0</v>
       </c>
       <c r="O73" t="n">
-        <v>4.341883758983041</v>
+        <v>4.333373537311013</v>
       </c>
       <c r="P73" t="n">
-        <v>4.328693886773427</v>
+        <v>4.324640731115323</v>
       </c>
       <c r="Q73" t="n">
-        <v>0.9939987049766698</v>
+        <v>0.9937193844994046</v>
       </c>
       <c r="R73" t="n">
-        <v>0.005151985406082198</v>
+        <v>0.005270517247422762</v>
       </c>
       <c r="S73" t="inlineStr"/>
       <c r="T73" t="inlineStr"/>
@@ -8137,38 +8137,38 @@
       <c r="X73" t="inlineStr"/>
       <c r="Y73" t="inlineStr"/>
       <c r="Z73" t="n">
-        <v>0.9490814218129882</v>
+        <v>0.9485109185939504</v>
       </c>
       <c r="AA73" t="n">
-        <v>0.007747658999801856</v>
+        <v>0.007790941361724895</v>
       </c>
       <c r="AB73" t="inlineStr"/>
       <c r="AC73" t="n">
-        <v>0.6117652657776269</v>
+        <v>0.6027109001381328</v>
       </c>
       <c r="AD73" t="n">
-        <v>0.001245555888451064</v>
+        <v>0.001259996533246099</v>
       </c>
       <c r="AE73" t="inlineStr"/>
       <c r="AF73" t="n">
-        <v>0.9649111723746878</v>
+        <v>0.9608021383216085</v>
       </c>
       <c r="AG73" t="n">
-        <v>0.006284897670915332</v>
+        <v>0.006642705055605563</v>
       </c>
       <c r="AH73" t="inlineStr"/>
       <c r="AI73" t="n">
-        <v>0.8256670362030982</v>
+        <v>0.8207553972729323</v>
       </c>
       <c r="AJ73" t="n">
-        <v>0.005105101308953068</v>
+        <v>0.005176517095687594</v>
       </c>
       <c r="AK73" t="inlineStr"/>
       <c r="AL73" t="n">
-        <v>-0.07106758937209445</v>
+        <v>-0.091893121412705</v>
       </c>
       <c r="AM73" t="n">
-        <v>0.002361173556815051</v>
+        <v>0.002384018039688969</v>
       </c>
       <c r="AN73" t="inlineStr"/>
     </row>
@@ -8195,25 +8195,25 @@
         <v>59.11538461538462</v>
       </c>
       <c r="F74" t="n">
-        <v>0.2579745442485045</v>
+        <v>0.2579745444344787</v>
       </c>
       <c r="G74" t="n">
         <v>0.05370181037064575</v>
       </c>
       <c r="H74" t="n">
-        <v>0.3841123147856094</v>
+        <v>0.384112314707</v>
       </c>
       <c r="I74" t="n">
-        <v>0.2682526027331976</v>
+        <v>0.2682526026085332</v>
       </c>
       <c r="J74" t="n">
-        <v>0.03595872786204279</v>
+        <v>0.0359587278793424</v>
       </c>
       <c r="K74" t="n">
-        <v>0.0844764733101903</v>
+        <v>0.04323964738565159</v>
       </c>
       <c r="L74" t="n">
-        <v>0.1658803230615703</v>
+        <v>0.1274457998809921</v>
       </c>
       <c r="M74" t="n">
         <v>0</v>
@@ -8222,16 +8222,16 @@
         <v>0</v>
       </c>
       <c r="O74" t="n">
-        <v>4.399088907307153</v>
+        <v>4.405756282529816</v>
       </c>
       <c r="P74" t="n">
-        <v>4.387802559529828</v>
+        <v>4.379712336603393</v>
       </c>
       <c r="Q74" t="n">
-        <v>0.97270653762638</v>
+        <v>0.9726461788777437</v>
       </c>
       <c r="R74" t="n">
-        <v>0.007826087404419544</v>
+        <v>0.00783473621440257</v>
       </c>
       <c r="S74" t="inlineStr"/>
       <c r="T74" t="inlineStr"/>
@@ -8241,38 +8241,38 @@
       <c r="X74" t="inlineStr"/>
       <c r="Y74" t="inlineStr"/>
       <c r="Z74" t="n">
-        <v>0.8506089235589397</v>
+        <v>0.8723670698953041</v>
       </c>
       <c r="AA74" t="n">
-        <v>0.009234327024506673</v>
+        <v>0.008535408135009314</v>
       </c>
       <c r="AB74" t="inlineStr"/>
       <c r="AC74" t="n">
-        <v>0.8619262195327839</v>
+        <v>0.8584673758617899</v>
       </c>
       <c r="AD74" t="n">
-        <v>0.001234818278937854</v>
+        <v>0.001250189137552994</v>
       </c>
       <c r="AE74" t="inlineStr"/>
       <c r="AF74" t="n">
-        <v>0.8979989257542516</v>
+        <v>0.8904970232959282</v>
       </c>
       <c r="AG74" t="n">
-        <v>0.01257586947861658</v>
+        <v>0.01303012586655532</v>
       </c>
       <c r="AH74" t="inlineStr"/>
       <c r="AI74" t="n">
-        <v>0.8601893779407035</v>
+        <v>0.8567224864933068</v>
       </c>
       <c r="AJ74" t="n">
-        <v>0.007560234673324557</v>
+        <v>0.007653396441262219</v>
       </c>
       <c r="AK74" t="inlineStr"/>
       <c r="AL74" t="n">
-        <v>0.7035071016803413</v>
+        <v>0.7028160341109753</v>
       </c>
       <c r="AM74" t="n">
-        <v>0.002032487901956395</v>
+        <v>0.002034855191436901</v>
       </c>
       <c r="AN74" t="inlineStr"/>
     </row>
@@ -8299,25 +8299,25 @@
         <v>38.49019607843137</v>
       </c>
       <c r="F75" t="n">
-        <v>0.3797999037751007</v>
+        <v>0.379799903884584</v>
       </c>
       <c r="G75" t="n">
         <v>0.0824782281735924</v>
       </c>
       <c r="H75" t="n">
-        <v>0.2705342292388105</v>
+        <v>0.2705342288932795</v>
       </c>
       <c r="I75" t="n">
-        <v>0.2132258416518971</v>
+        <v>0.2132258419102607</v>
       </c>
       <c r="J75" t="n">
-        <v>0.05396179716059933</v>
+        <v>0.05396179713828334</v>
       </c>
       <c r="K75" t="n">
-        <v>0.207879713293752</v>
+        <v>0.1486427815751791</v>
       </c>
       <c r="L75" t="n">
-        <v>0.2635591019267816</v>
+        <v>0.2370916170858763</v>
       </c>
       <c r="M75" t="n">
         <v>0</v>
@@ -8326,16 +8326,16 @@
         <v>0</v>
       </c>
       <c r="O75" t="n">
-        <v>4.205773976883957</v>
+        <v>4.1963263632822</v>
       </c>
       <c r="P75" t="n">
-        <v>4.285134295724109</v>
+        <v>4.272932627071964</v>
       </c>
       <c r="Q75" t="n">
-        <v>0.9700352220929257</v>
+        <v>0.9697173268663822</v>
       </c>
       <c r="R75" t="n">
-        <v>0.006836281025551389</v>
+        <v>0.006872448280910571</v>
       </c>
       <c r="S75" t="inlineStr"/>
       <c r="T75" t="inlineStr"/>
@@ -8345,38 +8345,38 @@
       <c r="X75" t="inlineStr"/>
       <c r="Y75" t="inlineStr"/>
       <c r="Z75" t="n">
-        <v>0.8952312768612467</v>
+        <v>0.896371979642713</v>
       </c>
       <c r="AA75" t="n">
-        <v>0.01156611815438031</v>
+        <v>0.01150298093888978</v>
       </c>
       <c r="AB75" t="inlineStr"/>
       <c r="AC75" t="n">
-        <v>0.8435216367826263</v>
+        <v>0.8261306726317332</v>
       </c>
       <c r="AD75" t="n">
-        <v>0.002386865501858177</v>
+        <v>0.00251600956130023</v>
       </c>
       <c r="AE75" t="inlineStr"/>
       <c r="AF75" t="n">
-        <v>0.9316537784967639</v>
+        <v>0.9255611263427016</v>
       </c>
       <c r="AG75" t="n">
-        <v>0.006861349718007638</v>
+        <v>0.007160645872290858</v>
       </c>
       <c r="AH75" t="inlineStr"/>
       <c r="AI75" t="n">
-        <v>0.8718459282597438</v>
+        <v>0.8741274049922191</v>
       </c>
       <c r="AJ75" t="n">
-        <v>0.006790499346298951</v>
+        <v>0.006729783621730512</v>
       </c>
       <c r="AK75" t="inlineStr"/>
       <c r="AL75" t="n">
-        <v>0.9732191547832254</v>
+        <v>0.9751621987414116</v>
       </c>
       <c r="AM75" t="n">
-        <v>0.001006217616439601</v>
+        <v>0.0009690280554602878</v>
       </c>
       <c r="AN75" t="inlineStr"/>
     </row>
@@ -8403,25 +8403,25 @@
         <v>67.76923076923077</v>
       </c>
       <c r="F76" t="n">
-        <v>0.3107335005383793</v>
+        <v>0.3107335004737291</v>
       </c>
       <c r="G76" t="n">
         <v>0.04684431472172675</v>
       </c>
       <c r="H76" t="n">
-        <v>0.5076173756922413</v>
+        <v>0.5076173757282579</v>
       </c>
       <c r="I76" t="n">
-        <v>0.1034441405229936</v>
+        <v>0.1034441405920671</v>
       </c>
       <c r="J76" t="n">
-        <v>0.03136066852465918</v>
+        <v>0.03136066848421915</v>
       </c>
       <c r="K76" t="n">
-        <v>0.02053128897390902</v>
+        <v>0.006369178043669377</v>
       </c>
       <c r="L76" t="n">
-        <v>0.02507560144266702</v>
+        <v>0.012591555596974</v>
       </c>
       <c r="M76" t="n">
         <v>0</v>
@@ -8430,16 +8430,16 @@
         <v>0</v>
       </c>
       <c r="O76" t="n">
-        <v>4.358945383991737</v>
+        <v>4.366980950655456</v>
       </c>
       <c r="P76" t="n">
-        <v>4.318133968926499</v>
+        <v>4.315888312997329</v>
       </c>
       <c r="Q76" t="n">
-        <v>0.9931292055639458</v>
+        <v>0.9931999033983923</v>
       </c>
       <c r="R76" t="n">
-        <v>0.005201321772915624</v>
+        <v>0.00517449277825967</v>
       </c>
       <c r="S76" t="inlineStr"/>
       <c r="T76" t="inlineStr"/>
@@ -8449,38 +8449,38 @@
       <c r="X76" t="inlineStr"/>
       <c r="Y76" t="inlineStr"/>
       <c r="Z76" t="n">
-        <v>0.9362500298616629</v>
+        <v>0.9422554293165212</v>
       </c>
       <c r="AA76" t="n">
-        <v>0.007183577587467957</v>
+        <v>0.006836855045880201</v>
       </c>
       <c r="AB76" t="inlineStr"/>
       <c r="AC76" t="n">
-        <v>0.8852010840946726</v>
+        <v>0.8902913386208807</v>
       </c>
       <c r="AD76" t="n">
-        <v>0.0009341454369563394</v>
+        <v>0.0009132003332602361</v>
       </c>
       <c r="AE76" t="inlineStr"/>
       <c r="AF76" t="n">
-        <v>0.9547729414807739</v>
+        <v>0.9528115551154741</v>
       </c>
       <c r="AG76" t="n">
-        <v>0.008977588944218092</v>
+        <v>0.009170190923766938</v>
       </c>
       <c r="AH76" t="inlineStr"/>
       <c r="AI76" t="n">
-        <v>0.9887546086081793</v>
+        <v>0.9886575441925634</v>
       </c>
       <c r="AJ76" t="n">
-        <v>0.0008912618039564599</v>
+        <v>0.0008950999960561246</v>
       </c>
       <c r="AK76" t="inlineStr"/>
       <c r="AL76" t="n">
-        <v>0.5685447733808981</v>
+        <v>0.5667353945469962</v>
       </c>
       <c r="AM76" t="n">
-        <v>0.001183585831249137</v>
+        <v>0.001186065012124565</v>
       </c>
       <c r="AN76" t="inlineStr"/>
     </row>
@@ -8507,25 +8507,25 @@
         <v>84.83333333333333</v>
       </c>
       <c r="F77" t="n">
-        <v>0.2190992506065154</v>
+        <v>0.2190992505888929</v>
       </c>
       <c r="G77" t="n">
         <v>0.03742164842361306</v>
       </c>
       <c r="H77" t="n">
-        <v>0.4560940070375605</v>
+        <v>0.4560940072232207</v>
       </c>
       <c r="I77" t="n">
-        <v>0.2593330805653106</v>
+        <v>0.2593330804892675</v>
       </c>
       <c r="J77" t="n">
-        <v>0.02805201336700053</v>
+        <v>0.02805201327500588</v>
       </c>
       <c r="K77" t="n">
-        <v>0.03789390692492493</v>
+        <v>0.01471419240858703</v>
       </c>
       <c r="L77" t="n">
-        <v>0.08293632886498861</v>
+        <v>0.0488212880141077</v>
       </c>
       <c r="M77" t="n">
         <v>0</v>
@@ -8534,16 +8534,16 @@
         <v>0</v>
       </c>
       <c r="O77" t="n">
-        <v>4.275909837651753</v>
+        <v>4.278059968673261</v>
       </c>
       <c r="P77" t="n">
-        <v>4.243293106379868</v>
+        <v>4.23828495687153</v>
       </c>
       <c r="Q77" t="n">
-        <v>0.9728371946158348</v>
+        <v>0.9692699449780862</v>
       </c>
       <c r="R77" t="n">
-        <v>0.009883149324401437</v>
+        <v>0.01051210560460476</v>
       </c>
       <c r="S77" t="inlineStr"/>
       <c r="T77" t="inlineStr"/>
@@ -8553,38 +8553,38 @@
       <c r="X77" t="inlineStr"/>
       <c r="Y77" t="inlineStr"/>
       <c r="Z77" t="n">
-        <v>0.5403022448950849</v>
+        <v>0.4553818783772714</v>
       </c>
       <c r="AA77" t="n">
-        <v>0.01235283065536421</v>
+        <v>0.01344548090973197</v>
       </c>
       <c r="AB77" t="inlineStr"/>
       <c r="AC77" t="n">
-        <v>-0.6297403391754275</v>
+        <v>-0.5832811292205164</v>
       </c>
       <c r="AD77" t="n">
-        <v>0.00124843063454326</v>
+        <v>0.001230507392512299</v>
       </c>
       <c r="AE77" t="inlineStr"/>
       <c r="AF77" t="n">
-        <v>0.9210674752498865</v>
+        <v>0.9027644922647839</v>
       </c>
       <c r="AG77" t="n">
-        <v>0.01217914913857419</v>
+        <v>0.01351765613954515</v>
       </c>
       <c r="AH77" t="inlineStr"/>
       <c r="AI77" t="n">
-        <v>0.1692933316843996</v>
+        <v>0.1621997641485069</v>
       </c>
       <c r="AJ77" t="n">
-        <v>0.01361096832113987</v>
+        <v>0.0136689581830279</v>
       </c>
       <c r="AK77" t="inlineStr"/>
       <c r="AL77" t="n">
-        <v>0.8749901634310162</v>
+        <v>0.8716404885131864</v>
       </c>
       <c r="AM77" t="n">
-        <v>0.0008012903431373562</v>
+        <v>0.0008119547761249507</v>
       </c>
       <c r="AN77" t="inlineStr"/>
     </row>
@@ -8611,25 +8611,25 @@
         <v>194.7286349979082</v>
       </c>
       <c r="F78" t="n">
-        <v>0.1878797147510616</v>
+        <v>0.1878797146293589</v>
       </c>
       <c r="G78" t="n">
         <v>0.01630270337301587</v>
       </c>
       <c r="H78" t="n">
-        <v>0.486383629371598</v>
+        <v>0.48638362926571</v>
       </c>
       <c r="I78" t="n">
-        <v>0.2989072313345766</v>
+        <v>0.2989072315377535</v>
       </c>
       <c r="J78" t="n">
-        <v>0.01052672116974796</v>
+        <v>0.01052672119416169</v>
       </c>
       <c r="K78" t="n">
-        <v>0.02722131315634268</v>
+        <v>0.009270839155371313</v>
       </c>
       <c r="L78" t="n">
-        <v>0.07764629252821463</v>
+        <v>0.04556172815359773</v>
       </c>
       <c r="M78" t="n">
         <v>0</v>
@@ -8638,16 +8638,16 @@
         <v>0</v>
       </c>
       <c r="O78" t="n">
-        <v>4.411801604657093</v>
+        <v>4.408817932135783</v>
       </c>
       <c r="P78" t="n">
-        <v>4.3775281730888</v>
+        <v>4.362432991648956</v>
       </c>
       <c r="Q78" t="n">
-        <v>0.9790410756732091</v>
+        <v>0.9767966556308738</v>
       </c>
       <c r="R78" t="n">
-        <v>0.01051275169436136</v>
+        <v>0.01106132632374648</v>
       </c>
       <c r="S78" t="inlineStr"/>
       <c r="T78" t="inlineStr"/>
@@ -8657,38 +8657,38 @@
       <c r="X78" t="inlineStr"/>
       <c r="Y78" t="inlineStr"/>
       <c r="Z78" t="n">
-        <v>0.1225301556099971</v>
+        <v>0.0197310722319366</v>
       </c>
       <c r="AA78" t="n">
-        <v>0.01135571208248658</v>
+        <v>0.01200247724435576</v>
       </c>
       <c r="AB78" t="inlineStr"/>
       <c r="AC78" t="n">
-        <v>0.7096709745839889</v>
+        <v>0.04211667085445869</v>
       </c>
       <c r="AD78" t="n">
-        <v>0.0006302489600751789</v>
+        <v>0.001144783120083672</v>
       </c>
       <c r="AE78" t="inlineStr"/>
       <c r="AF78" t="n">
-        <v>0.8348689263672254</v>
+        <v>0.8096227107736678</v>
       </c>
       <c r="AG78" t="n">
-        <v>0.01671127413344865</v>
+        <v>0.01794331704929406</v>
       </c>
       <c r="AH78" t="inlineStr"/>
       <c r="AI78" t="n">
-        <v>-0.2437225258503379</v>
+        <v>-0.2434742649665742</v>
       </c>
       <c r="AJ78" t="n">
-        <v>0.01174896745641607</v>
+        <v>0.01174779484445083</v>
       </c>
       <c r="AK78" t="inlineStr"/>
       <c r="AL78" t="n">
-        <v>-1.722751445451205</v>
+        <v>-1.945690003028069</v>
       </c>
       <c r="AM78" t="n">
-        <v>0.002436269859700756</v>
+        <v>0.002534048415073153</v>
       </c>
       <c r="AN78" t="inlineStr"/>
     </row>
@@ -8709,31 +8709,31 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>21</v>
+        <v>10.7</v>
       </c>
       <c r="E79" t="n">
         <v>46.1</v>
       </c>
       <c r="F79" t="n">
-        <v>0.5078749311749362</v>
+        <v>0.507874931382013</v>
       </c>
       <c r="G79" t="n">
         <v>0.06886340942740074</v>
       </c>
       <c r="H79" t="n">
-        <v>0.224536369038535</v>
+        <v>0.2245363687099741</v>
       </c>
       <c r="I79" t="n">
-        <v>0.198725290359128</v>
+        <v>0.1987252904806123</v>
       </c>
       <c r="J79" t="n">
-        <v>3.234988232153624e-17</v>
+        <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>0.291298707758667</v>
+        <v>0.2303690117158935</v>
       </c>
       <c r="L79" t="n">
-        <v>0.3304035059681816</v>
+        <v>0.2922512004012426</v>
       </c>
       <c r="M79" t="n">
         <v>0</v>
@@ -8742,58 +8742,58 @@
         <v>0</v>
       </c>
       <c r="O79" t="n">
-        <v>4.395075630781815</v>
+        <v>4.373390288550217</v>
       </c>
       <c r="P79" t="n">
-        <v>4.439066110577246</v>
+        <v>4.375242757853916</v>
       </c>
       <c r="Q79" t="n">
-        <v>0.9810896195208271</v>
+        <v>0.9808907815267717</v>
       </c>
       <c r="R79" t="n">
-        <v>0.02022836194988157</v>
+        <v>0.02033443197628049</v>
       </c>
       <c r="S79" t="inlineStr"/>
       <c r="T79" t="n">
-        <v>0.9173823247709172</v>
+        <v>0.9163598831413424</v>
       </c>
       <c r="U79" t="n">
-        <v>0.04464535478460659</v>
+        <v>0.04492076140010511</v>
       </c>
       <c r="V79" t="inlineStr"/>
       <c r="W79" t="n">
-        <v>0.3691180979314987</v>
+        <v>0.3157445816382826</v>
       </c>
       <c r="X79" t="n">
-        <v>0.00223543930990148</v>
+        <v>0.002328080384607792</v>
       </c>
       <c r="Y79" t="inlineStr"/>
       <c r="Z79" t="n">
-        <v>0.9955889158578903</v>
+        <v>0.9976432624425374</v>
       </c>
       <c r="AA79" t="n">
-        <v>0.005190526931061067</v>
+        <v>0.003793974338787635</v>
       </c>
       <c r="AB79" t="inlineStr"/>
       <c r="AC79" t="n">
-        <v>0.5906689916039923</v>
+        <v>0.5309433655666522</v>
       </c>
       <c r="AD79" t="n">
-        <v>0.0048355634456624</v>
+        <v>0.005176335353715041</v>
       </c>
       <c r="AE79" t="inlineStr"/>
       <c r="AF79" t="n">
-        <v>0.9850466385376752</v>
+        <v>0.9910869176209304</v>
       </c>
       <c r="AG79" t="n">
-        <v>0.00392341162287957</v>
+        <v>0.003029063788607225</v>
       </c>
       <c r="AH79" t="inlineStr"/>
       <c r="AI79" t="n">
-        <v>0.8652278378842142</v>
+        <v>0.84848294102597</v>
       </c>
       <c r="AJ79" t="n">
-        <v>0.009810176261362718</v>
+        <v>0.01040177554415342</v>
       </c>
       <c r="AK79" t="inlineStr"/>
       <c r="AL79" t="inlineStr"/>
@@ -8817,31 +8817,31 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>21</v>
+        <v>10.7</v>
       </c>
       <c r="E80" t="n">
         <v>45.1</v>
       </c>
       <c r="F80" t="n">
-        <v>0.3936300671811785</v>
+        <v>0.3936300668840204</v>
       </c>
       <c r="G80" t="n">
         <v>0.07039031429275332</v>
       </c>
       <c r="H80" t="n">
-        <v>0.3139495076888332</v>
+        <v>0.3139495080876725</v>
       </c>
       <c r="I80" t="n">
-        <v>0.2220301108372348</v>
+        <v>0.2220301107355537</v>
       </c>
       <c r="J80" t="n">
-        <v>7.592549229303372e-17</v>
+        <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>0.1623021847871931</v>
+        <v>0.1039261725912166</v>
       </c>
       <c r="L80" t="n">
-        <v>0.2458325049296386</v>
+        <v>0.2174564914215158</v>
       </c>
       <c r="M80" t="n">
         <v>0</v>
@@ -8850,58 +8850,58 @@
         <v>0</v>
       </c>
       <c r="O80" t="n">
-        <v>4.51750010072576</v>
+        <v>4.528963221921294</v>
       </c>
       <c r="P80" t="n">
-        <v>4.474103812650267</v>
+        <v>4.424729193308102</v>
       </c>
       <c r="Q80" t="n">
-        <v>0.9937421742225868</v>
+        <v>0.9946325656416439</v>
       </c>
       <c r="R80" t="n">
-        <v>0.01093382183032316</v>
+        <v>0.01012613305600414</v>
       </c>
       <c r="S80" t="inlineStr"/>
       <c r="T80" t="n">
-        <v>0.9791557110882316</v>
+        <v>0.9822787328478095</v>
       </c>
       <c r="U80" t="n">
-        <v>0.02292650890581743</v>
+        <v>0.02113935697584573</v>
       </c>
       <c r="V80" t="inlineStr"/>
       <c r="W80" t="n">
-        <v>0.7965904666481212</v>
+        <v>0.775825729595033</v>
       </c>
       <c r="X80" t="n">
-        <v>0.001206420214992126</v>
+        <v>0.001266501873173817</v>
       </c>
       <c r="Y80" t="inlineStr"/>
       <c r="Z80" t="n">
-        <v>0.9983500140171362</v>
+        <v>0.9992277168480969</v>
       </c>
       <c r="AA80" t="n">
-        <v>0.002607957713187918</v>
+        <v>0.001784221208935005</v>
       </c>
       <c r="AB80" t="inlineStr"/>
       <c r="AC80" t="n">
-        <v>0.8223784533859008</v>
+        <v>0.8016301743872633</v>
       </c>
       <c r="AD80" t="n">
-        <v>0.003506633486720634</v>
+        <v>0.003705786184713432</v>
       </c>
       <c r="AE80" t="inlineStr"/>
       <c r="AF80" t="n">
-        <v>0.9764504627317075</v>
+        <v>0.9841639170237896</v>
       </c>
       <c r="AG80" t="n">
-        <v>0.008139651575354715</v>
+        <v>0.006674803903250156</v>
       </c>
       <c r="AH80" t="inlineStr"/>
       <c r="AI80" t="n">
-        <v>0.969382218542139</v>
+        <v>0.9585997926081051</v>
       </c>
       <c r="AJ80" t="n">
-        <v>0.005732609682370402</v>
+        <v>0.00666602244157188</v>
       </c>
       <c r="AK80" t="inlineStr"/>
       <c r="AL80" t="inlineStr"/>
@@ -8925,31 +8925,31 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>21</v>
+        <v>13.7</v>
       </c>
       <c r="E81" t="n">
         <v>53.2</v>
       </c>
       <c r="F81" t="n">
-        <v>0.3868686426861032</v>
+        <v>0.386868642759827</v>
       </c>
       <c r="G81" t="n">
         <v>0.05967299200381906</v>
       </c>
       <c r="H81" t="n">
-        <v>0.2367160880230922</v>
+        <v>0.2367160880153139</v>
       </c>
       <c r="I81" t="n">
-        <v>0.3167422772869857</v>
+        <v>0.3167422772210401</v>
       </c>
       <c r="J81" t="n">
-        <v>9.901399624920571e-18</v>
+        <v>1.098340305577317e-17</v>
       </c>
       <c r="K81" t="n">
-        <v>0.2797133348512963</v>
+        <v>0.2166350389501655</v>
       </c>
       <c r="L81" t="n">
-        <v>0.2614622828200588</v>
+        <v>0.237244827662883</v>
       </c>
       <c r="M81" t="n">
         <v>0</v>
@@ -8958,54 +8958,54 @@
         <v>0</v>
       </c>
       <c r="O81" t="n">
-        <v>4.547852263736372</v>
+        <v>4.522784247933544</v>
       </c>
       <c r="P81" t="n">
-        <v>4.585225404430166</v>
+        <v>4.545004841620153</v>
       </c>
       <c r="Q81" t="n">
-        <v>0.9915073862567239</v>
+        <v>0.9924686950891002</v>
       </c>
       <c r="R81" t="n">
-        <v>0.01252382701626911</v>
+        <v>0.01179373838038089</v>
       </c>
       <c r="S81" t="inlineStr"/>
       <c r="T81" t="n">
-        <v>0.975550738508459</v>
+        <v>0.9780906020423523</v>
       </c>
       <c r="U81" t="n">
-        <v>0.02343259242457807</v>
+        <v>0.02218210148416111</v>
       </c>
       <c r="V81" t="inlineStr"/>
       <c r="W81" t="inlineStr"/>
       <c r="X81" t="inlineStr"/>
       <c r="Y81" t="inlineStr"/>
       <c r="Z81" t="n">
-        <v>0.9789300681838278</v>
+        <v>0.9856585831245859</v>
       </c>
       <c r="AA81" t="n">
-        <v>0.009566600492796364</v>
+        <v>0.007892636524348936</v>
       </c>
       <c r="AB81" t="inlineStr"/>
       <c r="AC81" t="n">
-        <v>0.7594125558772289</v>
+        <v>0.7150037744037052</v>
       </c>
       <c r="AD81" t="n">
-        <v>0.002978458250689731</v>
+        <v>0.003241713218457269</v>
       </c>
       <c r="AE81" t="inlineStr"/>
       <c r="AF81" t="n">
-        <v>0.9579897427500782</v>
+        <v>0.9555727072063726</v>
       </c>
       <c r="AG81" t="n">
-        <v>0.006575677562460379</v>
+        <v>0.006762196152289902</v>
       </c>
       <c r="AH81" t="inlineStr"/>
       <c r="AI81" t="n">
-        <v>0.9611088611477856</v>
+        <v>0.9639256919131974</v>
       </c>
       <c r="AJ81" t="n">
-        <v>0.00956630722825942</v>
+        <v>0.00921335910363166</v>
       </c>
       <c r="AK81" t="inlineStr"/>
       <c r="AL81" t="inlineStr"/>
@@ -9029,31 +9029,31 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>21</v>
+        <v>13.7</v>
       </c>
       <c r="E82" t="n">
         <v>57.4</v>
       </c>
       <c r="F82" t="n">
-        <v>0.3730456209331519</v>
+        <v>0.3730456210575596</v>
       </c>
       <c r="G82" t="n">
         <v>0.05530667551573475</v>
       </c>
       <c r="H82" t="n">
-        <v>0.261472183194441</v>
+        <v>0.2614721829646628</v>
       </c>
       <c r="I82" t="n">
-        <v>0.3101755203566725</v>
+        <v>0.3101755204620427</v>
       </c>
       <c r="J82" t="n">
-        <v>1.336850539002381e-17</v>
+        <v>8.893357462748227e-17</v>
       </c>
       <c r="K82" t="n">
-        <v>0.191395009818949</v>
+        <v>0.1242093141540693</v>
       </c>
       <c r="L82" t="n">
-        <v>0.1473499283749068</v>
+        <v>0.148945534072481</v>
       </c>
       <c r="M82" t="n">
         <v>0</v>
@@ -9062,54 +9062,54 @@
         <v>0</v>
       </c>
       <c r="O82" t="n">
-        <v>4.463985251926877</v>
+        <v>4.419262235589021</v>
       </c>
       <c r="P82" t="n">
-        <v>4.58495417747088</v>
+        <v>4.604082496248363</v>
       </c>
       <c r="Q82" t="n">
-        <v>0.9687450526266348</v>
+        <v>0.9754242248748078</v>
       </c>
       <c r="R82" t="n">
-        <v>0.0238486856326593</v>
+        <v>0.02114748254200301</v>
       </c>
       <c r="S82" t="inlineStr"/>
       <c r="T82" t="n">
-        <v>0.9136616596404042</v>
+        <v>0.9334055943655251</v>
       </c>
       <c r="U82" t="n">
-        <v>0.04587518123605714</v>
+        <v>0.04028977281277975</v>
       </c>
       <c r="V82" t="inlineStr"/>
       <c r="W82" t="inlineStr"/>
       <c r="X82" t="inlineStr"/>
       <c r="Y82" t="inlineStr"/>
       <c r="Z82" t="n">
-        <v>0.9469512795381505</v>
+        <v>0.9653890010837597</v>
       </c>
       <c r="AA82" t="n">
-        <v>0.01542197896616796</v>
+        <v>0.01245689251004697</v>
       </c>
       <c r="AB82" t="inlineStr"/>
       <c r="AC82" t="n">
-        <v>0.3206913083963491</v>
+        <v>0.41116183524369</v>
       </c>
       <c r="AD82" t="n">
-        <v>0.002419011034520423</v>
+        <v>0.002252175547996892</v>
       </c>
       <c r="AE82" t="inlineStr"/>
       <c r="AF82" t="n">
-        <v>0.6828999517878078</v>
+        <v>0.703466836809297</v>
       </c>
       <c r="AG82" t="n">
-        <v>0.02025899656040794</v>
+        <v>0.01959099127660886</v>
       </c>
       <c r="AH82" t="inlineStr"/>
       <c r="AI82" t="n">
-        <v>0.9695000519933915</v>
+        <v>0.97537070803253</v>
       </c>
       <c r="AJ82" t="n">
-        <v>0.009227718425119141</v>
+        <v>0.008292218708535195</v>
       </c>
       <c r="AK82" t="inlineStr"/>
       <c r="AL82" t="inlineStr"/>
@@ -9133,29 +9133,29 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>21</v>
+        <v>9.1</v>
       </c>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="n">
-        <v>0.3465778704093958</v>
+        <v>0.3465778699121797</v>
       </c>
       <c r="G83" t="n">
-        <v>0.07437667461883628</v>
+        <v>0.07437667876585422</v>
       </c>
       <c r="H83" t="n">
-        <v>0.2955634795127128</v>
+        <v>0.2955634788718243</v>
       </c>
       <c r="I83" t="n">
-        <v>0.2811992414815186</v>
+        <v>0.2811992393986867</v>
       </c>
       <c r="J83" t="n">
-        <v>0.002282733977536599</v>
+        <v>0.002282733051455125</v>
       </c>
       <c r="K83" t="n">
-        <v>0.189934792401037</v>
+        <v>0.1273374851235748</v>
       </c>
       <c r="L83" t="n">
-        <v>0.1826267284946377</v>
+        <v>0.1574197316565873</v>
       </c>
       <c r="M83" t="n">
         <v>0</v>
@@ -9164,54 +9164,54 @@
         <v>0</v>
       </c>
       <c r="O83" t="n">
-        <v>4.578578953049799</v>
+        <v>4.56844405665582</v>
       </c>
       <c r="P83" t="n">
-        <v>4.571960649035538</v>
+        <v>4.569037027833398</v>
       </c>
       <c r="Q83" t="n">
-        <v>0.975739278735116</v>
+        <v>0.9751081141222492</v>
       </c>
       <c r="R83" t="n">
-        <v>0.01864810179250103</v>
+        <v>0.01888911790275169</v>
       </c>
       <c r="S83" t="inlineStr"/>
       <c r="T83" t="n">
-        <v>0.9247478164506443</v>
+        <v>0.9222373462486447</v>
       </c>
       <c r="U83" t="n">
-        <v>0.03555231950112275</v>
+        <v>0.03614048060730951</v>
       </c>
       <c r="V83" t="inlineStr"/>
       <c r="W83" t="inlineStr"/>
       <c r="X83" t="inlineStr"/>
       <c r="Y83" t="inlineStr"/>
       <c r="Z83" t="n">
-        <v>0.9595067108214487</v>
+        <v>0.9581677611297498</v>
       </c>
       <c r="AA83" t="n">
-        <v>0.009703482150566864</v>
+        <v>0.009862604937353268</v>
       </c>
       <c r="AB83" t="inlineStr"/>
       <c r="AC83" t="n">
-        <v>0.2721584302524647</v>
+        <v>0.2494938805516836</v>
       </c>
       <c r="AD83" t="n">
-        <v>0.009535197718484453</v>
+        <v>0.00968252006466992</v>
       </c>
       <c r="AE83" t="inlineStr"/>
       <c r="AF83" t="n">
-        <v>0.92071581695676</v>
+        <v>0.9210452685771884</v>
       </c>
       <c r="AG83" t="n">
-        <v>0.01080899162941539</v>
+        <v>0.01078651076869192</v>
       </c>
       <c r="AH83" t="inlineStr"/>
       <c r="AI83" t="n">
-        <v>0.8756106397787032</v>
+        <v>0.8773307600014617</v>
       </c>
       <c r="AJ83" t="n">
-        <v>0.01314835423107227</v>
+        <v>0.01305712647088978</v>
       </c>
       <c r="AK83" t="inlineStr"/>
       <c r="AL83" t="inlineStr"/>
@@ -9235,29 +9235,29 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>21</v>
+        <v>9.1</v>
       </c>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="n">
-        <v>0.4410213099976569</v>
+        <v>0.4410213107040933</v>
       </c>
       <c r="G84" t="n">
-        <v>0.0196358885772423</v>
+        <v>0.01963588269307707</v>
       </c>
       <c r="H84" t="n">
-        <v>0.3091324863805823</v>
+        <v>0.3091324872855457</v>
       </c>
       <c r="I84" t="n">
-        <v>0.2286307167377633</v>
+        <v>0.2286307196912758</v>
       </c>
       <c r="J84" t="n">
-        <v>0.001579598306755124</v>
+        <v>0.001579599626008144</v>
       </c>
       <c r="K84" t="n">
-        <v>0.171344845273151</v>
+        <v>0.08008330526260318</v>
       </c>
       <c r="L84" t="n">
-        <v>0.3144608188889046</v>
+        <v>0.2339625120726014</v>
       </c>
       <c r="M84" t="n">
         <v>0</v>
@@ -9266,54 +9266,54 @@
         <v>0</v>
       </c>
       <c r="O84" t="n">
-        <v>4.585710978228106</v>
+        <v>3.382055805903954</v>
       </c>
       <c r="P84" t="n">
-        <v>4.51504935164796</v>
+        <v>4.437642616238247</v>
       </c>
       <c r="Q84" t="n">
-        <v>0.9903344577308121</v>
+        <v>0.9893889808462896</v>
       </c>
       <c r="R84" t="n">
-        <v>0.01154526369606604</v>
+        <v>0.01209676640713226</v>
       </c>
       <c r="S84" t="inlineStr"/>
       <c r="T84" t="n">
-        <v>0.9873913956404577</v>
+        <v>0.9818384689355362</v>
       </c>
       <c r="U84" t="n">
-        <v>0.01501815830575804</v>
+        <v>0.01802434112438521</v>
       </c>
       <c r="V84" t="inlineStr"/>
       <c r="W84" t="inlineStr"/>
       <c r="X84" t="inlineStr"/>
       <c r="Y84" t="inlineStr"/>
       <c r="Z84" t="n">
-        <v>0.9933130550836702</v>
+        <v>0.9903913707915402</v>
       </c>
       <c r="AA84" t="n">
-        <v>0.005578859917414843</v>
+        <v>0.006687477007709755</v>
       </c>
       <c r="AB84" t="inlineStr"/>
       <c r="AC84" t="n">
-        <v>0.5270393210160504</v>
+        <v>0.1560998600167813</v>
       </c>
       <c r="AD84" t="n">
-        <v>0.006226371265389735</v>
+        <v>0.008317026411614874</v>
       </c>
       <c r="AE84" t="inlineStr"/>
       <c r="AF84" t="n">
-        <v>0.7830435084276691</v>
+        <v>0.8289018488084052</v>
       </c>
       <c r="AG84" t="n">
-        <v>0.01919678194774724</v>
+        <v>0.01704765970182989</v>
       </c>
       <c r="AH84" t="inlineStr"/>
       <c r="AI84" t="n">
-        <v>0.9975782452931089</v>
+        <v>0.9978179844197249</v>
       </c>
       <c r="AJ84" t="n">
-        <v>0.0015851422332806</v>
+        <v>0.0015046382308956</v>
       </c>
       <c r="AK84" t="inlineStr"/>
       <c r="AL84" t="inlineStr"/>
@@ -9337,29 +9337,31 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>21</v>
-      </c>
-      <c r="E85" t="inlineStr"/>
+        <v>10.7</v>
+      </c>
+      <c r="E85" t="n">
+        <v>46.1</v>
+      </c>
       <c r="F85" t="n">
-        <v>0.5131512316840431</v>
+        <v>0.510053670891675</v>
       </c>
       <c r="G85" t="n">
-        <v>6.514458245503142e-16</v>
+        <v>0.06886340942740074</v>
       </c>
       <c r="H85" t="n">
-        <v>0.2632803536988662</v>
+        <v>0.2213241491814443</v>
       </c>
       <c r="I85" t="n">
-        <v>0.2235684146170903</v>
+        <v>0.19975877049948</v>
       </c>
       <c r="J85" t="n">
-        <v>0</v>
+        <v>2.168404344971009e-17</v>
       </c>
       <c r="K85" t="n">
-        <v>0.2347111018878213</v>
+        <v>0.232649974815383</v>
       </c>
       <c r="L85" t="n">
-        <v>0.2950582658013271</v>
+        <v>0.250511276483206</v>
       </c>
       <c r="M85" t="n">
         <v>0</v>
@@ -9368,54 +9370,54 @@
         <v>0</v>
       </c>
       <c r="O85" t="n">
-        <v>4.499856930037251</v>
+        <v>4.312526024436617</v>
       </c>
       <c r="P85" t="n">
-        <v>4.494335338061362</v>
+        <v>4.386010107012114</v>
       </c>
       <c r="Q85" t="n">
-        <v>0.9804738895804873</v>
+        <v>0.9919833692155775</v>
       </c>
       <c r="R85" t="n">
-        <v>0.01746361459638317</v>
+        <v>0.01132669231564241</v>
       </c>
       <c r="S85" t="inlineStr"/>
       <c r="T85" t="n">
-        <v>0.9535757123586837</v>
+        <v>0.9741551929558522</v>
       </c>
       <c r="U85" t="n">
-        <v>0.02766144752124787</v>
+        <v>0.02268930815332858</v>
       </c>
       <c r="V85" t="inlineStr"/>
       <c r="W85" t="inlineStr"/>
       <c r="X85" t="inlineStr"/>
       <c r="Y85" t="inlineStr"/>
       <c r="Z85" t="n">
-        <v>0.9918666485371912</v>
+        <v>0.9943428358976947</v>
       </c>
       <c r="AA85" t="n">
-        <v>0.006949897789780429</v>
+        <v>0.00611754595124686</v>
       </c>
       <c r="AB85" t="inlineStr"/>
       <c r="AC85" t="n">
-        <v>-0.08764342376728562</v>
+        <v>0.4911778107117194</v>
       </c>
       <c r="AD85" t="n">
-        <v>0.01629711392139493</v>
+        <v>0.005681289089860726</v>
       </c>
       <c r="AE85" t="inlineStr"/>
       <c r="AF85" t="n">
-        <v>0.572784553447327</v>
+        <v>0.9649199472882828</v>
       </c>
       <c r="AG85" t="n">
-        <v>0.02111067502000964</v>
+        <v>0.005759909587219552</v>
       </c>
       <c r="AH85" t="inlineStr"/>
       <c r="AI85" t="n">
-        <v>0.9997841094756301</v>
+        <v>0.9635814892915352</v>
       </c>
       <c r="AJ85" t="n">
-        <v>0.0004193967435592211</v>
+        <v>0.004877203804264377</v>
       </c>
       <c r="AK85" t="inlineStr"/>
       <c r="AL85" t="inlineStr"/>
@@ -9439,29 +9441,31 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>21</v>
-      </c>
-      <c r="E86" t="inlineStr"/>
+        <v>10.7</v>
+      </c>
+      <c r="E86" t="n">
+        <v>45.1</v>
+      </c>
       <c r="F86" t="n">
-        <v>0.3947553823403973</v>
+        <v>0.3945200239537214</v>
       </c>
       <c r="G86" t="n">
-        <v>0.0245670665763035</v>
+        <v>0.07039031429275332</v>
       </c>
       <c r="H86" t="n">
-        <v>0.3466305638791009</v>
+        <v>0.3115441195160394</v>
       </c>
       <c r="I86" t="n">
-        <v>0.2327646937884924</v>
+        <v>0.2235455422374857</v>
       </c>
       <c r="J86" t="n">
-        <v>0.001282293415705915</v>
+        <v>4.155543639229597e-17</v>
       </c>
       <c r="K86" t="n">
-        <v>0.1247724149338163</v>
+        <v>0.1063207427095769</v>
       </c>
       <c r="L86" t="n">
-        <v>0.1593436216466051</v>
+        <v>0.1880447549481098</v>
       </c>
       <c r="M86" t="n">
         <v>0</v>
@@ -9470,54 +9474,54 @@
         <v>0</v>
       </c>
       <c r="O86" t="n">
-        <v>4.570462719990509</v>
+        <v>4.515115790775487</v>
       </c>
       <c r="P86" t="n">
-        <v>4.515742961794027</v>
+        <v>4.437239690074709</v>
       </c>
       <c r="Q86" t="n">
-        <v>0.9903940418722199</v>
+        <v>0.9925981720188748</v>
       </c>
       <c r="R86" t="n">
-        <v>0.01168937498319476</v>
+        <v>0.0107009497129165</v>
       </c>
       <c r="S86" t="inlineStr"/>
       <c r="T86" t="n">
-        <v>0.9850744497473672</v>
+        <v>0.9812567749842462</v>
       </c>
       <c r="U86" t="n">
-        <v>0.01698183892126025</v>
+        <v>0.02129180191579711</v>
       </c>
       <c r="V86" t="inlineStr"/>
       <c r="W86" t="inlineStr"/>
       <c r="X86" t="inlineStr"/>
       <c r="Y86" t="inlineStr"/>
       <c r="Z86" t="n">
-        <v>0.9963065060987834</v>
+        <v>0.9984018985385641</v>
       </c>
       <c r="AA86" t="n">
-        <v>0.003535138875647679</v>
+        <v>0.002542298956410744</v>
       </c>
       <c r="AB86" t="inlineStr"/>
       <c r="AC86" t="n">
-        <v>-0.3773211717237219</v>
+        <v>0.7217579806729524</v>
       </c>
       <c r="AD86" t="n">
-        <v>0.01756688986452823</v>
+        <v>0.004433773488736337</v>
       </c>
       <c r="AE86" t="inlineStr"/>
       <c r="AF86" t="n">
-        <v>0.9812247563569276</v>
+        <v>0.9713078457630941</v>
       </c>
       <c r="AG86" t="n">
-        <v>0.007005455428793422</v>
+        <v>0.008855102484899964</v>
       </c>
       <c r="AH86" t="inlineStr"/>
       <c r="AI86" t="n">
-        <v>0.9766567408923517</v>
+        <v>0.9864908326718069</v>
       </c>
       <c r="AJ86" t="n">
-        <v>0.004965415611374016</v>
+        <v>0.003830969018280812</v>
       </c>
       <c r="AK86" t="inlineStr"/>
       <c r="AL86" t="inlineStr"/>
@@ -9541,29 +9545,31 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>21</v>
-      </c>
-      <c r="E87" t="inlineStr"/>
+        <v>13.7</v>
+      </c>
+      <c r="E87" t="n">
+        <v>57.4</v>
+      </c>
       <c r="F87" t="n">
-        <v>0.3717923415656336</v>
+        <v>0.3694757755244492</v>
       </c>
       <c r="G87" t="n">
-        <v>0</v>
+        <v>0.05530667551573475</v>
       </c>
       <c r="H87" t="n">
-        <v>0.3014084132402625</v>
+        <v>0.2674527900009642</v>
       </c>
       <c r="I87" t="n">
-        <v>0.3267992451941039</v>
+        <v>0.3077647589588519</v>
       </c>
       <c r="J87" t="n">
-        <v>1.327388309752159e-16</v>
+        <v>2.355429219724758e-17</v>
       </c>
       <c r="K87" t="n">
-        <v>0.1836932533354582</v>
+        <v>0.140655276469967</v>
       </c>
       <c r="L87" t="n">
-        <v>0.3212047022172082</v>
+        <v>0.1439228931899299</v>
       </c>
       <c r="M87" t="n">
         <v>0</v>
@@ -9572,54 +9578,54 @@
         <v>0</v>
       </c>
       <c r="O87" t="n">
-        <v>4.671002060938001</v>
+        <v>4.405005859431377</v>
       </c>
       <c r="P87" t="n">
-        <v>4.625013059199635</v>
+        <v>4.602207269884047</v>
       </c>
       <c r="Q87" t="n">
-        <v>0.9528376089871131</v>
+        <v>0.9735717477205749</v>
       </c>
       <c r="R87" t="n">
-        <v>0.02434592963474631</v>
+        <v>0.0217397406566478</v>
       </c>
       <c r="S87" t="inlineStr"/>
       <c r="T87" t="n">
-        <v>0.9101214237899498</v>
+        <v>0.9380898472004836</v>
       </c>
       <c r="U87" t="n">
-        <v>0.0388730195583844</v>
+        <v>0.04104236862088976</v>
       </c>
       <c r="V87" t="inlineStr"/>
       <c r="W87" t="inlineStr"/>
       <c r="X87" t="inlineStr"/>
       <c r="Y87" t="inlineStr"/>
       <c r="Z87" t="n">
-        <v>0.8400135984614169</v>
+        <v>0.9694731373686784</v>
       </c>
       <c r="AA87" t="n">
-        <v>0.02235533765295454</v>
+        <v>0.01198458328579419</v>
       </c>
       <c r="AB87" t="inlineStr"/>
       <c r="AC87" t="n">
-        <v>0.770358936234994</v>
+        <v>0.6375075089055844</v>
       </c>
       <c r="AD87" t="n">
-        <v>0.005617092758887966</v>
+        <v>0.002355362841955057</v>
       </c>
       <c r="AE87" t="inlineStr"/>
       <c r="AF87" t="n">
-        <v>0.3037102188035828</v>
+        <v>0.7208583163090007</v>
       </c>
       <c r="AG87" t="n">
-        <v>0.02948246663492235</v>
+        <v>0.02111288873214654</v>
       </c>
       <c r="AH87" t="inlineStr"/>
       <c r="AI87" t="n">
-        <v>0.9794634899388649</v>
+        <v>0.9719320840991892</v>
       </c>
       <c r="AJ87" t="n">
-        <v>0.007209792493178158</v>
+        <v>0.009147325063160834</v>
       </c>
       <c r="AK87" t="inlineStr"/>
       <c r="AL87" t="inlineStr"/>
@@ -9643,29 +9649,31 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>21</v>
-      </c>
-      <c r="E88" t="inlineStr"/>
+        <v>13.7</v>
+      </c>
+      <c r="E88" t="n">
+        <v>53.2</v>
+      </c>
       <c r="F88" t="n">
-        <v>0.3917057203335357</v>
+        <v>0.3890440313612025</v>
       </c>
       <c r="G88" t="n">
-        <v>0</v>
+        <v>0.05967299200381906</v>
       </c>
       <c r="H88" t="n">
-        <v>0.2685425476164555</v>
+        <v>0.2320759063377122</v>
       </c>
       <c r="I88" t="n">
-        <v>0.3397517320500086</v>
+        <v>0.3192070702972664</v>
       </c>
       <c r="J88" t="n">
-        <v>1.912261794240524e-16</v>
+        <v>2.419504177564497e-17</v>
       </c>
       <c r="K88" t="n">
-        <v>0.2269187226468679</v>
+        <v>0.1958473687662303</v>
       </c>
       <c r="L88" t="n">
-        <v>0.1610926939247017</v>
+        <v>0.2436095446658882</v>
       </c>
       <c r="M88" t="n">
         <v>0</v>
@@ -9674,54 +9682,54 @@
         <v>0</v>
       </c>
       <c r="O88" t="n">
-        <v>4.508038364188548</v>
+        <v>4.5240596280908</v>
       </c>
       <c r="P88" t="n">
-        <v>4.616014940025162</v>
+        <v>4.546344891170229</v>
       </c>
       <c r="Q88" t="n">
-        <v>0.9911677616073298</v>
+        <v>0.990113532996749</v>
       </c>
       <c r="R88" t="n">
-        <v>0.01101856547280698</v>
+        <v>0.01337710119506095</v>
       </c>
       <c r="S88" t="inlineStr"/>
       <c r="T88" t="n">
-        <v>0.9747457378410946</v>
+        <v>0.9731869478336322</v>
       </c>
       <c r="U88" t="n">
-        <v>0.02002915652684809</v>
+        <v>0.02544246087279837</v>
       </c>
       <c r="V88" t="inlineStr"/>
       <c r="W88" t="inlineStr"/>
       <c r="X88" t="inlineStr"/>
       <c r="Y88" t="inlineStr"/>
       <c r="Z88" t="n">
-        <v>0.9859123894171555</v>
+        <v>0.9820635280145389</v>
       </c>
       <c r="AA88" t="n">
-        <v>0.006715559807302352</v>
+        <v>0.009110247729552318</v>
       </c>
       <c r="AB88" t="inlineStr"/>
       <c r="AC88" t="n">
-        <v>0.5661360363941335</v>
+        <v>0.8180600647204139</v>
       </c>
       <c r="AD88" t="n">
-        <v>0.004108756832110564</v>
+        <v>0.002614376010725667</v>
       </c>
       <c r="AE88" t="inlineStr"/>
       <c r="AF88" t="n">
-        <v>0.9549354921117436</v>
+        <v>0.9531269074876954</v>
       </c>
       <c r="AG88" t="n">
-        <v>0.006327418183435707</v>
+        <v>0.00708278764367738</v>
       </c>
       <c r="AH88" t="inlineStr"/>
       <c r="AI88" t="n">
-        <v>0.9499380485828203</v>
+        <v>0.9582447890239489</v>
       </c>
       <c r="AJ88" t="n">
-        <v>0.01019117103755729</v>
+        <v>0.01036426120019796</v>
       </c>
       <c r="AK88" t="inlineStr"/>
       <c r="AL88" t="inlineStr"/>
@@ -9745,29 +9753,29 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>21</v>
+        <v>22.9</v>
       </c>
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="n">
-        <v>0.468689526729295</v>
+        <v>0.4686895267262085</v>
       </c>
       <c r="G89" t="n">
-        <v>3.650881409255485e-16</v>
+        <v>2.428629807026475e-16</v>
       </c>
       <c r="H89" t="n">
-        <v>0.1956707823068736</v>
+        <v>0.1956707823126708</v>
       </c>
       <c r="I89" t="n">
-        <v>0.335639690963831</v>
+        <v>0.3356396909611205</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
       </c>
       <c r="K89" t="n">
-        <v>0.3352916146113781</v>
+        <v>0.2882739572399665</v>
       </c>
       <c r="L89" t="n">
-        <v>0.3410086197232753</v>
+        <v>0.2786753401394514</v>
       </c>
       <c r="M89" t="n">
         <v>0</v>
@@ -9776,54 +9784,54 @@
         <v>0</v>
       </c>
       <c r="O89" t="n">
-        <v>4.501914574676857</v>
+        <v>4.43262461682365</v>
       </c>
       <c r="P89" t="n">
-        <v>4.601731646475884</v>
+        <v>4.569431973007477</v>
       </c>
       <c r="Q89" t="n">
-        <v>0.9957838033026417</v>
+        <v>0.9943210413628463</v>
       </c>
       <c r="R89" t="n">
-        <v>0.007684071480909165</v>
+        <v>0.008917955839406005</v>
       </c>
       <c r="S89" t="inlineStr"/>
       <c r="T89" t="n">
-        <v>0.9946008588252906</v>
+        <v>0.9889930455394388</v>
       </c>
       <c r="U89" t="n">
-        <v>0.0100416439721599</v>
+        <v>0.01433758687703173</v>
       </c>
       <c r="V89" t="inlineStr"/>
       <c r="W89" t="inlineStr"/>
       <c r="X89" t="inlineStr"/>
       <c r="Y89" t="inlineStr"/>
       <c r="Z89" t="n">
-        <v>0.9957107577597389</v>
+        <v>0.9987886895505075</v>
       </c>
       <c r="AA89" t="n">
-        <v>0.004991014083450027</v>
+        <v>0.002652321955039827</v>
       </c>
       <c r="AB89" t="inlineStr"/>
       <c r="AC89" t="n">
-        <v>0.7657550291055167</v>
+        <v>0.6272531046048448</v>
       </c>
       <c r="AD89" t="n">
-        <v>0.004690403196969636</v>
+        <v>0.005916733607750403</v>
       </c>
       <c r="AE89" t="inlineStr"/>
       <c r="AF89" t="n">
-        <v>0.9544023076400937</v>
+        <v>0.9669916825472034</v>
       </c>
       <c r="AG89" t="n">
-        <v>0.005188037271933559</v>
+        <v>0.004414112024656249</v>
       </c>
       <c r="AH89" t="inlineStr"/>
       <c r="AI89" t="n">
-        <v>0.9417803380929247</v>
+        <v>0.9369552591891064</v>
       </c>
       <c r="AJ89" t="n">
-        <v>0.01098017870932351</v>
+        <v>0.01142612580917354</v>
       </c>
       <c r="AK89" t="inlineStr"/>
       <c r="AL89" t="inlineStr"/>
@@ -9849,27 +9857,29 @@
       <c r="D90" t="n">
         <v>12.8</v>
       </c>
-      <c r="E90" t="inlineStr"/>
+      <c r="E90" t="n">
+        <v>30.13605442176871</v>
+      </c>
       <c r="F90" t="n">
-        <v>0.6963378304438156</v>
+        <v>0.6739262842370797</v>
       </c>
       <c r="G90" t="n">
-        <v>0.06121827372612768</v>
+        <v>0.1053423626787058</v>
       </c>
       <c r="H90" t="n">
-        <v>0.04157121397092656</v>
+        <v>0.01105388716074765</v>
       </c>
       <c r="I90" t="n">
-        <v>0.1708251520974169</v>
+        <v>0.1819763294359777</v>
       </c>
       <c r="J90" t="n">
-        <v>0.03004752976171331</v>
+        <v>0.02770113648748916</v>
       </c>
       <c r="K90" t="n">
-        <v>0.2309014164628462</v>
+        <v>0.4614348426234621</v>
       </c>
       <c r="L90" t="n">
-        <v>0.4817050030759927</v>
+        <v>0.5236258361419488</v>
       </c>
       <c r="M90" t="n">
         <v>0</v>
@@ -9878,54 +9888,56 @@
         <v>0</v>
       </c>
       <c r="O90" t="n">
-        <v>4.475080783493183</v>
+        <v>4.51157711099569</v>
       </c>
       <c r="P90" t="n">
-        <v>4.2844261121447</v>
+        <v>4.296698700739978</v>
       </c>
       <c r="Q90" t="n">
-        <v>0.985661543993274</v>
+        <v>0.9830201146487042</v>
       </c>
       <c r="R90" t="n">
-        <v>0.01583401243658747</v>
+        <v>0.0154713005218967</v>
       </c>
       <c r="S90" t="inlineStr"/>
       <c r="T90" t="n">
-        <v>0.9692310029207792</v>
+        <v>0.9622156371068542</v>
       </c>
       <c r="U90" t="n">
-        <v>0.02840812414501118</v>
+        <v>0.02830980923983524</v>
       </c>
       <c r="V90" t="inlineStr"/>
       <c r="W90" t="inlineStr"/>
-      <c r="X90" t="inlineStr"/>
+      <c r="X90" t="n">
+        <v>5.204170427930421e-18</v>
+      </c>
       <c r="Y90" t="inlineStr"/>
       <c r="Z90" t="n">
-        <v>0.9923017691763977</v>
+        <v>0.9895478016977564</v>
       </c>
       <c r="AA90" t="n">
-        <v>0.01133445195626342</v>
+        <v>0.01111006393851131</v>
       </c>
       <c r="AB90" t="inlineStr"/>
       <c r="AC90" t="n">
-        <v>0.7983048294673831</v>
+        <v>0.8642320968652055</v>
       </c>
       <c r="AD90" t="n">
-        <v>0.005116754437832481</v>
+        <v>0.005729154826780923</v>
       </c>
       <c r="AE90" t="inlineStr"/>
       <c r="AF90" t="n">
-        <v>0.9910837831172993</v>
+        <v>0.9523356739684372</v>
       </c>
       <c r="AG90" t="n">
-        <v>0.0007192178317817351</v>
+        <v>0.0007207616573619726</v>
       </c>
       <c r="AH90" t="inlineStr"/>
       <c r="AI90" t="n">
-        <v>0.9876793180592091</v>
+        <v>0.9816237656397415</v>
       </c>
       <c r="AJ90" t="n">
-        <v>0.003638295831568752</v>
+        <v>0.004169217212593351</v>
       </c>
       <c r="AK90" t="inlineStr"/>
       <c r="AL90" t="inlineStr"/>
